--- a/enflasyon/enflasyon.xlsx
+++ b/enflasyon/enflasyon.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Genel" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AltKalem_Endeks" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AltKalem_Yillik" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AltKalem_Ozet" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Genel" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="AltKalem_Endeks" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="AltKalem_Yillik" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="AltKalem_Ozet" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,16 +23,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -43,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -51,21 +48,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -436,34 +424,34 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>tarih</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>endeks</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>aylik</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>yillik</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>ytd</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="1" t="n">
         <v>38353</v>
       </c>
       <c r="B2" t="n">
@@ -474,7 +462,7 @@
       <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="1" t="n">
         <v>38384</v>
       </c>
       <c r="B3" t="n">
@@ -487,7 +475,7 @@
       <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="1" t="n">
         <v>38412</v>
       </c>
       <c r="B4" t="n">
@@ -500,7 +488,7 @@
       <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="1" t="n">
         <v>38443</v>
       </c>
       <c r="B5" t="n">
@@ -513,7 +501,7 @@
       <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="1" t="n">
         <v>38473</v>
       </c>
       <c r="B6" t="n">
@@ -526,7 +514,7 @@
       <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="1" t="n">
         <v>38504</v>
       </c>
       <c r="B7" t="n">
@@ -539,7 +527,7 @@
       <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="1" t="n">
         <v>38534</v>
       </c>
       <c r="B8" t="n">
@@ -552,7 +540,7 @@
       <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="1" t="n">
         <v>38565</v>
       </c>
       <c r="B9" t="n">
@@ -565,7 +553,7 @@
       <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="1" t="n">
         <v>38596</v>
       </c>
       <c r="B10" t="n">
@@ -578,7 +566,7 @@
       <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="1" t="n">
         <v>38626</v>
       </c>
       <c r="B11" t="n">
@@ -591,7 +579,7 @@
       <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="1" t="n">
         <v>38657</v>
       </c>
       <c r="B12" t="n">
@@ -604,7 +592,7 @@
       <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="1" t="n">
         <v>38687</v>
       </c>
       <c r="B13" t="n">
@@ -617,7 +605,7 @@
       <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="1" t="n">
         <v>38718</v>
       </c>
       <c r="B14" t="n">
@@ -634,7 +622,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="1" t="n">
         <v>38749</v>
       </c>
       <c r="B15" t="n">
@@ -651,7 +639,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="1" t="n">
         <v>38777</v>
       </c>
       <c r="B16" t="n">
@@ -668,7 +656,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="1" t="n">
         <v>38808</v>
       </c>
       <c r="B17" t="n">
@@ -685,7 +673,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="1" t="n">
         <v>38838</v>
       </c>
       <c r="B18" t="n">
@@ -702,7 +690,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="1" t="n">
         <v>38869</v>
       </c>
       <c r="B19" t="n">
@@ -719,7 +707,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="1" t="n">
         <v>38899</v>
       </c>
       <c r="B20" t="n">
@@ -736,7 +724,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="1" t="n">
         <v>38930</v>
       </c>
       <c r="B21" t="n">
@@ -753,7 +741,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="1" t="n">
         <v>38961</v>
       </c>
       <c r="B22" t="n">
@@ -770,7 +758,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="1" t="n">
         <v>38991</v>
       </c>
       <c r="B23" t="n">
@@ -787,7 +775,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="1" t="n">
         <v>39022</v>
       </c>
       <c r="B24" t="n">
@@ -804,7 +792,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="1" t="n">
         <v>39052</v>
       </c>
       <c r="B25" t="n">
@@ -821,7 +809,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="1" t="n">
         <v>39083</v>
       </c>
       <c r="B26" t="n">
@@ -838,7 +826,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="1" t="n">
         <v>39114</v>
       </c>
       <c r="B27" t="n">
@@ -855,7 +843,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="1" t="n">
         <v>39142</v>
       </c>
       <c r="B28" t="n">
@@ -872,7 +860,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="1" t="n">
         <v>39173</v>
       </c>
       <c r="B29" t="n">
@@ -889,7 +877,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="1" t="n">
         <v>39203</v>
       </c>
       <c r="B30" t="n">
@@ -906,7 +894,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="1" t="n">
         <v>39234</v>
       </c>
       <c r="B31" t="n">
@@ -923,7 +911,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="1" t="n">
         <v>39264</v>
       </c>
       <c r="B32" t="n">
@@ -940,7 +928,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="1" t="n">
         <v>39295</v>
       </c>
       <c r="B33" t="n">
@@ -957,7 +945,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="1" t="n">
         <v>39326</v>
       </c>
       <c r="B34" t="n">
@@ -974,7 +962,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="1" t="n">
         <v>39356</v>
       </c>
       <c r="B35" t="n">
@@ -991,7 +979,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="1" t="n">
         <v>39387</v>
       </c>
       <c r="B36" t="n">
@@ -1008,7 +996,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="1" t="n">
         <v>39417</v>
       </c>
       <c r="B37" t="n">
@@ -1025,7 +1013,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="1" t="n">
         <v>39448</v>
       </c>
       <c r="B38" t="n">
@@ -1042,7 +1030,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="1" t="n">
         <v>39479</v>
       </c>
       <c r="B39" t="n">
@@ -1059,7 +1047,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="1" t="n">
         <v>39508</v>
       </c>
       <c r="B40" t="n">
@@ -1076,7 +1064,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" s="1" t="n">
         <v>39539</v>
       </c>
       <c r="B41" t="n">
@@ -1093,7 +1081,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="1" t="n">
         <v>39569</v>
       </c>
       <c r="B42" t="n">
@@ -1110,7 +1098,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" s="1" t="n">
         <v>39600</v>
       </c>
       <c r="B43" t="n">
@@ -1127,7 +1115,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" s="1" t="n">
         <v>39630</v>
       </c>
       <c r="B44" t="n">
@@ -1144,7 +1132,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" s="1" t="n">
         <v>39661</v>
       </c>
       <c r="B45" t="n">
@@ -1161,7 +1149,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="1" t="n">
         <v>39692</v>
       </c>
       <c r="B46" t="n">
@@ -1178,7 +1166,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="A47" s="1" t="n">
         <v>39722</v>
       </c>
       <c r="B47" t="n">
@@ -1195,7 +1183,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="1" t="n">
         <v>39753</v>
       </c>
       <c r="B48" t="n">
@@ -1212,7 +1200,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="A49" s="1" t="n">
         <v>39783</v>
       </c>
       <c r="B49" t="n">
@@ -1229,7 +1217,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="1" t="n">
         <v>39814</v>
       </c>
       <c r="B50" t="n">
@@ -1246,7 +1234,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" s="1" t="n">
         <v>39845</v>
       </c>
       <c r="B51" t="n">
@@ -1263,7 +1251,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="A52" s="1" t="n">
         <v>39873</v>
       </c>
       <c r="B52" t="n">
@@ -1280,7 +1268,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" s="1" t="n">
         <v>39904</v>
       </c>
       <c r="B53" t="n">
@@ -1297,7 +1285,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n">
+      <c r="A54" s="1" t="n">
         <v>39934</v>
       </c>
       <c r="B54" t="n">
@@ -1314,7 +1302,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n">
+      <c r="A55" s="1" t="n">
         <v>39965</v>
       </c>
       <c r="B55" t="n">
@@ -1331,7 +1319,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
+      <c r="A56" s="1" t="n">
         <v>39995</v>
       </c>
       <c r="B56" t="n">
@@ -1348,7 +1336,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="A57" s="1" t="n">
         <v>40026</v>
       </c>
       <c r="B57" t="n">
@@ -1365,7 +1353,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
+      <c r="A58" s="1" t="n">
         <v>40057</v>
       </c>
       <c r="B58" t="n">
@@ -1382,7 +1370,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
+      <c r="A59" s="1" t="n">
         <v>40087</v>
       </c>
       <c r="B59" t="n">
@@ -1399,7 +1387,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
+      <c r="A60" s="1" t="n">
         <v>40118</v>
       </c>
       <c r="B60" t="n">
@@ -1416,7 +1404,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
+      <c r="A61" s="1" t="n">
         <v>40148</v>
       </c>
       <c r="B61" t="n">
@@ -1433,7 +1421,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
+      <c r="A62" s="1" t="n">
         <v>40179</v>
       </c>
       <c r="B62" t="n">
@@ -1450,7 +1438,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n">
+      <c r="A63" s="1" t="n">
         <v>40210</v>
       </c>
       <c r="B63" t="n">
@@ -1467,7 +1455,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n">
+      <c r="A64" s="1" t="n">
         <v>40238</v>
       </c>
       <c r="B64" t="n">
@@ -1484,7 +1472,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n">
+      <c r="A65" s="1" t="n">
         <v>40269</v>
       </c>
       <c r="B65" t="n">
@@ -1501,7 +1489,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n">
+      <c r="A66" s="1" t="n">
         <v>40299</v>
       </c>
       <c r="B66" t="n">
@@ -1518,7 +1506,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n">
+      <c r="A67" s="1" t="n">
         <v>40330</v>
       </c>
       <c r="B67" t="n">
@@ -1535,7 +1523,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n">
+      <c r="A68" s="1" t="n">
         <v>40360</v>
       </c>
       <c r="B68" t="n">
@@ -1552,7 +1540,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n">
+      <c r="A69" s="1" t="n">
         <v>40391</v>
       </c>
       <c r="B69" t="n">
@@ -1569,7 +1557,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="n">
+      <c r="A70" s="1" t="n">
         <v>40422</v>
       </c>
       <c r="B70" t="n">
@@ -1586,7 +1574,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="n">
+      <c r="A71" s="1" t="n">
         <v>40452</v>
       </c>
       <c r="B71" t="n">
@@ -1603,7 +1591,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="n">
+      <c r="A72" s="1" t="n">
         <v>40483</v>
       </c>
       <c r="B72" t="n">
@@ -1620,7 +1608,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="n">
+      <c r="A73" s="1" t="n">
         <v>40513</v>
       </c>
       <c r="B73" t="n">
@@ -1637,7 +1625,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="n">
+      <c r="A74" s="1" t="n">
         <v>40544</v>
       </c>
       <c r="B74" t="n">
@@ -1654,7 +1642,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="n">
+      <c r="A75" s="1" t="n">
         <v>40575</v>
       </c>
       <c r="B75" t="n">
@@ -1671,7 +1659,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="n">
+      <c r="A76" s="1" t="n">
         <v>40603</v>
       </c>
       <c r="B76" t="n">
@@ -1688,7 +1676,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n">
+      <c r="A77" s="1" t="n">
         <v>40634</v>
       </c>
       <c r="B77" t="n">
@@ -1705,7 +1693,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n">
+      <c r="A78" s="1" t="n">
         <v>40664</v>
       </c>
       <c r="B78" t="n">
@@ -1722,7 +1710,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="n">
+      <c r="A79" s="1" t="n">
         <v>40695</v>
       </c>
       <c r="B79" t="n">
@@ -1739,7 +1727,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="n">
+      <c r="A80" s="1" t="n">
         <v>40725</v>
       </c>
       <c r="B80" t="n">
@@ -1756,7 +1744,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="n">
+      <c r="A81" s="1" t="n">
         <v>40756</v>
       </c>
       <c r="B81" t="n">
@@ -1773,7 +1761,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="n">
+      <c r="A82" s="1" t="n">
         <v>40787</v>
       </c>
       <c r="B82" t="n">
@@ -1790,7 +1778,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="n">
+      <c r="A83" s="1" t="n">
         <v>40817</v>
       </c>
       <c r="B83" t="n">
@@ -1807,7 +1795,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="n">
+      <c r="A84" s="1" t="n">
         <v>40848</v>
       </c>
       <c r="B84" t="n">
@@ -1824,7 +1812,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="n">
+      <c r="A85" s="1" t="n">
         <v>40878</v>
       </c>
       <c r="B85" t="n">
@@ -1841,7 +1829,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="n">
+      <c r="A86" s="1" t="n">
         <v>40909</v>
       </c>
       <c r="B86" t="n">
@@ -1858,7 +1846,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="n">
+      <c r="A87" s="1" t="n">
         <v>40940</v>
       </c>
       <c r="B87" t="n">
@@ -1875,7 +1863,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="n">
+      <c r="A88" s="1" t="n">
         <v>40969</v>
       </c>
       <c r="B88" t="n">
@@ -1892,7 +1880,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="n">
+      <c r="A89" s="1" t="n">
         <v>41000</v>
       </c>
       <c r="B89" t="n">
@@ -1909,7 +1897,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="n">
+      <c r="A90" s="1" t="n">
         <v>41030</v>
       </c>
       <c r="B90" t="n">
@@ -1926,7 +1914,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="n">
+      <c r="A91" s="1" t="n">
         <v>41061</v>
       </c>
       <c r="B91" t="n">
@@ -1943,7 +1931,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="n">
+      <c r="A92" s="1" t="n">
         <v>41091</v>
       </c>
       <c r="B92" t="n">
@@ -1960,7 +1948,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="n">
+      <c r="A93" s="1" t="n">
         <v>41122</v>
       </c>
       <c r="B93" t="n">
@@ -1977,7 +1965,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="n">
+      <c r="A94" s="1" t="n">
         <v>41153</v>
       </c>
       <c r="B94" t="n">
@@ -1994,7 +1982,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="n">
+      <c r="A95" s="1" t="n">
         <v>41183</v>
       </c>
       <c r="B95" t="n">
@@ -2011,7 +1999,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="n">
+      <c r="A96" s="1" t="n">
         <v>41214</v>
       </c>
       <c r="B96" t="n">
@@ -2028,7 +2016,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="n">
+      <c r="A97" s="1" t="n">
         <v>41244</v>
       </c>
       <c r="B97" t="n">
@@ -2045,7 +2033,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="n">
+      <c r="A98" s="1" t="n">
         <v>41275</v>
       </c>
       <c r="B98" t="n">
@@ -2062,7 +2050,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="n">
+      <c r="A99" s="1" t="n">
         <v>41306</v>
       </c>
       <c r="B99" t="n">
@@ -2079,7 +2067,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="n">
+      <c r="A100" s="1" t="n">
         <v>41334</v>
       </c>
       <c r="B100" t="n">
@@ -2096,7 +2084,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="n">
+      <c r="A101" s="1" t="n">
         <v>41365</v>
       </c>
       <c r="B101" t="n">
@@ -2113,7 +2101,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="n">
+      <c r="A102" s="1" t="n">
         <v>41395</v>
       </c>
       <c r="B102" t="n">
@@ -2130,7 +2118,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="n">
+      <c r="A103" s="1" t="n">
         <v>41426</v>
       </c>
       <c r="B103" t="n">
@@ -2147,7 +2135,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="2" t="n">
+      <c r="A104" s="1" t="n">
         <v>41456</v>
       </c>
       <c r="B104" t="n">
@@ -2164,7 +2152,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="2" t="n">
+      <c r="A105" s="1" t="n">
         <v>41487</v>
       </c>
       <c r="B105" t="n">
@@ -2181,7 +2169,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="n">
+      <c r="A106" s="1" t="n">
         <v>41518</v>
       </c>
       <c r="B106" t="n">
@@ -2198,7 +2186,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="n">
+      <c r="A107" s="1" t="n">
         <v>41548</v>
       </c>
       <c r="B107" t="n">
@@ -2215,7 +2203,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="n">
+      <c r="A108" s="1" t="n">
         <v>41579</v>
       </c>
       <c r="B108" t="n">
@@ -2232,7 +2220,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="n">
+      <c r="A109" s="1" t="n">
         <v>41609</v>
       </c>
       <c r="B109" t="n">
@@ -2249,7 +2237,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="n">
+      <c r="A110" s="1" t="n">
         <v>41640</v>
       </c>
       <c r="B110" t="n">
@@ -2266,7 +2254,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="n">
+      <c r="A111" s="1" t="n">
         <v>41671</v>
       </c>
       <c r="B111" t="n">
@@ -2283,7 +2271,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="n">
+      <c r="A112" s="1" t="n">
         <v>41699</v>
       </c>
       <c r="B112" t="n">
@@ -2300,7 +2288,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="2" t="n">
+      <c r="A113" s="1" t="n">
         <v>41730</v>
       </c>
       <c r="B113" t="n">
@@ -2317,7 +2305,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="2" t="n">
+      <c r="A114" s="1" t="n">
         <v>41760</v>
       </c>
       <c r="B114" t="n">
@@ -2334,7 +2322,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="n">
+      <c r="A115" s="1" t="n">
         <v>41791</v>
       </c>
       <c r="B115" t="n">
@@ -2351,7 +2339,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="n">
+      <c r="A116" s="1" t="n">
         <v>41821</v>
       </c>
       <c r="B116" t="n">
@@ -2368,7 +2356,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="2" t="n">
+      <c r="A117" s="1" t="n">
         <v>41852</v>
       </c>
       <c r="B117" t="n">
@@ -2385,7 +2373,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="2" t="n">
+      <c r="A118" s="1" t="n">
         <v>41883</v>
       </c>
       <c r="B118" t="n">
@@ -2402,7 +2390,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="n">
+      <c r="A119" s="1" t="n">
         <v>41913</v>
       </c>
       <c r="B119" t="n">
@@ -2419,7 +2407,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="n">
+      <c r="A120" s="1" t="n">
         <v>41944</v>
       </c>
       <c r="B120" t="n">
@@ -2436,7 +2424,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="2" t="n">
+      <c r="A121" s="1" t="n">
         <v>41974</v>
       </c>
       <c r="B121" t="n">
@@ -2453,7 +2441,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="2" t="n">
+      <c r="A122" s="1" t="n">
         <v>42005</v>
       </c>
       <c r="B122" t="n">
@@ -2470,7 +2458,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="2" t="n">
+      <c r="A123" s="1" t="n">
         <v>42036</v>
       </c>
       <c r="B123" t="n">
@@ -2487,7 +2475,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="n">
+      <c r="A124" s="1" t="n">
         <v>42064</v>
       </c>
       <c r="B124" t="n">
@@ -2504,7 +2492,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="2" t="n">
+      <c r="A125" s="1" t="n">
         <v>42095</v>
       </c>
       <c r="B125" t="n">
@@ -2521,7 +2509,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="2" t="n">
+      <c r="A126" s="1" t="n">
         <v>42125</v>
       </c>
       <c r="B126" t="n">
@@ -2538,7 +2526,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="2" t="n">
+      <c r="A127" s="1" t="n">
         <v>42156</v>
       </c>
       <c r="B127" t="n">
@@ -2555,7 +2543,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="2" t="n">
+      <c r="A128" s="1" t="n">
         <v>42186</v>
       </c>
       <c r="B128" t="n">
@@ -2572,7 +2560,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="2" t="n">
+      <c r="A129" s="1" t="n">
         <v>42217</v>
       </c>
       <c r="B129" t="n">
@@ -2589,7 +2577,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="2" t="n">
+      <c r="A130" s="1" t="n">
         <v>42248</v>
       </c>
       <c r="B130" t="n">
@@ -2606,7 +2594,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="2" t="n">
+      <c r="A131" s="1" t="n">
         <v>42278</v>
       </c>
       <c r="B131" t="n">
@@ -2623,7 +2611,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="2" t="n">
+      <c r="A132" s="1" t="n">
         <v>42309</v>
       </c>
       <c r="B132" t="n">
@@ -2640,7 +2628,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="2" t="n">
+      <c r="A133" s="1" t="n">
         <v>42339</v>
       </c>
       <c r="B133" t="n">
@@ -2657,7 +2645,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="2" t="n">
+      <c r="A134" s="1" t="n">
         <v>42370</v>
       </c>
       <c r="B134" t="n">
@@ -2674,7 +2662,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="2" t="n">
+      <c r="A135" s="1" t="n">
         <v>42401</v>
       </c>
       <c r="B135" t="n">
@@ -2691,7 +2679,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="2" t="n">
+      <c r="A136" s="1" t="n">
         <v>42430</v>
       </c>
       <c r="B136" t="n">
@@ -2708,7 +2696,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="2" t="n">
+      <c r="A137" s="1" t="n">
         <v>42461</v>
       </c>
       <c r="B137" t="n">
@@ -2725,7 +2713,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="2" t="n">
+      <c r="A138" s="1" t="n">
         <v>42491</v>
       </c>
       <c r="B138" t="n">
@@ -2742,7 +2730,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="2" t="n">
+      <c r="A139" s="1" t="n">
         <v>42522</v>
       </c>
       <c r="B139" t="n">
@@ -2759,7 +2747,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="2" t="n">
+      <c r="A140" s="1" t="n">
         <v>42552</v>
       </c>
       <c r="B140" t="n">
@@ -2776,7 +2764,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="2" t="n">
+      <c r="A141" s="1" t="n">
         <v>42583</v>
       </c>
       <c r="B141" t="n">
@@ -2793,7 +2781,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="2" t="n">
+      <c r="A142" s="1" t="n">
         <v>42614</v>
       </c>
       <c r="B142" t="n">
@@ -2810,7 +2798,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="2" t="n">
+      <c r="A143" s="1" t="n">
         <v>42644</v>
       </c>
       <c r="B143" t="n">
@@ -2827,7 +2815,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="2" t="n">
+      <c r="A144" s="1" t="n">
         <v>42675</v>
       </c>
       <c r="B144" t="n">
@@ -2844,7 +2832,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="2" t="n">
+      <c r="A145" s="1" t="n">
         <v>42705</v>
       </c>
       <c r="B145" t="n">
@@ -2861,7 +2849,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="2" t="n">
+      <c r="A146" s="1" t="n">
         <v>42736</v>
       </c>
       <c r="B146" t="n">
@@ -2878,7 +2866,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="2" t="n">
+      <c r="A147" s="1" t="n">
         <v>42767</v>
       </c>
       <c r="B147" t="n">
@@ -2895,7 +2883,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="2" t="n">
+      <c r="A148" s="1" t="n">
         <v>42795</v>
       </c>
       <c r="B148" t="n">
@@ -2912,7 +2900,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="2" t="n">
+      <c r="A149" s="1" t="n">
         <v>42826</v>
       </c>
       <c r="B149" t="n">
@@ -2929,7 +2917,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="2" t="n">
+      <c r="A150" s="1" t="n">
         <v>42856</v>
       </c>
       <c r="B150" t="n">
@@ -2946,7 +2934,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="2" t="n">
+      <c r="A151" s="1" t="n">
         <v>42887</v>
       </c>
       <c r="B151" t="n">
@@ -2963,7 +2951,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="2" t="n">
+      <c r="A152" s="1" t="n">
         <v>42917</v>
       </c>
       <c r="B152" t="n">
@@ -2980,7 +2968,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="2" t="n">
+      <c r="A153" s="1" t="n">
         <v>42948</v>
       </c>
       <c r="B153" t="n">
@@ -2997,7 +2985,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="2" t="n">
+      <c r="A154" s="1" t="n">
         <v>42979</v>
       </c>
       <c r="B154" t="n">
@@ -3014,7 +3002,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="2" t="n">
+      <c r="A155" s="1" t="n">
         <v>43009</v>
       </c>
       <c r="B155" t="n">
@@ -3031,7 +3019,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="2" t="n">
+      <c r="A156" s="1" t="n">
         <v>43040</v>
       </c>
       <c r="B156" t="n">
@@ -3048,7 +3036,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="2" t="n">
+      <c r="A157" s="1" t="n">
         <v>43070</v>
       </c>
       <c r="B157" t="n">
@@ -3065,7 +3053,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="2" t="n">
+      <c r="A158" s="1" t="n">
         <v>43101</v>
       </c>
       <c r="B158" t="n">
@@ -3082,7 +3070,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="2" t="n">
+      <c r="A159" s="1" t="n">
         <v>43132</v>
       </c>
       <c r="B159" t="n">
@@ -3099,7 +3087,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="2" t="n">
+      <c r="A160" s="1" t="n">
         <v>43160</v>
       </c>
       <c r="B160" t="n">
@@ -3116,7 +3104,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="2" t="n">
+      <c r="A161" s="1" t="n">
         <v>43191</v>
       </c>
       <c r="B161" t="n">
@@ -3133,7 +3121,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="2" t="n">
+      <c r="A162" s="1" t="n">
         <v>43221</v>
       </c>
       <c r="B162" t="n">
@@ -3150,7 +3138,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="2" t="n">
+      <c r="A163" s="1" t="n">
         <v>43252</v>
       </c>
       <c r="B163" t="n">
@@ -3167,7 +3155,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="2" t="n">
+      <c r="A164" s="1" t="n">
         <v>43282</v>
       </c>
       <c r="B164" t="n">
@@ -3184,7 +3172,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="2" t="n">
+      <c r="A165" s="1" t="n">
         <v>43313</v>
       </c>
       <c r="B165" t="n">
@@ -3201,7 +3189,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="2" t="n">
+      <c r="A166" s="1" t="n">
         <v>43344</v>
       </c>
       <c r="B166" t="n">
@@ -3218,7 +3206,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="2" t="n">
+      <c r="A167" s="1" t="n">
         <v>43374</v>
       </c>
       <c r="B167" t="n">
@@ -3235,7 +3223,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="2" t="n">
+      <c r="A168" s="1" t="n">
         <v>43405</v>
       </c>
       <c r="B168" t="n">
@@ -3252,7 +3240,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="2" t="n">
+      <c r="A169" s="1" t="n">
         <v>43435</v>
       </c>
       <c r="B169" t="n">
@@ -3269,7 +3257,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="2" t="n">
+      <c r="A170" s="1" t="n">
         <v>43466</v>
       </c>
       <c r="B170" t="n">
@@ -3286,7 +3274,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="2" t="n">
+      <c r="A171" s="1" t="n">
         <v>43497</v>
       </c>
       <c r="B171" t="n">
@@ -3303,7 +3291,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="2" t="n">
+      <c r="A172" s="1" t="n">
         <v>43525</v>
       </c>
       <c r="B172" t="n">
@@ -3320,7 +3308,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="2" t="n">
+      <c r="A173" s="1" t="n">
         <v>43556</v>
       </c>
       <c r="B173" t="n">
@@ -3337,7 +3325,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="2" t="n">
+      <c r="A174" s="1" t="n">
         <v>43586</v>
       </c>
       <c r="B174" t="n">
@@ -3354,7 +3342,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="2" t="n">
+      <c r="A175" s="1" t="n">
         <v>43617</v>
       </c>
       <c r="B175" t="n">
@@ -3371,7 +3359,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="2" t="n">
+      <c r="A176" s="1" t="n">
         <v>43647</v>
       </c>
       <c r="B176" t="n">
@@ -3388,7 +3376,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="2" t="n">
+      <c r="A177" s="1" t="n">
         <v>43678</v>
       </c>
       <c r="B177" t="n">
@@ -3405,7 +3393,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="2" t="n">
+      <c r="A178" s="1" t="n">
         <v>43709</v>
       </c>
       <c r="B178" t="n">
@@ -3422,7 +3410,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="2" t="n">
+      <c r="A179" s="1" t="n">
         <v>43739</v>
       </c>
       <c r="B179" t="n">
@@ -3439,7 +3427,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="2" t="n">
+      <c r="A180" s="1" t="n">
         <v>43770</v>
       </c>
       <c r="B180" t="n">
@@ -3456,7 +3444,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="2" t="n">
+      <c r="A181" s="1" t="n">
         <v>43800</v>
       </c>
       <c r="B181" t="n">
@@ -3473,7 +3461,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="2" t="n">
+      <c r="A182" s="1" t="n">
         <v>43831</v>
       </c>
       <c r="B182" t="n">
@@ -3490,7 +3478,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="2" t="n">
+      <c r="A183" s="1" t="n">
         <v>43862</v>
       </c>
       <c r="B183" t="n">
@@ -3507,7 +3495,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="2" t="n">
+      <c r="A184" s="1" t="n">
         <v>43891</v>
       </c>
       <c r="B184" t="n">
@@ -3524,7 +3512,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="2" t="n">
+      <c r="A185" s="1" t="n">
         <v>43922</v>
       </c>
       <c r="B185" t="n">
@@ -3541,7 +3529,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="2" t="n">
+      <c r="A186" s="1" t="n">
         <v>43952</v>
       </c>
       <c r="B186" t="n">
@@ -3558,7 +3546,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="2" t="n">
+      <c r="A187" s="1" t="n">
         <v>43983</v>
       </c>
       <c r="B187" t="n">
@@ -3575,7 +3563,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="2" t="n">
+      <c r="A188" s="1" t="n">
         <v>44013</v>
       </c>
       <c r="B188" t="n">
@@ -3592,7 +3580,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="2" t="n">
+      <c r="A189" s="1" t="n">
         <v>44044</v>
       </c>
       <c r="B189" t="n">
@@ -3609,7 +3597,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="2" t="n">
+      <c r="A190" s="1" t="n">
         <v>44075</v>
       </c>
       <c r="B190" t="n">
@@ -3626,7 +3614,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="2" t="n">
+      <c r="A191" s="1" t="n">
         <v>44105</v>
       </c>
       <c r="B191" t="n">
@@ -3643,7 +3631,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="2" t="n">
+      <c r="A192" s="1" t="n">
         <v>44136</v>
       </c>
       <c r="B192" t="n">
@@ -3660,7 +3648,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="2" t="n">
+      <c r="A193" s="1" t="n">
         <v>44166</v>
       </c>
       <c r="B193" t="n">
@@ -3677,7 +3665,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="2" t="n">
+      <c r="A194" s="1" t="n">
         <v>44197</v>
       </c>
       <c r="B194" t="n">
@@ -3694,7 +3682,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="2" t="n">
+      <c r="A195" s="1" t="n">
         <v>44228</v>
       </c>
       <c r="B195" t="n">
@@ -3711,7 +3699,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="2" t="n">
+      <c r="A196" s="1" t="n">
         <v>44256</v>
       </c>
       <c r="B196" t="n">
@@ -3728,7 +3716,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="2" t="n">
+      <c r="A197" s="1" t="n">
         <v>44287</v>
       </c>
       <c r="B197" t="n">
@@ -3745,7 +3733,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="2" t="n">
+      <c r="A198" s="1" t="n">
         <v>44317</v>
       </c>
       <c r="B198" t="n">
@@ -3762,7 +3750,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="2" t="n">
+      <c r="A199" s="1" t="n">
         <v>44348</v>
       </c>
       <c r="B199" t="n">
@@ -3779,7 +3767,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="2" t="n">
+      <c r="A200" s="1" t="n">
         <v>44378</v>
       </c>
       <c r="B200" t="n">
@@ -3796,7 +3784,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="2" t="n">
+      <c r="A201" s="1" t="n">
         <v>44409</v>
       </c>
       <c r="B201" t="n">
@@ -3813,7 +3801,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="2" t="n">
+      <c r="A202" s="1" t="n">
         <v>44440</v>
       </c>
       <c r="B202" t="n">
@@ -3830,7 +3818,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="2" t="n">
+      <c r="A203" s="1" t="n">
         <v>44470</v>
       </c>
       <c r="B203" t="n">
@@ -3847,7 +3835,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="2" t="n">
+      <c r="A204" s="1" t="n">
         <v>44501</v>
       </c>
       <c r="B204" t="n">
@@ -3864,7 +3852,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="2" t="n">
+      <c r="A205" s="1" t="n">
         <v>44531</v>
       </c>
       <c r="B205" t="n">
@@ -3881,7 +3869,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="2" t="n">
+      <c r="A206" s="1" t="n">
         <v>44562</v>
       </c>
       <c r="B206" t="n">
@@ -3898,7 +3886,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="2" t="n">
+      <c r="A207" s="1" t="n">
         <v>44593</v>
       </c>
       <c r="B207" t="n">
@@ -3915,7 +3903,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="2" t="n">
+      <c r="A208" s="1" t="n">
         <v>44621</v>
       </c>
       <c r="B208" t="n">
@@ -3932,7 +3920,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="2" t="n">
+      <c r="A209" s="1" t="n">
         <v>44652</v>
       </c>
       <c r="B209" t="n">
@@ -3949,7 +3937,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="2" t="n">
+      <c r="A210" s="1" t="n">
         <v>44682</v>
       </c>
       <c r="B210" t="n">
@@ -3966,7 +3954,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="2" t="n">
+      <c r="A211" s="1" t="n">
         <v>44713</v>
       </c>
       <c r="B211" t="n">
@@ -3983,7 +3971,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="2" t="n">
+      <c r="A212" s="1" t="n">
         <v>44743</v>
       </c>
       <c r="B212" t="n">
@@ -4000,7 +3988,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="2" t="n">
+      <c r="A213" s="1" t="n">
         <v>44774</v>
       </c>
       <c r="B213" t="n">
@@ -4017,7 +4005,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="2" t="n">
+      <c r="A214" s="1" t="n">
         <v>44805</v>
       </c>
       <c r="B214" t="n">
@@ -4034,7 +4022,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="2" t="n">
+      <c r="A215" s="1" t="n">
         <v>44835</v>
       </c>
       <c r="B215" t="n">
@@ -4051,7 +4039,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="2" t="n">
+      <c r="A216" s="1" t="n">
         <v>44866</v>
       </c>
       <c r="B216" t="n">
@@ -4068,7 +4056,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="2" t="n">
+      <c r="A217" s="1" t="n">
         <v>44896</v>
       </c>
       <c r="B217" t="n">
@@ -4085,7 +4073,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="2" t="n">
+      <c r="A218" s="1" t="n">
         <v>44927</v>
       </c>
       <c r="B218" t="n">
@@ -4102,7 +4090,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="2" t="n">
+      <c r="A219" s="1" t="n">
         <v>44958</v>
       </c>
       <c r="B219" t="n">
@@ -4119,7 +4107,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="2" t="n">
+      <c r="A220" s="1" t="n">
         <v>44986</v>
       </c>
       <c r="B220" t="n">
@@ -4136,7 +4124,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="2" t="n">
+      <c r="A221" s="1" t="n">
         <v>45017</v>
       </c>
       <c r="B221" t="n">
@@ -4153,7 +4141,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="2" t="n">
+      <c r="A222" s="1" t="n">
         <v>45047</v>
       </c>
       <c r="B222" t="n">
@@ -4170,7 +4158,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="2" t="n">
+      <c r="A223" s="1" t="n">
         <v>45078</v>
       </c>
       <c r="B223" t="n">
@@ -4187,7 +4175,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="2" t="n">
+      <c r="A224" s="1" t="n">
         <v>45108</v>
       </c>
       <c r="B224" t="n">
@@ -4204,7 +4192,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="2" t="n">
+      <c r="A225" s="1" t="n">
         <v>45139</v>
       </c>
       <c r="B225" t="n">
@@ -4221,7 +4209,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="2" t="n">
+      <c r="A226" s="1" t="n">
         <v>45170</v>
       </c>
       <c r="B226" t="n">
@@ -4238,7 +4226,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="2" t="n">
+      <c r="A227" s="1" t="n">
         <v>45200</v>
       </c>
       <c r="B227" t="n">
@@ -4255,7 +4243,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="2" t="n">
+      <c r="A228" s="1" t="n">
         <v>45231</v>
       </c>
       <c r="B228" t="n">
@@ -4272,7 +4260,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="2" t="n">
+      <c r="A229" s="1" t="n">
         <v>45261</v>
       </c>
       <c r="B229" t="n">
@@ -4289,7 +4277,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="2" t="n">
+      <c r="A230" s="1" t="n">
         <v>45292</v>
       </c>
       <c r="B230" t="n">
@@ -4306,7 +4294,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="2" t="n">
+      <c r="A231" s="1" t="n">
         <v>45323</v>
       </c>
       <c r="B231" t="n">
@@ -4323,7 +4311,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="2" t="n">
+      <c r="A232" s="1" t="n">
         <v>45352</v>
       </c>
       <c r="B232" t="n">
@@ -4340,7 +4328,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="2" t="n">
+      <c r="A233" s="1" t="n">
         <v>45383</v>
       </c>
       <c r="B233" t="n">
@@ -4357,7 +4345,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="2" t="n">
+      <c r="A234" s="1" t="n">
         <v>45413</v>
       </c>
       <c r="B234" t="n">
@@ -4374,7 +4362,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="2" t="n">
+      <c r="A235" s="1" t="n">
         <v>45444</v>
       </c>
       <c r="B235" t="n">
@@ -4391,7 +4379,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="2" t="n">
+      <c r="A236" s="1" t="n">
         <v>45474</v>
       </c>
       <c r="B236" t="n">
@@ -4408,7 +4396,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="2" t="n">
+      <c r="A237" s="1" t="n">
         <v>45505</v>
       </c>
       <c r="B237" t="n">
@@ -4425,7 +4413,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="2" t="n">
+      <c r="A238" s="1" t="n">
         <v>45536</v>
       </c>
       <c r="B238" t="n">
@@ -4442,7 +4430,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="2" t="n">
+      <c r="A239" s="1" t="n">
         <v>45566</v>
       </c>
       <c r="B239" t="n">
@@ -4459,7 +4447,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="2" t="n">
+      <c r="A240" s="1" t="n">
         <v>45597</v>
       </c>
       <c r="B240" t="n">
@@ -4476,7 +4464,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="2" t="n">
+      <c r="A241" s="1" t="n">
         <v>45627</v>
       </c>
       <c r="B241" t="n">
@@ -4493,7 +4481,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="2" t="n">
+      <c r="A242" s="1" t="n">
         <v>45658</v>
       </c>
       <c r="B242" t="n">
@@ -4510,7 +4498,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="2" t="n">
+      <c r="A243" s="1" t="n">
         <v>45689</v>
       </c>
       <c r="B243" t="n">
@@ -4527,7 +4515,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="2" t="n">
+      <c r="A244" s="1" t="n">
         <v>45717</v>
       </c>
       <c r="B244" t="n">
@@ -4544,7 +4532,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="2" t="n">
+      <c r="A245" s="1" t="n">
         <v>45748</v>
       </c>
       <c r="B245" t="n">
@@ -4561,7 +4549,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="2" t="n">
+      <c r="A246" s="1" t="n">
         <v>45778</v>
       </c>
       <c r="B246" t="n">
@@ -4578,7 +4566,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="2" t="n">
+      <c r="A247" s="1" t="n">
         <v>45809</v>
       </c>
       <c r="B247" t="n">
@@ -4595,7 +4583,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="2" t="n">
+      <c r="A248" s="1" t="n">
         <v>45839</v>
       </c>
       <c r="B248" t="n">
@@ -4612,7 +4600,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="2" t="n">
+      <c r="A249" s="1" t="n">
         <v>45870</v>
       </c>
       <c r="B249" t="n">
@@ -4629,7 +4617,7 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="2" t="n">
+      <c r="A250" s="1" t="n">
         <v>45901</v>
       </c>
       <c r="B250" t="n">
@@ -4646,7 +4634,7 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="2" t="n">
+      <c r="A251" s="1" t="n">
         <v>45931</v>
       </c>
       <c r="B251" t="n">
@@ -4663,7 +4651,7 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="2" t="n">
+      <c r="A252" s="1" t="n">
         <v>45962</v>
       </c>
       <c r="B252" t="n">
@@ -4680,7 +4668,7 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="2" t="n">
+      <c r="A253" s="1" t="n">
         <v>45992</v>
       </c>
       <c r="B253" t="n">
@@ -4697,7 +4685,7 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="2" t="n">
+      <c r="A254" s="1" t="n">
         <v>46023</v>
       </c>
       <c r="B254" t="n">
@@ -4714,7 +4702,7 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="2" t="n">
+      <c r="A255" s="1" t="n">
         <v>46054</v>
       </c>
       <c r="B255" t="n">
@@ -4731,7 +4719,7 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="2" t="n">
+      <c r="A256" s="1" t="n">
         <v>46082</v>
       </c>
       <c r="B256" t="n">
@@ -4748,7 +4736,7 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="2" t="n">
+      <c r="A257" s="1" t="n">
         <v>46113</v>
       </c>
       <c r="B257" t="n">
@@ -4765,7 +4753,7 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="2" t="n">
+      <c r="A258" s="1" t="n">
         <v>46143</v>
       </c>
       <c r="B258" t="n">
@@ -4782,7 +4770,7 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="2" t="n">
+      <c r="A259" s="1" t="n">
         <v>46174</v>
       </c>
       <c r="B259" t="n">
@@ -4813,79 +4801,79 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>tarih</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>01. Gıda Ve Alkolsüz İçecekler</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>02. Alkollü İçecekler, Tütün Ve Tütün Ürünleri</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>03. Giyim Ve Ayakkabı</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>04. Konut, Su, Elektrik, Gaz Ve Diğer Yakıtlar</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>05. Mobilya, Mefruşat Ve Evde Kullanılan Ekipmanlar İle Rutin Ev Bakım Ve Onarımı</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>06. Sağlık</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>07. Ulaştırma</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>08. Bilgi Ve İletişim</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>09. Eğlence, Dinlence, Spor Ve Kültür</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>10. Eğitim Hizmetleri</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>11. Lokantalar Ve Konaklama Hizmetleri</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>12. Sigorta Ve Finansal Hizmetler</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>13. Kişisel Bakım, Sosyal Koruma Ve Çeşitli Mal Ve Hizmetler</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="1" t="n">
         <v>38353</v>
       </c>
       <c r="B2" t="n">
@@ -4929,7 +4917,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="1" t="n">
         <v>38384</v>
       </c>
       <c r="B3" t="n">
@@ -4973,7 +4961,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="1" t="n">
         <v>38412</v>
       </c>
       <c r="B4" t="n">
@@ -5017,7 +5005,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="1" t="n">
         <v>38443</v>
       </c>
       <c r="B5" t="n">
@@ -5061,7 +5049,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="1" t="n">
         <v>38473</v>
       </c>
       <c r="B6" t="n">
@@ -5105,7 +5093,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="1" t="n">
         <v>38504</v>
       </c>
       <c r="B7" t="n">
@@ -5149,7 +5137,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="1" t="n">
         <v>38534</v>
       </c>
       <c r="B8" t="n">
@@ -5193,7 +5181,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="1" t="n">
         <v>38565</v>
       </c>
       <c r="B9" t="n">
@@ -5237,7 +5225,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="1" t="n">
         <v>38596</v>
       </c>
       <c r="B10" t="n">
@@ -5281,7 +5269,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="1" t="n">
         <v>38626</v>
       </c>
       <c r="B11" t="n">
@@ -5325,7 +5313,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="1" t="n">
         <v>38657</v>
       </c>
       <c r="B12" t="n">
@@ -5369,7 +5357,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="1" t="n">
         <v>38687</v>
       </c>
       <c r="B13" t="n">
@@ -5413,7 +5401,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="1" t="n">
         <v>38718</v>
       </c>
       <c r="B14" t="n">
@@ -5457,7 +5445,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="1" t="n">
         <v>38749</v>
       </c>
       <c r="B15" t="n">
@@ -5501,7 +5489,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="1" t="n">
         <v>38777</v>
       </c>
       <c r="B16" t="n">
@@ -5545,7 +5533,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="1" t="n">
         <v>38808</v>
       </c>
       <c r="B17" t="n">
@@ -5589,7 +5577,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="1" t="n">
         <v>38838</v>
       </c>
       <c r="B18" t="n">
@@ -5633,7 +5621,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="1" t="n">
         <v>38869</v>
       </c>
       <c r="B19" t="n">
@@ -5677,7 +5665,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="1" t="n">
         <v>38899</v>
       </c>
       <c r="B20" t="n">
@@ -5721,7 +5709,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="1" t="n">
         <v>38930</v>
       </c>
       <c r="B21" t="n">
@@ -5765,7 +5753,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="1" t="n">
         <v>38961</v>
       </c>
       <c r="B22" t="n">
@@ -5809,7 +5797,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="1" t="n">
         <v>38991</v>
       </c>
       <c r="B23" t="n">
@@ -5853,7 +5841,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="1" t="n">
         <v>39022</v>
       </c>
       <c r="B24" t="n">
@@ -5897,7 +5885,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="1" t="n">
         <v>39052</v>
       </c>
       <c r="B25" t="n">
@@ -5941,7 +5929,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="1" t="n">
         <v>39083</v>
       </c>
       <c r="B26" t="n">
@@ -5985,7 +5973,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="1" t="n">
         <v>39114</v>
       </c>
       <c r="B27" t="n">
@@ -6029,7 +6017,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="1" t="n">
         <v>39142</v>
       </c>
       <c r="B28" t="n">
@@ -6073,7 +6061,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="1" t="n">
         <v>39173</v>
       </c>
       <c r="B29" t="n">
@@ -6117,7 +6105,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="1" t="n">
         <v>39203</v>
       </c>
       <c r="B30" t="n">
@@ -6161,7 +6149,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="1" t="n">
         <v>39234</v>
       </c>
       <c r="B31" t="n">
@@ -6205,7 +6193,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="1" t="n">
         <v>39264</v>
       </c>
       <c r="B32" t="n">
@@ -6249,7 +6237,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="1" t="n">
         <v>39295</v>
       </c>
       <c r="B33" t="n">
@@ -6293,7 +6281,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="1" t="n">
         <v>39326</v>
       </c>
       <c r="B34" t="n">
@@ -6337,7 +6325,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="1" t="n">
         <v>39356</v>
       </c>
       <c r="B35" t="n">
@@ -6381,7 +6369,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="1" t="n">
         <v>39387</v>
       </c>
       <c r="B36" t="n">
@@ -6425,7 +6413,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="1" t="n">
         <v>39417</v>
       </c>
       <c r="B37" t="n">
@@ -6469,7 +6457,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="1" t="n">
         <v>39448</v>
       </c>
       <c r="B38" t="n">
@@ -6513,7 +6501,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="1" t="n">
         <v>39479</v>
       </c>
       <c r="B39" t="n">
@@ -6557,7 +6545,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="1" t="n">
         <v>39508</v>
       </c>
       <c r="B40" t="n">
@@ -6601,7 +6589,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" s="1" t="n">
         <v>39539</v>
       </c>
       <c r="B41" t="n">
@@ -6645,7 +6633,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="1" t="n">
         <v>39569</v>
       </c>
       <c r="B42" t="n">
@@ -6689,7 +6677,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" s="1" t="n">
         <v>39600</v>
       </c>
       <c r="B43" t="n">
@@ -6733,7 +6721,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" s="1" t="n">
         <v>39630</v>
       </c>
       <c r="B44" t="n">
@@ -6777,7 +6765,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" s="1" t="n">
         <v>39661</v>
       </c>
       <c r="B45" t="n">
@@ -6821,7 +6809,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="1" t="n">
         <v>39692</v>
       </c>
       <c r="B46" t="n">
@@ -6865,7 +6853,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="A47" s="1" t="n">
         <v>39722</v>
       </c>
       <c r="B47" t="n">
@@ -6909,7 +6897,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="1" t="n">
         <v>39753</v>
       </c>
       <c r="B48" t="n">
@@ -6953,7 +6941,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="A49" s="1" t="n">
         <v>39783</v>
       </c>
       <c r="B49" t="n">
@@ -6997,7 +6985,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="1" t="n">
         <v>39814</v>
       </c>
       <c r="B50" t="n">
@@ -7041,7 +7029,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" s="1" t="n">
         <v>39845</v>
       </c>
       <c r="B51" t="n">
@@ -7085,7 +7073,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="A52" s="1" t="n">
         <v>39873</v>
       </c>
       <c r="B52" t="n">
@@ -7129,7 +7117,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" s="1" t="n">
         <v>39904</v>
       </c>
       <c r="B53" t="n">
@@ -7173,7 +7161,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n">
+      <c r="A54" s="1" t="n">
         <v>39934</v>
       </c>
       <c r="B54" t="n">
@@ -7217,7 +7205,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n">
+      <c r="A55" s="1" t="n">
         <v>39965</v>
       </c>
       <c r="B55" t="n">
@@ -7261,7 +7249,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
+      <c r="A56" s="1" t="n">
         <v>39995</v>
       </c>
       <c r="B56" t="n">
@@ -7305,7 +7293,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="A57" s="1" t="n">
         <v>40026</v>
       </c>
       <c r="B57" t="n">
@@ -7349,7 +7337,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
+      <c r="A58" s="1" t="n">
         <v>40057</v>
       </c>
       <c r="B58" t="n">
@@ -7393,7 +7381,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
+      <c r="A59" s="1" t="n">
         <v>40087</v>
       </c>
       <c r="B59" t="n">
@@ -7437,7 +7425,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
+      <c r="A60" s="1" t="n">
         <v>40118</v>
       </c>
       <c r="B60" t="n">
@@ -7481,7 +7469,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
+      <c r="A61" s="1" t="n">
         <v>40148</v>
       </c>
       <c r="B61" t="n">
@@ -7525,7 +7513,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
+      <c r="A62" s="1" t="n">
         <v>40179</v>
       </c>
       <c r="B62" t="n">
@@ -7569,7 +7557,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n">
+      <c r="A63" s="1" t="n">
         <v>40210</v>
       </c>
       <c r="B63" t="n">
@@ -7613,7 +7601,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n">
+      <c r="A64" s="1" t="n">
         <v>40238</v>
       </c>
       <c r="B64" t="n">
@@ -7657,7 +7645,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n">
+      <c r="A65" s="1" t="n">
         <v>40269</v>
       </c>
       <c r="B65" t="n">
@@ -7701,7 +7689,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n">
+      <c r="A66" s="1" t="n">
         <v>40299</v>
       </c>
       <c r="B66" t="n">
@@ -7745,7 +7733,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n">
+      <c r="A67" s="1" t="n">
         <v>40330</v>
       </c>
       <c r="B67" t="n">
@@ -7789,7 +7777,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n">
+      <c r="A68" s="1" t="n">
         <v>40360</v>
       </c>
       <c r="B68" t="n">
@@ -7833,7 +7821,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n">
+      <c r="A69" s="1" t="n">
         <v>40391</v>
       </c>
       <c r="B69" t="n">
@@ -7877,7 +7865,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="n">
+      <c r="A70" s="1" t="n">
         <v>40422</v>
       </c>
       <c r="B70" t="n">
@@ -7921,7 +7909,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="n">
+      <c r="A71" s="1" t="n">
         <v>40452</v>
       </c>
       <c r="B71" t="n">
@@ -7965,7 +7953,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="n">
+      <c r="A72" s="1" t="n">
         <v>40483</v>
       </c>
       <c r="B72" t="n">
@@ -8009,7 +7997,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="n">
+      <c r="A73" s="1" t="n">
         <v>40513</v>
       </c>
       <c r="B73" t="n">
@@ -8053,7 +8041,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="n">
+      <c r="A74" s="1" t="n">
         <v>40544</v>
       </c>
       <c r="B74" t="n">
@@ -8097,7 +8085,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="n">
+      <c r="A75" s="1" t="n">
         <v>40575</v>
       </c>
       <c r="B75" t="n">
@@ -8141,7 +8129,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="n">
+      <c r="A76" s="1" t="n">
         <v>40603</v>
       </c>
       <c r="B76" t="n">
@@ -8185,7 +8173,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n">
+      <c r="A77" s="1" t="n">
         <v>40634</v>
       </c>
       <c r="B77" t="n">
@@ -8229,7 +8217,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n">
+      <c r="A78" s="1" t="n">
         <v>40664</v>
       </c>
       <c r="B78" t="n">
@@ -8273,7 +8261,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="n">
+      <c r="A79" s="1" t="n">
         <v>40695</v>
       </c>
       <c r="B79" t="n">
@@ -8317,7 +8305,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="n">
+      <c r="A80" s="1" t="n">
         <v>40725</v>
       </c>
       <c r="B80" t="n">
@@ -8361,7 +8349,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="n">
+      <c r="A81" s="1" t="n">
         <v>40756</v>
       </c>
       <c r="B81" t="n">
@@ -8405,7 +8393,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="n">
+      <c r="A82" s="1" t="n">
         <v>40787</v>
       </c>
       <c r="B82" t="n">
@@ -8449,7 +8437,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="n">
+      <c r="A83" s="1" t="n">
         <v>40817</v>
       </c>
       <c r="B83" t="n">
@@ -8493,7 +8481,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="n">
+      <c r="A84" s="1" t="n">
         <v>40848</v>
       </c>
       <c r="B84" t="n">
@@ -8537,7 +8525,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="n">
+      <c r="A85" s="1" t="n">
         <v>40878</v>
       </c>
       <c r="B85" t="n">
@@ -8581,7 +8569,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="n">
+      <c r="A86" s="1" t="n">
         <v>40909</v>
       </c>
       <c r="B86" t="n">
@@ -8625,7 +8613,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="n">
+      <c r="A87" s="1" t="n">
         <v>40940</v>
       </c>
       <c r="B87" t="n">
@@ -8669,7 +8657,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="n">
+      <c r="A88" s="1" t="n">
         <v>40969</v>
       </c>
       <c r="B88" t="n">
@@ -8713,7 +8701,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="n">
+      <c r="A89" s="1" t="n">
         <v>41000</v>
       </c>
       <c r="B89" t="n">
@@ -8757,7 +8745,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="n">
+      <c r="A90" s="1" t="n">
         <v>41030</v>
       </c>
       <c r="B90" t="n">
@@ -8801,7 +8789,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="n">
+      <c r="A91" s="1" t="n">
         <v>41061</v>
       </c>
       <c r="B91" t="n">
@@ -8845,7 +8833,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="n">
+      <c r="A92" s="1" t="n">
         <v>41091</v>
       </c>
       <c r="B92" t="n">
@@ -8889,7 +8877,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="n">
+      <c r="A93" s="1" t="n">
         <v>41122</v>
       </c>
       <c r="B93" t="n">
@@ -8933,7 +8921,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="n">
+      <c r="A94" s="1" t="n">
         <v>41153</v>
       </c>
       <c r="B94" t="n">
@@ -8977,7 +8965,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="n">
+      <c r="A95" s="1" t="n">
         <v>41183</v>
       </c>
       <c r="B95" t="n">
@@ -9021,7 +9009,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="n">
+      <c r="A96" s="1" t="n">
         <v>41214</v>
       </c>
       <c r="B96" t="n">
@@ -9065,7 +9053,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="n">
+      <c r="A97" s="1" t="n">
         <v>41244</v>
       </c>
       <c r="B97" t="n">
@@ -9109,7 +9097,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="n">
+      <c r="A98" s="1" t="n">
         <v>41275</v>
       </c>
       <c r="B98" t="n">
@@ -9153,7 +9141,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="n">
+      <c r="A99" s="1" t="n">
         <v>41306</v>
       </c>
       <c r="B99" t="n">
@@ -9197,7 +9185,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="n">
+      <c r="A100" s="1" t="n">
         <v>41334</v>
       </c>
       <c r="B100" t="n">
@@ -9241,7 +9229,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="n">
+      <c r="A101" s="1" t="n">
         <v>41365</v>
       </c>
       <c r="B101" t="n">
@@ -9285,7 +9273,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="n">
+      <c r="A102" s="1" t="n">
         <v>41395</v>
       </c>
       <c r="B102" t="n">
@@ -9329,7 +9317,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="n">
+      <c r="A103" s="1" t="n">
         <v>41426</v>
       </c>
       <c r="B103" t="n">
@@ -9373,7 +9361,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="2" t="n">
+      <c r="A104" s="1" t="n">
         <v>41456</v>
       </c>
       <c r="B104" t="n">
@@ -9417,7 +9405,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="2" t="n">
+      <c r="A105" s="1" t="n">
         <v>41487</v>
       </c>
       <c r="B105" t="n">
@@ -9461,7 +9449,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="n">
+      <c r="A106" s="1" t="n">
         <v>41518</v>
       </c>
       <c r="B106" t="n">
@@ -9505,7 +9493,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="n">
+      <c r="A107" s="1" t="n">
         <v>41548</v>
       </c>
       <c r="B107" t="n">
@@ -9549,7 +9537,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="n">
+      <c r="A108" s="1" t="n">
         <v>41579</v>
       </c>
       <c r="B108" t="n">
@@ -9593,7 +9581,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="n">
+      <c r="A109" s="1" t="n">
         <v>41609</v>
       </c>
       <c r="B109" t="n">
@@ -9637,7 +9625,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="n">
+      <c r="A110" s="1" t="n">
         <v>41640</v>
       </c>
       <c r="B110" t="n">
@@ -9681,7 +9669,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="n">
+      <c r="A111" s="1" t="n">
         <v>41671</v>
       </c>
       <c r="B111" t="n">
@@ -9725,7 +9713,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="n">
+      <c r="A112" s="1" t="n">
         <v>41699</v>
       </c>
       <c r="B112" t="n">
@@ -9769,7 +9757,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="2" t="n">
+      <c r="A113" s="1" t="n">
         <v>41730</v>
       </c>
       <c r="B113" t="n">
@@ -9813,7 +9801,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="2" t="n">
+      <c r="A114" s="1" t="n">
         <v>41760</v>
       </c>
       <c r="B114" t="n">
@@ -9857,7 +9845,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="n">
+      <c r="A115" s="1" t="n">
         <v>41791</v>
       </c>
       <c r="B115" t="n">
@@ -9901,7 +9889,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="n">
+      <c r="A116" s="1" t="n">
         <v>41821</v>
       </c>
       <c r="B116" t="n">
@@ -9945,7 +9933,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="2" t="n">
+      <c r="A117" s="1" t="n">
         <v>41852</v>
       </c>
       <c r="B117" t="n">
@@ -9989,7 +9977,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="2" t="n">
+      <c r="A118" s="1" t="n">
         <v>41883</v>
       </c>
       <c r="B118" t="n">
@@ -10033,7 +10021,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="n">
+      <c r="A119" s="1" t="n">
         <v>41913</v>
       </c>
       <c r="B119" t="n">
@@ -10077,7 +10065,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="n">
+      <c r="A120" s="1" t="n">
         <v>41944</v>
       </c>
       <c r="B120" t="n">
@@ -10121,7 +10109,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="2" t="n">
+      <c r="A121" s="1" t="n">
         <v>41974</v>
       </c>
       <c r="B121" t="n">
@@ -10165,7 +10153,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="2" t="n">
+      <c r="A122" s="1" t="n">
         <v>42005</v>
       </c>
       <c r="B122" t="n">
@@ -10209,7 +10197,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="2" t="n">
+      <c r="A123" s="1" t="n">
         <v>42036</v>
       </c>
       <c r="B123" t="n">
@@ -10253,7 +10241,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="n">
+      <c r="A124" s="1" t="n">
         <v>42064</v>
       </c>
       <c r="B124" t="n">
@@ -10297,7 +10285,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="2" t="n">
+      <c r="A125" s="1" t="n">
         <v>42095</v>
       </c>
       <c r="B125" t="n">
@@ -10341,7 +10329,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="2" t="n">
+      <c r="A126" s="1" t="n">
         <v>42125</v>
       </c>
       <c r="B126" t="n">
@@ -10385,7 +10373,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="2" t="n">
+      <c r="A127" s="1" t="n">
         <v>42156</v>
       </c>
       <c r="B127" t="n">
@@ -10429,7 +10417,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="2" t="n">
+      <c r="A128" s="1" t="n">
         <v>42186</v>
       </c>
       <c r="B128" t="n">
@@ -10473,7 +10461,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="2" t="n">
+      <c r="A129" s="1" t="n">
         <v>42217</v>
       </c>
       <c r="B129" t="n">
@@ -10517,7 +10505,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="2" t="n">
+      <c r="A130" s="1" t="n">
         <v>42248</v>
       </c>
       <c r="B130" t="n">
@@ -10561,7 +10549,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="2" t="n">
+      <c r="A131" s="1" t="n">
         <v>42278</v>
       </c>
       <c r="B131" t="n">
@@ -10605,7 +10593,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="2" t="n">
+      <c r="A132" s="1" t="n">
         <v>42309</v>
       </c>
       <c r="B132" t="n">
@@ -10649,7 +10637,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="2" t="n">
+      <c r="A133" s="1" t="n">
         <v>42339</v>
       </c>
       <c r="B133" t="n">
@@ -10693,7 +10681,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="2" t="n">
+      <c r="A134" s="1" t="n">
         <v>42370</v>
       </c>
       <c r="B134" t="n">
@@ -10737,7 +10725,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="2" t="n">
+      <c r="A135" s="1" t="n">
         <v>42401</v>
       </c>
       <c r="B135" t="n">
@@ -10781,7 +10769,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="2" t="n">
+      <c r="A136" s="1" t="n">
         <v>42430</v>
       </c>
       <c r="B136" t="n">
@@ -10825,7 +10813,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="2" t="n">
+      <c r="A137" s="1" t="n">
         <v>42461</v>
       </c>
       <c r="B137" t="n">
@@ -10869,7 +10857,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="2" t="n">
+      <c r="A138" s="1" t="n">
         <v>42491</v>
       </c>
       <c r="B138" t="n">
@@ -10913,7 +10901,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="2" t="n">
+      <c r="A139" s="1" t="n">
         <v>42522</v>
       </c>
       <c r="B139" t="n">
@@ -10957,7 +10945,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="2" t="n">
+      <c r="A140" s="1" t="n">
         <v>42552</v>
       </c>
       <c r="B140" t="n">
@@ -11001,7 +10989,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="2" t="n">
+      <c r="A141" s="1" t="n">
         <v>42583</v>
       </c>
       <c r="B141" t="n">
@@ -11045,7 +11033,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="2" t="n">
+      <c r="A142" s="1" t="n">
         <v>42614</v>
       </c>
       <c r="B142" t="n">
@@ -11089,7 +11077,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="2" t="n">
+      <c r="A143" s="1" t="n">
         <v>42644</v>
       </c>
       <c r="B143" t="n">
@@ -11133,7 +11121,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="2" t="n">
+      <c r="A144" s="1" t="n">
         <v>42675</v>
       </c>
       <c r="B144" t="n">
@@ -11177,7 +11165,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="2" t="n">
+      <c r="A145" s="1" t="n">
         <v>42705</v>
       </c>
       <c r="B145" t="n">
@@ -11221,7 +11209,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="2" t="n">
+      <c r="A146" s="1" t="n">
         <v>42736</v>
       </c>
       <c r="B146" t="n">
@@ -11265,7 +11253,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="2" t="n">
+      <c r="A147" s="1" t="n">
         <v>42767</v>
       </c>
       <c r="B147" t="n">
@@ -11309,7 +11297,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="2" t="n">
+      <c r="A148" s="1" t="n">
         <v>42795</v>
       </c>
       <c r="B148" t="n">
@@ -11353,7 +11341,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="2" t="n">
+      <c r="A149" s="1" t="n">
         <v>42826</v>
       </c>
       <c r="B149" t="n">
@@ -11397,7 +11385,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="2" t="n">
+      <c r="A150" s="1" t="n">
         <v>42856</v>
       </c>
       <c r="B150" t="n">
@@ -11441,7 +11429,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="2" t="n">
+      <c r="A151" s="1" t="n">
         <v>42887</v>
       </c>
       <c r="B151" t="n">
@@ -11485,7 +11473,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="2" t="n">
+      <c r="A152" s="1" t="n">
         <v>42917</v>
       </c>
       <c r="B152" t="n">
@@ -11529,7 +11517,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="2" t="n">
+      <c r="A153" s="1" t="n">
         <v>42948</v>
       </c>
       <c r="B153" t="n">
@@ -11573,7 +11561,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="2" t="n">
+      <c r="A154" s="1" t="n">
         <v>42979</v>
       </c>
       <c r="B154" t="n">
@@ -11617,7 +11605,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="2" t="n">
+      <c r="A155" s="1" t="n">
         <v>43009</v>
       </c>
       <c r="B155" t="n">
@@ -11661,7 +11649,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="2" t="n">
+      <c r="A156" s="1" t="n">
         <v>43040</v>
       </c>
       <c r="B156" t="n">
@@ -11705,7 +11693,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="2" t="n">
+      <c r="A157" s="1" t="n">
         <v>43070</v>
       </c>
       <c r="B157" t="n">
@@ -11749,7 +11737,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="2" t="n">
+      <c r="A158" s="1" t="n">
         <v>43101</v>
       </c>
       <c r="B158" t="n">
@@ -11793,7 +11781,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="2" t="n">
+      <c r="A159" s="1" t="n">
         <v>43132</v>
       </c>
       <c r="B159" t="n">
@@ -11837,7 +11825,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="2" t="n">
+      <c r="A160" s="1" t="n">
         <v>43160</v>
       </c>
       <c r="B160" t="n">
@@ -11881,7 +11869,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="2" t="n">
+      <c r="A161" s="1" t="n">
         <v>43191</v>
       </c>
       <c r="B161" t="n">
@@ -11925,7 +11913,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="2" t="n">
+      <c r="A162" s="1" t="n">
         <v>43221</v>
       </c>
       <c r="B162" t="n">
@@ -11969,7 +11957,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="2" t="n">
+      <c r="A163" s="1" t="n">
         <v>43252</v>
       </c>
       <c r="B163" t="n">
@@ -12013,7 +12001,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="2" t="n">
+      <c r="A164" s="1" t="n">
         <v>43282</v>
       </c>
       <c r="B164" t="n">
@@ -12057,7 +12045,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="2" t="n">
+      <c r="A165" s="1" t="n">
         <v>43313</v>
       </c>
       <c r="B165" t="n">
@@ -12101,7 +12089,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="2" t="n">
+      <c r="A166" s="1" t="n">
         <v>43344</v>
       </c>
       <c r="B166" t="n">
@@ -12145,7 +12133,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="2" t="n">
+      <c r="A167" s="1" t="n">
         <v>43374</v>
       </c>
       <c r="B167" t="n">
@@ -12189,7 +12177,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="2" t="n">
+      <c r="A168" s="1" t="n">
         <v>43405</v>
       </c>
       <c r="B168" t="n">
@@ -12233,7 +12221,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="2" t="n">
+      <c r="A169" s="1" t="n">
         <v>43435</v>
       </c>
       <c r="B169" t="n">
@@ -12277,7 +12265,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="2" t="n">
+      <c r="A170" s="1" t="n">
         <v>43466</v>
       </c>
       <c r="B170" t="n">
@@ -12321,7 +12309,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="2" t="n">
+      <c r="A171" s="1" t="n">
         <v>43497</v>
       </c>
       <c r="B171" t="n">
@@ -12365,7 +12353,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="2" t="n">
+      <c r="A172" s="1" t="n">
         <v>43525</v>
       </c>
       <c r="B172" t="n">
@@ -12409,7 +12397,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="2" t="n">
+      <c r="A173" s="1" t="n">
         <v>43556</v>
       </c>
       <c r="B173" t="n">
@@ -12453,7 +12441,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="2" t="n">
+      <c r="A174" s="1" t="n">
         <v>43586</v>
       </c>
       <c r="B174" t="n">
@@ -12497,7 +12485,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="2" t="n">
+      <c r="A175" s="1" t="n">
         <v>43617</v>
       </c>
       <c r="B175" t="n">
@@ -12541,7 +12529,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="2" t="n">
+      <c r="A176" s="1" t="n">
         <v>43647</v>
       </c>
       <c r="B176" t="n">
@@ -12585,7 +12573,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="2" t="n">
+      <c r="A177" s="1" t="n">
         <v>43678</v>
       </c>
       <c r="B177" t="n">
@@ -12629,7 +12617,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="2" t="n">
+      <c r="A178" s="1" t="n">
         <v>43709</v>
       </c>
       <c r="B178" t="n">
@@ -12673,7 +12661,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="2" t="n">
+      <c r="A179" s="1" t="n">
         <v>43739</v>
       </c>
       <c r="B179" t="n">
@@ -12717,7 +12705,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="2" t="n">
+      <c r="A180" s="1" t="n">
         <v>43770</v>
       </c>
       <c r="B180" t="n">
@@ -12761,7 +12749,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="2" t="n">
+      <c r="A181" s="1" t="n">
         <v>43800</v>
       </c>
       <c r="B181" t="n">
@@ -12805,7 +12793,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="2" t="n">
+      <c r="A182" s="1" t="n">
         <v>43831</v>
       </c>
       <c r="B182" t="n">
@@ -12849,7 +12837,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="2" t="n">
+      <c r="A183" s="1" t="n">
         <v>43862</v>
       </c>
       <c r="B183" t="n">
@@ -12893,7 +12881,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="2" t="n">
+      <c r="A184" s="1" t="n">
         <v>43891</v>
       </c>
       <c r="B184" t="n">
@@ -12937,7 +12925,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="2" t="n">
+      <c r="A185" s="1" t="n">
         <v>43922</v>
       </c>
       <c r="B185" t="n">
@@ -12981,7 +12969,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="2" t="n">
+      <c r="A186" s="1" t="n">
         <v>43952</v>
       </c>
       <c r="B186" t="n">
@@ -13025,7 +13013,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="2" t="n">
+      <c r="A187" s="1" t="n">
         <v>43983</v>
       </c>
       <c r="B187" t="n">
@@ -13069,7 +13057,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="2" t="n">
+      <c r="A188" s="1" t="n">
         <v>44013</v>
       </c>
       <c r="B188" t="n">
@@ -13113,7 +13101,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="2" t="n">
+      <c r="A189" s="1" t="n">
         <v>44044</v>
       </c>
       <c r="B189" t="n">
@@ -13157,7 +13145,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="2" t="n">
+      <c r="A190" s="1" t="n">
         <v>44075</v>
       </c>
       <c r="B190" t="n">
@@ -13201,7 +13189,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="2" t="n">
+      <c r="A191" s="1" t="n">
         <v>44105</v>
       </c>
       <c r="B191" t="n">
@@ -13245,7 +13233,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="2" t="n">
+      <c r="A192" s="1" t="n">
         <v>44136</v>
       </c>
       <c r="B192" t="n">
@@ -13289,7 +13277,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="2" t="n">
+      <c r="A193" s="1" t="n">
         <v>44166</v>
       </c>
       <c r="B193" t="n">
@@ -13333,7 +13321,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="2" t="n">
+      <c r="A194" s="1" t="n">
         <v>44197</v>
       </c>
       <c r="B194" t="n">
@@ -13377,7 +13365,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="2" t="n">
+      <c r="A195" s="1" t="n">
         <v>44228</v>
       </c>
       <c r="B195" t="n">
@@ -13421,7 +13409,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="2" t="n">
+      <c r="A196" s="1" t="n">
         <v>44256</v>
       </c>
       <c r="B196" t="n">
@@ -13465,7 +13453,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="2" t="n">
+      <c r="A197" s="1" t="n">
         <v>44287</v>
       </c>
       <c r="B197" t="n">
@@ -13509,7 +13497,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="2" t="n">
+      <c r="A198" s="1" t="n">
         <v>44317</v>
       </c>
       <c r="B198" t="n">
@@ -13553,7 +13541,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="2" t="n">
+      <c r="A199" s="1" t="n">
         <v>44348</v>
       </c>
       <c r="B199" t="n">
@@ -13597,7 +13585,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="2" t="n">
+      <c r="A200" s="1" t="n">
         <v>44378</v>
       </c>
       <c r="B200" t="n">
@@ -13641,7 +13629,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="2" t="n">
+      <c r="A201" s="1" t="n">
         <v>44409</v>
       </c>
       <c r="B201" t="n">
@@ -13685,7 +13673,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="2" t="n">
+      <c r="A202" s="1" t="n">
         <v>44440</v>
       </c>
       <c r="B202" t="n">
@@ -13729,7 +13717,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="2" t="n">
+      <c r="A203" s="1" t="n">
         <v>44470</v>
       </c>
       <c r="B203" t="n">
@@ -13773,7 +13761,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="2" t="n">
+      <c r="A204" s="1" t="n">
         <v>44501</v>
       </c>
       <c r="B204" t="n">
@@ -13817,7 +13805,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="2" t="n">
+      <c r="A205" s="1" t="n">
         <v>44531</v>
       </c>
       <c r="B205" t="n">
@@ -13861,7 +13849,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="2" t="n">
+      <c r="A206" s="1" t="n">
         <v>44562</v>
       </c>
       <c r="B206" t="n">
@@ -13905,7 +13893,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="2" t="n">
+      <c r="A207" s="1" t="n">
         <v>44593</v>
       </c>
       <c r="B207" t="n">
@@ -13949,7 +13937,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="2" t="n">
+      <c r="A208" s="1" t="n">
         <v>44621</v>
       </c>
       <c r="B208" t="n">
@@ -13993,7 +13981,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="2" t="n">
+      <c r="A209" s="1" t="n">
         <v>44652</v>
       </c>
       <c r="B209" t="n">
@@ -14037,7 +14025,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="2" t="n">
+      <c r="A210" s="1" t="n">
         <v>44682</v>
       </c>
       <c r="B210" t="n">
@@ -14081,7 +14069,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="2" t="n">
+      <c r="A211" s="1" t="n">
         <v>44713</v>
       </c>
       <c r="B211" t="n">
@@ -14125,7 +14113,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="2" t="n">
+      <c r="A212" s="1" t="n">
         <v>44743</v>
       </c>
       <c r="B212" t="n">
@@ -14169,7 +14157,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="2" t="n">
+      <c r="A213" s="1" t="n">
         <v>44774</v>
       </c>
       <c r="B213" t="n">
@@ -14213,7 +14201,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="2" t="n">
+      <c r="A214" s="1" t="n">
         <v>44805</v>
       </c>
       <c r="B214" t="n">
@@ -14257,7 +14245,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="2" t="n">
+      <c r="A215" s="1" t="n">
         <v>44835</v>
       </c>
       <c r="B215" t="n">
@@ -14301,7 +14289,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="2" t="n">
+      <c r="A216" s="1" t="n">
         <v>44866</v>
       </c>
       <c r="B216" t="n">
@@ -14345,7 +14333,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="2" t="n">
+      <c r="A217" s="1" t="n">
         <v>44896</v>
       </c>
       <c r="B217" t="n">
@@ -14389,7 +14377,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="2" t="n">
+      <c r="A218" s="1" t="n">
         <v>44927</v>
       </c>
       <c r="B218" t="n">
@@ -14433,7 +14421,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="2" t="n">
+      <c r="A219" s="1" t="n">
         <v>44958</v>
       </c>
       <c r="B219" t="n">
@@ -14477,7 +14465,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="2" t="n">
+      <c r="A220" s="1" t="n">
         <v>44986</v>
       </c>
       <c r="B220" t="n">
@@ -14521,7 +14509,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="2" t="n">
+      <c r="A221" s="1" t="n">
         <v>45017</v>
       </c>
       <c r="B221" t="n">
@@ -14565,7 +14553,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="2" t="n">
+      <c r="A222" s="1" t="n">
         <v>45047</v>
       </c>
       <c r="B222" t="n">
@@ -14609,7 +14597,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="2" t="n">
+      <c r="A223" s="1" t="n">
         <v>45078</v>
       </c>
       <c r="B223" t="n">
@@ -14653,7 +14641,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="2" t="n">
+      <c r="A224" s="1" t="n">
         <v>45108</v>
       </c>
       <c r="B224" t="n">
@@ -14697,7 +14685,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="2" t="n">
+      <c r="A225" s="1" t="n">
         <v>45139</v>
       </c>
       <c r="B225" t="n">
@@ -14741,7 +14729,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="2" t="n">
+      <c r="A226" s="1" t="n">
         <v>45170</v>
       </c>
       <c r="B226" t="n">
@@ -14785,7 +14773,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="2" t="n">
+      <c r="A227" s="1" t="n">
         <v>45200</v>
       </c>
       <c r="B227" t="n">
@@ -14829,7 +14817,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="2" t="n">
+      <c r="A228" s="1" t="n">
         <v>45231</v>
       </c>
       <c r="B228" t="n">
@@ -14873,7 +14861,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="2" t="n">
+      <c r="A229" s="1" t="n">
         <v>45261</v>
       </c>
       <c r="B229" t="n">
@@ -14917,7 +14905,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="2" t="n">
+      <c r="A230" s="1" t="n">
         <v>45292</v>
       </c>
       <c r="B230" t="n">
@@ -14961,7 +14949,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="2" t="n">
+      <c r="A231" s="1" t="n">
         <v>45323</v>
       </c>
       <c r="B231" t="n">
@@ -15005,7 +14993,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="2" t="n">
+      <c r="A232" s="1" t="n">
         <v>45352</v>
       </c>
       <c r="B232" t="n">
@@ -15049,7 +15037,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="2" t="n">
+      <c r="A233" s="1" t="n">
         <v>45383</v>
       </c>
       <c r="B233" t="n">
@@ -15093,7 +15081,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="2" t="n">
+      <c r="A234" s="1" t="n">
         <v>45413</v>
       </c>
       <c r="B234" t="n">
@@ -15137,7 +15125,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="2" t="n">
+      <c r="A235" s="1" t="n">
         <v>45444</v>
       </c>
       <c r="B235" t="n">
@@ -15181,7 +15169,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="2" t="n">
+      <c r="A236" s="1" t="n">
         <v>45474</v>
       </c>
       <c r="B236" t="n">
@@ -15225,7 +15213,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="2" t="n">
+      <c r="A237" s="1" t="n">
         <v>45505</v>
       </c>
       <c r="B237" t="n">
@@ -15269,7 +15257,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="2" t="n">
+      <c r="A238" s="1" t="n">
         <v>45536</v>
       </c>
       <c r="B238" t="n">
@@ -15313,7 +15301,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="2" t="n">
+      <c r="A239" s="1" t="n">
         <v>45566</v>
       </c>
       <c r="B239" t="n">
@@ -15357,7 +15345,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="2" t="n">
+      <c r="A240" s="1" t="n">
         <v>45597</v>
       </c>
       <c r="B240" t="n">
@@ -15401,7 +15389,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="2" t="n">
+      <c r="A241" s="1" t="n">
         <v>45627</v>
       </c>
       <c r="B241" t="n">
@@ -15445,7 +15433,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="2" t="n">
+      <c r="A242" s="1" t="n">
         <v>45658</v>
       </c>
       <c r="B242" t="n">
@@ -15489,7 +15477,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="2" t="n">
+      <c r="A243" s="1" t="n">
         <v>45689</v>
       </c>
       <c r="B243" t="n">
@@ -15533,7 +15521,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="2" t="n">
+      <c r="A244" s="1" t="n">
         <v>45717</v>
       </c>
       <c r="B244" t="n">
@@ -15577,7 +15565,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="2" t="n">
+      <c r="A245" s="1" t="n">
         <v>45748</v>
       </c>
       <c r="B245" t="n">
@@ -15621,7 +15609,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="2" t="n">
+      <c r="A246" s="1" t="n">
         <v>45778</v>
       </c>
       <c r="B246" t="n">
@@ -15665,7 +15653,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="2" t="n">
+      <c r="A247" s="1" t="n">
         <v>45809</v>
       </c>
       <c r="B247" t="n">
@@ -15709,7 +15697,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="2" t="n">
+      <c r="A248" s="1" t="n">
         <v>45839</v>
       </c>
       <c r="B248" t="n">
@@ -15753,7 +15741,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="2" t="n">
+      <c r="A249" s="1" t="n">
         <v>45870</v>
       </c>
       <c r="B249" t="n">
@@ -15797,7 +15785,7 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="2" t="n">
+      <c r="A250" s="1" t="n">
         <v>45901</v>
       </c>
       <c r="B250" t="n">
@@ -15841,7 +15829,7 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="2" t="n">
+      <c r="A251" s="1" t="n">
         <v>45931</v>
       </c>
       <c r="B251" t="n">
@@ -15885,7 +15873,7 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="2" t="n">
+      <c r="A252" s="1" t="n">
         <v>45962</v>
       </c>
       <c r="B252" t="n">
@@ -15929,7 +15917,7 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="2" t="n">
+      <c r="A253" s="1" t="n">
         <v>45992</v>
       </c>
       <c r="B253" t="n">
@@ -15973,7 +15961,7 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="2" t="n">
+      <c r="A254" s="1" t="n">
         <v>46023</v>
       </c>
       <c r="B254" t="n">
@@ -16017,7 +16005,7 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="2" t="n">
+      <c r="A255" s="1" t="n">
         <v>46054</v>
       </c>
       <c r="B255" t="n">
@@ -16061,7 +16049,7 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="2" t="n">
+      <c r="A256" s="1" t="n">
         <v>46082</v>
       </c>
       <c r="B256" t="n">
@@ -16105,7 +16093,7 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="2" t="n">
+      <c r="A257" s="1" t="n">
         <v>46113</v>
       </c>
       <c r="B257" t="n">
@@ -16149,7 +16137,7 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="2" t="n">
+      <c r="A258" s="1" t="n">
         <v>46143</v>
       </c>
       <c r="B258" t="n">
@@ -16193,7 +16181,7 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="2" t="n">
+      <c r="A259" s="1" t="n">
         <v>46174</v>
       </c>
       <c r="B259" t="n">
@@ -16251,79 +16239,79 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>tarih</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>01. Gıda Ve Alkolsüz İçecekler</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>02. Alkollü İçecekler, Tütün Ve Tütün Ürünleri</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>03. Giyim Ve Ayakkabı</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>04. Konut, Su, Elektrik, Gaz Ve Diğer Yakıtlar</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>05. Mobilya, Mefruşat Ve Evde Kullanılan Ekipmanlar İle Rutin Ev Bakım Ve Onarımı</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>06. Sağlık</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>07. Ulaştırma</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>08. Bilgi Ve İletişim</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>09. Eğlence, Dinlence, Spor Ve Kültür</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>10. Eğitim Hizmetleri</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>11. Lokantalar Ve Konaklama Hizmetleri</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>12. Sigorta Ve Finansal Hizmetler</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>13. Kişisel Bakım, Sosyal Koruma Ve Çeşitli Mal Ve Hizmetler</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="1" t="n">
         <v>38353</v>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -16341,7 +16329,7 @@
       <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="1" t="n">
         <v>38384</v>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -16359,7 +16347,7 @@
       <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="1" t="n">
         <v>38412</v>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -16377,7 +16365,7 @@
       <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="1" t="n">
         <v>38443</v>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -16395,7 +16383,7 @@
       <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="1" t="n">
         <v>38473</v>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -16413,7 +16401,7 @@
       <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="1" t="n">
         <v>38504</v>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -16431,7 +16419,7 @@
       <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="1" t="n">
         <v>38534</v>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -16449,7 +16437,7 @@
       <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="1" t="n">
         <v>38565</v>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -16467,7 +16455,7 @@
       <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="1" t="n">
         <v>38596</v>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -16485,7 +16473,7 @@
       <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="1" t="n">
         <v>38626</v>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -16503,7 +16491,7 @@
       <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="1" t="n">
         <v>38657</v>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -16521,7 +16509,7 @@
       <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="1" t="n">
         <v>38687</v>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -16539,7 +16527,7 @@
       <c r="N13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="1" t="n">
         <v>38718</v>
       </c>
       <c r="B14" t="n">
@@ -16583,7 +16571,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="1" t="n">
         <v>38749</v>
       </c>
       <c r="B15" t="n">
@@ -16627,7 +16615,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="1" t="n">
         <v>38777</v>
       </c>
       <c r="B16" t="n">
@@ -16671,7 +16659,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="1" t="n">
         <v>38808</v>
       </c>
       <c r="B17" t="n">
@@ -16715,7 +16703,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="1" t="n">
         <v>38838</v>
       </c>
       <c r="B18" t="n">
@@ -16759,7 +16747,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="1" t="n">
         <v>38869</v>
       </c>
       <c r="B19" t="n">
@@ -16803,7 +16791,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="1" t="n">
         <v>38899</v>
       </c>
       <c r="B20" t="n">
@@ -16847,7 +16835,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="1" t="n">
         <v>38930</v>
       </c>
       <c r="B21" t="n">
@@ -16891,7 +16879,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="1" t="n">
         <v>38961</v>
       </c>
       <c r="B22" t="n">
@@ -16935,7 +16923,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="1" t="n">
         <v>38991</v>
       </c>
       <c r="B23" t="n">
@@ -16979,7 +16967,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="1" t="n">
         <v>39022</v>
       </c>
       <c r="B24" t="n">
@@ -17023,7 +17011,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="1" t="n">
         <v>39052</v>
       </c>
       <c r="B25" t="n">
@@ -17067,7 +17055,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="1" t="n">
         <v>39083</v>
       </c>
       <c r="B26" t="n">
@@ -17111,7 +17099,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="1" t="n">
         <v>39114</v>
       </c>
       <c r="B27" t="n">
@@ -17155,7 +17143,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="1" t="n">
         <v>39142</v>
       </c>
       <c r="B28" t="n">
@@ -17199,7 +17187,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="1" t="n">
         <v>39173</v>
       </c>
       <c r="B29" t="n">
@@ -17243,7 +17231,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="1" t="n">
         <v>39203</v>
       </c>
       <c r="B30" t="n">
@@ -17287,7 +17275,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="1" t="n">
         <v>39234</v>
       </c>
       <c r="B31" t="n">
@@ -17331,7 +17319,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="1" t="n">
         <v>39264</v>
       </c>
       <c r="B32" t="n">
@@ -17375,7 +17363,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="1" t="n">
         <v>39295</v>
       </c>
       <c r="B33" t="n">
@@ -17419,7 +17407,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="1" t="n">
         <v>39326</v>
       </c>
       <c r="B34" t="n">
@@ -17463,7 +17451,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="1" t="n">
         <v>39356</v>
       </c>
       <c r="B35" t="n">
@@ -17507,7 +17495,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="1" t="n">
         <v>39387</v>
       </c>
       <c r="B36" t="n">
@@ -17551,7 +17539,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="1" t="n">
         <v>39417</v>
       </c>
       <c r="B37" t="n">
@@ -17595,7 +17583,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="1" t="n">
         <v>39448</v>
       </c>
       <c r="B38" t="n">
@@ -17639,7 +17627,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="1" t="n">
         <v>39479</v>
       </c>
       <c r="B39" t="n">
@@ -17683,7 +17671,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="1" t="n">
         <v>39508</v>
       </c>
       <c r="B40" t="n">
@@ -17727,7 +17715,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" s="1" t="n">
         <v>39539</v>
       </c>
       <c r="B41" t="n">
@@ -17771,7 +17759,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="1" t="n">
         <v>39569</v>
       </c>
       <c r="B42" t="n">
@@ -17815,7 +17803,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" s="1" t="n">
         <v>39600</v>
       </c>
       <c r="B43" t="n">
@@ -17859,7 +17847,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" s="1" t="n">
         <v>39630</v>
       </c>
       <c r="B44" t="n">
@@ -17903,7 +17891,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" s="1" t="n">
         <v>39661</v>
       </c>
       <c r="B45" t="n">
@@ -17947,7 +17935,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="1" t="n">
         <v>39692</v>
       </c>
       <c r="B46" t="n">
@@ -17991,7 +17979,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="A47" s="1" t="n">
         <v>39722</v>
       </c>
       <c r="B47" t="n">
@@ -18035,7 +18023,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="1" t="n">
         <v>39753</v>
       </c>
       <c r="B48" t="n">
@@ -18079,7 +18067,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="A49" s="1" t="n">
         <v>39783</v>
       </c>
       <c r="B49" t="n">
@@ -18123,7 +18111,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="1" t="n">
         <v>39814</v>
       </c>
       <c r="B50" t="n">
@@ -18167,7 +18155,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" s="1" t="n">
         <v>39845</v>
       </c>
       <c r="B51" t="n">
@@ -18211,7 +18199,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="A52" s="1" t="n">
         <v>39873</v>
       </c>
       <c r="B52" t="n">
@@ -18255,7 +18243,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" s="1" t="n">
         <v>39904</v>
       </c>
       <c r="B53" t="n">
@@ -18299,7 +18287,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n">
+      <c r="A54" s="1" t="n">
         <v>39934</v>
       </c>
       <c r="B54" t="n">
@@ -18343,7 +18331,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n">
+      <c r="A55" s="1" t="n">
         <v>39965</v>
       </c>
       <c r="B55" t="n">
@@ -18387,7 +18375,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
+      <c r="A56" s="1" t="n">
         <v>39995</v>
       </c>
       <c r="B56" t="n">
@@ -18431,7 +18419,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="A57" s="1" t="n">
         <v>40026</v>
       </c>
       <c r="B57" t="n">
@@ -18475,7 +18463,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
+      <c r="A58" s="1" t="n">
         <v>40057</v>
       </c>
       <c r="B58" t="n">
@@ -18519,7 +18507,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
+      <c r="A59" s="1" t="n">
         <v>40087</v>
       </c>
       <c r="B59" t="n">
@@ -18563,7 +18551,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
+      <c r="A60" s="1" t="n">
         <v>40118</v>
       </c>
       <c r="B60" t="n">
@@ -18607,7 +18595,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
+      <c r="A61" s="1" t="n">
         <v>40148</v>
       </c>
       <c r="B61" t="n">
@@ -18651,7 +18639,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
+      <c r="A62" s="1" t="n">
         <v>40179</v>
       </c>
       <c r="B62" t="n">
@@ -18695,7 +18683,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n">
+      <c r="A63" s="1" t="n">
         <v>40210</v>
       </c>
       <c r="B63" t="n">
@@ -18739,7 +18727,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n">
+      <c r="A64" s="1" t="n">
         <v>40238</v>
       </c>
       <c r="B64" t="n">
@@ -18783,7 +18771,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n">
+      <c r="A65" s="1" t="n">
         <v>40269</v>
       </c>
       <c r="B65" t="n">
@@ -18827,7 +18815,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n">
+      <c r="A66" s="1" t="n">
         <v>40299</v>
       </c>
       <c r="B66" t="n">
@@ -18871,7 +18859,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n">
+      <c r="A67" s="1" t="n">
         <v>40330</v>
       </c>
       <c r="B67" t="n">
@@ -18915,7 +18903,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n">
+      <c r="A68" s="1" t="n">
         <v>40360</v>
       </c>
       <c r="B68" t="n">
@@ -18959,7 +18947,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n">
+      <c r="A69" s="1" t="n">
         <v>40391</v>
       </c>
       <c r="B69" t="n">
@@ -19003,7 +18991,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="n">
+      <c r="A70" s="1" t="n">
         <v>40422</v>
       </c>
       <c r="B70" t="n">
@@ -19047,7 +19035,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="n">
+      <c r="A71" s="1" t="n">
         <v>40452</v>
       </c>
       <c r="B71" t="n">
@@ -19091,7 +19079,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="n">
+      <c r="A72" s="1" t="n">
         <v>40483</v>
       </c>
       <c r="B72" t="n">
@@ -19135,7 +19123,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="n">
+      <c r="A73" s="1" t="n">
         <v>40513</v>
       </c>
       <c r="B73" t="n">
@@ -19179,7 +19167,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="n">
+      <c r="A74" s="1" t="n">
         <v>40544</v>
       </c>
       <c r="B74" t="n">
@@ -19223,7 +19211,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="n">
+      <c r="A75" s="1" t="n">
         <v>40575</v>
       </c>
       <c r="B75" t="n">
@@ -19267,7 +19255,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="n">
+      <c r="A76" s="1" t="n">
         <v>40603</v>
       </c>
       <c r="B76" t="n">
@@ -19311,7 +19299,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n">
+      <c r="A77" s="1" t="n">
         <v>40634</v>
       </c>
       <c r="B77" t="n">
@@ -19355,7 +19343,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n">
+      <c r="A78" s="1" t="n">
         <v>40664</v>
       </c>
       <c r="B78" t="n">
@@ -19399,7 +19387,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="n">
+      <c r="A79" s="1" t="n">
         <v>40695</v>
       </c>
       <c r="B79" t="n">
@@ -19443,7 +19431,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="n">
+      <c r="A80" s="1" t="n">
         <v>40725</v>
       </c>
       <c r="B80" t="n">
@@ -19487,7 +19475,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="n">
+      <c r="A81" s="1" t="n">
         <v>40756</v>
       </c>
       <c r="B81" t="n">
@@ -19531,7 +19519,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="n">
+      <c r="A82" s="1" t="n">
         <v>40787</v>
       </c>
       <c r="B82" t="n">
@@ -19575,7 +19563,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="n">
+      <c r="A83" s="1" t="n">
         <v>40817</v>
       </c>
       <c r="B83" t="n">
@@ -19619,7 +19607,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="n">
+      <c r="A84" s="1" t="n">
         <v>40848</v>
       </c>
       <c r="B84" t="n">
@@ -19663,7 +19651,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="n">
+      <c r="A85" s="1" t="n">
         <v>40878</v>
       </c>
       <c r="B85" t="n">
@@ -19707,7 +19695,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="n">
+      <c r="A86" s="1" t="n">
         <v>40909</v>
       </c>
       <c r="B86" t="n">
@@ -19751,7 +19739,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="n">
+      <c r="A87" s="1" t="n">
         <v>40940</v>
       </c>
       <c r="B87" t="n">
@@ -19795,7 +19783,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="n">
+      <c r="A88" s="1" t="n">
         <v>40969</v>
       </c>
       <c r="B88" t="n">
@@ -19839,7 +19827,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="n">
+      <c r="A89" s="1" t="n">
         <v>41000</v>
       </c>
       <c r="B89" t="n">
@@ -19883,7 +19871,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="n">
+      <c r="A90" s="1" t="n">
         <v>41030</v>
       </c>
       <c r="B90" t="n">
@@ -19927,7 +19915,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="n">
+      <c r="A91" s="1" t="n">
         <v>41061</v>
       </c>
       <c r="B91" t="n">
@@ -19971,7 +19959,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="n">
+      <c r="A92" s="1" t="n">
         <v>41091</v>
       </c>
       <c r="B92" t="n">
@@ -20015,7 +20003,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="n">
+      <c r="A93" s="1" t="n">
         <v>41122</v>
       </c>
       <c r="B93" t="n">
@@ -20059,7 +20047,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="n">
+      <c r="A94" s="1" t="n">
         <v>41153</v>
       </c>
       <c r="B94" t="n">
@@ -20103,7 +20091,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="n">
+      <c r="A95" s="1" t="n">
         <v>41183</v>
       </c>
       <c r="B95" t="n">
@@ -20147,7 +20135,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="n">
+      <c r="A96" s="1" t="n">
         <v>41214</v>
       </c>
       <c r="B96" t="n">
@@ -20191,7 +20179,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="n">
+      <c r="A97" s="1" t="n">
         <v>41244</v>
       </c>
       <c r="B97" t="n">
@@ -20235,7 +20223,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="n">
+      <c r="A98" s="1" t="n">
         <v>41275</v>
       </c>
       <c r="B98" t="n">
@@ -20279,7 +20267,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="n">
+      <c r="A99" s="1" t="n">
         <v>41306</v>
       </c>
       <c r="B99" t="n">
@@ -20323,7 +20311,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="n">
+      <c r="A100" s="1" t="n">
         <v>41334</v>
       </c>
       <c r="B100" t="n">
@@ -20367,7 +20355,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="n">
+      <c r="A101" s="1" t="n">
         <v>41365</v>
       </c>
       <c r="B101" t="n">
@@ -20411,7 +20399,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="n">
+      <c r="A102" s="1" t="n">
         <v>41395</v>
       </c>
       <c r="B102" t="n">
@@ -20455,7 +20443,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="n">
+      <c r="A103" s="1" t="n">
         <v>41426</v>
       </c>
       <c r="B103" t="n">
@@ -20499,7 +20487,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="2" t="n">
+      <c r="A104" s="1" t="n">
         <v>41456</v>
       </c>
       <c r="B104" t="n">
@@ -20543,7 +20531,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="2" t="n">
+      <c r="A105" s="1" t="n">
         <v>41487</v>
       </c>
       <c r="B105" t="n">
@@ -20587,7 +20575,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="n">
+      <c r="A106" s="1" t="n">
         <v>41518</v>
       </c>
       <c r="B106" t="n">
@@ -20631,7 +20619,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="n">
+      <c r="A107" s="1" t="n">
         <v>41548</v>
       </c>
       <c r="B107" t="n">
@@ -20675,7 +20663,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="n">
+      <c r="A108" s="1" t="n">
         <v>41579</v>
       </c>
       <c r="B108" t="n">
@@ -20719,7 +20707,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="n">
+      <c r="A109" s="1" t="n">
         <v>41609</v>
       </c>
       <c r="B109" t="n">
@@ -20763,7 +20751,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="n">
+      <c r="A110" s="1" t="n">
         <v>41640</v>
       </c>
       <c r="B110" t="n">
@@ -20807,7 +20795,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="n">
+      <c r="A111" s="1" t="n">
         <v>41671</v>
       </c>
       <c r="B111" t="n">
@@ -20851,7 +20839,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="n">
+      <c r="A112" s="1" t="n">
         <v>41699</v>
       </c>
       <c r="B112" t="n">
@@ -20895,7 +20883,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="2" t="n">
+      <c r="A113" s="1" t="n">
         <v>41730</v>
       </c>
       <c r="B113" t="n">
@@ -20939,7 +20927,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="2" t="n">
+      <c r="A114" s="1" t="n">
         <v>41760</v>
       </c>
       <c r="B114" t="n">
@@ -20983,7 +20971,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="n">
+      <c r="A115" s="1" t="n">
         <v>41791</v>
       </c>
       <c r="B115" t="n">
@@ -21027,7 +21015,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="n">
+      <c r="A116" s="1" t="n">
         <v>41821</v>
       </c>
       <c r="B116" t="n">
@@ -21071,7 +21059,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="2" t="n">
+      <c r="A117" s="1" t="n">
         <v>41852</v>
       </c>
       <c r="B117" t="n">
@@ -21115,7 +21103,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="2" t="n">
+      <c r="A118" s="1" t="n">
         <v>41883</v>
       </c>
       <c r="B118" t="n">
@@ -21159,7 +21147,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="n">
+      <c r="A119" s="1" t="n">
         <v>41913</v>
       </c>
       <c r="B119" t="n">
@@ -21203,7 +21191,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="n">
+      <c r="A120" s="1" t="n">
         <v>41944</v>
       </c>
       <c r="B120" t="n">
@@ -21247,7 +21235,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="2" t="n">
+      <c r="A121" s="1" t="n">
         <v>41974</v>
       </c>
       <c r="B121" t="n">
@@ -21291,7 +21279,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="2" t="n">
+      <c r="A122" s="1" t="n">
         <v>42005</v>
       </c>
       <c r="B122" t="n">
@@ -21335,7 +21323,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="2" t="n">
+      <c r="A123" s="1" t="n">
         <v>42036</v>
       </c>
       <c r="B123" t="n">
@@ -21379,7 +21367,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="n">
+      <c r="A124" s="1" t="n">
         <v>42064</v>
       </c>
       <c r="B124" t="n">
@@ -21423,7 +21411,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="2" t="n">
+      <c r="A125" s="1" t="n">
         <v>42095</v>
       </c>
       <c r="B125" t="n">
@@ -21467,7 +21455,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="2" t="n">
+      <c r="A126" s="1" t="n">
         <v>42125</v>
       </c>
       <c r="B126" t="n">
@@ -21511,7 +21499,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="2" t="n">
+      <c r="A127" s="1" t="n">
         <v>42156</v>
       </c>
       <c r="B127" t="n">
@@ -21555,7 +21543,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="2" t="n">
+      <c r="A128" s="1" t="n">
         <v>42186</v>
       </c>
       <c r="B128" t="n">
@@ -21599,7 +21587,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="2" t="n">
+      <c r="A129" s="1" t="n">
         <v>42217</v>
       </c>
       <c r="B129" t="n">
@@ -21643,7 +21631,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="2" t="n">
+      <c r="A130" s="1" t="n">
         <v>42248</v>
       </c>
       <c r="B130" t="n">
@@ -21687,7 +21675,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="2" t="n">
+      <c r="A131" s="1" t="n">
         <v>42278</v>
       </c>
       <c r="B131" t="n">
@@ -21731,7 +21719,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="2" t="n">
+      <c r="A132" s="1" t="n">
         <v>42309</v>
       </c>
       <c r="B132" t="n">
@@ -21775,7 +21763,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="2" t="n">
+      <c r="A133" s="1" t="n">
         <v>42339</v>
       </c>
       <c r="B133" t="n">
@@ -21819,7 +21807,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="2" t="n">
+      <c r="A134" s="1" t="n">
         <v>42370</v>
       </c>
       <c r="B134" t="n">
@@ -21863,7 +21851,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="2" t="n">
+      <c r="A135" s="1" t="n">
         <v>42401</v>
       </c>
       <c r="B135" t="n">
@@ -21907,7 +21895,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="2" t="n">
+      <c r="A136" s="1" t="n">
         <v>42430</v>
       </c>
       <c r="B136" t="n">
@@ -21951,7 +21939,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="2" t="n">
+      <c r="A137" s="1" t="n">
         <v>42461</v>
       </c>
       <c r="B137" t="n">
@@ -21995,7 +21983,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="2" t="n">
+      <c r="A138" s="1" t="n">
         <v>42491</v>
       </c>
       <c r="B138" t="n">
@@ -22039,7 +22027,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="2" t="n">
+      <c r="A139" s="1" t="n">
         <v>42522</v>
       </c>
       <c r="B139" t="n">
@@ -22083,7 +22071,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="2" t="n">
+      <c r="A140" s="1" t="n">
         <v>42552</v>
       </c>
       <c r="B140" t="n">
@@ -22127,7 +22115,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="2" t="n">
+      <c r="A141" s="1" t="n">
         <v>42583</v>
       </c>
       <c r="B141" t="n">
@@ -22171,7 +22159,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="2" t="n">
+      <c r="A142" s="1" t="n">
         <v>42614</v>
       </c>
       <c r="B142" t="n">
@@ -22215,7 +22203,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="2" t="n">
+      <c r="A143" s="1" t="n">
         <v>42644</v>
       </c>
       <c r="B143" t="n">
@@ -22259,7 +22247,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="2" t="n">
+      <c r="A144" s="1" t="n">
         <v>42675</v>
       </c>
       <c r="B144" t="n">
@@ -22303,7 +22291,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="2" t="n">
+      <c r="A145" s="1" t="n">
         <v>42705</v>
       </c>
       <c r="B145" t="n">
@@ -22347,7 +22335,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="2" t="n">
+      <c r="A146" s="1" t="n">
         <v>42736</v>
       </c>
       <c r="B146" t="n">
@@ -22391,7 +22379,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="2" t="n">
+      <c r="A147" s="1" t="n">
         <v>42767</v>
       </c>
       <c r="B147" t="n">
@@ -22435,7 +22423,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="2" t="n">
+      <c r="A148" s="1" t="n">
         <v>42795</v>
       </c>
       <c r="B148" t="n">
@@ -22479,7 +22467,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="2" t="n">
+      <c r="A149" s="1" t="n">
         <v>42826</v>
       </c>
       <c r="B149" t="n">
@@ -22523,7 +22511,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="2" t="n">
+      <c r="A150" s="1" t="n">
         <v>42856</v>
       </c>
       <c r="B150" t="n">
@@ -22567,7 +22555,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="2" t="n">
+      <c r="A151" s="1" t="n">
         <v>42887</v>
       </c>
       <c r="B151" t="n">
@@ -22611,7 +22599,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="2" t="n">
+      <c r="A152" s="1" t="n">
         <v>42917</v>
       </c>
       <c r="B152" t="n">
@@ -22655,7 +22643,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="2" t="n">
+      <c r="A153" s="1" t="n">
         <v>42948</v>
       </c>
       <c r="B153" t="n">
@@ -22699,7 +22687,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="2" t="n">
+      <c r="A154" s="1" t="n">
         <v>42979</v>
       </c>
       <c r="B154" t="n">
@@ -22743,7 +22731,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="2" t="n">
+      <c r="A155" s="1" t="n">
         <v>43009</v>
       </c>
       <c r="B155" t="n">
@@ -22787,7 +22775,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="2" t="n">
+      <c r="A156" s="1" t="n">
         <v>43040</v>
       </c>
       <c r="B156" t="n">
@@ -22831,7 +22819,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="2" t="n">
+      <c r="A157" s="1" t="n">
         <v>43070</v>
       </c>
       <c r="B157" t="n">
@@ -22875,7 +22863,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="2" t="n">
+      <c r="A158" s="1" t="n">
         <v>43101</v>
       </c>
       <c r="B158" t="n">
@@ -22919,7 +22907,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="2" t="n">
+      <c r="A159" s="1" t="n">
         <v>43132</v>
       </c>
       <c r="B159" t="n">
@@ -22963,7 +22951,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="2" t="n">
+      <c r="A160" s="1" t="n">
         <v>43160</v>
       </c>
       <c r="B160" t="n">
@@ -23007,7 +22995,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="2" t="n">
+      <c r="A161" s="1" t="n">
         <v>43191</v>
       </c>
       <c r="B161" t="n">
@@ -23051,7 +23039,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="2" t="n">
+      <c r="A162" s="1" t="n">
         <v>43221</v>
       </c>
       <c r="B162" t="n">
@@ -23095,7 +23083,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="2" t="n">
+      <c r="A163" s="1" t="n">
         <v>43252</v>
       </c>
       <c r="B163" t="n">
@@ -23139,7 +23127,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="2" t="n">
+      <c r="A164" s="1" t="n">
         <v>43282</v>
       </c>
       <c r="B164" t="n">
@@ -23183,7 +23171,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="2" t="n">
+      <c r="A165" s="1" t="n">
         <v>43313</v>
       </c>
       <c r="B165" t="n">
@@ -23227,7 +23215,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="2" t="n">
+      <c r="A166" s="1" t="n">
         <v>43344</v>
       </c>
       <c r="B166" t="n">
@@ -23271,7 +23259,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="2" t="n">
+      <c r="A167" s="1" t="n">
         <v>43374</v>
       </c>
       <c r="B167" t="n">
@@ -23315,7 +23303,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="2" t="n">
+      <c r="A168" s="1" t="n">
         <v>43405</v>
       </c>
       <c r="B168" t="n">
@@ -23359,7 +23347,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="2" t="n">
+      <c r="A169" s="1" t="n">
         <v>43435</v>
       </c>
       <c r="B169" t="n">
@@ -23403,7 +23391,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="2" t="n">
+      <c r="A170" s="1" t="n">
         <v>43466</v>
       </c>
       <c r="B170" t="n">
@@ -23447,7 +23435,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="2" t="n">
+      <c r="A171" s="1" t="n">
         <v>43497</v>
       </c>
       <c r="B171" t="n">
@@ -23491,7 +23479,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="2" t="n">
+      <c r="A172" s="1" t="n">
         <v>43525</v>
       </c>
       <c r="B172" t="n">
@@ -23535,7 +23523,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="2" t="n">
+      <c r="A173" s="1" t="n">
         <v>43556</v>
       </c>
       <c r="B173" t="n">
@@ -23579,7 +23567,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="2" t="n">
+      <c r="A174" s="1" t="n">
         <v>43586</v>
       </c>
       <c r="B174" t="n">
@@ -23623,7 +23611,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="2" t="n">
+      <c r="A175" s="1" t="n">
         <v>43617</v>
       </c>
       <c r="B175" t="n">
@@ -23667,7 +23655,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="2" t="n">
+      <c r="A176" s="1" t="n">
         <v>43647</v>
       </c>
       <c r="B176" t="n">
@@ -23711,7 +23699,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="2" t="n">
+      <c r="A177" s="1" t="n">
         <v>43678</v>
       </c>
       <c r="B177" t="n">
@@ -23755,7 +23743,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="2" t="n">
+      <c r="A178" s="1" t="n">
         <v>43709</v>
       </c>
       <c r="B178" t="n">
@@ -23799,7 +23787,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="2" t="n">
+      <c r="A179" s="1" t="n">
         <v>43739</v>
       </c>
       <c r="B179" t="n">
@@ -23843,7 +23831,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="2" t="n">
+      <c r="A180" s="1" t="n">
         <v>43770</v>
       </c>
       <c r="B180" t="n">
@@ -23887,7 +23875,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="2" t="n">
+      <c r="A181" s="1" t="n">
         <v>43800</v>
       </c>
       <c r="B181" t="n">
@@ -23931,7 +23919,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="2" t="n">
+      <c r="A182" s="1" t="n">
         <v>43831</v>
       </c>
       <c r="B182" t="n">
@@ -23975,7 +23963,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="2" t="n">
+      <c r="A183" s="1" t="n">
         <v>43862</v>
       </c>
       <c r="B183" t="n">
@@ -24019,7 +24007,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="2" t="n">
+      <c r="A184" s="1" t="n">
         <v>43891</v>
       </c>
       <c r="B184" t="n">
@@ -24063,7 +24051,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="2" t="n">
+      <c r="A185" s="1" t="n">
         <v>43922</v>
       </c>
       <c r="B185" t="n">
@@ -24107,7 +24095,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="2" t="n">
+      <c r="A186" s="1" t="n">
         <v>43952</v>
       </c>
       <c r="B186" t="n">
@@ -24151,7 +24139,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="2" t="n">
+      <c r="A187" s="1" t="n">
         <v>43983</v>
       </c>
       <c r="B187" t="n">
@@ -24195,7 +24183,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="2" t="n">
+      <c r="A188" s="1" t="n">
         <v>44013</v>
       </c>
       <c r="B188" t="n">
@@ -24239,7 +24227,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="2" t="n">
+      <c r="A189" s="1" t="n">
         <v>44044</v>
       </c>
       <c r="B189" t="n">
@@ -24283,7 +24271,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="2" t="n">
+      <c r="A190" s="1" t="n">
         <v>44075</v>
       </c>
       <c r="B190" t="n">
@@ -24327,7 +24315,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="2" t="n">
+      <c r="A191" s="1" t="n">
         <v>44105</v>
       </c>
       <c r="B191" t="n">
@@ -24371,7 +24359,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="2" t="n">
+      <c r="A192" s="1" t="n">
         <v>44136</v>
       </c>
       <c r="B192" t="n">
@@ -24415,7 +24403,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="2" t="n">
+      <c r="A193" s="1" t="n">
         <v>44166</v>
       </c>
       <c r="B193" t="n">
@@ -24459,7 +24447,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="2" t="n">
+      <c r="A194" s="1" t="n">
         <v>44197</v>
       </c>
       <c r="B194" t="n">
@@ -24503,7 +24491,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="2" t="n">
+      <c r="A195" s="1" t="n">
         <v>44228</v>
       </c>
       <c r="B195" t="n">
@@ -24547,7 +24535,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="2" t="n">
+      <c r="A196" s="1" t="n">
         <v>44256</v>
       </c>
       <c r="B196" t="n">
@@ -24591,7 +24579,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="2" t="n">
+      <c r="A197" s="1" t="n">
         <v>44287</v>
       </c>
       <c r="B197" t="n">
@@ -24635,7 +24623,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="2" t="n">
+      <c r="A198" s="1" t="n">
         <v>44317</v>
       </c>
       <c r="B198" t="n">
@@ -24679,7 +24667,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="2" t="n">
+      <c r="A199" s="1" t="n">
         <v>44348</v>
       </c>
       <c r="B199" t="n">
@@ -24723,7 +24711,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="2" t="n">
+      <c r="A200" s="1" t="n">
         <v>44378</v>
       </c>
       <c r="B200" t="n">
@@ -24767,7 +24755,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="2" t="n">
+      <c r="A201" s="1" t="n">
         <v>44409</v>
       </c>
       <c r="B201" t="n">
@@ -24811,7 +24799,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="2" t="n">
+      <c r="A202" s="1" t="n">
         <v>44440</v>
       </c>
       <c r="B202" t="n">
@@ -24855,7 +24843,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="2" t="n">
+      <c r="A203" s="1" t="n">
         <v>44470</v>
       </c>
       <c r="B203" t="n">
@@ -24899,7 +24887,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="2" t="n">
+      <c r="A204" s="1" t="n">
         <v>44501</v>
       </c>
       <c r="B204" t="n">
@@ -24943,7 +24931,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="2" t="n">
+      <c r="A205" s="1" t="n">
         <v>44531</v>
       </c>
       <c r="B205" t="n">
@@ -24987,7 +24975,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="2" t="n">
+      <c r="A206" s="1" t="n">
         <v>44562</v>
       </c>
       <c r="B206" t="n">
@@ -25031,7 +25019,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="2" t="n">
+      <c r="A207" s="1" t="n">
         <v>44593</v>
       </c>
       <c r="B207" t="n">
@@ -25075,7 +25063,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="2" t="n">
+      <c r="A208" s="1" t="n">
         <v>44621</v>
       </c>
       <c r="B208" t="n">
@@ -25119,7 +25107,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="2" t="n">
+      <c r="A209" s="1" t="n">
         <v>44652</v>
       </c>
       <c r="B209" t="n">
@@ -25163,7 +25151,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="2" t="n">
+      <c r="A210" s="1" t="n">
         <v>44682</v>
       </c>
       <c r="B210" t="n">
@@ -25207,7 +25195,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="2" t="n">
+      <c r="A211" s="1" t="n">
         <v>44713</v>
       </c>
       <c r="B211" t="n">
@@ -25251,7 +25239,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="2" t="n">
+      <c r="A212" s="1" t="n">
         <v>44743</v>
       </c>
       <c r="B212" t="n">
@@ -25295,7 +25283,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="2" t="n">
+      <c r="A213" s="1" t="n">
         <v>44774</v>
       </c>
       <c r="B213" t="n">
@@ -25339,7 +25327,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="2" t="n">
+      <c r="A214" s="1" t="n">
         <v>44805</v>
       </c>
       <c r="B214" t="n">
@@ -25383,7 +25371,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="2" t="n">
+      <c r="A215" s="1" t="n">
         <v>44835</v>
       </c>
       <c r="B215" t="n">
@@ -25427,7 +25415,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="2" t="n">
+      <c r="A216" s="1" t="n">
         <v>44866</v>
       </c>
       <c r="B216" t="n">
@@ -25471,7 +25459,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="2" t="n">
+      <c r="A217" s="1" t="n">
         <v>44896</v>
       </c>
       <c r="B217" t="n">
@@ -25515,7 +25503,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="2" t="n">
+      <c r="A218" s="1" t="n">
         <v>44927</v>
       </c>
       <c r="B218" t="n">
@@ -25559,7 +25547,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="2" t="n">
+      <c r="A219" s="1" t="n">
         <v>44958</v>
       </c>
       <c r="B219" t="n">
@@ -25603,7 +25591,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="2" t="n">
+      <c r="A220" s="1" t="n">
         <v>44986</v>
       </c>
       <c r="B220" t="n">
@@ -25647,7 +25635,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="2" t="n">
+      <c r="A221" s="1" t="n">
         <v>45017</v>
       </c>
       <c r="B221" t="n">
@@ -25691,7 +25679,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="2" t="n">
+      <c r="A222" s="1" t="n">
         <v>45047</v>
       </c>
       <c r="B222" t="n">
@@ -25735,7 +25723,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="2" t="n">
+      <c r="A223" s="1" t="n">
         <v>45078</v>
       </c>
       <c r="B223" t="n">
@@ -25779,7 +25767,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="2" t="n">
+      <c r="A224" s="1" t="n">
         <v>45108</v>
       </c>
       <c r="B224" t="n">
@@ -25823,7 +25811,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="2" t="n">
+      <c r="A225" s="1" t="n">
         <v>45139</v>
       </c>
       <c r="B225" t="n">
@@ -25867,7 +25855,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="2" t="n">
+      <c r="A226" s="1" t="n">
         <v>45170</v>
       </c>
       <c r="B226" t="n">
@@ -25911,7 +25899,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="2" t="n">
+      <c r="A227" s="1" t="n">
         <v>45200</v>
       </c>
       <c r="B227" t="n">
@@ -25955,7 +25943,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="2" t="n">
+      <c r="A228" s="1" t="n">
         <v>45231</v>
       </c>
       <c r="B228" t="n">
@@ -25999,7 +25987,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="2" t="n">
+      <c r="A229" s="1" t="n">
         <v>45261</v>
       </c>
       <c r="B229" t="n">
@@ -26043,7 +26031,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="2" t="n">
+      <c r="A230" s="1" t="n">
         <v>45292</v>
       </c>
       <c r="B230" t="n">
@@ -26087,7 +26075,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="2" t="n">
+      <c r="A231" s="1" t="n">
         <v>45323</v>
       </c>
       <c r="B231" t="n">
@@ -26131,7 +26119,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="2" t="n">
+      <c r="A232" s="1" t="n">
         <v>45352</v>
       </c>
       <c r="B232" t="n">
@@ -26175,7 +26163,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="2" t="n">
+      <c r="A233" s="1" t="n">
         <v>45383</v>
       </c>
       <c r="B233" t="n">
@@ -26219,7 +26207,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="2" t="n">
+      <c r="A234" s="1" t="n">
         <v>45413</v>
       </c>
       <c r="B234" t="n">
@@ -26263,7 +26251,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="2" t="n">
+      <c r="A235" s="1" t="n">
         <v>45444</v>
       </c>
       <c r="B235" t="n">
@@ -26307,7 +26295,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="2" t="n">
+      <c r="A236" s="1" t="n">
         <v>45474</v>
       </c>
       <c r="B236" t="n">
@@ -26351,7 +26339,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="2" t="n">
+      <c r="A237" s="1" t="n">
         <v>45505</v>
       </c>
       <c r="B237" t="n">
@@ -26395,7 +26383,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="2" t="n">
+      <c r="A238" s="1" t="n">
         <v>45536</v>
       </c>
       <c r="B238" t="n">
@@ -26439,7 +26427,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="2" t="n">
+      <c r="A239" s="1" t="n">
         <v>45566</v>
       </c>
       <c r="B239" t="n">
@@ -26483,7 +26471,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="2" t="n">
+      <c r="A240" s="1" t="n">
         <v>45597</v>
       </c>
       <c r="B240" t="n">
@@ -26527,7 +26515,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="2" t="n">
+      <c r="A241" s="1" t="n">
         <v>45627</v>
       </c>
       <c r="B241" t="n">
@@ -26571,7 +26559,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="2" t="n">
+      <c r="A242" s="1" t="n">
         <v>45658</v>
       </c>
       <c r="B242" t="n">
@@ -26615,7 +26603,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="2" t="n">
+      <c r="A243" s="1" t="n">
         <v>45689</v>
       </c>
       <c r="B243" t="n">
@@ -26659,7 +26647,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="2" t="n">
+      <c r="A244" s="1" t="n">
         <v>45717</v>
       </c>
       <c r="B244" t="n">
@@ -26703,7 +26691,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="2" t="n">
+      <c r="A245" s="1" t="n">
         <v>45748</v>
       </c>
       <c r="B245" t="n">
@@ -26747,7 +26735,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="2" t="n">
+      <c r="A246" s="1" t="n">
         <v>45778</v>
       </c>
       <c r="B246" t="n">
@@ -26791,7 +26779,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="2" t="n">
+      <c r="A247" s="1" t="n">
         <v>45809</v>
       </c>
       <c r="B247" t="n">
@@ -26835,7 +26823,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="2" t="n">
+      <c r="A248" s="1" t="n">
         <v>45839</v>
       </c>
       <c r="B248" t="n">
@@ -26879,7 +26867,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="2" t="n">
+      <c r="A249" s="1" t="n">
         <v>45870</v>
       </c>
       <c r="B249" t="n">
@@ -26923,7 +26911,7 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="2" t="n">
+      <c r="A250" s="1" t="n">
         <v>45901</v>
       </c>
       <c r="B250" t="n">
@@ -26967,7 +26955,7 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="2" t="n">
+      <c r="A251" s="1" t="n">
         <v>45931</v>
       </c>
       <c r="B251" t="n">
@@ -27011,7 +26999,7 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="2" t="n">
+      <c r="A252" s="1" t="n">
         <v>45962</v>
       </c>
       <c r="B252" t="n">
@@ -27055,7 +27043,7 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="2" t="n">
+      <c r="A253" s="1" t="n">
         <v>45992</v>
       </c>
       <c r="B253" t="n">
@@ -27099,7 +27087,7 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="2" t="n">
+      <c r="A254" s="1" t="n">
         <v>46023</v>
       </c>
       <c r="B254" t="n">
@@ -27143,7 +27131,7 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="2" t="n">
+      <c r="A255" s="1" t="n">
         <v>46054</v>
       </c>
       <c r="B255" t="n">
@@ -27187,7 +27175,7 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="2" t="n">
+      <c r="A256" s="1" t="n">
         <v>46082</v>
       </c>
       <c r="B256" t="n">
@@ -27231,7 +27219,7 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="2" t="n">
+      <c r="A257" s="1" t="n">
         <v>46113</v>
       </c>
       <c r="B257" t="n">
@@ -27275,7 +27263,7 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="2" t="n">
+      <c r="A258" s="1" t="n">
         <v>46143</v>
       </c>
       <c r="B258" t="n">
@@ -27319,7 +27307,7 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="2" t="n">
+      <c r="A259" s="1" t="n">
         <v>46174</v>
       </c>
       <c r="B259" t="n">
@@ -27377,32 +27365,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Kalem</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Endeks</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Aylık %</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Yıllık %</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Yılbaşından %</t>
         </is>

--- a/enflasyon/enflasyon.xlsx
+++ b/enflasyon/enflasyon.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Genel" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="AltKalem_Endeks" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="AltKalem_Yillik" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="AltKalem_Ozet" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Genel" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AltKalem_Endeks" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AltKalem_Yillik" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AltKalem_Ozet" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -424,34 +436,34 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>tarih</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>endeks</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>aylik</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>yillik</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>ytd</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38353</v>
       </c>
       <c r="B2" t="n">
@@ -462,7 +474,7 @@
       <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38384</v>
       </c>
       <c r="B3" t="n">
@@ -475,7 +487,7 @@
       <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38412</v>
       </c>
       <c r="B4" t="n">
@@ -488,7 +500,7 @@
       <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38443</v>
       </c>
       <c r="B5" t="n">
@@ -501,7 +513,7 @@
       <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38473</v>
       </c>
       <c r="B6" t="n">
@@ -514,7 +526,7 @@
       <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38504</v>
       </c>
       <c r="B7" t="n">
@@ -527,7 +539,7 @@
       <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38534</v>
       </c>
       <c r="B8" t="n">
@@ -540,7 +552,7 @@
       <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38565</v>
       </c>
       <c r="B9" t="n">
@@ -553,7 +565,7 @@
       <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38596</v>
       </c>
       <c r="B10" t="n">
@@ -566,7 +578,7 @@
       <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>38626</v>
       </c>
       <c r="B11" t="n">
@@ -579,7 +591,7 @@
       <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>38657</v>
       </c>
       <c r="B12" t="n">
@@ -592,7 +604,7 @@
       <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>38687</v>
       </c>
       <c r="B13" t="n">
@@ -605,7 +617,7 @@
       <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>38718</v>
       </c>
       <c r="B14" t="n">
@@ -622,7 +634,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>38749</v>
       </c>
       <c r="B15" t="n">
@@ -639,7 +651,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>38777</v>
       </c>
       <c r="B16" t="n">
@@ -656,7 +668,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>38808</v>
       </c>
       <c r="B17" t="n">
@@ -673,7 +685,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>38838</v>
       </c>
       <c r="B18" t="n">
@@ -690,7 +702,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>38869</v>
       </c>
       <c r="B19" t="n">
@@ -707,7 +719,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>38899</v>
       </c>
       <c r="B20" t="n">
@@ -724,7 +736,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>38930</v>
       </c>
       <c r="B21" t="n">
@@ -741,7 +753,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>38961</v>
       </c>
       <c r="B22" t="n">
@@ -758,7 +770,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>38991</v>
       </c>
       <c r="B23" t="n">
@@ -775,7 +787,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39022</v>
       </c>
       <c r="B24" t="n">
@@ -792,7 +804,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39052</v>
       </c>
       <c r="B25" t="n">
@@ -809,7 +821,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39083</v>
       </c>
       <c r="B26" t="n">
@@ -826,7 +838,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39114</v>
       </c>
       <c r="B27" t="n">
@@ -843,7 +855,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39142</v>
       </c>
       <c r="B28" t="n">
@@ -860,7 +872,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39173</v>
       </c>
       <c r="B29" t="n">
@@ -877,7 +889,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39203</v>
       </c>
       <c r="B30" t="n">
@@ -894,7 +906,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39234</v>
       </c>
       <c r="B31" t="n">
@@ -911,7 +923,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39264</v>
       </c>
       <c r="B32" t="n">
@@ -928,7 +940,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39295</v>
       </c>
       <c r="B33" t="n">
@@ -945,7 +957,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39326</v>
       </c>
       <c r="B34" t="n">
@@ -962,7 +974,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39356</v>
       </c>
       <c r="B35" t="n">
@@ -979,7 +991,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39387</v>
       </c>
       <c r="B36" t="n">
@@ -996,7 +1008,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39417</v>
       </c>
       <c r="B37" t="n">
@@ -1013,7 +1025,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39448</v>
       </c>
       <c r="B38" t="n">
@@ -1030,7 +1042,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39479</v>
       </c>
       <c r="B39" t="n">
@@ -1047,7 +1059,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39508</v>
       </c>
       <c r="B40" t="n">
@@ -1064,7 +1076,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39539</v>
       </c>
       <c r="B41" t="n">
@@ -1081,7 +1093,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39569</v>
       </c>
       <c r="B42" t="n">
@@ -1098,7 +1110,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39600</v>
       </c>
       <c r="B43" t="n">
@@ -1115,7 +1127,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>39630</v>
       </c>
       <c r="B44" t="n">
@@ -1132,7 +1144,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>39661</v>
       </c>
       <c r="B45" t="n">
@@ -1149,7 +1161,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>39692</v>
       </c>
       <c r="B46" t="n">
@@ -1166,7 +1178,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>39722</v>
       </c>
       <c r="B47" t="n">
@@ -1183,7 +1195,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>39753</v>
       </c>
       <c r="B48" t="n">
@@ -1200,7 +1212,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>39783</v>
       </c>
       <c r="B49" t="n">
@@ -1217,7 +1229,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>39814</v>
       </c>
       <c r="B50" t="n">
@@ -1234,7 +1246,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>39845</v>
       </c>
       <c r="B51" t="n">
@@ -1251,7 +1263,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>39873</v>
       </c>
       <c r="B52" t="n">
@@ -1268,7 +1280,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>39904</v>
       </c>
       <c r="B53" t="n">
@@ -1285,7 +1297,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>39934</v>
       </c>
       <c r="B54" t="n">
@@ -1302,7 +1314,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>39965</v>
       </c>
       <c r="B55" t="n">
@@ -1319,7 +1331,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>39995</v>
       </c>
       <c r="B56" t="n">
@@ -1336,7 +1348,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40026</v>
       </c>
       <c r="B57" t="n">
@@ -1353,7 +1365,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40057</v>
       </c>
       <c r="B58" t="n">
@@ -1370,7 +1382,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40087</v>
       </c>
       <c r="B59" t="n">
@@ -1387,7 +1399,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40118</v>
       </c>
       <c r="B60" t="n">
@@ -1404,7 +1416,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40148</v>
       </c>
       <c r="B61" t="n">
@@ -1421,7 +1433,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40179</v>
       </c>
       <c r="B62" t="n">
@@ -1438,7 +1450,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40210</v>
       </c>
       <c r="B63" t="n">
@@ -1455,7 +1467,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40238</v>
       </c>
       <c r="B64" t="n">
@@ -1472,7 +1484,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40269</v>
       </c>
       <c r="B65" t="n">
@@ -1489,7 +1501,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40299</v>
       </c>
       <c r="B66" t="n">
@@ -1506,7 +1518,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40330</v>
       </c>
       <c r="B67" t="n">
@@ -1523,7 +1535,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40360</v>
       </c>
       <c r="B68" t="n">
@@ -1540,7 +1552,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40391</v>
       </c>
       <c r="B69" t="n">
@@ -1557,7 +1569,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40422</v>
       </c>
       <c r="B70" t="n">
@@ -1574,7 +1586,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40452</v>
       </c>
       <c r="B71" t="n">
@@ -1591,7 +1603,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40483</v>
       </c>
       <c r="B72" t="n">
@@ -1608,7 +1620,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40513</v>
       </c>
       <c r="B73" t="n">
@@ -1625,7 +1637,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40544</v>
       </c>
       <c r="B74" t="n">
@@ -1642,7 +1654,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40575</v>
       </c>
       <c r="B75" t="n">
@@ -1659,7 +1671,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40603</v>
       </c>
       <c r="B76" t="n">
@@ -1676,7 +1688,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>40634</v>
       </c>
       <c r="B77" t="n">
@@ -1693,7 +1705,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>40664</v>
       </c>
       <c r="B78" t="n">
@@ -1710,7 +1722,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>40695</v>
       </c>
       <c r="B79" t="n">
@@ -1727,7 +1739,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>40725</v>
       </c>
       <c r="B80" t="n">
@@ -1744,7 +1756,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>40756</v>
       </c>
       <c r="B81" t="n">
@@ -1761,7 +1773,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>40787</v>
       </c>
       <c r="B82" t="n">
@@ -1778,7 +1790,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>40817</v>
       </c>
       <c r="B83" t="n">
@@ -1795,7 +1807,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>40848</v>
       </c>
       <c r="B84" t="n">
@@ -1812,7 +1824,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>40878</v>
       </c>
       <c r="B85" t="n">
@@ -1829,7 +1841,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>40909</v>
       </c>
       <c r="B86" t="n">
@@ -1846,7 +1858,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>40940</v>
       </c>
       <c r="B87" t="n">
@@ -1863,7 +1875,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>40969</v>
       </c>
       <c r="B88" t="n">
@@ -1880,7 +1892,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41000</v>
       </c>
       <c r="B89" t="n">
@@ -1897,7 +1909,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41030</v>
       </c>
       <c r="B90" t="n">
@@ -1914,7 +1926,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41061</v>
       </c>
       <c r="B91" t="n">
@@ -1931,7 +1943,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41091</v>
       </c>
       <c r="B92" t="n">
@@ -1948,7 +1960,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41122</v>
       </c>
       <c r="B93" t="n">
@@ -1965,7 +1977,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41153</v>
       </c>
       <c r="B94" t="n">
@@ -1982,7 +1994,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41183</v>
       </c>
       <c r="B95" t="n">
@@ -1999,7 +2011,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41214</v>
       </c>
       <c r="B96" t="n">
@@ -2016,7 +2028,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41244</v>
       </c>
       <c r="B97" t="n">
@@ -2033,7 +2045,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41275</v>
       </c>
       <c r="B98" t="n">
@@ -2050,7 +2062,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41306</v>
       </c>
       <c r="B99" t="n">
@@ -2067,7 +2079,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41334</v>
       </c>
       <c r="B100" t="n">
@@ -2084,7 +2096,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41365</v>
       </c>
       <c r="B101" t="n">
@@ -2101,7 +2113,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41395</v>
       </c>
       <c r="B102" t="n">
@@ -2118,7 +2130,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41426</v>
       </c>
       <c r="B103" t="n">
@@ -2135,7 +2147,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41456</v>
       </c>
       <c r="B104" t="n">
@@ -2152,7 +2164,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41487</v>
       </c>
       <c r="B105" t="n">
@@ -2169,7 +2181,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41518</v>
       </c>
       <c r="B106" t="n">
@@ -2186,7 +2198,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41548</v>
       </c>
       <c r="B107" t="n">
@@ -2203,7 +2215,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41579</v>
       </c>
       <c r="B108" t="n">
@@ -2220,7 +2232,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>41609</v>
       </c>
       <c r="B109" t="n">
@@ -2237,7 +2249,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>41640</v>
       </c>
       <c r="B110" t="n">
@@ -2254,7 +2266,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>41671</v>
       </c>
       <c r="B111" t="n">
@@ -2271,7 +2283,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>41699</v>
       </c>
       <c r="B112" t="n">
@@ -2288,7 +2300,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>41730</v>
       </c>
       <c r="B113" t="n">
@@ -2305,7 +2317,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>41760</v>
       </c>
       <c r="B114" t="n">
@@ -2322,7 +2334,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>41791</v>
       </c>
       <c r="B115" t="n">
@@ -2339,7 +2351,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>41821</v>
       </c>
       <c r="B116" t="n">
@@ -2356,7 +2368,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>41852</v>
       </c>
       <c r="B117" t="n">
@@ -2373,7 +2385,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>41883</v>
       </c>
       <c r="B118" t="n">
@@ -2390,7 +2402,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>41913</v>
       </c>
       <c r="B119" t="n">
@@ -2407,7 +2419,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>41944</v>
       </c>
       <c r="B120" t="n">
@@ -2424,7 +2436,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>41974</v>
       </c>
       <c r="B121" t="n">
@@ -2441,7 +2453,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42005</v>
       </c>
       <c r="B122" t="n">
@@ -2458,7 +2470,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42036</v>
       </c>
       <c r="B123" t="n">
@@ -2475,7 +2487,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42064</v>
       </c>
       <c r="B124" t="n">
@@ -2492,7 +2504,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42095</v>
       </c>
       <c r="B125" t="n">
@@ -2509,7 +2521,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42125</v>
       </c>
       <c r="B126" t="n">
@@ -2526,7 +2538,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42156</v>
       </c>
       <c r="B127" t="n">
@@ -2543,7 +2555,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42186</v>
       </c>
       <c r="B128" t="n">
@@ -2560,7 +2572,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42217</v>
       </c>
       <c r="B129" t="n">
@@ -2577,7 +2589,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42248</v>
       </c>
       <c r="B130" t="n">
@@ -2594,7 +2606,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42278</v>
       </c>
       <c r="B131" t="n">
@@ -2611,7 +2623,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42309</v>
       </c>
       <c r="B132" t="n">
@@ -2628,7 +2640,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42339</v>
       </c>
       <c r="B133" t="n">
@@ -2645,7 +2657,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42370</v>
       </c>
       <c r="B134" t="n">
@@ -2662,7 +2674,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42401</v>
       </c>
       <c r="B135" t="n">
@@ -2679,7 +2691,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42430</v>
       </c>
       <c r="B136" t="n">
@@ -2696,7 +2708,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42461</v>
       </c>
       <c r="B137" t="n">
@@ -2713,7 +2725,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42491</v>
       </c>
       <c r="B138" t="n">
@@ -2730,7 +2742,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42522</v>
       </c>
       <c r="B139" t="n">
@@ -2747,7 +2759,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42552</v>
       </c>
       <c r="B140" t="n">
@@ -2764,7 +2776,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42583</v>
       </c>
       <c r="B141" t="n">
@@ -2781,7 +2793,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>42614</v>
       </c>
       <c r="B142" t="n">
@@ -2798,7 +2810,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>42644</v>
       </c>
       <c r="B143" t="n">
@@ -2815,7 +2827,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>42675</v>
       </c>
       <c r="B144" t="n">
@@ -2832,7 +2844,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>42705</v>
       </c>
       <c r="B145" t="n">
@@ -2849,7 +2861,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>42736</v>
       </c>
       <c r="B146" t="n">
@@ -2866,7 +2878,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>42767</v>
       </c>
       <c r="B147" t="n">
@@ -2883,7 +2895,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>42795</v>
       </c>
       <c r="B148" t="n">
@@ -2900,7 +2912,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>42826</v>
       </c>
       <c r="B149" t="n">
@@ -2917,7 +2929,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>42856</v>
       </c>
       <c r="B150" t="n">
@@ -2934,7 +2946,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>42887</v>
       </c>
       <c r="B151" t="n">
@@ -2951,7 +2963,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>42917</v>
       </c>
       <c r="B152" t="n">
@@ -2968,7 +2980,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>42948</v>
       </c>
       <c r="B153" t="n">
@@ -2985,7 +2997,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>42979</v>
       </c>
       <c r="B154" t="n">
@@ -3002,7 +3014,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43009</v>
       </c>
       <c r="B155" t="n">
@@ -3019,7 +3031,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43040</v>
       </c>
       <c r="B156" t="n">
@@ -3036,7 +3048,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43070</v>
       </c>
       <c r="B157" t="n">
@@ -3053,7 +3065,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43101</v>
       </c>
       <c r="B158" t="n">
@@ -3070,7 +3082,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43132</v>
       </c>
       <c r="B159" t="n">
@@ -3087,7 +3099,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43160</v>
       </c>
       <c r="B160" t="n">
@@ -3104,7 +3116,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43191</v>
       </c>
       <c r="B161" t="n">
@@ -3121,7 +3133,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43221</v>
       </c>
       <c r="B162" t="n">
@@ -3138,7 +3150,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43252</v>
       </c>
       <c r="B163" t="n">
@@ -3155,7 +3167,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43282</v>
       </c>
       <c r="B164" t="n">
@@ -3172,7 +3184,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43313</v>
       </c>
       <c r="B165" t="n">
@@ -3189,7 +3201,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43344</v>
       </c>
       <c r="B166" t="n">
@@ -3206,7 +3218,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43374</v>
       </c>
       <c r="B167" t="n">
@@ -3223,7 +3235,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43405</v>
       </c>
       <c r="B168" t="n">
@@ -3240,7 +3252,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43435</v>
       </c>
       <c r="B169" t="n">
@@ -3257,7 +3269,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43466</v>
       </c>
       <c r="B170" t="n">
@@ -3274,7 +3286,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43497</v>
       </c>
       <c r="B171" t="n">
@@ -3291,7 +3303,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43525</v>
       </c>
       <c r="B172" t="n">
@@ -3308,7 +3320,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43556</v>
       </c>
       <c r="B173" t="n">
@@ -3325,7 +3337,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43586</v>
       </c>
       <c r="B174" t="n">
@@ -3342,7 +3354,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>43617</v>
       </c>
       <c r="B175" t="n">
@@ -3359,7 +3371,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>43647</v>
       </c>
       <c r="B176" t="n">
@@ -3376,7 +3388,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>43678</v>
       </c>
       <c r="B177" t="n">
@@ -3393,7 +3405,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>43709</v>
       </c>
       <c r="B178" t="n">
@@ -3410,7 +3422,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>43739</v>
       </c>
       <c r="B179" t="n">
@@ -3427,7 +3439,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>43770</v>
       </c>
       <c r="B180" t="n">
@@ -3444,7 +3456,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>43800</v>
       </c>
       <c r="B181" t="n">
@@ -3461,7 +3473,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>43831</v>
       </c>
       <c r="B182" t="n">
@@ -3478,7 +3490,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>43862</v>
       </c>
       <c r="B183" t="n">
@@ -3495,7 +3507,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>43891</v>
       </c>
       <c r="B184" t="n">
@@ -3512,7 +3524,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>43922</v>
       </c>
       <c r="B185" t="n">
@@ -3529,7 +3541,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>43952</v>
       </c>
       <c r="B186" t="n">
@@ -3546,7 +3558,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>43983</v>
       </c>
       <c r="B187" t="n">
@@ -3563,7 +3575,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44013</v>
       </c>
       <c r="B188" t="n">
@@ -3580,7 +3592,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44044</v>
       </c>
       <c r="B189" t="n">
@@ -3597,7 +3609,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44075</v>
       </c>
       <c r="B190" t="n">
@@ -3614,7 +3626,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44105</v>
       </c>
       <c r="B191" t="n">
@@ -3631,7 +3643,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44136</v>
       </c>
       <c r="B192" t="n">
@@ -3648,7 +3660,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44166</v>
       </c>
       <c r="B193" t="n">
@@ -3665,7 +3677,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44197</v>
       </c>
       <c r="B194" t="n">
@@ -3682,7 +3694,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44228</v>
       </c>
       <c r="B195" t="n">
@@ -3699,7 +3711,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44256</v>
       </c>
       <c r="B196" t="n">
@@ -3716,7 +3728,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44287</v>
       </c>
       <c r="B197" t="n">
@@ -3733,7 +3745,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44317</v>
       </c>
       <c r="B198" t="n">
@@ -3750,7 +3762,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44348</v>
       </c>
       <c r="B199" t="n">
@@ -3767,7 +3779,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44378</v>
       </c>
       <c r="B200" t="n">
@@ -3784,7 +3796,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44409</v>
       </c>
       <c r="B201" t="n">
@@ -3801,7 +3813,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44440</v>
       </c>
       <c r="B202" t="n">
@@ -3818,7 +3830,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44470</v>
       </c>
       <c r="B203" t="n">
@@ -3835,7 +3847,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44501</v>
       </c>
       <c r="B204" t="n">
@@ -3852,7 +3864,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44531</v>
       </c>
       <c r="B205" t="n">
@@ -3869,7 +3881,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44562</v>
       </c>
       <c r="B206" t="n">
@@ -3886,7 +3898,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44593</v>
       </c>
       <c r="B207" t="n">
@@ -3903,7 +3915,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>44621</v>
       </c>
       <c r="B208" t="n">
@@ -3920,7 +3932,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>44652</v>
       </c>
       <c r="B209" t="n">
@@ -3937,7 +3949,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>44682</v>
       </c>
       <c r="B210" t="n">
@@ -3954,7 +3966,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>44713</v>
       </c>
       <c r="B211" t="n">
@@ -3971,7 +3983,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>44743</v>
       </c>
       <c r="B212" t="n">
@@ -3988,7 +4000,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>44774</v>
       </c>
       <c r="B213" t="n">
@@ -4005,7 +4017,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>44805</v>
       </c>
       <c r="B214" t="n">
@@ -4022,7 +4034,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>44835</v>
       </c>
       <c r="B215" t="n">
@@ -4039,7 +4051,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>44866</v>
       </c>
       <c r="B216" t="n">
@@ -4056,7 +4068,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>44896</v>
       </c>
       <c r="B217" t="n">
@@ -4073,7 +4085,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>44927</v>
       </c>
       <c r="B218" t="n">
@@ -4090,7 +4102,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>44958</v>
       </c>
       <c r="B219" t="n">
@@ -4107,7 +4119,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>44986</v>
       </c>
       <c r="B220" t="n">
@@ -4124,7 +4136,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45017</v>
       </c>
       <c r="B221" t="n">
@@ -4141,7 +4153,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45047</v>
       </c>
       <c r="B222" t="n">
@@ -4158,7 +4170,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45078</v>
       </c>
       <c r="B223" t="n">
@@ -4175,7 +4187,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45108</v>
       </c>
       <c r="B224" t="n">
@@ -4192,7 +4204,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45139</v>
       </c>
       <c r="B225" t="n">
@@ -4209,7 +4221,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45170</v>
       </c>
       <c r="B226" t="n">
@@ -4226,7 +4238,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45200</v>
       </c>
       <c r="B227" t="n">
@@ -4243,7 +4255,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45231</v>
       </c>
       <c r="B228" t="n">
@@ -4260,7 +4272,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45261</v>
       </c>
       <c r="B229" t="n">
@@ -4277,7 +4289,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45292</v>
       </c>
       <c r="B230" t="n">
@@ -4294,7 +4306,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45323</v>
       </c>
       <c r="B231" t="n">
@@ -4311,7 +4323,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45352</v>
       </c>
       <c r="B232" t="n">
@@ -4328,7 +4340,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45383</v>
       </c>
       <c r="B233" t="n">
@@ -4345,7 +4357,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45413</v>
       </c>
       <c r="B234" t="n">
@@ -4362,7 +4374,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45444</v>
       </c>
       <c r="B235" t="n">
@@ -4379,7 +4391,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45474</v>
       </c>
       <c r="B236" t="n">
@@ -4396,7 +4408,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="B237" t="n">
@@ -4413,7 +4425,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45536</v>
       </c>
       <c r="B238" t="n">
@@ -4430,7 +4442,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45566</v>
       </c>
       <c r="B239" t="n">
@@ -4447,7 +4459,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="B240" t="n">
@@ -4464,7 +4476,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>45627</v>
       </c>
       <c r="B241" t="n">
@@ -4481,7 +4493,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>45658</v>
       </c>
       <c r="B242" t="n">
@@ -4498,7 +4510,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>45689</v>
       </c>
       <c r="B243" t="n">
@@ -4515,7 +4527,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>45717</v>
       </c>
       <c r="B244" t="n">
@@ -4532,7 +4544,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>45748</v>
       </c>
       <c r="B245" t="n">
@@ -4549,7 +4561,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="B246" t="n">
@@ -4566,7 +4578,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>45809</v>
       </c>
       <c r="B247" t="n">
@@ -4583,7 +4595,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>45839</v>
       </c>
       <c r="B248" t="n">
@@ -4600,7 +4612,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="B249" t="n">
@@ -4617,7 +4629,7 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>45901</v>
       </c>
       <c r="B250" t="n">
@@ -4634,7 +4646,7 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="1" t="n">
+      <c r="A251" s="2" t="n">
         <v>45931</v>
       </c>
       <c r="B251" t="n">
@@ -4651,7 +4663,7 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="1" t="n">
+      <c r="A252" s="2" t="n">
         <v>45962</v>
       </c>
       <c r="B252" t="n">
@@ -4668,7 +4680,7 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="1" t="n">
+      <c r="A253" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="B253" t="n">
@@ -4685,7 +4697,7 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="1" t="n">
+      <c r="A254" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B254" t="n">
@@ -4702,7 +4714,7 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="1" t="n">
+      <c r="A255" s="2" t="n">
         <v>46054</v>
       </c>
       <c r="B255" t="n">
@@ -4719,7 +4731,7 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="1" t="n">
+      <c r="A256" s="2" t="n">
         <v>46082</v>
       </c>
       <c r="B256" t="n">
@@ -4736,7 +4748,7 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="1" t="n">
+      <c r="A257" s="2" t="n">
         <v>46113</v>
       </c>
       <c r="B257" t="n">
@@ -4753,7 +4765,7 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="1" t="n">
+      <c r="A258" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="B258" t="n">
@@ -4770,7 +4782,7 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="1" t="n">
+      <c r="A259" s="2" t="n">
         <v>46174</v>
       </c>
       <c r="B259" t="n">
@@ -4801,79 +4813,79 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>tarih</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>01. Gıda Ve Alkolsüz İçecekler</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>02. Alkollü İçecekler, Tütün Ve Tütün Ürünleri</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>03. Giyim Ve Ayakkabı</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>04. Konut, Su, Elektrik, Gaz Ve Diğer Yakıtlar</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>05. Mobilya, Mefruşat Ve Evde Kullanılan Ekipmanlar İle Rutin Ev Bakım Ve Onarımı</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>06. Sağlık</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>07. Ulaştırma</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>08. Bilgi Ve İletişim</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>09. Eğlence, Dinlence, Spor Ve Kültür</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>10. Eğitim Hizmetleri</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>11. Lokantalar Ve Konaklama Hizmetleri</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>12. Sigorta Ve Finansal Hizmetler</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>13. Kişisel Bakım, Sosyal Koruma Ve Çeşitli Mal Ve Hizmetler</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38353</v>
       </c>
       <c r="B2" t="n">
@@ -4917,7 +4929,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38384</v>
       </c>
       <c r="B3" t="n">
@@ -4961,7 +4973,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38412</v>
       </c>
       <c r="B4" t="n">
@@ -5005,7 +5017,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38443</v>
       </c>
       <c r="B5" t="n">
@@ -5049,7 +5061,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38473</v>
       </c>
       <c r="B6" t="n">
@@ -5093,7 +5105,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38504</v>
       </c>
       <c r="B7" t="n">
@@ -5137,7 +5149,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38534</v>
       </c>
       <c r="B8" t="n">
@@ -5181,7 +5193,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38565</v>
       </c>
       <c r="B9" t="n">
@@ -5225,7 +5237,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38596</v>
       </c>
       <c r="B10" t="n">
@@ -5269,7 +5281,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>38626</v>
       </c>
       <c r="B11" t="n">
@@ -5313,7 +5325,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>38657</v>
       </c>
       <c r="B12" t="n">
@@ -5357,7 +5369,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>38687</v>
       </c>
       <c r="B13" t="n">
@@ -5401,7 +5413,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>38718</v>
       </c>
       <c r="B14" t="n">
@@ -5445,7 +5457,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>38749</v>
       </c>
       <c r="B15" t="n">
@@ -5489,7 +5501,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>38777</v>
       </c>
       <c r="B16" t="n">
@@ -5533,7 +5545,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>38808</v>
       </c>
       <c r="B17" t="n">
@@ -5577,7 +5589,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>38838</v>
       </c>
       <c r="B18" t="n">
@@ -5621,7 +5633,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>38869</v>
       </c>
       <c r="B19" t="n">
@@ -5665,7 +5677,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>38899</v>
       </c>
       <c r="B20" t="n">
@@ -5709,7 +5721,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>38930</v>
       </c>
       <c r="B21" t="n">
@@ -5753,7 +5765,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>38961</v>
       </c>
       <c r="B22" t="n">
@@ -5797,7 +5809,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>38991</v>
       </c>
       <c r="B23" t="n">
@@ -5841,7 +5853,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39022</v>
       </c>
       <c r="B24" t="n">
@@ -5885,7 +5897,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39052</v>
       </c>
       <c r="B25" t="n">
@@ -5929,7 +5941,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39083</v>
       </c>
       <c r="B26" t="n">
@@ -5973,7 +5985,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39114</v>
       </c>
       <c r="B27" t="n">
@@ -6017,7 +6029,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39142</v>
       </c>
       <c r="B28" t="n">
@@ -6061,7 +6073,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39173</v>
       </c>
       <c r="B29" t="n">
@@ -6105,7 +6117,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39203</v>
       </c>
       <c r="B30" t="n">
@@ -6149,7 +6161,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39234</v>
       </c>
       <c r="B31" t="n">
@@ -6193,7 +6205,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39264</v>
       </c>
       <c r="B32" t="n">
@@ -6237,7 +6249,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39295</v>
       </c>
       <c r="B33" t="n">
@@ -6281,7 +6293,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39326</v>
       </c>
       <c r="B34" t="n">
@@ -6325,7 +6337,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39356</v>
       </c>
       <c r="B35" t="n">
@@ -6369,7 +6381,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39387</v>
       </c>
       <c r="B36" t="n">
@@ -6413,7 +6425,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39417</v>
       </c>
       <c r="B37" t="n">
@@ -6457,7 +6469,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39448</v>
       </c>
       <c r="B38" t="n">
@@ -6501,7 +6513,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39479</v>
       </c>
       <c r="B39" t="n">
@@ -6545,7 +6557,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39508</v>
       </c>
       <c r="B40" t="n">
@@ -6589,7 +6601,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39539</v>
       </c>
       <c r="B41" t="n">
@@ -6633,7 +6645,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39569</v>
       </c>
       <c r="B42" t="n">
@@ -6677,7 +6689,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39600</v>
       </c>
       <c r="B43" t="n">
@@ -6721,7 +6733,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>39630</v>
       </c>
       <c r="B44" t="n">
@@ -6765,7 +6777,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>39661</v>
       </c>
       <c r="B45" t="n">
@@ -6809,7 +6821,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>39692</v>
       </c>
       <c r="B46" t="n">
@@ -6853,7 +6865,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>39722</v>
       </c>
       <c r="B47" t="n">
@@ -6897,7 +6909,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>39753</v>
       </c>
       <c r="B48" t="n">
@@ -6941,7 +6953,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>39783</v>
       </c>
       <c r="B49" t="n">
@@ -6985,7 +6997,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>39814</v>
       </c>
       <c r="B50" t="n">
@@ -7029,7 +7041,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>39845</v>
       </c>
       <c r="B51" t="n">
@@ -7073,7 +7085,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>39873</v>
       </c>
       <c r="B52" t="n">
@@ -7117,7 +7129,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>39904</v>
       </c>
       <c r="B53" t="n">
@@ -7161,7 +7173,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>39934</v>
       </c>
       <c r="B54" t="n">
@@ -7205,7 +7217,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>39965</v>
       </c>
       <c r="B55" t="n">
@@ -7249,7 +7261,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>39995</v>
       </c>
       <c r="B56" t="n">
@@ -7293,7 +7305,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40026</v>
       </c>
       <c r="B57" t="n">
@@ -7337,7 +7349,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40057</v>
       </c>
       <c r="B58" t="n">
@@ -7381,7 +7393,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40087</v>
       </c>
       <c r="B59" t="n">
@@ -7425,7 +7437,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40118</v>
       </c>
       <c r="B60" t="n">
@@ -7469,7 +7481,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40148</v>
       </c>
       <c r="B61" t="n">
@@ -7513,7 +7525,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40179</v>
       </c>
       <c r="B62" t="n">
@@ -7557,7 +7569,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40210</v>
       </c>
       <c r="B63" t="n">
@@ -7601,7 +7613,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40238</v>
       </c>
       <c r="B64" t="n">
@@ -7645,7 +7657,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40269</v>
       </c>
       <c r="B65" t="n">
@@ -7689,7 +7701,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40299</v>
       </c>
       <c r="B66" t="n">
@@ -7733,7 +7745,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40330</v>
       </c>
       <c r="B67" t="n">
@@ -7777,7 +7789,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40360</v>
       </c>
       <c r="B68" t="n">
@@ -7821,7 +7833,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40391</v>
       </c>
       <c r="B69" t="n">
@@ -7865,7 +7877,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40422</v>
       </c>
       <c r="B70" t="n">
@@ -7909,7 +7921,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40452</v>
       </c>
       <c r="B71" t="n">
@@ -7953,7 +7965,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40483</v>
       </c>
       <c r="B72" t="n">
@@ -7997,7 +8009,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40513</v>
       </c>
       <c r="B73" t="n">
@@ -8041,7 +8053,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40544</v>
       </c>
       <c r="B74" t="n">
@@ -8085,7 +8097,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40575</v>
       </c>
       <c r="B75" t="n">
@@ -8129,7 +8141,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40603</v>
       </c>
       <c r="B76" t="n">
@@ -8173,7 +8185,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>40634</v>
       </c>
       <c r="B77" t="n">
@@ -8217,7 +8229,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>40664</v>
       </c>
       <c r="B78" t="n">
@@ -8261,7 +8273,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>40695</v>
       </c>
       <c r="B79" t="n">
@@ -8305,7 +8317,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>40725</v>
       </c>
       <c r="B80" t="n">
@@ -8349,7 +8361,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>40756</v>
       </c>
       <c r="B81" t="n">
@@ -8393,7 +8405,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>40787</v>
       </c>
       <c r="B82" t="n">
@@ -8437,7 +8449,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>40817</v>
       </c>
       <c r="B83" t="n">
@@ -8481,7 +8493,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>40848</v>
       </c>
       <c r="B84" t="n">
@@ -8525,7 +8537,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>40878</v>
       </c>
       <c r="B85" t="n">
@@ -8569,7 +8581,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>40909</v>
       </c>
       <c r="B86" t="n">
@@ -8613,7 +8625,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>40940</v>
       </c>
       <c r="B87" t="n">
@@ -8657,7 +8669,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>40969</v>
       </c>
       <c r="B88" t="n">
@@ -8701,7 +8713,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41000</v>
       </c>
       <c r="B89" t="n">
@@ -8745,7 +8757,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41030</v>
       </c>
       <c r="B90" t="n">
@@ -8789,7 +8801,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41061</v>
       </c>
       <c r="B91" t="n">
@@ -8833,7 +8845,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41091</v>
       </c>
       <c r="B92" t="n">
@@ -8877,7 +8889,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41122</v>
       </c>
       <c r="B93" t="n">
@@ -8921,7 +8933,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41153</v>
       </c>
       <c r="B94" t="n">
@@ -8965,7 +8977,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41183</v>
       </c>
       <c r="B95" t="n">
@@ -9009,7 +9021,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41214</v>
       </c>
       <c r="B96" t="n">
@@ -9053,7 +9065,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41244</v>
       </c>
       <c r="B97" t="n">
@@ -9097,7 +9109,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41275</v>
       </c>
       <c r="B98" t="n">
@@ -9141,7 +9153,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41306</v>
       </c>
       <c r="B99" t="n">
@@ -9185,7 +9197,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41334</v>
       </c>
       <c r="B100" t="n">
@@ -9229,7 +9241,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41365</v>
       </c>
       <c r="B101" t="n">
@@ -9273,7 +9285,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41395</v>
       </c>
       <c r="B102" t="n">
@@ -9317,7 +9329,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41426</v>
       </c>
       <c r="B103" t="n">
@@ -9361,7 +9373,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41456</v>
       </c>
       <c r="B104" t="n">
@@ -9405,7 +9417,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41487</v>
       </c>
       <c r="B105" t="n">
@@ -9449,7 +9461,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41518</v>
       </c>
       <c r="B106" t="n">
@@ -9493,7 +9505,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41548</v>
       </c>
       <c r="B107" t="n">
@@ -9537,7 +9549,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41579</v>
       </c>
       <c r="B108" t="n">
@@ -9581,7 +9593,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>41609</v>
       </c>
       <c r="B109" t="n">
@@ -9625,7 +9637,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>41640</v>
       </c>
       <c r="B110" t="n">
@@ -9669,7 +9681,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>41671</v>
       </c>
       <c r="B111" t="n">
@@ -9713,7 +9725,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>41699</v>
       </c>
       <c r="B112" t="n">
@@ -9757,7 +9769,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>41730</v>
       </c>
       <c r="B113" t="n">
@@ -9801,7 +9813,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>41760</v>
       </c>
       <c r="B114" t="n">
@@ -9845,7 +9857,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>41791</v>
       </c>
       <c r="B115" t="n">
@@ -9889,7 +9901,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>41821</v>
       </c>
       <c r="B116" t="n">
@@ -9933,7 +9945,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>41852</v>
       </c>
       <c r="B117" t="n">
@@ -9977,7 +9989,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>41883</v>
       </c>
       <c r="B118" t="n">
@@ -10021,7 +10033,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>41913</v>
       </c>
       <c r="B119" t="n">
@@ -10065,7 +10077,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>41944</v>
       </c>
       <c r="B120" t="n">
@@ -10109,7 +10121,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>41974</v>
       </c>
       <c r="B121" t="n">
@@ -10153,7 +10165,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42005</v>
       </c>
       <c r="B122" t="n">
@@ -10197,7 +10209,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42036</v>
       </c>
       <c r="B123" t="n">
@@ -10241,7 +10253,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42064</v>
       </c>
       <c r="B124" t="n">
@@ -10285,7 +10297,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42095</v>
       </c>
       <c r="B125" t="n">
@@ -10329,7 +10341,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42125</v>
       </c>
       <c r="B126" t="n">
@@ -10373,7 +10385,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42156</v>
       </c>
       <c r="B127" t="n">
@@ -10417,7 +10429,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42186</v>
       </c>
       <c r="B128" t="n">
@@ -10461,7 +10473,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42217</v>
       </c>
       <c r="B129" t="n">
@@ -10505,7 +10517,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42248</v>
       </c>
       <c r="B130" t="n">
@@ -10549,7 +10561,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42278</v>
       </c>
       <c r="B131" t="n">
@@ -10593,7 +10605,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42309</v>
       </c>
       <c r="B132" t="n">
@@ -10637,7 +10649,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42339</v>
       </c>
       <c r="B133" t="n">
@@ -10681,7 +10693,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42370</v>
       </c>
       <c r="B134" t="n">
@@ -10725,7 +10737,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42401</v>
       </c>
       <c r="B135" t="n">
@@ -10769,7 +10781,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42430</v>
       </c>
       <c r="B136" t="n">
@@ -10813,7 +10825,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42461</v>
       </c>
       <c r="B137" t="n">
@@ -10857,7 +10869,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42491</v>
       </c>
       <c r="B138" t="n">
@@ -10901,7 +10913,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42522</v>
       </c>
       <c r="B139" t="n">
@@ -10945,7 +10957,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42552</v>
       </c>
       <c r="B140" t="n">
@@ -10989,7 +11001,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42583</v>
       </c>
       <c r="B141" t="n">
@@ -11033,7 +11045,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>42614</v>
       </c>
       <c r="B142" t="n">
@@ -11077,7 +11089,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>42644</v>
       </c>
       <c r="B143" t="n">
@@ -11121,7 +11133,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>42675</v>
       </c>
       <c r="B144" t="n">
@@ -11165,7 +11177,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>42705</v>
       </c>
       <c r="B145" t="n">
@@ -11209,7 +11221,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>42736</v>
       </c>
       <c r="B146" t="n">
@@ -11253,7 +11265,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>42767</v>
       </c>
       <c r="B147" t="n">
@@ -11297,7 +11309,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>42795</v>
       </c>
       <c r="B148" t="n">
@@ -11341,7 +11353,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>42826</v>
       </c>
       <c r="B149" t="n">
@@ -11385,7 +11397,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>42856</v>
       </c>
       <c r="B150" t="n">
@@ -11429,7 +11441,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>42887</v>
       </c>
       <c r="B151" t="n">
@@ -11473,7 +11485,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>42917</v>
       </c>
       <c r="B152" t="n">
@@ -11517,7 +11529,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>42948</v>
       </c>
       <c r="B153" t="n">
@@ -11561,7 +11573,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>42979</v>
       </c>
       <c r="B154" t="n">
@@ -11605,7 +11617,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43009</v>
       </c>
       <c r="B155" t="n">
@@ -11649,7 +11661,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43040</v>
       </c>
       <c r="B156" t="n">
@@ -11693,7 +11705,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43070</v>
       </c>
       <c r="B157" t="n">
@@ -11737,7 +11749,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43101</v>
       </c>
       <c r="B158" t="n">
@@ -11781,7 +11793,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43132</v>
       </c>
       <c r="B159" t="n">
@@ -11825,7 +11837,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43160</v>
       </c>
       <c r="B160" t="n">
@@ -11869,7 +11881,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43191</v>
       </c>
       <c r="B161" t="n">
@@ -11913,7 +11925,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43221</v>
       </c>
       <c r="B162" t="n">
@@ -11957,7 +11969,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43252</v>
       </c>
       <c r="B163" t="n">
@@ -12001,7 +12013,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43282</v>
       </c>
       <c r="B164" t="n">
@@ -12045,7 +12057,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43313</v>
       </c>
       <c r="B165" t="n">
@@ -12089,7 +12101,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43344</v>
       </c>
       <c r="B166" t="n">
@@ -12133,7 +12145,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43374</v>
       </c>
       <c r="B167" t="n">
@@ -12177,7 +12189,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43405</v>
       </c>
       <c r="B168" t="n">
@@ -12221,7 +12233,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43435</v>
       </c>
       <c r="B169" t="n">
@@ -12265,7 +12277,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43466</v>
       </c>
       <c r="B170" t="n">
@@ -12309,7 +12321,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43497</v>
       </c>
       <c r="B171" t="n">
@@ -12353,7 +12365,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43525</v>
       </c>
       <c r="B172" t="n">
@@ -12397,7 +12409,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43556</v>
       </c>
       <c r="B173" t="n">
@@ -12441,7 +12453,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43586</v>
       </c>
       <c r="B174" t="n">
@@ -12485,7 +12497,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>43617</v>
       </c>
       <c r="B175" t="n">
@@ -12529,7 +12541,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>43647</v>
       </c>
       <c r="B176" t="n">
@@ -12573,7 +12585,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>43678</v>
       </c>
       <c r="B177" t="n">
@@ -12617,7 +12629,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>43709</v>
       </c>
       <c r="B178" t="n">
@@ -12661,7 +12673,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>43739</v>
       </c>
       <c r="B179" t="n">
@@ -12705,7 +12717,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>43770</v>
       </c>
       <c r="B180" t="n">
@@ -12749,7 +12761,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>43800</v>
       </c>
       <c r="B181" t="n">
@@ -12793,7 +12805,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>43831</v>
       </c>
       <c r="B182" t="n">
@@ -12837,7 +12849,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>43862</v>
       </c>
       <c r="B183" t="n">
@@ -12881,7 +12893,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>43891</v>
       </c>
       <c r="B184" t="n">
@@ -12925,7 +12937,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>43922</v>
       </c>
       <c r="B185" t="n">
@@ -12969,7 +12981,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>43952</v>
       </c>
       <c r="B186" t="n">
@@ -13013,7 +13025,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>43983</v>
       </c>
       <c r="B187" t="n">
@@ -13057,7 +13069,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44013</v>
       </c>
       <c r="B188" t="n">
@@ -13101,7 +13113,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44044</v>
       </c>
       <c r="B189" t="n">
@@ -13145,7 +13157,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44075</v>
       </c>
       <c r="B190" t="n">
@@ -13189,7 +13201,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44105</v>
       </c>
       <c r="B191" t="n">
@@ -13233,7 +13245,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44136</v>
       </c>
       <c r="B192" t="n">
@@ -13277,7 +13289,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44166</v>
       </c>
       <c r="B193" t="n">
@@ -13321,7 +13333,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44197</v>
       </c>
       <c r="B194" t="n">
@@ -13365,7 +13377,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44228</v>
       </c>
       <c r="B195" t="n">
@@ -13409,7 +13421,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44256</v>
       </c>
       <c r="B196" t="n">
@@ -13453,7 +13465,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44287</v>
       </c>
       <c r="B197" t="n">
@@ -13497,7 +13509,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44317</v>
       </c>
       <c r="B198" t="n">
@@ -13541,7 +13553,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44348</v>
       </c>
       <c r="B199" t="n">
@@ -13585,7 +13597,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44378</v>
       </c>
       <c r="B200" t="n">
@@ -13629,7 +13641,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44409</v>
       </c>
       <c r="B201" t="n">
@@ -13673,7 +13685,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44440</v>
       </c>
       <c r="B202" t="n">
@@ -13717,7 +13729,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44470</v>
       </c>
       <c r="B203" t="n">
@@ -13761,7 +13773,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44501</v>
       </c>
       <c r="B204" t="n">
@@ -13805,7 +13817,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44531</v>
       </c>
       <c r="B205" t="n">
@@ -13849,7 +13861,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44562</v>
       </c>
       <c r="B206" t="n">
@@ -13893,7 +13905,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44593</v>
       </c>
       <c r="B207" t="n">
@@ -13937,7 +13949,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>44621</v>
       </c>
       <c r="B208" t="n">
@@ -13981,7 +13993,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>44652</v>
       </c>
       <c r="B209" t="n">
@@ -14025,7 +14037,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>44682</v>
       </c>
       <c r="B210" t="n">
@@ -14069,7 +14081,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>44713</v>
       </c>
       <c r="B211" t="n">
@@ -14113,7 +14125,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>44743</v>
       </c>
       <c r="B212" t="n">
@@ -14157,7 +14169,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>44774</v>
       </c>
       <c r="B213" t="n">
@@ -14201,7 +14213,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>44805</v>
       </c>
       <c r="B214" t="n">
@@ -14245,7 +14257,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>44835</v>
       </c>
       <c r="B215" t="n">
@@ -14289,7 +14301,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>44866</v>
       </c>
       <c r="B216" t="n">
@@ -14333,7 +14345,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>44896</v>
       </c>
       <c r="B217" t="n">
@@ -14377,7 +14389,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>44927</v>
       </c>
       <c r="B218" t="n">
@@ -14421,7 +14433,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>44958</v>
       </c>
       <c r="B219" t="n">
@@ -14465,7 +14477,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>44986</v>
       </c>
       <c r="B220" t="n">
@@ -14509,7 +14521,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45017</v>
       </c>
       <c r="B221" t="n">
@@ -14553,7 +14565,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45047</v>
       </c>
       <c r="B222" t="n">
@@ -14597,7 +14609,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45078</v>
       </c>
       <c r="B223" t="n">
@@ -14641,7 +14653,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45108</v>
       </c>
       <c r="B224" t="n">
@@ -14685,7 +14697,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45139</v>
       </c>
       <c r="B225" t="n">
@@ -14729,7 +14741,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45170</v>
       </c>
       <c r="B226" t="n">
@@ -14773,7 +14785,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45200</v>
       </c>
       <c r="B227" t="n">
@@ -14817,7 +14829,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45231</v>
       </c>
       <c r="B228" t="n">
@@ -14861,7 +14873,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45261</v>
       </c>
       <c r="B229" t="n">
@@ -14905,7 +14917,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45292</v>
       </c>
       <c r="B230" t="n">
@@ -14949,7 +14961,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45323</v>
       </c>
       <c r="B231" t="n">
@@ -14993,7 +15005,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45352</v>
       </c>
       <c r="B232" t="n">
@@ -15037,7 +15049,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45383</v>
       </c>
       <c r="B233" t="n">
@@ -15081,7 +15093,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45413</v>
       </c>
       <c r="B234" t="n">
@@ -15125,7 +15137,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45444</v>
       </c>
       <c r="B235" t="n">
@@ -15169,7 +15181,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45474</v>
       </c>
       <c r="B236" t="n">
@@ -15213,7 +15225,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="B237" t="n">
@@ -15257,7 +15269,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45536</v>
       </c>
       <c r="B238" t="n">
@@ -15301,7 +15313,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45566</v>
       </c>
       <c r="B239" t="n">
@@ -15345,7 +15357,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="B240" t="n">
@@ -15389,7 +15401,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>45627</v>
       </c>
       <c r="B241" t="n">
@@ -15433,7 +15445,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>45658</v>
       </c>
       <c r="B242" t="n">
@@ -15477,7 +15489,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>45689</v>
       </c>
       <c r="B243" t="n">
@@ -15521,7 +15533,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>45717</v>
       </c>
       <c r="B244" t="n">
@@ -15565,7 +15577,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>45748</v>
       </c>
       <c r="B245" t="n">
@@ -15609,7 +15621,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="B246" t="n">
@@ -15653,7 +15665,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>45809</v>
       </c>
       <c r="B247" t="n">
@@ -15697,7 +15709,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>45839</v>
       </c>
       <c r="B248" t="n">
@@ -15741,7 +15753,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="B249" t="n">
@@ -15785,7 +15797,7 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>45901</v>
       </c>
       <c r="B250" t="n">
@@ -15829,7 +15841,7 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="1" t="n">
+      <c r="A251" s="2" t="n">
         <v>45931</v>
       </c>
       <c r="B251" t="n">
@@ -15873,7 +15885,7 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="1" t="n">
+      <c r="A252" s="2" t="n">
         <v>45962</v>
       </c>
       <c r="B252" t="n">
@@ -15917,7 +15929,7 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="1" t="n">
+      <c r="A253" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="B253" t="n">
@@ -15961,7 +15973,7 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="1" t="n">
+      <c r="A254" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B254" t="n">
@@ -16005,7 +16017,7 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="1" t="n">
+      <c r="A255" s="2" t="n">
         <v>46054</v>
       </c>
       <c r="B255" t="n">
@@ -16049,7 +16061,7 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="1" t="n">
+      <c r="A256" s="2" t="n">
         <v>46082</v>
       </c>
       <c r="B256" t="n">
@@ -16093,7 +16105,7 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="1" t="n">
+      <c r="A257" s="2" t="n">
         <v>46113</v>
       </c>
       <c r="B257" t="n">
@@ -16137,7 +16149,7 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="1" t="n">
+      <c r="A258" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="B258" t="n">
@@ -16181,7 +16193,7 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="1" t="n">
+      <c r="A259" s="2" t="n">
         <v>46174</v>
       </c>
       <c r="B259" t="n">
@@ -16239,79 +16251,79 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>tarih</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>01. Gıda Ve Alkolsüz İçecekler</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>02. Alkollü İçecekler, Tütün Ve Tütün Ürünleri</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>03. Giyim Ve Ayakkabı</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>04. Konut, Su, Elektrik, Gaz Ve Diğer Yakıtlar</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>05. Mobilya, Mefruşat Ve Evde Kullanılan Ekipmanlar İle Rutin Ev Bakım Ve Onarımı</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>06. Sağlık</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>07. Ulaştırma</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>08. Bilgi Ve İletişim</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>09. Eğlence, Dinlence, Spor Ve Kültür</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>10. Eğitim Hizmetleri</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>11. Lokantalar Ve Konaklama Hizmetleri</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>12. Sigorta Ve Finansal Hizmetler</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>13. Kişisel Bakım, Sosyal Koruma Ve Çeşitli Mal Ve Hizmetler</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38353</v>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -16329,7 +16341,7 @@
       <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38384</v>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -16347,7 +16359,7 @@
       <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38412</v>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -16365,7 +16377,7 @@
       <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38443</v>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -16383,7 +16395,7 @@
       <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38473</v>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -16401,7 +16413,7 @@
       <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38504</v>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -16419,7 +16431,7 @@
       <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38534</v>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -16437,7 +16449,7 @@
       <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38565</v>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -16455,7 +16467,7 @@
       <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38596</v>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -16473,7 +16485,7 @@
       <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>38626</v>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -16491,7 +16503,7 @@
       <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>38657</v>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -16509,7 +16521,7 @@
       <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>38687</v>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -16527,7 +16539,7 @@
       <c r="N13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>38718</v>
       </c>
       <c r="B14" t="n">
@@ -16571,7 +16583,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>38749</v>
       </c>
       <c r="B15" t="n">
@@ -16615,7 +16627,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>38777</v>
       </c>
       <c r="B16" t="n">
@@ -16659,7 +16671,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>38808</v>
       </c>
       <c r="B17" t="n">
@@ -16703,7 +16715,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>38838</v>
       </c>
       <c r="B18" t="n">
@@ -16747,7 +16759,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>38869</v>
       </c>
       <c r="B19" t="n">
@@ -16791,7 +16803,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>38899</v>
       </c>
       <c r="B20" t="n">
@@ -16835,7 +16847,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>38930</v>
       </c>
       <c r="B21" t="n">
@@ -16879,7 +16891,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>38961</v>
       </c>
       <c r="B22" t="n">
@@ -16923,7 +16935,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>38991</v>
       </c>
       <c r="B23" t="n">
@@ -16967,7 +16979,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39022</v>
       </c>
       <c r="B24" t="n">
@@ -17011,7 +17023,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39052</v>
       </c>
       <c r="B25" t="n">
@@ -17055,7 +17067,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39083</v>
       </c>
       <c r="B26" t="n">
@@ -17099,7 +17111,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39114</v>
       </c>
       <c r="B27" t="n">
@@ -17143,7 +17155,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39142</v>
       </c>
       <c r="B28" t="n">
@@ -17187,7 +17199,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39173</v>
       </c>
       <c r="B29" t="n">
@@ -17231,7 +17243,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39203</v>
       </c>
       <c r="B30" t="n">
@@ -17275,7 +17287,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39234</v>
       </c>
       <c r="B31" t="n">
@@ -17319,7 +17331,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39264</v>
       </c>
       <c r="B32" t="n">
@@ -17363,7 +17375,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39295</v>
       </c>
       <c r="B33" t="n">
@@ -17407,7 +17419,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39326</v>
       </c>
       <c r="B34" t="n">
@@ -17451,7 +17463,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39356</v>
       </c>
       <c r="B35" t="n">
@@ -17495,7 +17507,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39387</v>
       </c>
       <c r="B36" t="n">
@@ -17539,7 +17551,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39417</v>
       </c>
       <c r="B37" t="n">
@@ -17583,7 +17595,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39448</v>
       </c>
       <c r="B38" t="n">
@@ -17627,7 +17639,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39479</v>
       </c>
       <c r="B39" t="n">
@@ -17671,7 +17683,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39508</v>
       </c>
       <c r="B40" t="n">
@@ -17715,7 +17727,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39539</v>
       </c>
       <c r="B41" t="n">
@@ -17759,7 +17771,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39569</v>
       </c>
       <c r="B42" t="n">
@@ -17803,7 +17815,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39600</v>
       </c>
       <c r="B43" t="n">
@@ -17847,7 +17859,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>39630</v>
       </c>
       <c r="B44" t="n">
@@ -17891,7 +17903,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>39661</v>
       </c>
       <c r="B45" t="n">
@@ -17935,7 +17947,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>39692</v>
       </c>
       <c r="B46" t="n">
@@ -17979,7 +17991,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>39722</v>
       </c>
       <c r="B47" t="n">
@@ -18023,7 +18035,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>39753</v>
       </c>
       <c r="B48" t="n">
@@ -18067,7 +18079,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>39783</v>
       </c>
       <c r="B49" t="n">
@@ -18111,7 +18123,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>39814</v>
       </c>
       <c r="B50" t="n">
@@ -18155,7 +18167,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>39845</v>
       </c>
       <c r="B51" t="n">
@@ -18199,7 +18211,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>39873</v>
       </c>
       <c r="B52" t="n">
@@ -18243,7 +18255,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>39904</v>
       </c>
       <c r="B53" t="n">
@@ -18287,7 +18299,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>39934</v>
       </c>
       <c r="B54" t="n">
@@ -18331,7 +18343,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>39965</v>
       </c>
       <c r="B55" t="n">
@@ -18375,7 +18387,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>39995</v>
       </c>
       <c r="B56" t="n">
@@ -18419,7 +18431,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40026</v>
       </c>
       <c r="B57" t="n">
@@ -18463,7 +18475,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40057</v>
       </c>
       <c r="B58" t="n">
@@ -18507,7 +18519,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40087</v>
       </c>
       <c r="B59" t="n">
@@ -18551,7 +18563,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40118</v>
       </c>
       <c r="B60" t="n">
@@ -18595,7 +18607,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40148</v>
       </c>
       <c r="B61" t="n">
@@ -18639,7 +18651,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40179</v>
       </c>
       <c r="B62" t="n">
@@ -18683,7 +18695,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40210</v>
       </c>
       <c r="B63" t="n">
@@ -18727,7 +18739,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40238</v>
       </c>
       <c r="B64" t="n">
@@ -18771,7 +18783,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40269</v>
       </c>
       <c r="B65" t="n">
@@ -18815,7 +18827,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40299</v>
       </c>
       <c r="B66" t="n">
@@ -18859,7 +18871,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40330</v>
       </c>
       <c r="B67" t="n">
@@ -18903,7 +18915,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40360</v>
       </c>
       <c r="B68" t="n">
@@ -18947,7 +18959,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40391</v>
       </c>
       <c r="B69" t="n">
@@ -18991,7 +19003,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40422</v>
       </c>
       <c r="B70" t="n">
@@ -19035,7 +19047,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40452</v>
       </c>
       <c r="B71" t="n">
@@ -19079,7 +19091,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40483</v>
       </c>
       <c r="B72" t="n">
@@ -19123,7 +19135,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40513</v>
       </c>
       <c r="B73" t="n">
@@ -19167,7 +19179,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40544</v>
       </c>
       <c r="B74" t="n">
@@ -19211,7 +19223,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40575</v>
       </c>
       <c r="B75" t="n">
@@ -19255,7 +19267,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40603</v>
       </c>
       <c r="B76" t="n">
@@ -19299,7 +19311,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>40634</v>
       </c>
       <c r="B77" t="n">
@@ -19343,7 +19355,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>40664</v>
       </c>
       <c r="B78" t="n">
@@ -19387,7 +19399,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>40695</v>
       </c>
       <c r="B79" t="n">
@@ -19431,7 +19443,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>40725</v>
       </c>
       <c r="B80" t="n">
@@ -19475,7 +19487,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>40756</v>
       </c>
       <c r="B81" t="n">
@@ -19519,7 +19531,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>40787</v>
       </c>
       <c r="B82" t="n">
@@ -19563,7 +19575,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>40817</v>
       </c>
       <c r="B83" t="n">
@@ -19607,7 +19619,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>40848</v>
       </c>
       <c r="B84" t="n">
@@ -19651,7 +19663,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>40878</v>
       </c>
       <c r="B85" t="n">
@@ -19695,7 +19707,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>40909</v>
       </c>
       <c r="B86" t="n">
@@ -19739,7 +19751,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>40940</v>
       </c>
       <c r="B87" t="n">
@@ -19783,7 +19795,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>40969</v>
       </c>
       <c r="B88" t="n">
@@ -19827,7 +19839,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41000</v>
       </c>
       <c r="B89" t="n">
@@ -19871,7 +19883,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41030</v>
       </c>
       <c r="B90" t="n">
@@ -19915,7 +19927,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41061</v>
       </c>
       <c r="B91" t="n">
@@ -19959,7 +19971,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41091</v>
       </c>
       <c r="B92" t="n">
@@ -20003,7 +20015,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41122</v>
       </c>
       <c r="B93" t="n">
@@ -20047,7 +20059,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41153</v>
       </c>
       <c r="B94" t="n">
@@ -20091,7 +20103,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41183</v>
       </c>
       <c r="B95" t="n">
@@ -20135,7 +20147,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41214</v>
       </c>
       <c r="B96" t="n">
@@ -20179,7 +20191,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41244</v>
       </c>
       <c r="B97" t="n">
@@ -20223,7 +20235,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41275</v>
       </c>
       <c r="B98" t="n">
@@ -20267,7 +20279,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41306</v>
       </c>
       <c r="B99" t="n">
@@ -20311,7 +20323,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41334</v>
       </c>
       <c r="B100" t="n">
@@ -20355,7 +20367,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41365</v>
       </c>
       <c r="B101" t="n">
@@ -20399,7 +20411,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41395</v>
       </c>
       <c r="B102" t="n">
@@ -20443,7 +20455,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41426</v>
       </c>
       <c r="B103" t="n">
@@ -20487,7 +20499,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41456</v>
       </c>
       <c r="B104" t="n">
@@ -20531,7 +20543,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41487</v>
       </c>
       <c r="B105" t="n">
@@ -20575,7 +20587,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41518</v>
       </c>
       <c r="B106" t="n">
@@ -20619,7 +20631,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41548</v>
       </c>
       <c r="B107" t="n">
@@ -20663,7 +20675,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41579</v>
       </c>
       <c r="B108" t="n">
@@ -20707,7 +20719,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>41609</v>
       </c>
       <c r="B109" t="n">
@@ -20751,7 +20763,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>41640</v>
       </c>
       <c r="B110" t="n">
@@ -20795,7 +20807,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>41671</v>
       </c>
       <c r="B111" t="n">
@@ -20839,7 +20851,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>41699</v>
       </c>
       <c r="B112" t="n">
@@ -20883,7 +20895,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>41730</v>
       </c>
       <c r="B113" t="n">
@@ -20927,7 +20939,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>41760</v>
       </c>
       <c r="B114" t="n">
@@ -20971,7 +20983,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>41791</v>
       </c>
       <c r="B115" t="n">
@@ -21015,7 +21027,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>41821</v>
       </c>
       <c r="B116" t="n">
@@ -21059,7 +21071,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>41852</v>
       </c>
       <c r="B117" t="n">
@@ -21103,7 +21115,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>41883</v>
       </c>
       <c r="B118" t="n">
@@ -21147,7 +21159,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>41913</v>
       </c>
       <c r="B119" t="n">
@@ -21191,7 +21203,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>41944</v>
       </c>
       <c r="B120" t="n">
@@ -21235,7 +21247,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>41974</v>
       </c>
       <c r="B121" t="n">
@@ -21279,7 +21291,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42005</v>
       </c>
       <c r="B122" t="n">
@@ -21323,7 +21335,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42036</v>
       </c>
       <c r="B123" t="n">
@@ -21367,7 +21379,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42064</v>
       </c>
       <c r="B124" t="n">
@@ -21411,7 +21423,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42095</v>
       </c>
       <c r="B125" t="n">
@@ -21455,7 +21467,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42125</v>
       </c>
       <c r="B126" t="n">
@@ -21499,7 +21511,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42156</v>
       </c>
       <c r="B127" t="n">
@@ -21543,7 +21555,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42186</v>
       </c>
       <c r="B128" t="n">
@@ -21587,7 +21599,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42217</v>
       </c>
       <c r="B129" t="n">
@@ -21631,7 +21643,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42248</v>
       </c>
       <c r="B130" t="n">
@@ -21675,7 +21687,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42278</v>
       </c>
       <c r="B131" t="n">
@@ -21719,7 +21731,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42309</v>
       </c>
       <c r="B132" t="n">
@@ -21763,7 +21775,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42339</v>
       </c>
       <c r="B133" t="n">
@@ -21807,7 +21819,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42370</v>
       </c>
       <c r="B134" t="n">
@@ -21851,7 +21863,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42401</v>
       </c>
       <c r="B135" t="n">
@@ -21895,7 +21907,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42430</v>
       </c>
       <c r="B136" t="n">
@@ -21939,7 +21951,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42461</v>
       </c>
       <c r="B137" t="n">
@@ -21983,7 +21995,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42491</v>
       </c>
       <c r="B138" t="n">
@@ -22027,7 +22039,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42522</v>
       </c>
       <c r="B139" t="n">
@@ -22071,7 +22083,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42552</v>
       </c>
       <c r="B140" t="n">
@@ -22115,7 +22127,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42583</v>
       </c>
       <c r="B141" t="n">
@@ -22159,7 +22171,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>42614</v>
       </c>
       <c r="B142" t="n">
@@ -22203,7 +22215,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>42644</v>
       </c>
       <c r="B143" t="n">
@@ -22247,7 +22259,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>42675</v>
       </c>
       <c r="B144" t="n">
@@ -22291,7 +22303,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>42705</v>
       </c>
       <c r="B145" t="n">
@@ -22335,7 +22347,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>42736</v>
       </c>
       <c r="B146" t="n">
@@ -22379,7 +22391,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>42767</v>
       </c>
       <c r="B147" t="n">
@@ -22423,7 +22435,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>42795</v>
       </c>
       <c r="B148" t="n">
@@ -22467,7 +22479,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>42826</v>
       </c>
       <c r="B149" t="n">
@@ -22511,7 +22523,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>42856</v>
       </c>
       <c r="B150" t="n">
@@ -22555,7 +22567,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>42887</v>
       </c>
       <c r="B151" t="n">
@@ -22599,7 +22611,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>42917</v>
       </c>
       <c r="B152" t="n">
@@ -22643,7 +22655,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>42948</v>
       </c>
       <c r="B153" t="n">
@@ -22687,7 +22699,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>42979</v>
       </c>
       <c r="B154" t="n">
@@ -22731,7 +22743,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43009</v>
       </c>
       <c r="B155" t="n">
@@ -22775,7 +22787,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43040</v>
       </c>
       <c r="B156" t="n">
@@ -22819,7 +22831,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43070</v>
       </c>
       <c r="B157" t="n">
@@ -22863,7 +22875,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43101</v>
       </c>
       <c r="B158" t="n">
@@ -22907,7 +22919,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43132</v>
       </c>
       <c r="B159" t="n">
@@ -22951,7 +22963,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43160</v>
       </c>
       <c r="B160" t="n">
@@ -22995,7 +23007,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43191</v>
       </c>
       <c r="B161" t="n">
@@ -23039,7 +23051,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43221</v>
       </c>
       <c r="B162" t="n">
@@ -23083,7 +23095,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43252</v>
       </c>
       <c r="B163" t="n">
@@ -23127,7 +23139,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43282</v>
       </c>
       <c r="B164" t="n">
@@ -23171,7 +23183,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43313</v>
       </c>
       <c r="B165" t="n">
@@ -23215,7 +23227,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43344</v>
       </c>
       <c r="B166" t="n">
@@ -23259,7 +23271,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43374</v>
       </c>
       <c r="B167" t="n">
@@ -23303,7 +23315,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43405</v>
       </c>
       <c r="B168" t="n">
@@ -23347,7 +23359,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43435</v>
       </c>
       <c r="B169" t="n">
@@ -23391,7 +23403,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43466</v>
       </c>
       <c r="B170" t="n">
@@ -23435,7 +23447,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43497</v>
       </c>
       <c r="B171" t="n">
@@ -23479,7 +23491,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43525</v>
       </c>
       <c r="B172" t="n">
@@ -23523,7 +23535,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43556</v>
       </c>
       <c r="B173" t="n">
@@ -23567,7 +23579,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43586</v>
       </c>
       <c r="B174" t="n">
@@ -23611,7 +23623,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>43617</v>
       </c>
       <c r="B175" t="n">
@@ -23655,7 +23667,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>43647</v>
       </c>
       <c r="B176" t="n">
@@ -23699,7 +23711,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>43678</v>
       </c>
       <c r="B177" t="n">
@@ -23743,7 +23755,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>43709</v>
       </c>
       <c r="B178" t="n">
@@ -23787,7 +23799,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>43739</v>
       </c>
       <c r="B179" t="n">
@@ -23831,7 +23843,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>43770</v>
       </c>
       <c r="B180" t="n">
@@ -23875,7 +23887,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>43800</v>
       </c>
       <c r="B181" t="n">
@@ -23919,7 +23931,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>43831</v>
       </c>
       <c r="B182" t="n">
@@ -23963,7 +23975,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>43862</v>
       </c>
       <c r="B183" t="n">
@@ -24007,7 +24019,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>43891</v>
       </c>
       <c r="B184" t="n">
@@ -24051,7 +24063,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>43922</v>
       </c>
       <c r="B185" t="n">
@@ -24095,7 +24107,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>43952</v>
       </c>
       <c r="B186" t="n">
@@ -24139,7 +24151,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>43983</v>
       </c>
       <c r="B187" t="n">
@@ -24183,7 +24195,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44013</v>
       </c>
       <c r="B188" t="n">
@@ -24227,7 +24239,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44044</v>
       </c>
       <c r="B189" t="n">
@@ -24271,7 +24283,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44075</v>
       </c>
       <c r="B190" t="n">
@@ -24315,7 +24327,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44105</v>
       </c>
       <c r="B191" t="n">
@@ -24359,7 +24371,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44136</v>
       </c>
       <c r="B192" t="n">
@@ -24403,7 +24415,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44166</v>
       </c>
       <c r="B193" t="n">
@@ -24447,7 +24459,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44197</v>
       </c>
       <c r="B194" t="n">
@@ -24491,7 +24503,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44228</v>
       </c>
       <c r="B195" t="n">
@@ -24535,7 +24547,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44256</v>
       </c>
       <c r="B196" t="n">
@@ -24579,7 +24591,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44287</v>
       </c>
       <c r="B197" t="n">
@@ -24623,7 +24635,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44317</v>
       </c>
       <c r="B198" t="n">
@@ -24667,7 +24679,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44348</v>
       </c>
       <c r="B199" t="n">
@@ -24711,7 +24723,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44378</v>
       </c>
       <c r="B200" t="n">
@@ -24755,7 +24767,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44409</v>
       </c>
       <c r="B201" t="n">
@@ -24799,7 +24811,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44440</v>
       </c>
       <c r="B202" t="n">
@@ -24843,7 +24855,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44470</v>
       </c>
       <c r="B203" t="n">
@@ -24887,7 +24899,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44501</v>
       </c>
       <c r="B204" t="n">
@@ -24931,7 +24943,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44531</v>
       </c>
       <c r="B205" t="n">
@@ -24975,7 +24987,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44562</v>
       </c>
       <c r="B206" t="n">
@@ -25019,7 +25031,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44593</v>
       </c>
       <c r="B207" t="n">
@@ -25063,7 +25075,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>44621</v>
       </c>
       <c r="B208" t="n">
@@ -25107,7 +25119,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>44652</v>
       </c>
       <c r="B209" t="n">
@@ -25151,7 +25163,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>44682</v>
       </c>
       <c r="B210" t="n">
@@ -25195,7 +25207,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>44713</v>
       </c>
       <c r="B211" t="n">
@@ -25239,7 +25251,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>44743</v>
       </c>
       <c r="B212" t="n">
@@ -25283,7 +25295,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>44774</v>
       </c>
       <c r="B213" t="n">
@@ -25327,7 +25339,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>44805</v>
       </c>
       <c r="B214" t="n">
@@ -25371,7 +25383,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>44835</v>
       </c>
       <c r="B215" t="n">
@@ -25415,7 +25427,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>44866</v>
       </c>
       <c r="B216" t="n">
@@ -25459,7 +25471,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>44896</v>
       </c>
       <c r="B217" t="n">
@@ -25503,7 +25515,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>44927</v>
       </c>
       <c r="B218" t="n">
@@ -25547,7 +25559,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>44958</v>
       </c>
       <c r="B219" t="n">
@@ -25591,7 +25603,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>44986</v>
       </c>
       <c r="B220" t="n">
@@ -25635,7 +25647,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45017</v>
       </c>
       <c r="B221" t="n">
@@ -25679,7 +25691,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45047</v>
       </c>
       <c r="B222" t="n">
@@ -25723,7 +25735,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45078</v>
       </c>
       <c r="B223" t="n">
@@ -25767,7 +25779,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45108</v>
       </c>
       <c r="B224" t="n">
@@ -25811,7 +25823,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45139</v>
       </c>
       <c r="B225" t="n">
@@ -25855,7 +25867,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45170</v>
       </c>
       <c r="B226" t="n">
@@ -25899,7 +25911,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45200</v>
       </c>
       <c r="B227" t="n">
@@ -25943,7 +25955,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45231</v>
       </c>
       <c r="B228" t="n">
@@ -25987,7 +25999,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45261</v>
       </c>
       <c r="B229" t="n">
@@ -26031,7 +26043,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45292</v>
       </c>
       <c r="B230" t="n">
@@ -26075,7 +26087,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45323</v>
       </c>
       <c r="B231" t="n">
@@ -26119,7 +26131,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45352</v>
       </c>
       <c r="B232" t="n">
@@ -26163,7 +26175,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45383</v>
       </c>
       <c r="B233" t="n">
@@ -26207,7 +26219,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45413</v>
       </c>
       <c r="B234" t="n">
@@ -26251,7 +26263,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45444</v>
       </c>
       <c r="B235" t="n">
@@ -26295,7 +26307,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45474</v>
       </c>
       <c r="B236" t="n">
@@ -26339,7 +26351,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="B237" t="n">
@@ -26383,7 +26395,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45536</v>
       </c>
       <c r="B238" t="n">
@@ -26427,7 +26439,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45566</v>
       </c>
       <c r="B239" t="n">
@@ -26471,7 +26483,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="B240" t="n">
@@ -26515,7 +26527,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>45627</v>
       </c>
       <c r="B241" t="n">
@@ -26559,7 +26571,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>45658</v>
       </c>
       <c r="B242" t="n">
@@ -26603,7 +26615,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>45689</v>
       </c>
       <c r="B243" t="n">
@@ -26647,7 +26659,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>45717</v>
       </c>
       <c r="B244" t="n">
@@ -26691,7 +26703,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>45748</v>
       </c>
       <c r="B245" t="n">
@@ -26735,7 +26747,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="B246" t="n">
@@ -26779,7 +26791,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>45809</v>
       </c>
       <c r="B247" t="n">
@@ -26823,7 +26835,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>45839</v>
       </c>
       <c r="B248" t="n">
@@ -26867,7 +26879,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="B249" t="n">
@@ -26911,7 +26923,7 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>45901</v>
       </c>
       <c r="B250" t="n">
@@ -26955,7 +26967,7 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="1" t="n">
+      <c r="A251" s="2" t="n">
         <v>45931</v>
       </c>
       <c r="B251" t="n">
@@ -26999,7 +27011,7 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="1" t="n">
+      <c r="A252" s="2" t="n">
         <v>45962</v>
       </c>
       <c r="B252" t="n">
@@ -27043,7 +27055,7 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="1" t="n">
+      <c r="A253" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="B253" t="n">
@@ -27087,7 +27099,7 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="1" t="n">
+      <c r="A254" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B254" t="n">
@@ -27131,7 +27143,7 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="1" t="n">
+      <c r="A255" s="2" t="n">
         <v>46054</v>
       </c>
       <c r="B255" t="n">
@@ -27175,7 +27187,7 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="1" t="n">
+      <c r="A256" s="2" t="n">
         <v>46082</v>
       </c>
       <c r="B256" t="n">
@@ -27219,7 +27231,7 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="1" t="n">
+      <c r="A257" s="2" t="n">
         <v>46113</v>
       </c>
       <c r="B257" t="n">
@@ -27263,7 +27275,7 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="1" t="n">
+      <c r="A258" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="B258" t="n">
@@ -27307,7 +27319,7 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="1" t="n">
+      <c r="A259" s="2" t="n">
         <v>46174</v>
       </c>
       <c r="B259" t="n">
@@ -27365,32 +27377,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Kalem</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Endeks</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Aylık %</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Yıllık %</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Yılbaşından %</t>
         </is>

--- a/enflasyon/enflasyon.xlsx
+++ b/enflasyon/enflasyon.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E259"/>
+  <dimension ref="A1:E260"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4784,6 +4784,23 @@
       </c>
       <c r="E259" t="n">
         <v>17.75847125552932</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B260" t="n">
+        <v>132.31</v>
+      </c>
+      <c r="C260" t="n">
+        <v>1.784752673282552</v>
+      </c>
+      <c r="D260" t="n">
+        <v>31.75409679062435</v>
+      </c>
+      <c r="E260" t="n">
+        <v>19.86016871927905</v>
       </c>
     </row>
   </sheetData>
@@ -4797,7 +4814,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N259"/>
+  <dimension ref="A1:N260"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16222,6 +16239,50 @@
       </c>
       <c r="N259" t="n">
         <v>122.11</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B260" t="n">
+        <v>134.02</v>
+      </c>
+      <c r="C260" t="n">
+        <v>130.15</v>
+      </c>
+      <c r="D260" t="n">
+        <v>111.73</v>
+      </c>
+      <c r="E260" t="n">
+        <v>144.81</v>
+      </c>
+      <c r="F260" t="n">
+        <v>124.31</v>
+      </c>
+      <c r="G260" t="n">
+        <v>145.05</v>
+      </c>
+      <c r="H260" t="n">
+        <v>133.69</v>
+      </c>
+      <c r="I260" t="n">
+        <v>125.22</v>
+      </c>
+      <c r="J260" t="n">
+        <v>126.2</v>
+      </c>
+      <c r="K260" t="n">
+        <v>141.62</v>
+      </c>
+      <c r="L260" t="n">
+        <v>133.7</v>
+      </c>
+      <c r="M260" t="n">
+        <v>130.47</v>
+      </c>
+      <c r="N260" t="n">
+        <v>123.47</v>
       </c>
     </row>
   </sheetData>
@@ -16235,7 +16296,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N259"/>
+  <dimension ref="A1:N260"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27348,6 +27409,50 @@
       </c>
       <c r="N259" t="n">
         <v>22.71116817298007</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B260" t="n">
+        <v>37.53005127954092</v>
+      </c>
+      <c r="C260" t="n">
+        <v>29.38189201377268</v>
+      </c>
+      <c r="D260" t="n">
+        <v>16.47854628756089</v>
+      </c>
+      <c r="E260" t="n">
+        <v>40.32266749804405</v>
+      </c>
+      <c r="F260" t="n">
+        <v>22.40688250729537</v>
+      </c>
+      <c r="G260" t="n">
+        <v>43.89126368322292</v>
+      </c>
+      <c r="H260" t="n">
+        <v>30.83239164895124</v>
+      </c>
+      <c r="I260" t="n">
+        <v>23.96797719523978</v>
+      </c>
+      <c r="J260" t="n">
+        <v>23.35550153845947</v>
+      </c>
+      <c r="K260" t="n">
+        <v>44.18197132280049</v>
+      </c>
+      <c r="L260" t="n">
+        <v>31.65071076529042</v>
+      </c>
+      <c r="M260" t="n">
+        <v>25.64466844969539</v>
+      </c>
+      <c r="N260" t="n">
+        <v>21.73888482986941</v>
       </c>
     </row>
   </sheetData>
@@ -27408,16 +27513,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>131.89</v>
+        <v>134.02</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1670843776106823</v>
+        <v>1.614982182121483</v>
       </c>
       <c r="E2" t="n">
-        <v>35.44570668685729</v>
+        <v>37.53005127954092</v>
       </c>
       <c r="F2" t="n">
-        <v>19.89031433398294</v>
+        <v>21.82652154856619</v>
       </c>
     </row>
     <row r="3">
@@ -27432,16 +27537,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>127.68</v>
+        <v>130.15</v>
       </c>
       <c r="D3" t="n">
-        <v>3.460011344299496</v>
+        <v>1.934523809523814</v>
       </c>
       <c r="E3" t="n">
-        <v>34.15396359365354</v>
+        <v>29.38189201377268</v>
       </c>
       <c r="F3" t="n">
-        <v>14.07994837880906</v>
+        <v>16.2868521420896</v>
       </c>
     </row>
     <row r="4">
@@ -27456,16 +27561,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>116.3</v>
+        <v>111.73</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1802420393099413</v>
+        <v>-3.929492691315561</v>
       </c>
       <c r="E4" t="n">
-        <v>14.18455344206522</v>
+        <v>16.47854628756089</v>
       </c>
       <c r="F4" t="n">
-        <v>6.961654984383214</v>
+        <v>2.758604569261713</v>
       </c>
     </row>
     <row r="5">
@@ -27480,16 +27585,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>141.62</v>
+        <v>144.81</v>
       </c>
       <c r="D5" t="n">
-        <v>2.297023981508239</v>
+        <v>2.252506708092072</v>
       </c>
       <c r="E5" t="n">
-        <v>45.14201960040407</v>
+        <v>40.32266749804405</v>
       </c>
       <c r="F5" t="n">
-        <v>23.14544261226892</v>
+        <v>25.91930196781995</v>
       </c>
     </row>
     <row r="6">
@@ -27504,16 +27609,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>122.23</v>
+        <v>124.31</v>
       </c>
       <c r="D6" t="n">
-        <v>1.977306858001016</v>
+        <v>1.701709891188741</v>
       </c>
       <c r="E6" t="n">
-        <v>22.31805634064645</v>
+        <v>22.40688250729537</v>
       </c>
       <c r="F6" t="n">
-        <v>13.00830076571879</v>
+        <v>14.93137419771335</v>
       </c>
     </row>
     <row r="7">
@@ -27528,16 +27633,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>130.98</v>
+        <v>145.05</v>
       </c>
       <c r="D7" t="n">
-        <v>1.166293349810754</v>
+        <v>10.74209803023365</v>
       </c>
       <c r="E7" t="n">
-        <v>33.61899840132232</v>
+        <v>43.89126368322292</v>
       </c>
       <c r="F7" t="n">
-        <v>24.11306746232529</v>
+        <v>37.44541483745827</v>
       </c>
     </row>
     <row r="8">
@@ -27552,16 +27657,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>130.31</v>
+        <v>133.69</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.04602285801948991</v>
+        <v>2.593814749443624</v>
       </c>
       <c r="E8" t="n">
-        <v>31.15206356846376</v>
+        <v>30.83239164895124</v>
       </c>
       <c r="F8" t="n">
-        <v>20.06630393925242</v>
+        <v>23.18060143994056</v>
       </c>
     </row>
     <row r="9">
@@ -27576,16 +27681,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>122.72</v>
+        <v>125.22</v>
       </c>
       <c r="D9" t="n">
-        <v>1.867684900805178</v>
+        <v>2.037157757496733</v>
       </c>
       <c r="E9" t="n">
-        <v>25.56608020896913</v>
+        <v>23.96797719523978</v>
       </c>
       <c r="F9" t="n">
-        <v>13.352297050706</v>
+        <v>15.66146216337521</v>
       </c>
     </row>
     <row r="10">
@@ -27600,16 +27705,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>124.65</v>
+        <v>126.2</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9965969859017987</v>
+        <v>1.243481748896902</v>
       </c>
       <c r="E10" t="n">
-        <v>25.38865879601126</v>
+        <v>23.35550153845947</v>
       </c>
       <c r="F10" t="n">
-        <v>14.80696792476981</v>
+        <v>16.23457161737625</v>
       </c>
     </row>
     <row r="11">
@@ -27624,16 +27729,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>139.77</v>
+        <v>141.62</v>
       </c>
       <c r="D11" t="n">
-        <v>1.717487810203044</v>
+        <v>1.323603062173562</v>
       </c>
       <c r="E11" t="n">
-        <v>46.09946350731025</v>
+        <v>44.18197132280049</v>
       </c>
       <c r="F11" t="n">
-        <v>17.66345925047919</v>
+        <v>19.22085640017788</v>
       </c>
     </row>
     <row r="12">
@@ -27648,16 +27753,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>130.72</v>
+        <v>133.7</v>
       </c>
       <c r="D12" t="n">
-        <v>2.109045461646608</v>
+        <v>2.279681762545893</v>
       </c>
       <c r="E12" t="n">
-        <v>31.60603899994874</v>
+        <v>31.65071076529042</v>
       </c>
       <c r="F12" t="n">
-        <v>18.56064368117501</v>
+        <v>21.26344905273177</v>
       </c>
     </row>
     <row r="13">
@@ -27672,16 +27777,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>129.17</v>
+        <v>130.47</v>
       </c>
       <c r="D13" t="n">
-        <v>1.056172742919737</v>
+        <v>1.006425640628628</v>
       </c>
       <c r="E13" t="n">
-        <v>28.07046898245202</v>
+        <v>25.64466844969539</v>
       </c>
       <c r="F13" t="n">
-        <v>26.45609032403999</v>
+        <v>27.72877684119763</v>
       </c>
     </row>
     <row r="14">
@@ -27696,16 +27801,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>122.11</v>
+        <v>123.47</v>
       </c>
       <c r="D14" t="n">
-        <v>1.042614811750098</v>
+        <v>1.113749897633287</v>
       </c>
       <c r="E14" t="n">
-        <v>22.71116817298007</v>
+        <v>21.73888482986941</v>
       </c>
       <c r="F14" t="n">
-        <v>11.54462694544249</v>
+        <v>12.78695511386278</v>
       </c>
     </row>
   </sheetData>

--- a/enflasyon/enflasyon.xlsx
+++ b/enflasyon/enflasyon.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Genel" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="AltKalem_Endeks" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="AltKalem_Yillik" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="AltKalem_Ozet" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Genel" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AltKalem_Endeks" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AltKalem_Yillik" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AltKalem_Ozet" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -424,34 +436,34 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>tarih</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>endeks</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>aylik</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>yillik</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>ytd</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38353</v>
       </c>
       <c r="B2" t="n">
@@ -462,7 +474,7 @@
       <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38384</v>
       </c>
       <c r="B3" t="n">
@@ -475,7 +487,7 @@
       <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38412</v>
       </c>
       <c r="B4" t="n">
@@ -488,7 +500,7 @@
       <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38443</v>
       </c>
       <c r="B5" t="n">
@@ -501,7 +513,7 @@
       <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38473</v>
       </c>
       <c r="B6" t="n">
@@ -514,7 +526,7 @@
       <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38504</v>
       </c>
       <c r="B7" t="n">
@@ -527,7 +539,7 @@
       <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38534</v>
       </c>
       <c r="B8" t="n">
@@ -540,7 +552,7 @@
       <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38565</v>
       </c>
       <c r="B9" t="n">
@@ -553,7 +565,7 @@
       <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38596</v>
       </c>
       <c r="B10" t="n">
@@ -566,7 +578,7 @@
       <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>38626</v>
       </c>
       <c r="B11" t="n">
@@ -579,7 +591,7 @@
       <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>38657</v>
       </c>
       <c r="B12" t="n">
@@ -592,7 +604,7 @@
       <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>38687</v>
       </c>
       <c r="B13" t="n">
@@ -605,7 +617,7 @@
       <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>38718</v>
       </c>
       <c r="B14" t="n">
@@ -622,7 +634,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>38749</v>
       </c>
       <c r="B15" t="n">
@@ -639,7 +651,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>38777</v>
       </c>
       <c r="B16" t="n">
@@ -656,7 +668,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>38808</v>
       </c>
       <c r="B17" t="n">
@@ -673,7 +685,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>38838</v>
       </c>
       <c r="B18" t="n">
@@ -690,7 +702,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>38869</v>
       </c>
       <c r="B19" t="n">
@@ -707,7 +719,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>38899</v>
       </c>
       <c r="B20" t="n">
@@ -724,7 +736,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>38930</v>
       </c>
       <c r="B21" t="n">
@@ -741,7 +753,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>38961</v>
       </c>
       <c r="B22" t="n">
@@ -758,7 +770,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>38991</v>
       </c>
       <c r="B23" t="n">
@@ -775,7 +787,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39022</v>
       </c>
       <c r="B24" t="n">
@@ -792,7 +804,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39052</v>
       </c>
       <c r="B25" t="n">
@@ -809,7 +821,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39083</v>
       </c>
       <c r="B26" t="n">
@@ -826,7 +838,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39114</v>
       </c>
       <c r="B27" t="n">
@@ -843,7 +855,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39142</v>
       </c>
       <c r="B28" t="n">
@@ -860,7 +872,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39173</v>
       </c>
       <c r="B29" t="n">
@@ -877,7 +889,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39203</v>
       </c>
       <c r="B30" t="n">
@@ -894,7 +906,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39234</v>
       </c>
       <c r="B31" t="n">
@@ -911,7 +923,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39264</v>
       </c>
       <c r="B32" t="n">
@@ -928,7 +940,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39295</v>
       </c>
       <c r="B33" t="n">
@@ -945,7 +957,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39326</v>
       </c>
       <c r="B34" t="n">
@@ -962,7 +974,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39356</v>
       </c>
       <c r="B35" t="n">
@@ -979,7 +991,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39387</v>
       </c>
       <c r="B36" t="n">
@@ -996,7 +1008,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39417</v>
       </c>
       <c r="B37" t="n">
@@ -1013,7 +1025,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39448</v>
       </c>
       <c r="B38" t="n">
@@ -1030,7 +1042,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39479</v>
       </c>
       <c r="B39" t="n">
@@ -1047,7 +1059,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39508</v>
       </c>
       <c r="B40" t="n">
@@ -1064,7 +1076,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39539</v>
       </c>
       <c r="B41" t="n">
@@ -1081,7 +1093,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39569</v>
       </c>
       <c r="B42" t="n">
@@ -1098,7 +1110,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39600</v>
       </c>
       <c r="B43" t="n">
@@ -1115,7 +1127,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>39630</v>
       </c>
       <c r="B44" t="n">
@@ -1132,7 +1144,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>39661</v>
       </c>
       <c r="B45" t="n">
@@ -1149,7 +1161,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>39692</v>
       </c>
       <c r="B46" t="n">
@@ -1166,7 +1178,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>39722</v>
       </c>
       <c r="B47" t="n">
@@ -1183,7 +1195,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>39753</v>
       </c>
       <c r="B48" t="n">
@@ -1200,7 +1212,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>39783</v>
       </c>
       <c r="B49" t="n">
@@ -1217,7 +1229,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>39814</v>
       </c>
       <c r="B50" t="n">
@@ -1234,7 +1246,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>39845</v>
       </c>
       <c r="B51" t="n">
@@ -1251,7 +1263,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>39873</v>
       </c>
       <c r="B52" t="n">
@@ -1268,7 +1280,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>39904</v>
       </c>
       <c r="B53" t="n">
@@ -1285,7 +1297,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>39934</v>
       </c>
       <c r="B54" t="n">
@@ -1302,7 +1314,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>39965</v>
       </c>
       <c r="B55" t="n">
@@ -1319,7 +1331,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>39995</v>
       </c>
       <c r="B56" t="n">
@@ -1336,7 +1348,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40026</v>
       </c>
       <c r="B57" t="n">
@@ -1353,7 +1365,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40057</v>
       </c>
       <c r="B58" t="n">
@@ -1370,7 +1382,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40087</v>
       </c>
       <c r="B59" t="n">
@@ -1387,7 +1399,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40118</v>
       </c>
       <c r="B60" t="n">
@@ -1404,7 +1416,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40148</v>
       </c>
       <c r="B61" t="n">
@@ -1421,7 +1433,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40179</v>
       </c>
       <c r="B62" t="n">
@@ -1438,7 +1450,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40210</v>
       </c>
       <c r="B63" t="n">
@@ -1455,7 +1467,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40238</v>
       </c>
       <c r="B64" t="n">
@@ -1472,7 +1484,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40269</v>
       </c>
       <c r="B65" t="n">
@@ -1489,7 +1501,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40299</v>
       </c>
       <c r="B66" t="n">
@@ -1506,7 +1518,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40330</v>
       </c>
       <c r="B67" t="n">
@@ -1523,7 +1535,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40360</v>
       </c>
       <c r="B68" t="n">
@@ -1540,7 +1552,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40391</v>
       </c>
       <c r="B69" t="n">
@@ -1557,7 +1569,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40422</v>
       </c>
       <c r="B70" t="n">
@@ -1574,7 +1586,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40452</v>
       </c>
       <c r="B71" t="n">
@@ -1591,7 +1603,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40483</v>
       </c>
       <c r="B72" t="n">
@@ -1608,7 +1620,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40513</v>
       </c>
       <c r="B73" t="n">
@@ -1625,7 +1637,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40544</v>
       </c>
       <c r="B74" t="n">
@@ -1642,7 +1654,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40575</v>
       </c>
       <c r="B75" t="n">
@@ -1659,7 +1671,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40603</v>
       </c>
       <c r="B76" t="n">
@@ -1676,7 +1688,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>40634</v>
       </c>
       <c r="B77" t="n">
@@ -1693,7 +1705,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>40664</v>
       </c>
       <c r="B78" t="n">
@@ -1710,7 +1722,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>40695</v>
       </c>
       <c r="B79" t="n">
@@ -1727,7 +1739,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>40725</v>
       </c>
       <c r="B80" t="n">
@@ -1744,7 +1756,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>40756</v>
       </c>
       <c r="B81" t="n">
@@ -1761,7 +1773,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>40787</v>
       </c>
       <c r="B82" t="n">
@@ -1778,7 +1790,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>40817</v>
       </c>
       <c r="B83" t="n">
@@ -1795,7 +1807,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>40848</v>
       </c>
       <c r="B84" t="n">
@@ -1812,7 +1824,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>40878</v>
       </c>
       <c r="B85" t="n">
@@ -1829,7 +1841,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>40909</v>
       </c>
       <c r="B86" t="n">
@@ -1846,7 +1858,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>40940</v>
       </c>
       <c r="B87" t="n">
@@ -1863,7 +1875,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>40969</v>
       </c>
       <c r="B88" t="n">
@@ -1880,7 +1892,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41000</v>
       </c>
       <c r="B89" t="n">
@@ -1897,7 +1909,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41030</v>
       </c>
       <c r="B90" t="n">
@@ -1914,7 +1926,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41061</v>
       </c>
       <c r="B91" t="n">
@@ -1931,7 +1943,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41091</v>
       </c>
       <c r="B92" t="n">
@@ -1948,7 +1960,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41122</v>
       </c>
       <c r="B93" t="n">
@@ -1965,7 +1977,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41153</v>
       </c>
       <c r="B94" t="n">
@@ -1982,7 +1994,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41183</v>
       </c>
       <c r="B95" t="n">
@@ -1999,7 +2011,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41214</v>
       </c>
       <c r="B96" t="n">
@@ -2016,7 +2028,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41244</v>
       </c>
       <c r="B97" t="n">
@@ -2033,7 +2045,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41275</v>
       </c>
       <c r="B98" t="n">
@@ -2050,7 +2062,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41306</v>
       </c>
       <c r="B99" t="n">
@@ -2067,7 +2079,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41334</v>
       </c>
       <c r="B100" t="n">
@@ -2084,7 +2096,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41365</v>
       </c>
       <c r="B101" t="n">
@@ -2101,7 +2113,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41395</v>
       </c>
       <c r="B102" t="n">
@@ -2118,7 +2130,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41426</v>
       </c>
       <c r="B103" t="n">
@@ -2135,7 +2147,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41456</v>
       </c>
       <c r="B104" t="n">
@@ -2152,7 +2164,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41487</v>
       </c>
       <c r="B105" t="n">
@@ -2169,7 +2181,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41518</v>
       </c>
       <c r="B106" t="n">
@@ -2186,7 +2198,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41548</v>
       </c>
       <c r="B107" t="n">
@@ -2203,7 +2215,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41579</v>
       </c>
       <c r="B108" t="n">
@@ -2220,7 +2232,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>41609</v>
       </c>
       <c r="B109" t="n">
@@ -2237,7 +2249,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>41640</v>
       </c>
       <c r="B110" t="n">
@@ -2254,7 +2266,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>41671</v>
       </c>
       <c r="B111" t="n">
@@ -2271,7 +2283,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>41699</v>
       </c>
       <c r="B112" t="n">
@@ -2288,7 +2300,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>41730</v>
       </c>
       <c r="B113" t="n">
@@ -2305,7 +2317,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>41760</v>
       </c>
       <c r="B114" t="n">
@@ -2322,7 +2334,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>41791</v>
       </c>
       <c r="B115" t="n">
@@ -2339,7 +2351,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>41821</v>
       </c>
       <c r="B116" t="n">
@@ -2356,7 +2368,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>41852</v>
       </c>
       <c r="B117" t="n">
@@ -2373,7 +2385,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>41883</v>
       </c>
       <c r="B118" t="n">
@@ -2390,7 +2402,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>41913</v>
       </c>
       <c r="B119" t="n">
@@ -2407,7 +2419,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>41944</v>
       </c>
       <c r="B120" t="n">
@@ -2424,7 +2436,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>41974</v>
       </c>
       <c r="B121" t="n">
@@ -2441,7 +2453,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42005</v>
       </c>
       <c r="B122" t="n">
@@ -2458,7 +2470,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42036</v>
       </c>
       <c r="B123" t="n">
@@ -2475,7 +2487,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42064</v>
       </c>
       <c r="B124" t="n">
@@ -2492,7 +2504,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42095</v>
       </c>
       <c r="B125" t="n">
@@ -2509,7 +2521,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42125</v>
       </c>
       <c r="B126" t="n">
@@ -2526,7 +2538,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42156</v>
       </c>
       <c r="B127" t="n">
@@ -2543,7 +2555,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42186</v>
       </c>
       <c r="B128" t="n">
@@ -2560,7 +2572,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42217</v>
       </c>
       <c r="B129" t="n">
@@ -2577,7 +2589,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42248</v>
       </c>
       <c r="B130" t="n">
@@ -2594,7 +2606,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42278</v>
       </c>
       <c r="B131" t="n">
@@ -2611,7 +2623,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42309</v>
       </c>
       <c r="B132" t="n">
@@ -2628,7 +2640,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42339</v>
       </c>
       <c r="B133" t="n">
@@ -2645,7 +2657,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42370</v>
       </c>
       <c r="B134" t="n">
@@ -2662,7 +2674,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42401</v>
       </c>
       <c r="B135" t="n">
@@ -2679,7 +2691,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42430</v>
       </c>
       <c r="B136" t="n">
@@ -2696,7 +2708,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42461</v>
       </c>
       <c r="B137" t="n">
@@ -2713,7 +2725,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42491</v>
       </c>
       <c r="B138" t="n">
@@ -2730,7 +2742,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42522</v>
       </c>
       <c r="B139" t="n">
@@ -2747,7 +2759,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42552</v>
       </c>
       <c r="B140" t="n">
@@ -2764,7 +2776,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42583</v>
       </c>
       <c r="B141" t="n">
@@ -2781,7 +2793,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>42614</v>
       </c>
       <c r="B142" t="n">
@@ -2798,7 +2810,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>42644</v>
       </c>
       <c r="B143" t="n">
@@ -2815,7 +2827,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>42675</v>
       </c>
       <c r="B144" t="n">
@@ -2832,7 +2844,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>42705</v>
       </c>
       <c r="B145" t="n">
@@ -2849,7 +2861,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>42736</v>
       </c>
       <c r="B146" t="n">
@@ -2866,7 +2878,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>42767</v>
       </c>
       <c r="B147" t="n">
@@ -2883,7 +2895,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>42795</v>
       </c>
       <c r="B148" t="n">
@@ -2900,7 +2912,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>42826</v>
       </c>
       <c r="B149" t="n">
@@ -2917,7 +2929,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>42856</v>
       </c>
       <c r="B150" t="n">
@@ -2934,7 +2946,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>42887</v>
       </c>
       <c r="B151" t="n">
@@ -2951,7 +2963,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>42917</v>
       </c>
       <c r="B152" t="n">
@@ -2968,7 +2980,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>42948</v>
       </c>
       <c r="B153" t="n">
@@ -2985,7 +2997,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>42979</v>
       </c>
       <c r="B154" t="n">
@@ -3002,7 +3014,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43009</v>
       </c>
       <c r="B155" t="n">
@@ -3019,7 +3031,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43040</v>
       </c>
       <c r="B156" t="n">
@@ -3036,7 +3048,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43070</v>
       </c>
       <c r="B157" t="n">
@@ -3053,7 +3065,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43101</v>
       </c>
       <c r="B158" t="n">
@@ -3070,7 +3082,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43132</v>
       </c>
       <c r="B159" t="n">
@@ -3087,7 +3099,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43160</v>
       </c>
       <c r="B160" t="n">
@@ -3104,7 +3116,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43191</v>
       </c>
       <c r="B161" t="n">
@@ -3121,7 +3133,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43221</v>
       </c>
       <c r="B162" t="n">
@@ -3138,7 +3150,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43252</v>
       </c>
       <c r="B163" t="n">
@@ -3155,7 +3167,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43282</v>
       </c>
       <c r="B164" t="n">
@@ -3172,7 +3184,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43313</v>
       </c>
       <c r="B165" t="n">
@@ -3189,7 +3201,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43344</v>
       </c>
       <c r="B166" t="n">
@@ -3206,7 +3218,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43374</v>
       </c>
       <c r="B167" t="n">
@@ -3223,7 +3235,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43405</v>
       </c>
       <c r="B168" t="n">
@@ -3240,7 +3252,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43435</v>
       </c>
       <c r="B169" t="n">
@@ -3257,7 +3269,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43466</v>
       </c>
       <c r="B170" t="n">
@@ -3274,7 +3286,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43497</v>
       </c>
       <c r="B171" t="n">
@@ -3291,7 +3303,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43525</v>
       </c>
       <c r="B172" t="n">
@@ -3308,7 +3320,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43556</v>
       </c>
       <c r="B173" t="n">
@@ -3325,7 +3337,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43586</v>
       </c>
       <c r="B174" t="n">
@@ -3342,7 +3354,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>43617</v>
       </c>
       <c r="B175" t="n">
@@ -3359,7 +3371,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>43647</v>
       </c>
       <c r="B176" t="n">
@@ -3376,7 +3388,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>43678</v>
       </c>
       <c r="B177" t="n">
@@ -3393,7 +3405,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>43709</v>
       </c>
       <c r="B178" t="n">
@@ -3410,7 +3422,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>43739</v>
       </c>
       <c r="B179" t="n">
@@ -3427,7 +3439,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>43770</v>
       </c>
       <c r="B180" t="n">
@@ -3444,7 +3456,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>43800</v>
       </c>
       <c r="B181" t="n">
@@ -3461,7 +3473,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>43831</v>
       </c>
       <c r="B182" t="n">
@@ -3478,7 +3490,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>43862</v>
       </c>
       <c r="B183" t="n">
@@ -3495,7 +3507,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>43891</v>
       </c>
       <c r="B184" t="n">
@@ -3512,7 +3524,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>43922</v>
       </c>
       <c r="B185" t="n">
@@ -3529,7 +3541,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>43952</v>
       </c>
       <c r="B186" t="n">
@@ -3546,7 +3558,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>43983</v>
       </c>
       <c r="B187" t="n">
@@ -3563,7 +3575,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44013</v>
       </c>
       <c r="B188" t="n">
@@ -3580,7 +3592,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44044</v>
       </c>
       <c r="B189" t="n">
@@ -3597,7 +3609,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44075</v>
       </c>
       <c r="B190" t="n">
@@ -3614,7 +3626,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44105</v>
       </c>
       <c r="B191" t="n">
@@ -3631,7 +3643,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44136</v>
       </c>
       <c r="B192" t="n">
@@ -3648,7 +3660,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44166</v>
       </c>
       <c r="B193" t="n">
@@ -3665,7 +3677,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44197</v>
       </c>
       <c r="B194" t="n">
@@ -3682,7 +3694,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44228</v>
       </c>
       <c r="B195" t="n">
@@ -3699,7 +3711,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44256</v>
       </c>
       <c r="B196" t="n">
@@ -3716,7 +3728,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44287</v>
       </c>
       <c r="B197" t="n">
@@ -3733,7 +3745,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44317</v>
       </c>
       <c r="B198" t="n">
@@ -3750,7 +3762,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44348</v>
       </c>
       <c r="B199" t="n">
@@ -3767,7 +3779,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44378</v>
       </c>
       <c r="B200" t="n">
@@ -3784,7 +3796,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44409</v>
       </c>
       <c r="B201" t="n">
@@ -3801,7 +3813,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44440</v>
       </c>
       <c r="B202" t="n">
@@ -3818,7 +3830,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44470</v>
       </c>
       <c r="B203" t="n">
@@ -3835,7 +3847,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44501</v>
       </c>
       <c r="B204" t="n">
@@ -3852,7 +3864,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44531</v>
       </c>
       <c r="B205" t="n">
@@ -3869,7 +3881,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44562</v>
       </c>
       <c r="B206" t="n">
@@ -3886,7 +3898,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44593</v>
       </c>
       <c r="B207" t="n">
@@ -3903,7 +3915,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>44621</v>
       </c>
       <c r="B208" t="n">
@@ -3920,7 +3932,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>44652</v>
       </c>
       <c r="B209" t="n">
@@ -3937,7 +3949,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>44682</v>
       </c>
       <c r="B210" t="n">
@@ -3954,7 +3966,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>44713</v>
       </c>
       <c r="B211" t="n">
@@ -3971,7 +3983,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>44743</v>
       </c>
       <c r="B212" t="n">
@@ -3988,7 +4000,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>44774</v>
       </c>
       <c r="B213" t="n">
@@ -4005,7 +4017,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>44805</v>
       </c>
       <c r="B214" t="n">
@@ -4022,7 +4034,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>44835</v>
       </c>
       <c r="B215" t="n">
@@ -4039,7 +4051,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>44866</v>
       </c>
       <c r="B216" t="n">
@@ -4056,7 +4068,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>44896</v>
       </c>
       <c r="B217" t="n">
@@ -4073,7 +4085,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>44927</v>
       </c>
       <c r="B218" t="n">
@@ -4090,7 +4102,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>44958</v>
       </c>
       <c r="B219" t="n">
@@ -4107,7 +4119,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>44986</v>
       </c>
       <c r="B220" t="n">
@@ -4124,7 +4136,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45017</v>
       </c>
       <c r="B221" t="n">
@@ -4141,7 +4153,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45047</v>
       </c>
       <c r="B222" t="n">
@@ -4158,7 +4170,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45078</v>
       </c>
       <c r="B223" t="n">
@@ -4175,7 +4187,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45108</v>
       </c>
       <c r="B224" t="n">
@@ -4192,7 +4204,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45139</v>
       </c>
       <c r="B225" t="n">
@@ -4209,7 +4221,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45170</v>
       </c>
       <c r="B226" t="n">
@@ -4226,7 +4238,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45200</v>
       </c>
       <c r="B227" t="n">
@@ -4243,7 +4255,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45231</v>
       </c>
       <c r="B228" t="n">
@@ -4260,7 +4272,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45261</v>
       </c>
       <c r="B229" t="n">
@@ -4277,7 +4289,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45292</v>
       </c>
       <c r="B230" t="n">
@@ -4294,7 +4306,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45323</v>
       </c>
       <c r="B231" t="n">
@@ -4311,7 +4323,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45352</v>
       </c>
       <c r="B232" t="n">
@@ -4328,7 +4340,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45383</v>
       </c>
       <c r="B233" t="n">
@@ -4345,7 +4357,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45413</v>
       </c>
       <c r="B234" t="n">
@@ -4362,7 +4374,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45444</v>
       </c>
       <c r="B235" t="n">
@@ -4379,7 +4391,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45474</v>
       </c>
       <c r="B236" t="n">
@@ -4396,7 +4408,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="B237" t="n">
@@ -4413,7 +4425,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45536</v>
       </c>
       <c r="B238" t="n">
@@ -4430,7 +4442,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45566</v>
       </c>
       <c r="B239" t="n">
@@ -4447,7 +4459,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="B240" t="n">
@@ -4464,7 +4476,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>45627</v>
       </c>
       <c r="B241" t="n">
@@ -4481,7 +4493,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>45658</v>
       </c>
       <c r="B242" t="n">
@@ -4498,7 +4510,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>45689</v>
       </c>
       <c r="B243" t="n">
@@ -4515,7 +4527,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>45717</v>
       </c>
       <c r="B244" t="n">
@@ -4532,7 +4544,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>45748</v>
       </c>
       <c r="B245" t="n">
@@ -4549,7 +4561,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="B246" t="n">
@@ -4566,7 +4578,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>45809</v>
       </c>
       <c r="B247" t="n">
@@ -4583,7 +4595,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>45839</v>
       </c>
       <c r="B248" t="n">
@@ -4600,7 +4612,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="B249" t="n">
@@ -4617,7 +4629,7 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>45901</v>
       </c>
       <c r="B250" t="n">
@@ -4634,7 +4646,7 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="1" t="n">
+      <c r="A251" s="2" t="n">
         <v>45931</v>
       </c>
       <c r="B251" t="n">
@@ -4651,7 +4663,7 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="1" t="n">
+      <c r="A252" s="2" t="n">
         <v>45962</v>
       </c>
       <c r="B252" t="n">
@@ -4668,7 +4680,7 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="1" t="n">
+      <c r="A253" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="B253" t="n">
@@ -4685,7 +4697,7 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="1" t="n">
+      <c r="A254" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B254" t="n">
@@ -4702,7 +4714,7 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="1" t="n">
+      <c r="A255" s="2" t="n">
         <v>46054</v>
       </c>
       <c r="B255" t="n">
@@ -4719,7 +4731,7 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="1" t="n">
+      <c r="A256" s="2" t="n">
         <v>46082</v>
       </c>
       <c r="B256" t="n">
@@ -4736,7 +4748,7 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="1" t="n">
+      <c r="A257" s="2" t="n">
         <v>46113</v>
       </c>
       <c r="B257" t="n">
@@ -4753,7 +4765,7 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="1" t="n">
+      <c r="A258" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="B258" t="n">
@@ -4770,7 +4782,7 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="1" t="n">
+      <c r="A259" s="2" t="n">
         <v>46174</v>
       </c>
       <c r="B259" t="n">
@@ -4787,7 +4799,7 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="1" t="n">
+      <c r="A260" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="B260" t="n">
@@ -4818,79 +4830,79 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>tarih</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>01. Gıda Ve Alkolsüz İçecekler</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>02. Alkollü İçecekler, Tütün Ve Tütün Ürünleri</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>03. Giyim Ve Ayakkabı</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>04. Konut, Su, Elektrik, Gaz Ve Diğer Yakıtlar</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>05. Mobilya, Mefruşat Ve Evde Kullanılan Ekipmanlar İle Rutin Ev Bakım Ve Onarımı</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>06. Sağlık</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>07. Ulaştırma</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>08. Bilgi Ve İletişim</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>09. Eğlence, Dinlence, Spor Ve Kültür</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>10. Eğitim Hizmetleri</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>11. Lokantalar Ve Konaklama Hizmetleri</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>12. Sigorta Ve Finansal Hizmetler</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>13. Kişisel Bakım, Sosyal Koruma Ve Çeşitli Mal Ve Hizmetler</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38353</v>
       </c>
       <c r="B2" t="n">
@@ -4934,7 +4946,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38384</v>
       </c>
       <c r="B3" t="n">
@@ -4978,7 +4990,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38412</v>
       </c>
       <c r="B4" t="n">
@@ -5022,7 +5034,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38443</v>
       </c>
       <c r="B5" t="n">
@@ -5066,7 +5078,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38473</v>
       </c>
       <c r="B6" t="n">
@@ -5110,7 +5122,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38504</v>
       </c>
       <c r="B7" t="n">
@@ -5154,7 +5166,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38534</v>
       </c>
       <c r="B8" t="n">
@@ -5198,7 +5210,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38565</v>
       </c>
       <c r="B9" t="n">
@@ -5242,7 +5254,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38596</v>
       </c>
       <c r="B10" t="n">
@@ -5286,7 +5298,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>38626</v>
       </c>
       <c r="B11" t="n">
@@ -5330,7 +5342,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>38657</v>
       </c>
       <c r="B12" t="n">
@@ -5374,7 +5386,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>38687</v>
       </c>
       <c r="B13" t="n">
@@ -5418,7 +5430,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>38718</v>
       </c>
       <c r="B14" t="n">
@@ -5462,7 +5474,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>38749</v>
       </c>
       <c r="B15" t="n">
@@ -5506,7 +5518,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>38777</v>
       </c>
       <c r="B16" t="n">
@@ -5550,7 +5562,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>38808</v>
       </c>
       <c r="B17" t="n">
@@ -5594,7 +5606,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>38838</v>
       </c>
       <c r="B18" t="n">
@@ -5638,7 +5650,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>38869</v>
       </c>
       <c r="B19" t="n">
@@ -5682,7 +5694,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>38899</v>
       </c>
       <c r="B20" t="n">
@@ -5726,7 +5738,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>38930</v>
       </c>
       <c r="B21" t="n">
@@ -5770,7 +5782,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>38961</v>
       </c>
       <c r="B22" t="n">
@@ -5814,7 +5826,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>38991</v>
       </c>
       <c r="B23" t="n">
@@ -5858,7 +5870,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39022</v>
       </c>
       <c r="B24" t="n">
@@ -5902,7 +5914,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39052</v>
       </c>
       <c r="B25" t="n">
@@ -5946,7 +5958,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39083</v>
       </c>
       <c r="B26" t="n">
@@ -5990,7 +6002,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39114</v>
       </c>
       <c r="B27" t="n">
@@ -6034,7 +6046,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39142</v>
       </c>
       <c r="B28" t="n">
@@ -6078,7 +6090,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39173</v>
       </c>
       <c r="B29" t="n">
@@ -6122,7 +6134,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39203</v>
       </c>
       <c r="B30" t="n">
@@ -6166,7 +6178,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39234</v>
       </c>
       <c r="B31" t="n">
@@ -6210,7 +6222,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39264</v>
       </c>
       <c r="B32" t="n">
@@ -6254,7 +6266,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39295</v>
       </c>
       <c r="B33" t="n">
@@ -6298,7 +6310,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39326</v>
       </c>
       <c r="B34" t="n">
@@ -6342,7 +6354,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39356</v>
       </c>
       <c r="B35" t="n">
@@ -6386,7 +6398,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39387</v>
       </c>
       <c r="B36" t="n">
@@ -6430,7 +6442,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39417</v>
       </c>
       <c r="B37" t="n">
@@ -6474,7 +6486,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39448</v>
       </c>
       <c r="B38" t="n">
@@ -6518,7 +6530,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39479</v>
       </c>
       <c r="B39" t="n">
@@ -6562,7 +6574,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39508</v>
       </c>
       <c r="B40" t="n">
@@ -6606,7 +6618,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39539</v>
       </c>
       <c r="B41" t="n">
@@ -6650,7 +6662,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39569</v>
       </c>
       <c r="B42" t="n">
@@ -6694,7 +6706,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39600</v>
       </c>
       <c r="B43" t="n">
@@ -6738,7 +6750,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>39630</v>
       </c>
       <c r="B44" t="n">
@@ -6782,7 +6794,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>39661</v>
       </c>
       <c r="B45" t="n">
@@ -6826,7 +6838,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>39692</v>
       </c>
       <c r="B46" t="n">
@@ -6870,7 +6882,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>39722</v>
       </c>
       <c r="B47" t="n">
@@ -6914,7 +6926,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>39753</v>
       </c>
       <c r="B48" t="n">
@@ -6958,7 +6970,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>39783</v>
       </c>
       <c r="B49" t="n">
@@ -7002,7 +7014,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>39814</v>
       </c>
       <c r="B50" t="n">
@@ -7046,7 +7058,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>39845</v>
       </c>
       <c r="B51" t="n">
@@ -7090,7 +7102,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>39873</v>
       </c>
       <c r="B52" t="n">
@@ -7134,7 +7146,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>39904</v>
       </c>
       <c r="B53" t="n">
@@ -7178,7 +7190,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>39934</v>
       </c>
       <c r="B54" t="n">
@@ -7222,7 +7234,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>39965</v>
       </c>
       <c r="B55" t="n">
@@ -7266,7 +7278,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>39995</v>
       </c>
       <c r="B56" t="n">
@@ -7310,7 +7322,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40026</v>
       </c>
       <c r="B57" t="n">
@@ -7354,7 +7366,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40057</v>
       </c>
       <c r="B58" t="n">
@@ -7398,7 +7410,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40087</v>
       </c>
       <c r="B59" t="n">
@@ -7442,7 +7454,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40118</v>
       </c>
       <c r="B60" t="n">
@@ -7486,7 +7498,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40148</v>
       </c>
       <c r="B61" t="n">
@@ -7530,7 +7542,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40179</v>
       </c>
       <c r="B62" t="n">
@@ -7574,7 +7586,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40210</v>
       </c>
       <c r="B63" t="n">
@@ -7618,7 +7630,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40238</v>
       </c>
       <c r="B64" t="n">
@@ -7662,7 +7674,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40269</v>
       </c>
       <c r="B65" t="n">
@@ -7706,7 +7718,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40299</v>
       </c>
       <c r="B66" t="n">
@@ -7750,7 +7762,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40330</v>
       </c>
       <c r="B67" t="n">
@@ -7794,7 +7806,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40360</v>
       </c>
       <c r="B68" t="n">
@@ -7838,7 +7850,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40391</v>
       </c>
       <c r="B69" t="n">
@@ -7882,7 +7894,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40422</v>
       </c>
       <c r="B70" t="n">
@@ -7926,7 +7938,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40452</v>
       </c>
       <c r="B71" t="n">
@@ -7970,7 +7982,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40483</v>
       </c>
       <c r="B72" t="n">
@@ -8014,7 +8026,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40513</v>
       </c>
       <c r="B73" t="n">
@@ -8058,7 +8070,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40544</v>
       </c>
       <c r="B74" t="n">
@@ -8102,7 +8114,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40575</v>
       </c>
       <c r="B75" t="n">
@@ -8146,7 +8158,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40603</v>
       </c>
       <c r="B76" t="n">
@@ -8190,7 +8202,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>40634</v>
       </c>
       <c r="B77" t="n">
@@ -8234,7 +8246,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>40664</v>
       </c>
       <c r="B78" t="n">
@@ -8278,7 +8290,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>40695</v>
       </c>
       <c r="B79" t="n">
@@ -8322,7 +8334,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>40725</v>
       </c>
       <c r="B80" t="n">
@@ -8366,7 +8378,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>40756</v>
       </c>
       <c r="B81" t="n">
@@ -8410,7 +8422,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>40787</v>
       </c>
       <c r="B82" t="n">
@@ -8454,7 +8466,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>40817</v>
       </c>
       <c r="B83" t="n">
@@ -8498,7 +8510,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>40848</v>
       </c>
       <c r="B84" t="n">
@@ -8542,7 +8554,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>40878</v>
       </c>
       <c r="B85" t="n">
@@ -8586,7 +8598,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>40909</v>
       </c>
       <c r="B86" t="n">
@@ -8630,7 +8642,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>40940</v>
       </c>
       <c r="B87" t="n">
@@ -8674,7 +8686,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>40969</v>
       </c>
       <c r="B88" t="n">
@@ -8718,7 +8730,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41000</v>
       </c>
       <c r="B89" t="n">
@@ -8762,7 +8774,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41030</v>
       </c>
       <c r="B90" t="n">
@@ -8806,7 +8818,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41061</v>
       </c>
       <c r="B91" t="n">
@@ -8850,7 +8862,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41091</v>
       </c>
       <c r="B92" t="n">
@@ -8894,7 +8906,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41122</v>
       </c>
       <c r="B93" t="n">
@@ -8938,7 +8950,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41153</v>
       </c>
       <c r="B94" t="n">
@@ -8982,7 +8994,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41183</v>
       </c>
       <c r="B95" t="n">
@@ -9026,7 +9038,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41214</v>
       </c>
       <c r="B96" t="n">
@@ -9070,7 +9082,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41244</v>
       </c>
       <c r="B97" t="n">
@@ -9114,7 +9126,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41275</v>
       </c>
       <c r="B98" t="n">
@@ -9158,7 +9170,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41306</v>
       </c>
       <c r="B99" t="n">
@@ -9202,7 +9214,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41334</v>
       </c>
       <c r="B100" t="n">
@@ -9246,7 +9258,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41365</v>
       </c>
       <c r="B101" t="n">
@@ -9290,7 +9302,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41395</v>
       </c>
       <c r="B102" t="n">
@@ -9334,7 +9346,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41426</v>
       </c>
       <c r="B103" t="n">
@@ -9378,7 +9390,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41456</v>
       </c>
       <c r="B104" t="n">
@@ -9422,7 +9434,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41487</v>
       </c>
       <c r="B105" t="n">
@@ -9466,7 +9478,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41518</v>
       </c>
       <c r="B106" t="n">
@@ -9510,7 +9522,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41548</v>
       </c>
       <c r="B107" t="n">
@@ -9554,7 +9566,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41579</v>
       </c>
       <c r="B108" t="n">
@@ -9598,7 +9610,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>41609</v>
       </c>
       <c r="B109" t="n">
@@ -9642,7 +9654,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>41640</v>
       </c>
       <c r="B110" t="n">
@@ -9686,7 +9698,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>41671</v>
       </c>
       <c r="B111" t="n">
@@ -9730,7 +9742,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>41699</v>
       </c>
       <c r="B112" t="n">
@@ -9774,7 +9786,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>41730</v>
       </c>
       <c r="B113" t="n">
@@ -9818,7 +9830,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>41760</v>
       </c>
       <c r="B114" t="n">
@@ -9862,7 +9874,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>41791</v>
       </c>
       <c r="B115" t="n">
@@ -9906,7 +9918,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>41821</v>
       </c>
       <c r="B116" t="n">
@@ -9950,7 +9962,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>41852</v>
       </c>
       <c r="B117" t="n">
@@ -9994,7 +10006,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>41883</v>
       </c>
       <c r="B118" t="n">
@@ -10038,7 +10050,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>41913</v>
       </c>
       <c r="B119" t="n">
@@ -10082,7 +10094,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>41944</v>
       </c>
       <c r="B120" t="n">
@@ -10126,7 +10138,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>41974</v>
       </c>
       <c r="B121" t="n">
@@ -10170,7 +10182,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42005</v>
       </c>
       <c r="B122" t="n">
@@ -10214,7 +10226,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42036</v>
       </c>
       <c r="B123" t="n">
@@ -10258,7 +10270,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42064</v>
       </c>
       <c r="B124" t="n">
@@ -10302,7 +10314,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42095</v>
       </c>
       <c r="B125" t="n">
@@ -10346,7 +10358,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42125</v>
       </c>
       <c r="B126" t="n">
@@ -10390,7 +10402,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42156</v>
       </c>
       <c r="B127" t="n">
@@ -10434,7 +10446,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42186</v>
       </c>
       <c r="B128" t="n">
@@ -10478,7 +10490,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42217</v>
       </c>
       <c r="B129" t="n">
@@ -10522,7 +10534,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42248</v>
       </c>
       <c r="B130" t="n">
@@ -10566,7 +10578,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42278</v>
       </c>
       <c r="B131" t="n">
@@ -10610,7 +10622,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42309</v>
       </c>
       <c r="B132" t="n">
@@ -10654,7 +10666,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42339</v>
       </c>
       <c r="B133" t="n">
@@ -10698,7 +10710,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42370</v>
       </c>
       <c r="B134" t="n">
@@ -10742,7 +10754,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42401</v>
       </c>
       <c r="B135" t="n">
@@ -10786,7 +10798,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42430</v>
       </c>
       <c r="B136" t="n">
@@ -10830,7 +10842,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42461</v>
       </c>
       <c r="B137" t="n">
@@ -10874,7 +10886,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42491</v>
       </c>
       <c r="B138" t="n">
@@ -10918,7 +10930,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42522</v>
       </c>
       <c r="B139" t="n">
@@ -10962,7 +10974,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42552</v>
       </c>
       <c r="B140" t="n">
@@ -11006,7 +11018,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42583</v>
       </c>
       <c r="B141" t="n">
@@ -11050,7 +11062,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>42614</v>
       </c>
       <c r="B142" t="n">
@@ -11094,7 +11106,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>42644</v>
       </c>
       <c r="B143" t="n">
@@ -11138,7 +11150,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>42675</v>
       </c>
       <c r="B144" t="n">
@@ -11182,7 +11194,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>42705</v>
       </c>
       <c r="B145" t="n">
@@ -11226,7 +11238,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>42736</v>
       </c>
       <c r="B146" t="n">
@@ -11270,7 +11282,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>42767</v>
       </c>
       <c r="B147" t="n">
@@ -11314,7 +11326,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>42795</v>
       </c>
       <c r="B148" t="n">
@@ -11358,7 +11370,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>42826</v>
       </c>
       <c r="B149" t="n">
@@ -11402,7 +11414,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>42856</v>
       </c>
       <c r="B150" t="n">
@@ -11446,7 +11458,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>42887</v>
       </c>
       <c r="B151" t="n">
@@ -11490,7 +11502,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>42917</v>
       </c>
       <c r="B152" t="n">
@@ -11534,7 +11546,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>42948</v>
       </c>
       <c r="B153" t="n">
@@ -11578,7 +11590,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>42979</v>
       </c>
       <c r="B154" t="n">
@@ -11622,7 +11634,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43009</v>
       </c>
       <c r="B155" t="n">
@@ -11666,7 +11678,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43040</v>
       </c>
       <c r="B156" t="n">
@@ -11710,7 +11722,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43070</v>
       </c>
       <c r="B157" t="n">
@@ -11754,7 +11766,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43101</v>
       </c>
       <c r="B158" t="n">
@@ -11798,7 +11810,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43132</v>
       </c>
       <c r="B159" t="n">
@@ -11842,7 +11854,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43160</v>
       </c>
       <c r="B160" t="n">
@@ -11886,7 +11898,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43191</v>
       </c>
       <c r="B161" t="n">
@@ -11930,7 +11942,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43221</v>
       </c>
       <c r="B162" t="n">
@@ -11974,7 +11986,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43252</v>
       </c>
       <c r="B163" t="n">
@@ -12018,7 +12030,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43282</v>
       </c>
       <c r="B164" t="n">
@@ -12062,7 +12074,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43313</v>
       </c>
       <c r="B165" t="n">
@@ -12106,7 +12118,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43344</v>
       </c>
       <c r="B166" t="n">
@@ -12150,7 +12162,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43374</v>
       </c>
       <c r="B167" t="n">
@@ -12194,7 +12206,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43405</v>
       </c>
       <c r="B168" t="n">
@@ -12238,7 +12250,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43435</v>
       </c>
       <c r="B169" t="n">
@@ -12282,7 +12294,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43466</v>
       </c>
       <c r="B170" t="n">
@@ -12326,7 +12338,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43497</v>
       </c>
       <c r="B171" t="n">
@@ -12370,7 +12382,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43525</v>
       </c>
       <c r="B172" t="n">
@@ -12414,7 +12426,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43556</v>
       </c>
       <c r="B173" t="n">
@@ -12458,7 +12470,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43586</v>
       </c>
       <c r="B174" t="n">
@@ -12502,7 +12514,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>43617</v>
       </c>
       <c r="B175" t="n">
@@ -12546,7 +12558,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>43647</v>
       </c>
       <c r="B176" t="n">
@@ -12590,7 +12602,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>43678</v>
       </c>
       <c r="B177" t="n">
@@ -12634,7 +12646,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>43709</v>
       </c>
       <c r="B178" t="n">
@@ -12678,7 +12690,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>43739</v>
       </c>
       <c r="B179" t="n">
@@ -12722,7 +12734,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>43770</v>
       </c>
       <c r="B180" t="n">
@@ -12766,7 +12778,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>43800</v>
       </c>
       <c r="B181" t="n">
@@ -12810,7 +12822,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>43831</v>
       </c>
       <c r="B182" t="n">
@@ -12854,7 +12866,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>43862</v>
       </c>
       <c r="B183" t="n">
@@ -12898,7 +12910,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>43891</v>
       </c>
       <c r="B184" t="n">
@@ -12942,7 +12954,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>43922</v>
       </c>
       <c r="B185" t="n">
@@ -12986,7 +12998,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>43952</v>
       </c>
       <c r="B186" t="n">
@@ -13030,7 +13042,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>43983</v>
       </c>
       <c r="B187" t="n">
@@ -13074,7 +13086,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44013</v>
       </c>
       <c r="B188" t="n">
@@ -13118,7 +13130,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44044</v>
       </c>
       <c r="B189" t="n">
@@ -13162,7 +13174,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44075</v>
       </c>
       <c r="B190" t="n">
@@ -13206,7 +13218,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44105</v>
       </c>
       <c r="B191" t="n">
@@ -13250,7 +13262,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44136</v>
       </c>
       <c r="B192" t="n">
@@ -13294,7 +13306,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44166</v>
       </c>
       <c r="B193" t="n">
@@ -13338,7 +13350,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44197</v>
       </c>
       <c r="B194" t="n">
@@ -13382,7 +13394,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44228</v>
       </c>
       <c r="B195" t="n">
@@ -13426,7 +13438,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44256</v>
       </c>
       <c r="B196" t="n">
@@ -13470,7 +13482,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44287</v>
       </c>
       <c r="B197" t="n">
@@ -13514,7 +13526,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44317</v>
       </c>
       <c r="B198" t="n">
@@ -13558,7 +13570,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44348</v>
       </c>
       <c r="B199" t="n">
@@ -13602,7 +13614,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44378</v>
       </c>
       <c r="B200" t="n">
@@ -13646,7 +13658,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44409</v>
       </c>
       <c r="B201" t="n">
@@ -13690,7 +13702,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44440</v>
       </c>
       <c r="B202" t="n">
@@ -13734,7 +13746,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44470</v>
       </c>
       <c r="B203" t="n">
@@ -13778,7 +13790,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44501</v>
       </c>
       <c r="B204" t="n">
@@ -13822,7 +13834,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44531</v>
       </c>
       <c r="B205" t="n">
@@ -13866,7 +13878,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44562</v>
       </c>
       <c r="B206" t="n">
@@ -13910,7 +13922,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44593</v>
       </c>
       <c r="B207" t="n">
@@ -13954,7 +13966,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>44621</v>
       </c>
       <c r="B208" t="n">
@@ -13998,7 +14010,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>44652</v>
       </c>
       <c r="B209" t="n">
@@ -14042,7 +14054,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>44682</v>
       </c>
       <c r="B210" t="n">
@@ -14086,7 +14098,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>44713</v>
       </c>
       <c r="B211" t="n">
@@ -14130,7 +14142,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>44743</v>
       </c>
       <c r="B212" t="n">
@@ -14174,7 +14186,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>44774</v>
       </c>
       <c r="B213" t="n">
@@ -14218,7 +14230,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>44805</v>
       </c>
       <c r="B214" t="n">
@@ -14262,7 +14274,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>44835</v>
       </c>
       <c r="B215" t="n">
@@ -14306,7 +14318,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>44866</v>
       </c>
       <c r="B216" t="n">
@@ -14350,7 +14362,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>44896</v>
       </c>
       <c r="B217" t="n">
@@ -14394,7 +14406,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>44927</v>
       </c>
       <c r="B218" t="n">
@@ -14438,7 +14450,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>44958</v>
       </c>
       <c r="B219" t="n">
@@ -14482,7 +14494,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>44986</v>
       </c>
       <c r="B220" t="n">
@@ -14526,7 +14538,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45017</v>
       </c>
       <c r="B221" t="n">
@@ -14570,7 +14582,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45047</v>
       </c>
       <c r="B222" t="n">
@@ -14614,7 +14626,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45078</v>
       </c>
       <c r="B223" t="n">
@@ -14658,7 +14670,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45108</v>
       </c>
       <c r="B224" t="n">
@@ -14702,7 +14714,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45139</v>
       </c>
       <c r="B225" t="n">
@@ -14746,7 +14758,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45170</v>
       </c>
       <c r="B226" t="n">
@@ -14790,7 +14802,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45200</v>
       </c>
       <c r="B227" t="n">
@@ -14834,7 +14846,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45231</v>
       </c>
       <c r="B228" t="n">
@@ -14878,7 +14890,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45261</v>
       </c>
       <c r="B229" t="n">
@@ -14922,7 +14934,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45292</v>
       </c>
       <c r="B230" t="n">
@@ -14966,7 +14978,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45323</v>
       </c>
       <c r="B231" t="n">
@@ -15010,7 +15022,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45352</v>
       </c>
       <c r="B232" t="n">
@@ -15054,7 +15066,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45383</v>
       </c>
       <c r="B233" t="n">
@@ -15098,7 +15110,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45413</v>
       </c>
       <c r="B234" t="n">
@@ -15142,7 +15154,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45444</v>
       </c>
       <c r="B235" t="n">
@@ -15186,7 +15198,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45474</v>
       </c>
       <c r="B236" t="n">
@@ -15230,7 +15242,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="B237" t="n">
@@ -15274,7 +15286,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45536</v>
       </c>
       <c r="B238" t="n">
@@ -15318,7 +15330,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45566</v>
       </c>
       <c r="B239" t="n">
@@ -15362,7 +15374,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="B240" t="n">
@@ -15406,7 +15418,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>45627</v>
       </c>
       <c r="B241" t="n">
@@ -15450,7 +15462,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>45658</v>
       </c>
       <c r="B242" t="n">
@@ -15494,7 +15506,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>45689</v>
       </c>
       <c r="B243" t="n">
@@ -15538,7 +15550,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>45717</v>
       </c>
       <c r="B244" t="n">
@@ -15582,7 +15594,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>45748</v>
       </c>
       <c r="B245" t="n">
@@ -15626,7 +15638,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="B246" t="n">
@@ -15670,7 +15682,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>45809</v>
       </c>
       <c r="B247" t="n">
@@ -15714,7 +15726,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>45839</v>
       </c>
       <c r="B248" t="n">
@@ -15758,7 +15770,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="B249" t="n">
@@ -15802,7 +15814,7 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>45901</v>
       </c>
       <c r="B250" t="n">
@@ -15846,7 +15858,7 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="1" t="n">
+      <c r="A251" s="2" t="n">
         <v>45931</v>
       </c>
       <c r="B251" t="n">
@@ -15890,7 +15902,7 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="1" t="n">
+      <c r="A252" s="2" t="n">
         <v>45962</v>
       </c>
       <c r="B252" t="n">
@@ -15934,7 +15946,7 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="1" t="n">
+      <c r="A253" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="B253" t="n">
@@ -15978,7 +15990,7 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="1" t="n">
+      <c r="A254" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B254" t="n">
@@ -16022,7 +16034,7 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="1" t="n">
+      <c r="A255" s="2" t="n">
         <v>46054</v>
       </c>
       <c r="B255" t="n">
@@ -16066,7 +16078,7 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="1" t="n">
+      <c r="A256" s="2" t="n">
         <v>46082</v>
       </c>
       <c r="B256" t="n">
@@ -16110,7 +16122,7 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="1" t="n">
+      <c r="A257" s="2" t="n">
         <v>46113</v>
       </c>
       <c r="B257" t="n">
@@ -16154,7 +16166,7 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="1" t="n">
+      <c r="A258" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="B258" t="n">
@@ -16198,7 +16210,7 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="1" t="n">
+      <c r="A259" s="2" t="n">
         <v>46174</v>
       </c>
       <c r="B259" t="n">
@@ -16242,7 +16254,7 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="1" t="n">
+      <c r="A260" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="B260" t="n">
@@ -16300,79 +16312,79 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>tarih</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>01. Gıda Ve Alkolsüz İçecekler</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>02. Alkollü İçecekler, Tütün Ve Tütün Ürünleri</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>03. Giyim Ve Ayakkabı</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>04. Konut, Su, Elektrik, Gaz Ve Diğer Yakıtlar</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>05. Mobilya, Mefruşat Ve Evde Kullanılan Ekipmanlar İle Rutin Ev Bakım Ve Onarımı</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>06. Sağlık</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>07. Ulaştırma</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>08. Bilgi Ve İletişim</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>09. Eğlence, Dinlence, Spor Ve Kültür</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>10. Eğitim Hizmetleri</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>11. Lokantalar Ve Konaklama Hizmetleri</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>12. Sigorta Ve Finansal Hizmetler</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>13. Kişisel Bakım, Sosyal Koruma Ve Çeşitli Mal Ve Hizmetler</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38353</v>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -16390,7 +16402,7 @@
       <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38384</v>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -16408,7 +16420,7 @@
       <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38412</v>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -16426,7 +16438,7 @@
       <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38443</v>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -16444,7 +16456,7 @@
       <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38473</v>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -16462,7 +16474,7 @@
       <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38504</v>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -16480,7 +16492,7 @@
       <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38534</v>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -16498,7 +16510,7 @@
       <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38565</v>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -16516,7 +16528,7 @@
       <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38596</v>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -16534,7 +16546,7 @@
       <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>38626</v>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -16552,7 +16564,7 @@
       <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>38657</v>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -16570,7 +16582,7 @@
       <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>38687</v>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -16588,7 +16600,7 @@
       <c r="N13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>38718</v>
       </c>
       <c r="B14" t="n">
@@ -16632,7 +16644,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>38749</v>
       </c>
       <c r="B15" t="n">
@@ -16676,7 +16688,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>38777</v>
       </c>
       <c r="B16" t="n">
@@ -16720,7 +16732,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>38808</v>
       </c>
       <c r="B17" t="n">
@@ -16764,7 +16776,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>38838</v>
       </c>
       <c r="B18" t="n">
@@ -16808,7 +16820,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>38869</v>
       </c>
       <c r="B19" t="n">
@@ -16852,7 +16864,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>38899</v>
       </c>
       <c r="B20" t="n">
@@ -16896,7 +16908,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>38930</v>
       </c>
       <c r="B21" t="n">
@@ -16940,7 +16952,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>38961</v>
       </c>
       <c r="B22" t="n">
@@ -16984,7 +16996,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>38991</v>
       </c>
       <c r="B23" t="n">
@@ -17028,7 +17040,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39022</v>
       </c>
       <c r="B24" t="n">
@@ -17072,7 +17084,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39052</v>
       </c>
       <c r="B25" t="n">
@@ -17116,7 +17128,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39083</v>
       </c>
       <c r="B26" t="n">
@@ -17160,7 +17172,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39114</v>
       </c>
       <c r="B27" t="n">
@@ -17204,7 +17216,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39142</v>
       </c>
       <c r="B28" t="n">
@@ -17248,7 +17260,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39173</v>
       </c>
       <c r="B29" t="n">
@@ -17292,7 +17304,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39203</v>
       </c>
       <c r="B30" t="n">
@@ -17336,7 +17348,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39234</v>
       </c>
       <c r="B31" t="n">
@@ -17380,7 +17392,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39264</v>
       </c>
       <c r="B32" t="n">
@@ -17424,7 +17436,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39295</v>
       </c>
       <c r="B33" t="n">
@@ -17468,7 +17480,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39326</v>
       </c>
       <c r="B34" t="n">
@@ -17512,7 +17524,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39356</v>
       </c>
       <c r="B35" t="n">
@@ -17556,7 +17568,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39387</v>
       </c>
       <c r="B36" t="n">
@@ -17600,7 +17612,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39417</v>
       </c>
       <c r="B37" t="n">
@@ -17644,7 +17656,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39448</v>
       </c>
       <c r="B38" t="n">
@@ -17688,7 +17700,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39479</v>
       </c>
       <c r="B39" t="n">
@@ -17732,7 +17744,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39508</v>
       </c>
       <c r="B40" t="n">
@@ -17776,7 +17788,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39539</v>
       </c>
       <c r="B41" t="n">
@@ -17820,7 +17832,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39569</v>
       </c>
       <c r="B42" t="n">
@@ -17864,7 +17876,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39600</v>
       </c>
       <c r="B43" t="n">
@@ -17908,7 +17920,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>39630</v>
       </c>
       <c r="B44" t="n">
@@ -17952,7 +17964,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>39661</v>
       </c>
       <c r="B45" t="n">
@@ -17996,7 +18008,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>39692</v>
       </c>
       <c r="B46" t="n">
@@ -18040,7 +18052,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>39722</v>
       </c>
       <c r="B47" t="n">
@@ -18084,7 +18096,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>39753</v>
       </c>
       <c r="B48" t="n">
@@ -18128,7 +18140,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>39783</v>
       </c>
       <c r="B49" t="n">
@@ -18172,7 +18184,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>39814</v>
       </c>
       <c r="B50" t="n">
@@ -18216,7 +18228,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>39845</v>
       </c>
       <c r="B51" t="n">
@@ -18260,7 +18272,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>39873</v>
       </c>
       <c r="B52" t="n">
@@ -18304,7 +18316,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>39904</v>
       </c>
       <c r="B53" t="n">
@@ -18348,7 +18360,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>39934</v>
       </c>
       <c r="B54" t="n">
@@ -18392,7 +18404,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>39965</v>
       </c>
       <c r="B55" t="n">
@@ -18436,7 +18448,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>39995</v>
       </c>
       <c r="B56" t="n">
@@ -18480,7 +18492,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40026</v>
       </c>
       <c r="B57" t="n">
@@ -18524,7 +18536,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40057</v>
       </c>
       <c r="B58" t="n">
@@ -18568,7 +18580,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40087</v>
       </c>
       <c r="B59" t="n">
@@ -18612,7 +18624,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40118</v>
       </c>
       <c r="B60" t="n">
@@ -18656,7 +18668,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40148</v>
       </c>
       <c r="B61" t="n">
@@ -18700,7 +18712,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40179</v>
       </c>
       <c r="B62" t="n">
@@ -18744,7 +18756,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40210</v>
       </c>
       <c r="B63" t="n">
@@ -18788,7 +18800,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40238</v>
       </c>
       <c r="B64" t="n">
@@ -18832,7 +18844,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40269</v>
       </c>
       <c r="B65" t="n">
@@ -18876,7 +18888,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40299</v>
       </c>
       <c r="B66" t="n">
@@ -18920,7 +18932,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40330</v>
       </c>
       <c r="B67" t="n">
@@ -18964,7 +18976,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40360</v>
       </c>
       <c r="B68" t="n">
@@ -19008,7 +19020,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40391</v>
       </c>
       <c r="B69" t="n">
@@ -19052,7 +19064,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40422</v>
       </c>
       <c r="B70" t="n">
@@ -19096,7 +19108,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40452</v>
       </c>
       <c r="B71" t="n">
@@ -19140,7 +19152,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40483</v>
       </c>
       <c r="B72" t="n">
@@ -19184,7 +19196,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40513</v>
       </c>
       <c r="B73" t="n">
@@ -19228,7 +19240,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40544</v>
       </c>
       <c r="B74" t="n">
@@ -19272,7 +19284,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40575</v>
       </c>
       <c r="B75" t="n">
@@ -19316,7 +19328,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40603</v>
       </c>
       <c r="B76" t="n">
@@ -19360,7 +19372,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>40634</v>
       </c>
       <c r="B77" t="n">
@@ -19404,7 +19416,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>40664</v>
       </c>
       <c r="B78" t="n">
@@ -19448,7 +19460,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>40695</v>
       </c>
       <c r="B79" t="n">
@@ -19492,7 +19504,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>40725</v>
       </c>
       <c r="B80" t="n">
@@ -19536,7 +19548,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>40756</v>
       </c>
       <c r="B81" t="n">
@@ -19580,7 +19592,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>40787</v>
       </c>
       <c r="B82" t="n">
@@ -19624,7 +19636,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>40817</v>
       </c>
       <c r="B83" t="n">
@@ -19668,7 +19680,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>40848</v>
       </c>
       <c r="B84" t="n">
@@ -19712,7 +19724,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>40878</v>
       </c>
       <c r="B85" t="n">
@@ -19756,7 +19768,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>40909</v>
       </c>
       <c r="B86" t="n">
@@ -19800,7 +19812,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>40940</v>
       </c>
       <c r="B87" t="n">
@@ -19844,7 +19856,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>40969</v>
       </c>
       <c r="B88" t="n">
@@ -19888,7 +19900,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41000</v>
       </c>
       <c r="B89" t="n">
@@ -19932,7 +19944,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41030</v>
       </c>
       <c r="B90" t="n">
@@ -19976,7 +19988,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41061</v>
       </c>
       <c r="B91" t="n">
@@ -20020,7 +20032,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41091</v>
       </c>
       <c r="B92" t="n">
@@ -20064,7 +20076,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41122</v>
       </c>
       <c r="B93" t="n">
@@ -20108,7 +20120,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41153</v>
       </c>
       <c r="B94" t="n">
@@ -20152,7 +20164,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41183</v>
       </c>
       <c r="B95" t="n">
@@ -20196,7 +20208,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41214</v>
       </c>
       <c r="B96" t="n">
@@ -20240,7 +20252,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41244</v>
       </c>
       <c r="B97" t="n">
@@ -20284,7 +20296,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41275</v>
       </c>
       <c r="B98" t="n">
@@ -20328,7 +20340,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41306</v>
       </c>
       <c r="B99" t="n">
@@ -20372,7 +20384,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41334</v>
       </c>
       <c r="B100" t="n">
@@ -20416,7 +20428,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41365</v>
       </c>
       <c r="B101" t="n">
@@ -20460,7 +20472,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41395</v>
       </c>
       <c r="B102" t="n">
@@ -20504,7 +20516,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41426</v>
       </c>
       <c r="B103" t="n">
@@ -20548,7 +20560,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41456</v>
       </c>
       <c r="B104" t="n">
@@ -20592,7 +20604,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41487</v>
       </c>
       <c r="B105" t="n">
@@ -20636,7 +20648,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41518</v>
       </c>
       <c r="B106" t="n">
@@ -20680,7 +20692,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41548</v>
       </c>
       <c r="B107" t="n">
@@ -20724,7 +20736,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41579</v>
       </c>
       <c r="B108" t="n">
@@ -20768,7 +20780,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>41609</v>
       </c>
       <c r="B109" t="n">
@@ -20812,7 +20824,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>41640</v>
       </c>
       <c r="B110" t="n">
@@ -20856,7 +20868,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>41671</v>
       </c>
       <c r="B111" t="n">
@@ -20900,7 +20912,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>41699</v>
       </c>
       <c r="B112" t="n">
@@ -20944,7 +20956,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>41730</v>
       </c>
       <c r="B113" t="n">
@@ -20988,7 +21000,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>41760</v>
       </c>
       <c r="B114" t="n">
@@ -21032,7 +21044,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>41791</v>
       </c>
       <c r="B115" t="n">
@@ -21076,7 +21088,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>41821</v>
       </c>
       <c r="B116" t="n">
@@ -21120,7 +21132,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>41852</v>
       </c>
       <c r="B117" t="n">
@@ -21164,7 +21176,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>41883</v>
       </c>
       <c r="B118" t="n">
@@ -21208,7 +21220,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>41913</v>
       </c>
       <c r="B119" t="n">
@@ -21252,7 +21264,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>41944</v>
       </c>
       <c r="B120" t="n">
@@ -21296,7 +21308,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>41974</v>
       </c>
       <c r="B121" t="n">
@@ -21340,7 +21352,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42005</v>
       </c>
       <c r="B122" t="n">
@@ -21384,7 +21396,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42036</v>
       </c>
       <c r="B123" t="n">
@@ -21428,7 +21440,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42064</v>
       </c>
       <c r="B124" t="n">
@@ -21472,7 +21484,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42095</v>
       </c>
       <c r="B125" t="n">
@@ -21516,7 +21528,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42125</v>
       </c>
       <c r="B126" t="n">
@@ -21560,7 +21572,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42156</v>
       </c>
       <c r="B127" t="n">
@@ -21604,7 +21616,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42186</v>
       </c>
       <c r="B128" t="n">
@@ -21648,7 +21660,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42217</v>
       </c>
       <c r="B129" t="n">
@@ -21692,7 +21704,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42248</v>
       </c>
       <c r="B130" t="n">
@@ -21736,7 +21748,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42278</v>
       </c>
       <c r="B131" t="n">
@@ -21780,7 +21792,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42309</v>
       </c>
       <c r="B132" t="n">
@@ -21824,7 +21836,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42339</v>
       </c>
       <c r="B133" t="n">
@@ -21868,7 +21880,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42370</v>
       </c>
       <c r="B134" t="n">
@@ -21912,7 +21924,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42401</v>
       </c>
       <c r="B135" t="n">
@@ -21956,7 +21968,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42430</v>
       </c>
       <c r="B136" t="n">
@@ -22000,7 +22012,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42461</v>
       </c>
       <c r="B137" t="n">
@@ -22044,7 +22056,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42491</v>
       </c>
       <c r="B138" t="n">
@@ -22088,7 +22100,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42522</v>
       </c>
       <c r="B139" t="n">
@@ -22132,7 +22144,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42552</v>
       </c>
       <c r="B140" t="n">
@@ -22176,7 +22188,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42583</v>
       </c>
       <c r="B141" t="n">
@@ -22220,7 +22232,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>42614</v>
       </c>
       <c r="B142" t="n">
@@ -22264,7 +22276,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>42644</v>
       </c>
       <c r="B143" t="n">
@@ -22308,7 +22320,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>42675</v>
       </c>
       <c r="B144" t="n">
@@ -22352,7 +22364,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>42705</v>
       </c>
       <c r="B145" t="n">
@@ -22396,7 +22408,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>42736</v>
       </c>
       <c r="B146" t="n">
@@ -22440,7 +22452,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>42767</v>
       </c>
       <c r="B147" t="n">
@@ -22484,7 +22496,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>42795</v>
       </c>
       <c r="B148" t="n">
@@ -22528,7 +22540,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>42826</v>
       </c>
       <c r="B149" t="n">
@@ -22572,7 +22584,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>42856</v>
       </c>
       <c r="B150" t="n">
@@ -22616,7 +22628,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>42887</v>
       </c>
       <c r="B151" t="n">
@@ -22660,7 +22672,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>42917</v>
       </c>
       <c r="B152" t="n">
@@ -22704,7 +22716,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>42948</v>
       </c>
       <c r="B153" t="n">
@@ -22748,7 +22760,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>42979</v>
       </c>
       <c r="B154" t="n">
@@ -22792,7 +22804,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43009</v>
       </c>
       <c r="B155" t="n">
@@ -22836,7 +22848,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43040</v>
       </c>
       <c r="B156" t="n">
@@ -22880,7 +22892,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43070</v>
       </c>
       <c r="B157" t="n">
@@ -22924,7 +22936,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43101</v>
       </c>
       <c r="B158" t="n">
@@ -22968,7 +22980,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43132</v>
       </c>
       <c r="B159" t="n">
@@ -23012,7 +23024,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43160</v>
       </c>
       <c r="B160" t="n">
@@ -23056,7 +23068,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43191</v>
       </c>
       <c r="B161" t="n">
@@ -23100,7 +23112,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43221</v>
       </c>
       <c r="B162" t="n">
@@ -23144,7 +23156,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43252</v>
       </c>
       <c r="B163" t="n">
@@ -23188,7 +23200,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43282</v>
       </c>
       <c r="B164" t="n">
@@ -23232,7 +23244,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43313</v>
       </c>
       <c r="B165" t="n">
@@ -23276,7 +23288,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43344</v>
       </c>
       <c r="B166" t="n">
@@ -23320,7 +23332,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43374</v>
       </c>
       <c r="B167" t="n">
@@ -23364,7 +23376,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43405</v>
       </c>
       <c r="B168" t="n">
@@ -23408,7 +23420,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43435</v>
       </c>
       <c r="B169" t="n">
@@ -23452,7 +23464,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43466</v>
       </c>
       <c r="B170" t="n">
@@ -23496,7 +23508,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43497</v>
       </c>
       <c r="B171" t="n">
@@ -23540,7 +23552,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43525</v>
       </c>
       <c r="B172" t="n">
@@ -23584,7 +23596,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43556</v>
       </c>
       <c r="B173" t="n">
@@ -23628,7 +23640,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43586</v>
       </c>
       <c r="B174" t="n">
@@ -23672,7 +23684,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>43617</v>
       </c>
       <c r="B175" t="n">
@@ -23716,7 +23728,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>43647</v>
       </c>
       <c r="B176" t="n">
@@ -23760,7 +23772,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>43678</v>
       </c>
       <c r="B177" t="n">
@@ -23804,7 +23816,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>43709</v>
       </c>
       <c r="B178" t="n">
@@ -23848,7 +23860,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>43739</v>
       </c>
       <c r="B179" t="n">
@@ -23892,7 +23904,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>43770</v>
       </c>
       <c r="B180" t="n">
@@ -23936,7 +23948,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>43800</v>
       </c>
       <c r="B181" t="n">
@@ -23980,7 +23992,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>43831</v>
       </c>
       <c r="B182" t="n">
@@ -24024,7 +24036,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>43862</v>
       </c>
       <c r="B183" t="n">
@@ -24068,7 +24080,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>43891</v>
       </c>
       <c r="B184" t="n">
@@ -24112,7 +24124,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>43922</v>
       </c>
       <c r="B185" t="n">
@@ -24156,7 +24168,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>43952</v>
       </c>
       <c r="B186" t="n">
@@ -24200,7 +24212,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>43983</v>
       </c>
       <c r="B187" t="n">
@@ -24244,7 +24256,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44013</v>
       </c>
       <c r="B188" t="n">
@@ -24288,7 +24300,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44044</v>
       </c>
       <c r="B189" t="n">
@@ -24332,7 +24344,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44075</v>
       </c>
       <c r="B190" t="n">
@@ -24376,7 +24388,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44105</v>
       </c>
       <c r="B191" t="n">
@@ -24420,7 +24432,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44136</v>
       </c>
       <c r="B192" t="n">
@@ -24464,7 +24476,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44166</v>
       </c>
       <c r="B193" t="n">
@@ -24508,7 +24520,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44197</v>
       </c>
       <c r="B194" t="n">
@@ -24552,7 +24564,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44228</v>
       </c>
       <c r="B195" t="n">
@@ -24596,7 +24608,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44256</v>
       </c>
       <c r="B196" t="n">
@@ -24640,7 +24652,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44287</v>
       </c>
       <c r="B197" t="n">
@@ -24684,7 +24696,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44317</v>
       </c>
       <c r="B198" t="n">
@@ -24728,7 +24740,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44348</v>
       </c>
       <c r="B199" t="n">
@@ -24772,7 +24784,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44378</v>
       </c>
       <c r="B200" t="n">
@@ -24816,7 +24828,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44409</v>
       </c>
       <c r="B201" t="n">
@@ -24860,7 +24872,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44440</v>
       </c>
       <c r="B202" t="n">
@@ -24904,7 +24916,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44470</v>
       </c>
       <c r="B203" t="n">
@@ -24948,7 +24960,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44501</v>
       </c>
       <c r="B204" t="n">
@@ -24992,7 +25004,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44531</v>
       </c>
       <c r="B205" t="n">
@@ -25036,7 +25048,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44562</v>
       </c>
       <c r="B206" t="n">
@@ -25080,7 +25092,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44593</v>
       </c>
       <c r="B207" t="n">
@@ -25124,7 +25136,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>44621</v>
       </c>
       <c r="B208" t="n">
@@ -25168,7 +25180,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>44652</v>
       </c>
       <c r="B209" t="n">
@@ -25212,7 +25224,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>44682</v>
       </c>
       <c r="B210" t="n">
@@ -25256,7 +25268,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>44713</v>
       </c>
       <c r="B211" t="n">
@@ -25300,7 +25312,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>44743</v>
       </c>
       <c r="B212" t="n">
@@ -25344,7 +25356,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>44774</v>
       </c>
       <c r="B213" t="n">
@@ -25388,7 +25400,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>44805</v>
       </c>
       <c r="B214" t="n">
@@ -25432,7 +25444,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>44835</v>
       </c>
       <c r="B215" t="n">
@@ -25476,7 +25488,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>44866</v>
       </c>
       <c r="B216" t="n">
@@ -25520,7 +25532,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>44896</v>
       </c>
       <c r="B217" t="n">
@@ -25564,7 +25576,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>44927</v>
       </c>
       <c r="B218" t="n">
@@ -25608,7 +25620,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>44958</v>
       </c>
       <c r="B219" t="n">
@@ -25652,7 +25664,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>44986</v>
       </c>
       <c r="B220" t="n">
@@ -25696,7 +25708,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45017</v>
       </c>
       <c r="B221" t="n">
@@ -25740,7 +25752,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45047</v>
       </c>
       <c r="B222" t="n">
@@ -25784,7 +25796,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45078</v>
       </c>
       <c r="B223" t="n">
@@ -25828,7 +25840,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45108</v>
       </c>
       <c r="B224" t="n">
@@ -25872,7 +25884,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45139</v>
       </c>
       <c r="B225" t="n">
@@ -25916,7 +25928,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45170</v>
       </c>
       <c r="B226" t="n">
@@ -25960,7 +25972,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45200</v>
       </c>
       <c r="B227" t="n">
@@ -26004,7 +26016,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45231</v>
       </c>
       <c r="B228" t="n">
@@ -26048,7 +26060,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45261</v>
       </c>
       <c r="B229" t="n">
@@ -26092,7 +26104,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45292</v>
       </c>
       <c r="B230" t="n">
@@ -26136,7 +26148,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45323</v>
       </c>
       <c r="B231" t="n">
@@ -26180,7 +26192,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45352</v>
       </c>
       <c r="B232" t="n">
@@ -26224,7 +26236,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45383</v>
       </c>
       <c r="B233" t="n">
@@ -26268,7 +26280,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45413</v>
       </c>
       <c r="B234" t="n">
@@ -26312,7 +26324,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45444</v>
       </c>
       <c r="B235" t="n">
@@ -26356,7 +26368,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45474</v>
       </c>
       <c r="B236" t="n">
@@ -26400,7 +26412,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="B237" t="n">
@@ -26444,7 +26456,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45536</v>
       </c>
       <c r="B238" t="n">
@@ -26488,7 +26500,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45566</v>
       </c>
       <c r="B239" t="n">
@@ -26532,7 +26544,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="B240" t="n">
@@ -26576,7 +26588,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>45627</v>
       </c>
       <c r="B241" t="n">
@@ -26620,7 +26632,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>45658</v>
       </c>
       <c r="B242" t="n">
@@ -26664,7 +26676,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>45689</v>
       </c>
       <c r="B243" t="n">
@@ -26708,7 +26720,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>45717</v>
       </c>
       <c r="B244" t="n">
@@ -26752,7 +26764,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>45748</v>
       </c>
       <c r="B245" t="n">
@@ -26796,7 +26808,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="B246" t="n">
@@ -26840,7 +26852,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>45809</v>
       </c>
       <c r="B247" t="n">
@@ -26884,7 +26896,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>45839</v>
       </c>
       <c r="B248" t="n">
@@ -26928,7 +26940,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="B249" t="n">
@@ -26972,7 +26984,7 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>45901</v>
       </c>
       <c r="B250" t="n">
@@ -27016,7 +27028,7 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="1" t="n">
+      <c r="A251" s="2" t="n">
         <v>45931</v>
       </c>
       <c r="B251" t="n">
@@ -27060,7 +27072,7 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="1" t="n">
+      <c r="A252" s="2" t="n">
         <v>45962</v>
       </c>
       <c r="B252" t="n">
@@ -27104,7 +27116,7 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="1" t="n">
+      <c r="A253" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="B253" t="n">
@@ -27148,7 +27160,7 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="1" t="n">
+      <c r="A254" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B254" t="n">
@@ -27192,7 +27204,7 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="1" t="n">
+      <c r="A255" s="2" t="n">
         <v>46054</v>
       </c>
       <c r="B255" t="n">
@@ -27236,7 +27248,7 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="1" t="n">
+      <c r="A256" s="2" t="n">
         <v>46082</v>
       </c>
       <c r="B256" t="n">
@@ -27280,7 +27292,7 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="1" t="n">
+      <c r="A257" s="2" t="n">
         <v>46113</v>
       </c>
       <c r="B257" t="n">
@@ -27324,7 +27336,7 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="1" t="n">
+      <c r="A258" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="B258" t="n">
@@ -27368,7 +27380,7 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="1" t="n">
+      <c r="A259" s="2" t="n">
         <v>46174</v>
       </c>
       <c r="B259" t="n">
@@ -27412,7 +27424,7 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="1" t="n">
+      <c r="A260" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="B260" t="n">
@@ -27470,32 +27482,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Kalem</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Endeks</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Aylık %</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Yıllık %</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Yılbaşından %</t>
         </is>

--- a/enflasyon/enflasyon.xlsx
+++ b/enflasyon/enflasyon.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Genel" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AltKalem_Endeks" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AltKalem_Yillik" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AltKalem_Ozet" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Genel" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="AltKalem_Endeks" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="AltKalem_Yillik" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="AltKalem_Ozet" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,16 +23,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -43,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -51,21 +48,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -436,34 +424,34 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>tarih</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>endeks</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>aylik</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>yillik</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>ytd</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="1" t="n">
         <v>38353</v>
       </c>
       <c r="B2" t="n">
@@ -474,7 +462,7 @@
       <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="1" t="n">
         <v>38384</v>
       </c>
       <c r="B3" t="n">
@@ -487,7 +475,7 @@
       <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="1" t="n">
         <v>38412</v>
       </c>
       <c r="B4" t="n">
@@ -500,7 +488,7 @@
       <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="1" t="n">
         <v>38443</v>
       </c>
       <c r="B5" t="n">
@@ -513,7 +501,7 @@
       <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="1" t="n">
         <v>38473</v>
       </c>
       <c r="B6" t="n">
@@ -526,7 +514,7 @@
       <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="1" t="n">
         <v>38504</v>
       </c>
       <c r="B7" t="n">
@@ -539,7 +527,7 @@
       <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="1" t="n">
         <v>38534</v>
       </c>
       <c r="B8" t="n">
@@ -552,7 +540,7 @@
       <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="1" t="n">
         <v>38565</v>
       </c>
       <c r="B9" t="n">
@@ -565,7 +553,7 @@
       <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="1" t="n">
         <v>38596</v>
       </c>
       <c r="B10" t="n">
@@ -578,7 +566,7 @@
       <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="1" t="n">
         <v>38626</v>
       </c>
       <c r="B11" t="n">
@@ -591,7 +579,7 @@
       <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="1" t="n">
         <v>38657</v>
       </c>
       <c r="B12" t="n">
@@ -604,7 +592,7 @@
       <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="1" t="n">
         <v>38687</v>
       </c>
       <c r="B13" t="n">
@@ -617,7 +605,7 @@
       <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="1" t="n">
         <v>38718</v>
       </c>
       <c r="B14" t="n">
@@ -634,7 +622,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="1" t="n">
         <v>38749</v>
       </c>
       <c r="B15" t="n">
@@ -651,7 +639,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="1" t="n">
         <v>38777</v>
       </c>
       <c r="B16" t="n">
@@ -668,7 +656,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="1" t="n">
         <v>38808</v>
       </c>
       <c r="B17" t="n">
@@ -685,7 +673,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="1" t="n">
         <v>38838</v>
       </c>
       <c r="B18" t="n">
@@ -702,7 +690,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="1" t="n">
         <v>38869</v>
       </c>
       <c r="B19" t="n">
@@ -719,7 +707,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="1" t="n">
         <v>38899</v>
       </c>
       <c r="B20" t="n">
@@ -736,7 +724,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="1" t="n">
         <v>38930</v>
       </c>
       <c r="B21" t="n">
@@ -753,7 +741,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="1" t="n">
         <v>38961</v>
       </c>
       <c r="B22" t="n">
@@ -770,7 +758,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="1" t="n">
         <v>38991</v>
       </c>
       <c r="B23" t="n">
@@ -787,7 +775,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="1" t="n">
         <v>39022</v>
       </c>
       <c r="B24" t="n">
@@ -804,7 +792,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="1" t="n">
         <v>39052</v>
       </c>
       <c r="B25" t="n">
@@ -821,7 +809,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="1" t="n">
         <v>39083</v>
       </c>
       <c r="B26" t="n">
@@ -838,7 +826,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="1" t="n">
         <v>39114</v>
       </c>
       <c r="B27" t="n">
@@ -855,7 +843,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="1" t="n">
         <v>39142</v>
       </c>
       <c r="B28" t="n">
@@ -872,7 +860,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="1" t="n">
         <v>39173</v>
       </c>
       <c r="B29" t="n">
@@ -889,7 +877,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="1" t="n">
         <v>39203</v>
       </c>
       <c r="B30" t="n">
@@ -906,7 +894,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="1" t="n">
         <v>39234</v>
       </c>
       <c r="B31" t="n">
@@ -923,7 +911,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="1" t="n">
         <v>39264</v>
       </c>
       <c r="B32" t="n">
@@ -940,7 +928,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="1" t="n">
         <v>39295</v>
       </c>
       <c r="B33" t="n">
@@ -957,7 +945,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="1" t="n">
         <v>39326</v>
       </c>
       <c r="B34" t="n">
@@ -974,7 +962,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="1" t="n">
         <v>39356</v>
       </c>
       <c r="B35" t="n">
@@ -991,7 +979,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="1" t="n">
         <v>39387</v>
       </c>
       <c r="B36" t="n">
@@ -1008,7 +996,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="1" t="n">
         <v>39417</v>
       </c>
       <c r="B37" t="n">
@@ -1025,7 +1013,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="1" t="n">
         <v>39448</v>
       </c>
       <c r="B38" t="n">
@@ -1042,7 +1030,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="1" t="n">
         <v>39479</v>
       </c>
       <c r="B39" t="n">
@@ -1059,7 +1047,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="1" t="n">
         <v>39508</v>
       </c>
       <c r="B40" t="n">
@@ -1076,7 +1064,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" s="1" t="n">
         <v>39539</v>
       </c>
       <c r="B41" t="n">
@@ -1093,7 +1081,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="1" t="n">
         <v>39569</v>
       </c>
       <c r="B42" t="n">
@@ -1110,7 +1098,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" s="1" t="n">
         <v>39600</v>
       </c>
       <c r="B43" t="n">
@@ -1127,7 +1115,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" s="1" t="n">
         <v>39630</v>
       </c>
       <c r="B44" t="n">
@@ -1144,7 +1132,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" s="1" t="n">
         <v>39661</v>
       </c>
       <c r="B45" t="n">
@@ -1161,7 +1149,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="1" t="n">
         <v>39692</v>
       </c>
       <c r="B46" t="n">
@@ -1178,7 +1166,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="A47" s="1" t="n">
         <v>39722</v>
       </c>
       <c r="B47" t="n">
@@ -1195,7 +1183,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="1" t="n">
         <v>39753</v>
       </c>
       <c r="B48" t="n">
@@ -1212,7 +1200,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="A49" s="1" t="n">
         <v>39783</v>
       </c>
       <c r="B49" t="n">
@@ -1229,7 +1217,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="1" t="n">
         <v>39814</v>
       </c>
       <c r="B50" t="n">
@@ -1246,7 +1234,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" s="1" t="n">
         <v>39845</v>
       </c>
       <c r="B51" t="n">
@@ -1263,7 +1251,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="A52" s="1" t="n">
         <v>39873</v>
       </c>
       <c r="B52" t="n">
@@ -1280,7 +1268,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" s="1" t="n">
         <v>39904</v>
       </c>
       <c r="B53" t="n">
@@ -1297,7 +1285,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n">
+      <c r="A54" s="1" t="n">
         <v>39934</v>
       </c>
       <c r="B54" t="n">
@@ -1314,7 +1302,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n">
+      <c r="A55" s="1" t="n">
         <v>39965</v>
       </c>
       <c r="B55" t="n">
@@ -1331,7 +1319,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
+      <c r="A56" s="1" t="n">
         <v>39995</v>
       </c>
       <c r="B56" t="n">
@@ -1348,7 +1336,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="A57" s="1" t="n">
         <v>40026</v>
       </c>
       <c r="B57" t="n">
@@ -1365,7 +1353,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
+      <c r="A58" s="1" t="n">
         <v>40057</v>
       </c>
       <c r="B58" t="n">
@@ -1382,7 +1370,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
+      <c r="A59" s="1" t="n">
         <v>40087</v>
       </c>
       <c r="B59" t="n">
@@ -1399,7 +1387,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
+      <c r="A60" s="1" t="n">
         <v>40118</v>
       </c>
       <c r="B60" t="n">
@@ -1416,7 +1404,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
+      <c r="A61" s="1" t="n">
         <v>40148</v>
       </c>
       <c r="B61" t="n">
@@ -1433,7 +1421,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
+      <c r="A62" s="1" t="n">
         <v>40179</v>
       </c>
       <c r="B62" t="n">
@@ -1450,7 +1438,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n">
+      <c r="A63" s="1" t="n">
         <v>40210</v>
       </c>
       <c r="B63" t="n">
@@ -1467,7 +1455,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n">
+      <c r="A64" s="1" t="n">
         <v>40238</v>
       </c>
       <c r="B64" t="n">
@@ -1484,7 +1472,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n">
+      <c r="A65" s="1" t="n">
         <v>40269</v>
       </c>
       <c r="B65" t="n">
@@ -1501,7 +1489,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n">
+      <c r="A66" s="1" t="n">
         <v>40299</v>
       </c>
       <c r="B66" t="n">
@@ -1518,7 +1506,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n">
+      <c r="A67" s="1" t="n">
         <v>40330</v>
       </c>
       <c r="B67" t="n">
@@ -1535,7 +1523,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n">
+      <c r="A68" s="1" t="n">
         <v>40360</v>
       </c>
       <c r="B68" t="n">
@@ -1552,7 +1540,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n">
+      <c r="A69" s="1" t="n">
         <v>40391</v>
       </c>
       <c r="B69" t="n">
@@ -1569,7 +1557,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="n">
+      <c r="A70" s="1" t="n">
         <v>40422</v>
       </c>
       <c r="B70" t="n">
@@ -1586,7 +1574,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="n">
+      <c r="A71" s="1" t="n">
         <v>40452</v>
       </c>
       <c r="B71" t="n">
@@ -1603,7 +1591,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="n">
+      <c r="A72" s="1" t="n">
         <v>40483</v>
       </c>
       <c r="B72" t="n">
@@ -1620,7 +1608,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="n">
+      <c r="A73" s="1" t="n">
         <v>40513</v>
       </c>
       <c r="B73" t="n">
@@ -1637,7 +1625,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="n">
+      <c r="A74" s="1" t="n">
         <v>40544</v>
       </c>
       <c r="B74" t="n">
@@ -1654,7 +1642,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="n">
+      <c r="A75" s="1" t="n">
         <v>40575</v>
       </c>
       <c r="B75" t="n">
@@ -1671,7 +1659,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="n">
+      <c r="A76" s="1" t="n">
         <v>40603</v>
       </c>
       <c r="B76" t="n">
@@ -1688,7 +1676,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n">
+      <c r="A77" s="1" t="n">
         <v>40634</v>
       </c>
       <c r="B77" t="n">
@@ -1705,7 +1693,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n">
+      <c r="A78" s="1" t="n">
         <v>40664</v>
       </c>
       <c r="B78" t="n">
@@ -1722,7 +1710,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="n">
+      <c r="A79" s="1" t="n">
         <v>40695</v>
       </c>
       <c r="B79" t="n">
@@ -1739,7 +1727,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="n">
+      <c r="A80" s="1" t="n">
         <v>40725</v>
       </c>
       <c r="B80" t="n">
@@ -1756,7 +1744,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="n">
+      <c r="A81" s="1" t="n">
         <v>40756</v>
       </c>
       <c r="B81" t="n">
@@ -1773,7 +1761,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="n">
+      <c r="A82" s="1" t="n">
         <v>40787</v>
       </c>
       <c r="B82" t="n">
@@ -1790,7 +1778,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="n">
+      <c r="A83" s="1" t="n">
         <v>40817</v>
       </c>
       <c r="B83" t="n">
@@ -1807,7 +1795,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="n">
+      <c r="A84" s="1" t="n">
         <v>40848</v>
       </c>
       <c r="B84" t="n">
@@ -1824,7 +1812,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="n">
+      <c r="A85" s="1" t="n">
         <v>40878</v>
       </c>
       <c r="B85" t="n">
@@ -1841,7 +1829,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="n">
+      <c r="A86" s="1" t="n">
         <v>40909</v>
       </c>
       <c r="B86" t="n">
@@ -1858,7 +1846,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="n">
+      <c r="A87" s="1" t="n">
         <v>40940</v>
       </c>
       <c r="B87" t="n">
@@ -1875,7 +1863,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="n">
+      <c r="A88" s="1" t="n">
         <v>40969</v>
       </c>
       <c r="B88" t="n">
@@ -1892,7 +1880,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="n">
+      <c r="A89" s="1" t="n">
         <v>41000</v>
       </c>
       <c r="B89" t="n">
@@ -1909,7 +1897,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="n">
+      <c r="A90" s="1" t="n">
         <v>41030</v>
       </c>
       <c r="B90" t="n">
@@ -1926,7 +1914,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="n">
+      <c r="A91" s="1" t="n">
         <v>41061</v>
       </c>
       <c r="B91" t="n">
@@ -1943,7 +1931,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="n">
+      <c r="A92" s="1" t="n">
         <v>41091</v>
       </c>
       <c r="B92" t="n">
@@ -1960,7 +1948,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="n">
+      <c r="A93" s="1" t="n">
         <v>41122</v>
       </c>
       <c r="B93" t="n">
@@ -1977,7 +1965,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="n">
+      <c r="A94" s="1" t="n">
         <v>41153</v>
       </c>
       <c r="B94" t="n">
@@ -1994,7 +1982,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="n">
+      <c r="A95" s="1" t="n">
         <v>41183</v>
       </c>
       <c r="B95" t="n">
@@ -2011,7 +1999,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="n">
+      <c r="A96" s="1" t="n">
         <v>41214</v>
       </c>
       <c r="B96" t="n">
@@ -2028,7 +2016,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="n">
+      <c r="A97" s="1" t="n">
         <v>41244</v>
       </c>
       <c r="B97" t="n">
@@ -2045,7 +2033,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="n">
+      <c r="A98" s="1" t="n">
         <v>41275</v>
       </c>
       <c r="B98" t="n">
@@ -2062,7 +2050,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="n">
+      <c r="A99" s="1" t="n">
         <v>41306</v>
       </c>
       <c r="B99" t="n">
@@ -2079,7 +2067,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="n">
+      <c r="A100" s="1" t="n">
         <v>41334</v>
       </c>
       <c r="B100" t="n">
@@ -2096,7 +2084,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="n">
+      <c r="A101" s="1" t="n">
         <v>41365</v>
       </c>
       <c r="B101" t="n">
@@ -2113,7 +2101,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="n">
+      <c r="A102" s="1" t="n">
         <v>41395</v>
       </c>
       <c r="B102" t="n">
@@ -2130,7 +2118,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="n">
+      <c r="A103" s="1" t="n">
         <v>41426</v>
       </c>
       <c r="B103" t="n">
@@ -2147,7 +2135,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="2" t="n">
+      <c r="A104" s="1" t="n">
         <v>41456</v>
       </c>
       <c r="B104" t="n">
@@ -2164,7 +2152,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="2" t="n">
+      <c r="A105" s="1" t="n">
         <v>41487</v>
       </c>
       <c r="B105" t="n">
@@ -2181,7 +2169,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="n">
+      <c r="A106" s="1" t="n">
         <v>41518</v>
       </c>
       <c r="B106" t="n">
@@ -2198,7 +2186,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="n">
+      <c r="A107" s="1" t="n">
         <v>41548</v>
       </c>
       <c r="B107" t="n">
@@ -2215,7 +2203,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="n">
+      <c r="A108" s="1" t="n">
         <v>41579</v>
       </c>
       <c r="B108" t="n">
@@ -2232,7 +2220,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="n">
+      <c r="A109" s="1" t="n">
         <v>41609</v>
       </c>
       <c r="B109" t="n">
@@ -2249,7 +2237,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="n">
+      <c r="A110" s="1" t="n">
         <v>41640</v>
       </c>
       <c r="B110" t="n">
@@ -2266,7 +2254,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="n">
+      <c r="A111" s="1" t="n">
         <v>41671</v>
       </c>
       <c r="B111" t="n">
@@ -2283,7 +2271,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="n">
+      <c r="A112" s="1" t="n">
         <v>41699</v>
       </c>
       <c r="B112" t="n">
@@ -2300,7 +2288,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="2" t="n">
+      <c r="A113" s="1" t="n">
         <v>41730</v>
       </c>
       <c r="B113" t="n">
@@ -2317,7 +2305,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="2" t="n">
+      <c r="A114" s="1" t="n">
         <v>41760</v>
       </c>
       <c r="B114" t="n">
@@ -2334,7 +2322,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="n">
+      <c r="A115" s="1" t="n">
         <v>41791</v>
       </c>
       <c r="B115" t="n">
@@ -2351,7 +2339,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="n">
+      <c r="A116" s="1" t="n">
         <v>41821</v>
       </c>
       <c r="B116" t="n">
@@ -2368,7 +2356,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="2" t="n">
+      <c r="A117" s="1" t="n">
         <v>41852</v>
       </c>
       <c r="B117" t="n">
@@ -2385,7 +2373,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="2" t="n">
+      <c r="A118" s="1" t="n">
         <v>41883</v>
       </c>
       <c r="B118" t="n">
@@ -2402,7 +2390,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="n">
+      <c r="A119" s="1" t="n">
         <v>41913</v>
       </c>
       <c r="B119" t="n">
@@ -2419,7 +2407,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="n">
+      <c r="A120" s="1" t="n">
         <v>41944</v>
       </c>
       <c r="B120" t="n">
@@ -2436,7 +2424,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="2" t="n">
+      <c r="A121" s="1" t="n">
         <v>41974</v>
       </c>
       <c r="B121" t="n">
@@ -2453,7 +2441,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="2" t="n">
+      <c r="A122" s="1" t="n">
         <v>42005</v>
       </c>
       <c r="B122" t="n">
@@ -2470,7 +2458,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="2" t="n">
+      <c r="A123" s="1" t="n">
         <v>42036</v>
       </c>
       <c r="B123" t="n">
@@ -2487,7 +2475,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="n">
+      <c r="A124" s="1" t="n">
         <v>42064</v>
       </c>
       <c r="B124" t="n">
@@ -2504,7 +2492,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="2" t="n">
+      <c r="A125" s="1" t="n">
         <v>42095</v>
       </c>
       <c r="B125" t="n">
@@ -2521,7 +2509,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="2" t="n">
+      <c r="A126" s="1" t="n">
         <v>42125</v>
       </c>
       <c r="B126" t="n">
@@ -2538,7 +2526,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="2" t="n">
+      <c r="A127" s="1" t="n">
         <v>42156</v>
       </c>
       <c r="B127" t="n">
@@ -2555,7 +2543,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="2" t="n">
+      <c r="A128" s="1" t="n">
         <v>42186</v>
       </c>
       <c r="B128" t="n">
@@ -2572,7 +2560,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="2" t="n">
+      <c r="A129" s="1" t="n">
         <v>42217</v>
       </c>
       <c r="B129" t="n">
@@ -2589,7 +2577,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="2" t="n">
+      <c r="A130" s="1" t="n">
         <v>42248</v>
       </c>
       <c r="B130" t="n">
@@ -2606,7 +2594,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="2" t="n">
+      <c r="A131" s="1" t="n">
         <v>42278</v>
       </c>
       <c r="B131" t="n">
@@ -2623,7 +2611,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="2" t="n">
+      <c r="A132" s="1" t="n">
         <v>42309</v>
       </c>
       <c r="B132" t="n">
@@ -2640,7 +2628,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="2" t="n">
+      <c r="A133" s="1" t="n">
         <v>42339</v>
       </c>
       <c r="B133" t="n">
@@ -2657,7 +2645,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="2" t="n">
+      <c r="A134" s="1" t="n">
         <v>42370</v>
       </c>
       <c r="B134" t="n">
@@ -2674,7 +2662,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="2" t="n">
+      <c r="A135" s="1" t="n">
         <v>42401</v>
       </c>
       <c r="B135" t="n">
@@ -2691,7 +2679,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="2" t="n">
+      <c r="A136" s="1" t="n">
         <v>42430</v>
       </c>
       <c r="B136" t="n">
@@ -2708,7 +2696,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="2" t="n">
+      <c r="A137" s="1" t="n">
         <v>42461</v>
       </c>
       <c r="B137" t="n">
@@ -2725,7 +2713,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="2" t="n">
+      <c r="A138" s="1" t="n">
         <v>42491</v>
       </c>
       <c r="B138" t="n">
@@ -2742,7 +2730,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="2" t="n">
+      <c r="A139" s="1" t="n">
         <v>42522</v>
       </c>
       <c r="B139" t="n">
@@ -2759,7 +2747,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="2" t="n">
+      <c r="A140" s="1" t="n">
         <v>42552</v>
       </c>
       <c r="B140" t="n">
@@ -2776,7 +2764,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="2" t="n">
+      <c r="A141" s="1" t="n">
         <v>42583</v>
       </c>
       <c r="B141" t="n">
@@ -2793,7 +2781,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="2" t="n">
+      <c r="A142" s="1" t="n">
         <v>42614</v>
       </c>
       <c r="B142" t="n">
@@ -2810,7 +2798,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="2" t="n">
+      <c r="A143" s="1" t="n">
         <v>42644</v>
       </c>
       <c r="B143" t="n">
@@ -2827,7 +2815,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="2" t="n">
+      <c r="A144" s="1" t="n">
         <v>42675</v>
       </c>
       <c r="B144" t="n">
@@ -2844,7 +2832,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="2" t="n">
+      <c r="A145" s="1" t="n">
         <v>42705</v>
       </c>
       <c r="B145" t="n">
@@ -2861,7 +2849,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="2" t="n">
+      <c r="A146" s="1" t="n">
         <v>42736</v>
       </c>
       <c r="B146" t="n">
@@ -2878,7 +2866,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="2" t="n">
+      <c r="A147" s="1" t="n">
         <v>42767</v>
       </c>
       <c r="B147" t="n">
@@ -2895,7 +2883,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="2" t="n">
+      <c r="A148" s="1" t="n">
         <v>42795</v>
       </c>
       <c r="B148" t="n">
@@ -2912,7 +2900,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="2" t="n">
+      <c r="A149" s="1" t="n">
         <v>42826</v>
       </c>
       <c r="B149" t="n">
@@ -2929,7 +2917,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="2" t="n">
+      <c r="A150" s="1" t="n">
         <v>42856</v>
       </c>
       <c r="B150" t="n">
@@ -2946,7 +2934,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="2" t="n">
+      <c r="A151" s="1" t="n">
         <v>42887</v>
       </c>
       <c r="B151" t="n">
@@ -2963,7 +2951,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="2" t="n">
+      <c r="A152" s="1" t="n">
         <v>42917</v>
       </c>
       <c r="B152" t="n">
@@ -2980,7 +2968,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="2" t="n">
+      <c r="A153" s="1" t="n">
         <v>42948</v>
       </c>
       <c r="B153" t="n">
@@ -2997,7 +2985,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="2" t="n">
+      <c r="A154" s="1" t="n">
         <v>42979</v>
       </c>
       <c r="B154" t="n">
@@ -3014,7 +3002,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="2" t="n">
+      <c r="A155" s="1" t="n">
         <v>43009</v>
       </c>
       <c r="B155" t="n">
@@ -3031,7 +3019,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="2" t="n">
+      <c r="A156" s="1" t="n">
         <v>43040</v>
       </c>
       <c r="B156" t="n">
@@ -3048,7 +3036,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="2" t="n">
+      <c r="A157" s="1" t="n">
         <v>43070</v>
       </c>
       <c r="B157" t="n">
@@ -3065,7 +3053,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="2" t="n">
+      <c r="A158" s="1" t="n">
         <v>43101</v>
       </c>
       <c r="B158" t="n">
@@ -3082,7 +3070,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="2" t="n">
+      <c r="A159" s="1" t="n">
         <v>43132</v>
       </c>
       <c r="B159" t="n">
@@ -3099,7 +3087,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="2" t="n">
+      <c r="A160" s="1" t="n">
         <v>43160</v>
       </c>
       <c r="B160" t="n">
@@ -3116,7 +3104,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="2" t="n">
+      <c r="A161" s="1" t="n">
         <v>43191</v>
       </c>
       <c r="B161" t="n">
@@ -3133,7 +3121,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="2" t="n">
+      <c r="A162" s="1" t="n">
         <v>43221</v>
       </c>
       <c r="B162" t="n">
@@ -3150,7 +3138,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="2" t="n">
+      <c r="A163" s="1" t="n">
         <v>43252</v>
       </c>
       <c r="B163" t="n">
@@ -3167,7 +3155,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="2" t="n">
+      <c r="A164" s="1" t="n">
         <v>43282</v>
       </c>
       <c r="B164" t="n">
@@ -3184,7 +3172,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="2" t="n">
+      <c r="A165" s="1" t="n">
         <v>43313</v>
       </c>
       <c r="B165" t="n">
@@ -3201,7 +3189,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="2" t="n">
+      <c r="A166" s="1" t="n">
         <v>43344</v>
       </c>
       <c r="B166" t="n">
@@ -3218,7 +3206,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="2" t="n">
+      <c r="A167" s="1" t="n">
         <v>43374</v>
       </c>
       <c r="B167" t="n">
@@ -3235,7 +3223,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="2" t="n">
+      <c r="A168" s="1" t="n">
         <v>43405</v>
       </c>
       <c r="B168" t="n">
@@ -3252,7 +3240,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="2" t="n">
+      <c r="A169" s="1" t="n">
         <v>43435</v>
       </c>
       <c r="B169" t="n">
@@ -3269,7 +3257,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="2" t="n">
+      <c r="A170" s="1" t="n">
         <v>43466</v>
       </c>
       <c r="B170" t="n">
@@ -3286,7 +3274,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="2" t="n">
+      <c r="A171" s="1" t="n">
         <v>43497</v>
       </c>
       <c r="B171" t="n">
@@ -3303,7 +3291,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="2" t="n">
+      <c r="A172" s="1" t="n">
         <v>43525</v>
       </c>
       <c r="B172" t="n">
@@ -3320,7 +3308,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="2" t="n">
+      <c r="A173" s="1" t="n">
         <v>43556</v>
       </c>
       <c r="B173" t="n">
@@ -3337,7 +3325,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="2" t="n">
+      <c r="A174" s="1" t="n">
         <v>43586</v>
       </c>
       <c r="B174" t="n">
@@ -3354,7 +3342,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="2" t="n">
+      <c r="A175" s="1" t="n">
         <v>43617</v>
       </c>
       <c r="B175" t="n">
@@ -3371,7 +3359,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="2" t="n">
+      <c r="A176" s="1" t="n">
         <v>43647</v>
       </c>
       <c r="B176" t="n">
@@ -3388,7 +3376,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="2" t="n">
+      <c r="A177" s="1" t="n">
         <v>43678</v>
       </c>
       <c r="B177" t="n">
@@ -3405,7 +3393,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="2" t="n">
+      <c r="A178" s="1" t="n">
         <v>43709</v>
       </c>
       <c r="B178" t="n">
@@ -3422,7 +3410,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="2" t="n">
+      <c r="A179" s="1" t="n">
         <v>43739</v>
       </c>
       <c r="B179" t="n">
@@ -3439,7 +3427,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="2" t="n">
+      <c r="A180" s="1" t="n">
         <v>43770</v>
       </c>
       <c r="B180" t="n">
@@ -3456,7 +3444,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="2" t="n">
+      <c r="A181" s="1" t="n">
         <v>43800</v>
       </c>
       <c r="B181" t="n">
@@ -3473,7 +3461,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="2" t="n">
+      <c r="A182" s="1" t="n">
         <v>43831</v>
       </c>
       <c r="B182" t="n">
@@ -3490,7 +3478,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="2" t="n">
+      <c r="A183" s="1" t="n">
         <v>43862</v>
       </c>
       <c r="B183" t="n">
@@ -3507,7 +3495,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="2" t="n">
+      <c r="A184" s="1" t="n">
         <v>43891</v>
       </c>
       <c r="B184" t="n">
@@ -3524,7 +3512,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="2" t="n">
+      <c r="A185" s="1" t="n">
         <v>43922</v>
       </c>
       <c r="B185" t="n">
@@ -3541,7 +3529,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="2" t="n">
+      <c r="A186" s="1" t="n">
         <v>43952</v>
       </c>
       <c r="B186" t="n">
@@ -3558,7 +3546,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="2" t="n">
+      <c r="A187" s="1" t="n">
         <v>43983</v>
       </c>
       <c r="B187" t="n">
@@ -3575,7 +3563,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="2" t="n">
+      <c r="A188" s="1" t="n">
         <v>44013</v>
       </c>
       <c r="B188" t="n">
@@ -3592,7 +3580,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="2" t="n">
+      <c r="A189" s="1" t="n">
         <v>44044</v>
       </c>
       <c r="B189" t="n">
@@ -3609,7 +3597,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="2" t="n">
+      <c r="A190" s="1" t="n">
         <v>44075</v>
       </c>
       <c r="B190" t="n">
@@ -3626,7 +3614,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="2" t="n">
+      <c r="A191" s="1" t="n">
         <v>44105</v>
       </c>
       <c r="B191" t="n">
@@ -3643,7 +3631,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="2" t="n">
+      <c r="A192" s="1" t="n">
         <v>44136</v>
       </c>
       <c r="B192" t="n">
@@ -3660,7 +3648,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="2" t="n">
+      <c r="A193" s="1" t="n">
         <v>44166</v>
       </c>
       <c r="B193" t="n">
@@ -3677,7 +3665,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="2" t="n">
+      <c r="A194" s="1" t="n">
         <v>44197</v>
       </c>
       <c r="B194" t="n">
@@ -3694,7 +3682,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="2" t="n">
+      <c r="A195" s="1" t="n">
         <v>44228</v>
       </c>
       <c r="B195" t="n">
@@ -3711,7 +3699,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="2" t="n">
+      <c r="A196" s="1" t="n">
         <v>44256</v>
       </c>
       <c r="B196" t="n">
@@ -3728,7 +3716,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="2" t="n">
+      <c r="A197" s="1" t="n">
         <v>44287</v>
       </c>
       <c r="B197" t="n">
@@ -3745,7 +3733,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="2" t="n">
+      <c r="A198" s="1" t="n">
         <v>44317</v>
       </c>
       <c r="B198" t="n">
@@ -3762,7 +3750,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="2" t="n">
+      <c r="A199" s="1" t="n">
         <v>44348</v>
       </c>
       <c r="B199" t="n">
@@ -3779,7 +3767,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="2" t="n">
+      <c r="A200" s="1" t="n">
         <v>44378</v>
       </c>
       <c r="B200" t="n">
@@ -3796,7 +3784,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="2" t="n">
+      <c r="A201" s="1" t="n">
         <v>44409</v>
       </c>
       <c r="B201" t="n">
@@ -3813,7 +3801,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="2" t="n">
+      <c r="A202" s="1" t="n">
         <v>44440</v>
       </c>
       <c r="B202" t="n">
@@ -3830,7 +3818,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="2" t="n">
+      <c r="A203" s="1" t="n">
         <v>44470</v>
       </c>
       <c r="B203" t="n">
@@ -3847,7 +3835,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="2" t="n">
+      <c r="A204" s="1" t="n">
         <v>44501</v>
       </c>
       <c r="B204" t="n">
@@ -3864,7 +3852,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="2" t="n">
+      <c r="A205" s="1" t="n">
         <v>44531</v>
       </c>
       <c r="B205" t="n">
@@ -3881,7 +3869,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="2" t="n">
+      <c r="A206" s="1" t="n">
         <v>44562</v>
       </c>
       <c r="B206" t="n">
@@ -3898,7 +3886,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="2" t="n">
+      <c r="A207" s="1" t="n">
         <v>44593</v>
       </c>
       <c r="B207" t="n">
@@ -3915,7 +3903,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="2" t="n">
+      <c r="A208" s="1" t="n">
         <v>44621</v>
       </c>
       <c r="B208" t="n">
@@ -3932,7 +3920,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="2" t="n">
+      <c r="A209" s="1" t="n">
         <v>44652</v>
       </c>
       <c r="B209" t="n">
@@ -3949,7 +3937,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="2" t="n">
+      <c r="A210" s="1" t="n">
         <v>44682</v>
       </c>
       <c r="B210" t="n">
@@ -3966,7 +3954,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="2" t="n">
+      <c r="A211" s="1" t="n">
         <v>44713</v>
       </c>
       <c r="B211" t="n">
@@ -3983,7 +3971,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="2" t="n">
+      <c r="A212" s="1" t="n">
         <v>44743</v>
       </c>
       <c r="B212" t="n">
@@ -4000,7 +3988,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="2" t="n">
+      <c r="A213" s="1" t="n">
         <v>44774</v>
       </c>
       <c r="B213" t="n">
@@ -4017,7 +4005,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="2" t="n">
+      <c r="A214" s="1" t="n">
         <v>44805</v>
       </c>
       <c r="B214" t="n">
@@ -4034,7 +4022,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="2" t="n">
+      <c r="A215" s="1" t="n">
         <v>44835</v>
       </c>
       <c r="B215" t="n">
@@ -4051,7 +4039,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="2" t="n">
+      <c r="A216" s="1" t="n">
         <v>44866</v>
       </c>
       <c r="B216" t="n">
@@ -4068,7 +4056,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="2" t="n">
+      <c r="A217" s="1" t="n">
         <v>44896</v>
       </c>
       <c r="B217" t="n">
@@ -4085,7 +4073,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="2" t="n">
+      <c r="A218" s="1" t="n">
         <v>44927</v>
       </c>
       <c r="B218" t="n">
@@ -4102,7 +4090,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="2" t="n">
+      <c r="A219" s="1" t="n">
         <v>44958</v>
       </c>
       <c r="B219" t="n">
@@ -4119,7 +4107,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="2" t="n">
+      <c r="A220" s="1" t="n">
         <v>44986</v>
       </c>
       <c r="B220" t="n">
@@ -4136,7 +4124,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="2" t="n">
+      <c r="A221" s="1" t="n">
         <v>45017</v>
       </c>
       <c r="B221" t="n">
@@ -4153,7 +4141,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="2" t="n">
+      <c r="A222" s="1" t="n">
         <v>45047</v>
       </c>
       <c r="B222" t="n">
@@ -4170,7 +4158,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="2" t="n">
+      <c r="A223" s="1" t="n">
         <v>45078</v>
       </c>
       <c r="B223" t="n">
@@ -4187,7 +4175,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="2" t="n">
+      <c r="A224" s="1" t="n">
         <v>45108</v>
       </c>
       <c r="B224" t="n">
@@ -4204,7 +4192,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="2" t="n">
+      <c r="A225" s="1" t="n">
         <v>45139</v>
       </c>
       <c r="B225" t="n">
@@ -4221,7 +4209,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="2" t="n">
+      <c r="A226" s="1" t="n">
         <v>45170</v>
       </c>
       <c r="B226" t="n">
@@ -4238,7 +4226,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="2" t="n">
+      <c r="A227" s="1" t="n">
         <v>45200</v>
       </c>
       <c r="B227" t="n">
@@ -4255,7 +4243,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="2" t="n">
+      <c r="A228" s="1" t="n">
         <v>45231</v>
       </c>
       <c r="B228" t="n">
@@ -4272,7 +4260,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="2" t="n">
+      <c r="A229" s="1" t="n">
         <v>45261</v>
       </c>
       <c r="B229" t="n">
@@ -4289,7 +4277,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="2" t="n">
+      <c r="A230" s="1" t="n">
         <v>45292</v>
       </c>
       <c r="B230" t="n">
@@ -4306,7 +4294,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="2" t="n">
+      <c r="A231" s="1" t="n">
         <v>45323</v>
       </c>
       <c r="B231" t="n">
@@ -4323,7 +4311,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="2" t="n">
+      <c r="A232" s="1" t="n">
         <v>45352</v>
       </c>
       <c r="B232" t="n">
@@ -4340,7 +4328,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="2" t="n">
+      <c r="A233" s="1" t="n">
         <v>45383</v>
       </c>
       <c r="B233" t="n">
@@ -4357,7 +4345,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="2" t="n">
+      <c r="A234" s="1" t="n">
         <v>45413</v>
       </c>
       <c r="B234" t="n">
@@ -4374,7 +4362,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="2" t="n">
+      <c r="A235" s="1" t="n">
         <v>45444</v>
       </c>
       <c r="B235" t="n">
@@ -4391,7 +4379,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="2" t="n">
+      <c r="A236" s="1" t="n">
         <v>45474</v>
       </c>
       <c r="B236" t="n">
@@ -4408,7 +4396,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="2" t="n">
+      <c r="A237" s="1" t="n">
         <v>45505</v>
       </c>
       <c r="B237" t="n">
@@ -4425,7 +4413,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="2" t="n">
+      <c r="A238" s="1" t="n">
         <v>45536</v>
       </c>
       <c r="B238" t="n">
@@ -4442,7 +4430,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="2" t="n">
+      <c r="A239" s="1" t="n">
         <v>45566</v>
       </c>
       <c r="B239" t="n">
@@ -4459,7 +4447,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="2" t="n">
+      <c r="A240" s="1" t="n">
         <v>45597</v>
       </c>
       <c r="B240" t="n">
@@ -4476,7 +4464,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="2" t="n">
+      <c r="A241" s="1" t="n">
         <v>45627</v>
       </c>
       <c r="B241" t="n">
@@ -4493,7 +4481,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="2" t="n">
+      <c r="A242" s="1" t="n">
         <v>45658</v>
       </c>
       <c r="B242" t="n">
@@ -4510,7 +4498,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="2" t="n">
+      <c r="A243" s="1" t="n">
         <v>45689</v>
       </c>
       <c r="B243" t="n">
@@ -4527,7 +4515,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="2" t="n">
+      <c r="A244" s="1" t="n">
         <v>45717</v>
       </c>
       <c r="B244" t="n">
@@ -4544,7 +4532,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="2" t="n">
+      <c r="A245" s="1" t="n">
         <v>45748</v>
       </c>
       <c r="B245" t="n">
@@ -4561,7 +4549,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="2" t="n">
+      <c r="A246" s="1" t="n">
         <v>45778</v>
       </c>
       <c r="B246" t="n">
@@ -4578,7 +4566,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="2" t="n">
+      <c r="A247" s="1" t="n">
         <v>45809</v>
       </c>
       <c r="B247" t="n">
@@ -4595,7 +4583,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="2" t="n">
+      <c r="A248" s="1" t="n">
         <v>45839</v>
       </c>
       <c r="B248" t="n">
@@ -4612,7 +4600,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="2" t="n">
+      <c r="A249" s="1" t="n">
         <v>45870</v>
       </c>
       <c r="B249" t="n">
@@ -4629,7 +4617,7 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="2" t="n">
+      <c r="A250" s="1" t="n">
         <v>45901</v>
       </c>
       <c r="B250" t="n">
@@ -4646,7 +4634,7 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="2" t="n">
+      <c r="A251" s="1" t="n">
         <v>45931</v>
       </c>
       <c r="B251" t="n">
@@ -4663,7 +4651,7 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="2" t="n">
+      <c r="A252" s="1" t="n">
         <v>45962</v>
       </c>
       <c r="B252" t="n">
@@ -4680,7 +4668,7 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="2" t="n">
+      <c r="A253" s="1" t="n">
         <v>45992</v>
       </c>
       <c r="B253" t="n">
@@ -4697,7 +4685,7 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="2" t="n">
+      <c r="A254" s="1" t="n">
         <v>46023</v>
       </c>
       <c r="B254" t="n">
@@ -4714,7 +4702,7 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="2" t="n">
+      <c r="A255" s="1" t="n">
         <v>46054</v>
       </c>
       <c r="B255" t="n">
@@ -4731,7 +4719,7 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="2" t="n">
+      <c r="A256" s="1" t="n">
         <v>46082</v>
       </c>
       <c r="B256" t="n">
@@ -4748,7 +4736,7 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="2" t="n">
+      <c r="A257" s="1" t="n">
         <v>46113</v>
       </c>
       <c r="B257" t="n">
@@ -4765,7 +4753,7 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="2" t="n">
+      <c r="A258" s="1" t="n">
         <v>46143</v>
       </c>
       <c r="B258" t="n">
@@ -4782,7 +4770,7 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="2" t="n">
+      <c r="A259" s="1" t="n">
         <v>46174</v>
       </c>
       <c r="B259" t="n">
@@ -4799,7 +4787,7 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="2" t="n">
+      <c r="A260" s="1" t="n">
         <v>46204</v>
       </c>
       <c r="B260" t="n">
@@ -4830,79 +4818,79 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>tarih</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>01. Gıda Ve Alkolsüz İçecekler</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>02. Alkollü İçecekler, Tütün Ve Tütün Ürünleri</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>03. Giyim Ve Ayakkabı</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>04. Konut, Su, Elektrik, Gaz Ve Diğer Yakıtlar</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>05. Mobilya, Mefruşat Ve Evde Kullanılan Ekipmanlar İle Rutin Ev Bakım Ve Onarımı</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>06. Sağlık</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>07. Ulaştırma</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>08. Bilgi Ve İletişim</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>09. Eğlence, Dinlence, Spor Ve Kültür</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>10. Eğitim Hizmetleri</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>11. Lokantalar Ve Konaklama Hizmetleri</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>12. Sigorta Ve Finansal Hizmetler</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>13. Kişisel Bakım, Sosyal Koruma Ve Çeşitli Mal Ve Hizmetler</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="1" t="n">
         <v>38353</v>
       </c>
       <c r="B2" t="n">
@@ -4946,7 +4934,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="1" t="n">
         <v>38384</v>
       </c>
       <c r="B3" t="n">
@@ -4990,7 +4978,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="1" t="n">
         <v>38412</v>
       </c>
       <c r="B4" t="n">
@@ -5034,7 +5022,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="1" t="n">
         <v>38443</v>
       </c>
       <c r="B5" t="n">
@@ -5078,7 +5066,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="1" t="n">
         <v>38473</v>
       </c>
       <c r="B6" t="n">
@@ -5122,7 +5110,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="1" t="n">
         <v>38504</v>
       </c>
       <c r="B7" t="n">
@@ -5166,7 +5154,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="1" t="n">
         <v>38534</v>
       </c>
       <c r="B8" t="n">
@@ -5210,7 +5198,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="1" t="n">
         <v>38565</v>
       </c>
       <c r="B9" t="n">
@@ -5254,7 +5242,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="1" t="n">
         <v>38596</v>
       </c>
       <c r="B10" t="n">
@@ -5298,7 +5286,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="1" t="n">
         <v>38626</v>
       </c>
       <c r="B11" t="n">
@@ -5342,7 +5330,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="1" t="n">
         <v>38657</v>
       </c>
       <c r="B12" t="n">
@@ -5386,7 +5374,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="1" t="n">
         <v>38687</v>
       </c>
       <c r="B13" t="n">
@@ -5430,7 +5418,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="1" t="n">
         <v>38718</v>
       </c>
       <c r="B14" t="n">
@@ -5474,7 +5462,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="1" t="n">
         <v>38749</v>
       </c>
       <c r="B15" t="n">
@@ -5518,7 +5506,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="1" t="n">
         <v>38777</v>
       </c>
       <c r="B16" t="n">
@@ -5562,7 +5550,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="1" t="n">
         <v>38808</v>
       </c>
       <c r="B17" t="n">
@@ -5606,7 +5594,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="1" t="n">
         <v>38838</v>
       </c>
       <c r="B18" t="n">
@@ -5650,7 +5638,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="1" t="n">
         <v>38869</v>
       </c>
       <c r="B19" t="n">
@@ -5694,7 +5682,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="1" t="n">
         <v>38899</v>
       </c>
       <c r="B20" t="n">
@@ -5738,7 +5726,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="1" t="n">
         <v>38930</v>
       </c>
       <c r="B21" t="n">
@@ -5782,7 +5770,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="1" t="n">
         <v>38961</v>
       </c>
       <c r="B22" t="n">
@@ -5826,7 +5814,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="1" t="n">
         <v>38991</v>
       </c>
       <c r="B23" t="n">
@@ -5870,7 +5858,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="1" t="n">
         <v>39022</v>
       </c>
       <c r="B24" t="n">
@@ -5914,7 +5902,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="1" t="n">
         <v>39052</v>
       </c>
       <c r="B25" t="n">
@@ -5958,7 +5946,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="1" t="n">
         <v>39083</v>
       </c>
       <c r="B26" t="n">
@@ -6002,7 +5990,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="1" t="n">
         <v>39114</v>
       </c>
       <c r="B27" t="n">
@@ -6046,7 +6034,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="1" t="n">
         <v>39142</v>
       </c>
       <c r="B28" t="n">
@@ -6090,7 +6078,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="1" t="n">
         <v>39173</v>
       </c>
       <c r="B29" t="n">
@@ -6134,7 +6122,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="1" t="n">
         <v>39203</v>
       </c>
       <c r="B30" t="n">
@@ -6178,7 +6166,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="1" t="n">
         <v>39234</v>
       </c>
       <c r="B31" t="n">
@@ -6222,7 +6210,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="1" t="n">
         <v>39264</v>
       </c>
       <c r="B32" t="n">
@@ -6266,7 +6254,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="1" t="n">
         <v>39295</v>
       </c>
       <c r="B33" t="n">
@@ -6310,7 +6298,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="1" t="n">
         <v>39326</v>
       </c>
       <c r="B34" t="n">
@@ -6354,7 +6342,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="1" t="n">
         <v>39356</v>
       </c>
       <c r="B35" t="n">
@@ -6398,7 +6386,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="1" t="n">
         <v>39387</v>
       </c>
       <c r="B36" t="n">
@@ -6442,7 +6430,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="1" t="n">
         <v>39417</v>
       </c>
       <c r="B37" t="n">
@@ -6486,7 +6474,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="1" t="n">
         <v>39448</v>
       </c>
       <c r="B38" t="n">
@@ -6530,7 +6518,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="1" t="n">
         <v>39479</v>
       </c>
       <c r="B39" t="n">
@@ -6574,7 +6562,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="1" t="n">
         <v>39508</v>
       </c>
       <c r="B40" t="n">
@@ -6618,7 +6606,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" s="1" t="n">
         <v>39539</v>
       </c>
       <c r="B41" t="n">
@@ -6662,7 +6650,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="1" t="n">
         <v>39569</v>
       </c>
       <c r="B42" t="n">
@@ -6706,7 +6694,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" s="1" t="n">
         <v>39600</v>
       </c>
       <c r="B43" t="n">
@@ -6750,7 +6738,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" s="1" t="n">
         <v>39630</v>
       </c>
       <c r="B44" t="n">
@@ -6794,7 +6782,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" s="1" t="n">
         <v>39661</v>
       </c>
       <c r="B45" t="n">
@@ -6838,7 +6826,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="1" t="n">
         <v>39692</v>
       </c>
       <c r="B46" t="n">
@@ -6882,7 +6870,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="A47" s="1" t="n">
         <v>39722</v>
       </c>
       <c r="B47" t="n">
@@ -6926,7 +6914,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="1" t="n">
         <v>39753</v>
       </c>
       <c r="B48" t="n">
@@ -6970,7 +6958,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="A49" s="1" t="n">
         <v>39783</v>
       </c>
       <c r="B49" t="n">
@@ -7014,7 +7002,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="1" t="n">
         <v>39814</v>
       </c>
       <c r="B50" t="n">
@@ -7058,7 +7046,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" s="1" t="n">
         <v>39845</v>
       </c>
       <c r="B51" t="n">
@@ -7102,7 +7090,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="A52" s="1" t="n">
         <v>39873</v>
       </c>
       <c r="B52" t="n">
@@ -7146,7 +7134,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" s="1" t="n">
         <v>39904</v>
       </c>
       <c r="B53" t="n">
@@ -7190,7 +7178,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n">
+      <c r="A54" s="1" t="n">
         <v>39934</v>
       </c>
       <c r="B54" t="n">
@@ -7234,7 +7222,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n">
+      <c r="A55" s="1" t="n">
         <v>39965</v>
       </c>
       <c r="B55" t="n">
@@ -7278,7 +7266,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
+      <c r="A56" s="1" t="n">
         <v>39995</v>
       </c>
       <c r="B56" t="n">
@@ -7322,7 +7310,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="A57" s="1" t="n">
         <v>40026</v>
       </c>
       <c r="B57" t="n">
@@ -7366,7 +7354,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
+      <c r="A58" s="1" t="n">
         <v>40057</v>
       </c>
       <c r="B58" t="n">
@@ -7410,7 +7398,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
+      <c r="A59" s="1" t="n">
         <v>40087</v>
       </c>
       <c r="B59" t="n">
@@ -7454,7 +7442,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
+      <c r="A60" s="1" t="n">
         <v>40118</v>
       </c>
       <c r="B60" t="n">
@@ -7498,7 +7486,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
+      <c r="A61" s="1" t="n">
         <v>40148</v>
       </c>
       <c r="B61" t="n">
@@ -7542,7 +7530,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
+      <c r="A62" s="1" t="n">
         <v>40179</v>
       </c>
       <c r="B62" t="n">
@@ -7586,7 +7574,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n">
+      <c r="A63" s="1" t="n">
         <v>40210</v>
       </c>
       <c r="B63" t="n">
@@ -7630,7 +7618,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n">
+      <c r="A64" s="1" t="n">
         <v>40238</v>
       </c>
       <c r="B64" t="n">
@@ -7674,7 +7662,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n">
+      <c r="A65" s="1" t="n">
         <v>40269</v>
       </c>
       <c r="B65" t="n">
@@ -7718,7 +7706,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n">
+      <c r="A66" s="1" t="n">
         <v>40299</v>
       </c>
       <c r="B66" t="n">
@@ -7762,7 +7750,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n">
+      <c r="A67" s="1" t="n">
         <v>40330</v>
       </c>
       <c r="B67" t="n">
@@ -7806,7 +7794,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n">
+      <c r="A68" s="1" t="n">
         <v>40360</v>
       </c>
       <c r="B68" t="n">
@@ -7850,7 +7838,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n">
+      <c r="A69" s="1" t="n">
         <v>40391</v>
       </c>
       <c r="B69" t="n">
@@ -7894,7 +7882,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="n">
+      <c r="A70" s="1" t="n">
         <v>40422</v>
       </c>
       <c r="B70" t="n">
@@ -7938,7 +7926,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="n">
+      <c r="A71" s="1" t="n">
         <v>40452</v>
       </c>
       <c r="B71" t="n">
@@ -7982,7 +7970,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="n">
+      <c r="A72" s="1" t="n">
         <v>40483</v>
       </c>
       <c r="B72" t="n">
@@ -8026,7 +8014,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="n">
+      <c r="A73" s="1" t="n">
         <v>40513</v>
       </c>
       <c r="B73" t="n">
@@ -8070,7 +8058,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="n">
+      <c r="A74" s="1" t="n">
         <v>40544</v>
       </c>
       <c r="B74" t="n">
@@ -8114,7 +8102,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="n">
+      <c r="A75" s="1" t="n">
         <v>40575</v>
       </c>
       <c r="B75" t="n">
@@ -8158,7 +8146,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="n">
+      <c r="A76" s="1" t="n">
         <v>40603</v>
       </c>
       <c r="B76" t="n">
@@ -8202,7 +8190,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n">
+      <c r="A77" s="1" t="n">
         <v>40634</v>
       </c>
       <c r="B77" t="n">
@@ -8246,7 +8234,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n">
+      <c r="A78" s="1" t="n">
         <v>40664</v>
       </c>
       <c r="B78" t="n">
@@ -8290,7 +8278,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="n">
+      <c r="A79" s="1" t="n">
         <v>40695</v>
       </c>
       <c r="B79" t="n">
@@ -8334,7 +8322,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="n">
+      <c r="A80" s="1" t="n">
         <v>40725</v>
       </c>
       <c r="B80" t="n">
@@ -8378,7 +8366,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="n">
+      <c r="A81" s="1" t="n">
         <v>40756</v>
       </c>
       <c r="B81" t="n">
@@ -8422,7 +8410,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="n">
+      <c r="A82" s="1" t="n">
         <v>40787</v>
       </c>
       <c r="B82" t="n">
@@ -8466,7 +8454,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="n">
+      <c r="A83" s="1" t="n">
         <v>40817</v>
       </c>
       <c r="B83" t="n">
@@ -8510,7 +8498,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="n">
+      <c r="A84" s="1" t="n">
         <v>40848</v>
       </c>
       <c r="B84" t="n">
@@ -8554,7 +8542,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="n">
+      <c r="A85" s="1" t="n">
         <v>40878</v>
       </c>
       <c r="B85" t="n">
@@ -8598,7 +8586,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="n">
+      <c r="A86" s="1" t="n">
         <v>40909</v>
       </c>
       <c r="B86" t="n">
@@ -8642,7 +8630,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="n">
+      <c r="A87" s="1" t="n">
         <v>40940</v>
       </c>
       <c r="B87" t="n">
@@ -8686,7 +8674,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="n">
+      <c r="A88" s="1" t="n">
         <v>40969</v>
       </c>
       <c r="B88" t="n">
@@ -8730,7 +8718,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="n">
+      <c r="A89" s="1" t="n">
         <v>41000</v>
       </c>
       <c r="B89" t="n">
@@ -8774,7 +8762,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="n">
+      <c r="A90" s="1" t="n">
         <v>41030</v>
       </c>
       <c r="B90" t="n">
@@ -8818,7 +8806,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="n">
+      <c r="A91" s="1" t="n">
         <v>41061</v>
       </c>
       <c r="B91" t="n">
@@ -8862,7 +8850,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="n">
+      <c r="A92" s="1" t="n">
         <v>41091</v>
       </c>
       <c r="B92" t="n">
@@ -8906,7 +8894,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="n">
+      <c r="A93" s="1" t="n">
         <v>41122</v>
       </c>
       <c r="B93" t="n">
@@ -8950,7 +8938,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="n">
+      <c r="A94" s="1" t="n">
         <v>41153</v>
       </c>
       <c r="B94" t="n">
@@ -8994,7 +8982,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="n">
+      <c r="A95" s="1" t="n">
         <v>41183</v>
       </c>
       <c r="B95" t="n">
@@ -9038,7 +9026,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="n">
+      <c r="A96" s="1" t="n">
         <v>41214</v>
       </c>
       <c r="B96" t="n">
@@ -9082,7 +9070,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="n">
+      <c r="A97" s="1" t="n">
         <v>41244</v>
       </c>
       <c r="B97" t="n">
@@ -9126,7 +9114,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="n">
+      <c r="A98" s="1" t="n">
         <v>41275</v>
       </c>
       <c r="B98" t="n">
@@ -9170,7 +9158,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="n">
+      <c r="A99" s="1" t="n">
         <v>41306</v>
       </c>
       <c r="B99" t="n">
@@ -9214,7 +9202,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="n">
+      <c r="A100" s="1" t="n">
         <v>41334</v>
       </c>
       <c r="B100" t="n">
@@ -9258,7 +9246,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="n">
+      <c r="A101" s="1" t="n">
         <v>41365</v>
       </c>
       <c r="B101" t="n">
@@ -9302,7 +9290,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="n">
+      <c r="A102" s="1" t="n">
         <v>41395</v>
       </c>
       <c r="B102" t="n">
@@ -9346,7 +9334,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="n">
+      <c r="A103" s="1" t="n">
         <v>41426</v>
       </c>
       <c r="B103" t="n">
@@ -9390,7 +9378,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="2" t="n">
+      <c r="A104" s="1" t="n">
         <v>41456</v>
       </c>
       <c r="B104" t="n">
@@ -9434,7 +9422,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="2" t="n">
+      <c r="A105" s="1" t="n">
         <v>41487</v>
       </c>
       <c r="B105" t="n">
@@ -9478,7 +9466,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="n">
+      <c r="A106" s="1" t="n">
         <v>41518</v>
       </c>
       <c r="B106" t="n">
@@ -9522,7 +9510,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="n">
+      <c r="A107" s="1" t="n">
         <v>41548</v>
       </c>
       <c r="B107" t="n">
@@ -9566,7 +9554,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="n">
+      <c r="A108" s="1" t="n">
         <v>41579</v>
       </c>
       <c r="B108" t="n">
@@ -9610,7 +9598,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="n">
+      <c r="A109" s="1" t="n">
         <v>41609</v>
       </c>
       <c r="B109" t="n">
@@ -9654,7 +9642,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="n">
+      <c r="A110" s="1" t="n">
         <v>41640</v>
       </c>
       <c r="B110" t="n">
@@ -9698,7 +9686,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="n">
+      <c r="A111" s="1" t="n">
         <v>41671</v>
       </c>
       <c r="B111" t="n">
@@ -9742,7 +9730,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="n">
+      <c r="A112" s="1" t="n">
         <v>41699</v>
       </c>
       <c r="B112" t="n">
@@ -9786,7 +9774,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="2" t="n">
+      <c r="A113" s="1" t="n">
         <v>41730</v>
       </c>
       <c r="B113" t="n">
@@ -9830,7 +9818,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="2" t="n">
+      <c r="A114" s="1" t="n">
         <v>41760</v>
       </c>
       <c r="B114" t="n">
@@ -9874,7 +9862,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="n">
+      <c r="A115" s="1" t="n">
         <v>41791</v>
       </c>
       <c r="B115" t="n">
@@ -9918,7 +9906,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="n">
+      <c r="A116" s="1" t="n">
         <v>41821</v>
       </c>
       <c r="B116" t="n">
@@ -9962,7 +9950,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="2" t="n">
+      <c r="A117" s="1" t="n">
         <v>41852</v>
       </c>
       <c r="B117" t="n">
@@ -10006,7 +9994,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="2" t="n">
+      <c r="A118" s="1" t="n">
         <v>41883</v>
       </c>
       <c r="B118" t="n">
@@ -10050,7 +10038,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="n">
+      <c r="A119" s="1" t="n">
         <v>41913</v>
       </c>
       <c r="B119" t="n">
@@ -10094,7 +10082,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="n">
+      <c r="A120" s="1" t="n">
         <v>41944</v>
       </c>
       <c r="B120" t="n">
@@ -10138,7 +10126,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="2" t="n">
+      <c r="A121" s="1" t="n">
         <v>41974</v>
       </c>
       <c r="B121" t="n">
@@ -10182,7 +10170,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="2" t="n">
+      <c r="A122" s="1" t="n">
         <v>42005</v>
       </c>
       <c r="B122" t="n">
@@ -10226,7 +10214,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="2" t="n">
+      <c r="A123" s="1" t="n">
         <v>42036</v>
       </c>
       <c r="B123" t="n">
@@ -10270,7 +10258,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="n">
+      <c r="A124" s="1" t="n">
         <v>42064</v>
       </c>
       <c r="B124" t="n">
@@ -10314,7 +10302,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="2" t="n">
+      <c r="A125" s="1" t="n">
         <v>42095</v>
       </c>
       <c r="B125" t="n">
@@ -10358,7 +10346,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="2" t="n">
+      <c r="A126" s="1" t="n">
         <v>42125</v>
       </c>
       <c r="B126" t="n">
@@ -10402,7 +10390,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="2" t="n">
+      <c r="A127" s="1" t="n">
         <v>42156</v>
       </c>
       <c r="B127" t="n">
@@ -10446,7 +10434,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="2" t="n">
+      <c r="A128" s="1" t="n">
         <v>42186</v>
       </c>
       <c r="B128" t="n">
@@ -10490,7 +10478,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="2" t="n">
+      <c r="A129" s="1" t="n">
         <v>42217</v>
       </c>
       <c r="B129" t="n">
@@ -10534,7 +10522,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="2" t="n">
+      <c r="A130" s="1" t="n">
         <v>42248</v>
       </c>
       <c r="B130" t="n">
@@ -10578,7 +10566,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="2" t="n">
+      <c r="A131" s="1" t="n">
         <v>42278</v>
       </c>
       <c r="B131" t="n">
@@ -10622,7 +10610,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="2" t="n">
+      <c r="A132" s="1" t="n">
         <v>42309</v>
       </c>
       <c r="B132" t="n">
@@ -10666,7 +10654,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="2" t="n">
+      <c r="A133" s="1" t="n">
         <v>42339</v>
       </c>
       <c r="B133" t="n">
@@ -10710,7 +10698,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="2" t="n">
+      <c r="A134" s="1" t="n">
         <v>42370</v>
       </c>
       <c r="B134" t="n">
@@ -10754,7 +10742,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="2" t="n">
+      <c r="A135" s="1" t="n">
         <v>42401</v>
       </c>
       <c r="B135" t="n">
@@ -10798,7 +10786,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="2" t="n">
+      <c r="A136" s="1" t="n">
         <v>42430</v>
       </c>
       <c r="B136" t="n">
@@ -10842,7 +10830,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="2" t="n">
+      <c r="A137" s="1" t="n">
         <v>42461</v>
       </c>
       <c r="B137" t="n">
@@ -10886,7 +10874,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="2" t="n">
+      <c r="A138" s="1" t="n">
         <v>42491</v>
       </c>
       <c r="B138" t="n">
@@ -10930,7 +10918,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="2" t="n">
+      <c r="A139" s="1" t="n">
         <v>42522</v>
       </c>
       <c r="B139" t="n">
@@ -10974,7 +10962,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="2" t="n">
+      <c r="A140" s="1" t="n">
         <v>42552</v>
       </c>
       <c r="B140" t="n">
@@ -11018,7 +11006,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="2" t="n">
+      <c r="A141" s="1" t="n">
         <v>42583</v>
       </c>
       <c r="B141" t="n">
@@ -11062,7 +11050,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="2" t="n">
+      <c r="A142" s="1" t="n">
         <v>42614</v>
       </c>
       <c r="B142" t="n">
@@ -11106,7 +11094,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="2" t="n">
+      <c r="A143" s="1" t="n">
         <v>42644</v>
       </c>
       <c r="B143" t="n">
@@ -11150,7 +11138,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="2" t="n">
+      <c r="A144" s="1" t="n">
         <v>42675</v>
       </c>
       <c r="B144" t="n">
@@ -11194,7 +11182,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="2" t="n">
+      <c r="A145" s="1" t="n">
         <v>42705</v>
       </c>
       <c r="B145" t="n">
@@ -11238,7 +11226,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="2" t="n">
+      <c r="A146" s="1" t="n">
         <v>42736</v>
       </c>
       <c r="B146" t="n">
@@ -11282,7 +11270,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="2" t="n">
+      <c r="A147" s="1" t="n">
         <v>42767</v>
       </c>
       <c r="B147" t="n">
@@ -11326,7 +11314,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="2" t="n">
+      <c r="A148" s="1" t="n">
         <v>42795</v>
       </c>
       <c r="B148" t="n">
@@ -11370,7 +11358,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="2" t="n">
+      <c r="A149" s="1" t="n">
         <v>42826</v>
       </c>
       <c r="B149" t="n">
@@ -11414,7 +11402,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="2" t="n">
+      <c r="A150" s="1" t="n">
         <v>42856</v>
       </c>
       <c r="B150" t="n">
@@ -11458,7 +11446,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="2" t="n">
+      <c r="A151" s="1" t="n">
         <v>42887</v>
       </c>
       <c r="B151" t="n">
@@ -11502,7 +11490,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="2" t="n">
+      <c r="A152" s="1" t="n">
         <v>42917</v>
       </c>
       <c r="B152" t="n">
@@ -11546,7 +11534,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="2" t="n">
+      <c r="A153" s="1" t="n">
         <v>42948</v>
       </c>
       <c r="B153" t="n">
@@ -11590,7 +11578,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="2" t="n">
+      <c r="A154" s="1" t="n">
         <v>42979</v>
       </c>
       <c r="B154" t="n">
@@ -11634,7 +11622,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="2" t="n">
+      <c r="A155" s="1" t="n">
         <v>43009</v>
       </c>
       <c r="B155" t="n">
@@ -11678,7 +11666,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="2" t="n">
+      <c r="A156" s="1" t="n">
         <v>43040</v>
       </c>
       <c r="B156" t="n">
@@ -11722,7 +11710,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="2" t="n">
+      <c r="A157" s="1" t="n">
         <v>43070</v>
       </c>
       <c r="B157" t="n">
@@ -11766,7 +11754,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="2" t="n">
+      <c r="A158" s="1" t="n">
         <v>43101</v>
       </c>
       <c r="B158" t="n">
@@ -11810,7 +11798,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="2" t="n">
+      <c r="A159" s="1" t="n">
         <v>43132</v>
       </c>
       <c r="B159" t="n">
@@ -11854,7 +11842,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="2" t="n">
+      <c r="A160" s="1" t="n">
         <v>43160</v>
       </c>
       <c r="B160" t="n">
@@ -11898,7 +11886,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="2" t="n">
+      <c r="A161" s="1" t="n">
         <v>43191</v>
       </c>
       <c r="B161" t="n">
@@ -11942,7 +11930,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="2" t="n">
+      <c r="A162" s="1" t="n">
         <v>43221</v>
       </c>
       <c r="B162" t="n">
@@ -11986,7 +11974,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="2" t="n">
+      <c r="A163" s="1" t="n">
         <v>43252</v>
       </c>
       <c r="B163" t="n">
@@ -12030,7 +12018,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="2" t="n">
+      <c r="A164" s="1" t="n">
         <v>43282</v>
       </c>
       <c r="B164" t="n">
@@ -12074,7 +12062,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="2" t="n">
+      <c r="A165" s="1" t="n">
         <v>43313</v>
       </c>
       <c r="B165" t="n">
@@ -12118,7 +12106,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="2" t="n">
+      <c r="A166" s="1" t="n">
         <v>43344</v>
       </c>
       <c r="B166" t="n">
@@ -12162,7 +12150,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="2" t="n">
+      <c r="A167" s="1" t="n">
         <v>43374</v>
       </c>
       <c r="B167" t="n">
@@ -12206,7 +12194,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="2" t="n">
+      <c r="A168" s="1" t="n">
         <v>43405</v>
       </c>
       <c r="B168" t="n">
@@ -12250,7 +12238,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="2" t="n">
+      <c r="A169" s="1" t="n">
         <v>43435</v>
       </c>
       <c r="B169" t="n">
@@ -12294,7 +12282,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="2" t="n">
+      <c r="A170" s="1" t="n">
         <v>43466</v>
       </c>
       <c r="B170" t="n">
@@ -12338,7 +12326,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="2" t="n">
+      <c r="A171" s="1" t="n">
         <v>43497</v>
       </c>
       <c r="B171" t="n">
@@ -12382,7 +12370,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="2" t="n">
+      <c r="A172" s="1" t="n">
         <v>43525</v>
       </c>
       <c r="B172" t="n">
@@ -12426,7 +12414,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="2" t="n">
+      <c r="A173" s="1" t="n">
         <v>43556</v>
       </c>
       <c r="B173" t="n">
@@ -12470,7 +12458,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="2" t="n">
+      <c r="A174" s="1" t="n">
         <v>43586</v>
       </c>
       <c r="B174" t="n">
@@ -12514,7 +12502,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="2" t="n">
+      <c r="A175" s="1" t="n">
         <v>43617</v>
       </c>
       <c r="B175" t="n">
@@ -12558,7 +12546,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="2" t="n">
+      <c r="A176" s="1" t="n">
         <v>43647</v>
       </c>
       <c r="B176" t="n">
@@ -12602,7 +12590,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="2" t="n">
+      <c r="A177" s="1" t="n">
         <v>43678</v>
       </c>
       <c r="B177" t="n">
@@ -12646,7 +12634,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="2" t="n">
+      <c r="A178" s="1" t="n">
         <v>43709</v>
       </c>
       <c r="B178" t="n">
@@ -12690,7 +12678,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="2" t="n">
+      <c r="A179" s="1" t="n">
         <v>43739</v>
       </c>
       <c r="B179" t="n">
@@ -12734,7 +12722,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="2" t="n">
+      <c r="A180" s="1" t="n">
         <v>43770</v>
       </c>
       <c r="B180" t="n">
@@ -12778,7 +12766,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="2" t="n">
+      <c r="A181" s="1" t="n">
         <v>43800</v>
       </c>
       <c r="B181" t="n">
@@ -12822,7 +12810,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="2" t="n">
+      <c r="A182" s="1" t="n">
         <v>43831</v>
       </c>
       <c r="B182" t="n">
@@ -12866,7 +12854,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="2" t="n">
+      <c r="A183" s="1" t="n">
         <v>43862</v>
       </c>
       <c r="B183" t="n">
@@ -12910,7 +12898,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="2" t="n">
+      <c r="A184" s="1" t="n">
         <v>43891</v>
       </c>
       <c r="B184" t="n">
@@ -12954,7 +12942,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="2" t="n">
+      <c r="A185" s="1" t="n">
         <v>43922</v>
       </c>
       <c r="B185" t="n">
@@ -12998,7 +12986,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="2" t="n">
+      <c r="A186" s="1" t="n">
         <v>43952</v>
       </c>
       <c r="B186" t="n">
@@ -13042,7 +13030,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="2" t="n">
+      <c r="A187" s="1" t="n">
         <v>43983</v>
       </c>
       <c r="B187" t="n">
@@ -13086,7 +13074,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="2" t="n">
+      <c r="A188" s="1" t="n">
         <v>44013</v>
       </c>
       <c r="B188" t="n">
@@ -13130,7 +13118,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="2" t="n">
+      <c r="A189" s="1" t="n">
         <v>44044</v>
       </c>
       <c r="B189" t="n">
@@ -13174,7 +13162,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="2" t="n">
+      <c r="A190" s="1" t="n">
         <v>44075</v>
       </c>
       <c r="B190" t="n">
@@ -13218,7 +13206,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="2" t="n">
+      <c r="A191" s="1" t="n">
         <v>44105</v>
       </c>
       <c r="B191" t="n">
@@ -13262,7 +13250,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="2" t="n">
+      <c r="A192" s="1" t="n">
         <v>44136</v>
       </c>
       <c r="B192" t="n">
@@ -13306,7 +13294,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="2" t="n">
+      <c r="A193" s="1" t="n">
         <v>44166</v>
       </c>
       <c r="B193" t="n">
@@ -13350,7 +13338,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="2" t="n">
+      <c r="A194" s="1" t="n">
         <v>44197</v>
       </c>
       <c r="B194" t="n">
@@ -13394,7 +13382,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="2" t="n">
+      <c r="A195" s="1" t="n">
         <v>44228</v>
       </c>
       <c r="B195" t="n">
@@ -13438,7 +13426,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="2" t="n">
+      <c r="A196" s="1" t="n">
         <v>44256</v>
       </c>
       <c r="B196" t="n">
@@ -13482,7 +13470,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="2" t="n">
+      <c r="A197" s="1" t="n">
         <v>44287</v>
       </c>
       <c r="B197" t="n">
@@ -13526,7 +13514,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="2" t="n">
+      <c r="A198" s="1" t="n">
         <v>44317</v>
       </c>
       <c r="B198" t="n">
@@ -13570,7 +13558,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="2" t="n">
+      <c r="A199" s="1" t="n">
         <v>44348</v>
       </c>
       <c r="B199" t="n">
@@ -13614,7 +13602,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="2" t="n">
+      <c r="A200" s="1" t="n">
         <v>44378</v>
       </c>
       <c r="B200" t="n">
@@ -13658,7 +13646,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="2" t="n">
+      <c r="A201" s="1" t="n">
         <v>44409</v>
       </c>
       <c r="B201" t="n">
@@ -13702,7 +13690,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="2" t="n">
+      <c r="A202" s="1" t="n">
         <v>44440</v>
       </c>
       <c r="B202" t="n">
@@ -13746,7 +13734,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="2" t="n">
+      <c r="A203" s="1" t="n">
         <v>44470</v>
       </c>
       <c r="B203" t="n">
@@ -13790,7 +13778,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="2" t="n">
+      <c r="A204" s="1" t="n">
         <v>44501</v>
       </c>
       <c r="B204" t="n">
@@ -13834,7 +13822,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="2" t="n">
+      <c r="A205" s="1" t="n">
         <v>44531</v>
       </c>
       <c r="B205" t="n">
@@ -13878,7 +13866,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="2" t="n">
+      <c r="A206" s="1" t="n">
         <v>44562</v>
       </c>
       <c r="B206" t="n">
@@ -13922,7 +13910,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="2" t="n">
+      <c r="A207" s="1" t="n">
         <v>44593</v>
       </c>
       <c r="B207" t="n">
@@ -13966,7 +13954,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="2" t="n">
+      <c r="A208" s="1" t="n">
         <v>44621</v>
       </c>
       <c r="B208" t="n">
@@ -14010,7 +13998,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="2" t="n">
+      <c r="A209" s="1" t="n">
         <v>44652</v>
       </c>
       <c r="B209" t="n">
@@ -14054,7 +14042,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="2" t="n">
+      <c r="A210" s="1" t="n">
         <v>44682</v>
       </c>
       <c r="B210" t="n">
@@ -14098,7 +14086,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="2" t="n">
+      <c r="A211" s="1" t="n">
         <v>44713</v>
       </c>
       <c r="B211" t="n">
@@ -14142,7 +14130,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="2" t="n">
+      <c r="A212" s="1" t="n">
         <v>44743</v>
       </c>
       <c r="B212" t="n">
@@ -14186,7 +14174,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="2" t="n">
+      <c r="A213" s="1" t="n">
         <v>44774</v>
       </c>
       <c r="B213" t="n">
@@ -14230,7 +14218,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="2" t="n">
+      <c r="A214" s="1" t="n">
         <v>44805</v>
       </c>
       <c r="B214" t="n">
@@ -14274,7 +14262,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="2" t="n">
+      <c r="A215" s="1" t="n">
         <v>44835</v>
       </c>
       <c r="B215" t="n">
@@ -14318,7 +14306,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="2" t="n">
+      <c r="A216" s="1" t="n">
         <v>44866</v>
       </c>
       <c r="B216" t="n">
@@ -14362,7 +14350,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="2" t="n">
+      <c r="A217" s="1" t="n">
         <v>44896</v>
       </c>
       <c r="B217" t="n">
@@ -14406,7 +14394,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="2" t="n">
+      <c r="A218" s="1" t="n">
         <v>44927</v>
       </c>
       <c r="B218" t="n">
@@ -14450,7 +14438,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="2" t="n">
+      <c r="A219" s="1" t="n">
         <v>44958</v>
       </c>
       <c r="B219" t="n">
@@ -14494,7 +14482,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="2" t="n">
+      <c r="A220" s="1" t="n">
         <v>44986</v>
       </c>
       <c r="B220" t="n">
@@ -14538,7 +14526,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="2" t="n">
+      <c r="A221" s="1" t="n">
         <v>45017</v>
       </c>
       <c r="B221" t="n">
@@ -14582,7 +14570,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="2" t="n">
+      <c r="A222" s="1" t="n">
         <v>45047</v>
       </c>
       <c r="B222" t="n">
@@ -14626,7 +14614,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="2" t="n">
+      <c r="A223" s="1" t="n">
         <v>45078</v>
       </c>
       <c r="B223" t="n">
@@ -14670,7 +14658,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="2" t="n">
+      <c r="A224" s="1" t="n">
         <v>45108</v>
       </c>
       <c r="B224" t="n">
@@ -14714,7 +14702,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="2" t="n">
+      <c r="A225" s="1" t="n">
         <v>45139</v>
       </c>
       <c r="B225" t="n">
@@ -14758,7 +14746,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="2" t="n">
+      <c r="A226" s="1" t="n">
         <v>45170</v>
       </c>
       <c r="B226" t="n">
@@ -14802,7 +14790,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="2" t="n">
+      <c r="A227" s="1" t="n">
         <v>45200</v>
       </c>
       <c r="B227" t="n">
@@ -14846,7 +14834,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="2" t="n">
+      <c r="A228" s="1" t="n">
         <v>45231</v>
       </c>
       <c r="B228" t="n">
@@ -14890,7 +14878,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="2" t="n">
+      <c r="A229" s="1" t="n">
         <v>45261</v>
       </c>
       <c r="B229" t="n">
@@ -14934,7 +14922,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="2" t="n">
+      <c r="A230" s="1" t="n">
         <v>45292</v>
       </c>
       <c r="B230" t="n">
@@ -14978,7 +14966,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="2" t="n">
+      <c r="A231" s="1" t="n">
         <v>45323</v>
       </c>
       <c r="B231" t="n">
@@ -15022,7 +15010,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="2" t="n">
+      <c r="A232" s="1" t="n">
         <v>45352</v>
       </c>
       <c r="B232" t="n">
@@ -15066,7 +15054,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="2" t="n">
+      <c r="A233" s="1" t="n">
         <v>45383</v>
       </c>
       <c r="B233" t="n">
@@ -15110,7 +15098,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="2" t="n">
+      <c r="A234" s="1" t="n">
         <v>45413</v>
       </c>
       <c r="B234" t="n">
@@ -15154,7 +15142,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="2" t="n">
+      <c r="A235" s="1" t="n">
         <v>45444</v>
       </c>
       <c r="B235" t="n">
@@ -15198,7 +15186,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="2" t="n">
+      <c r="A236" s="1" t="n">
         <v>45474</v>
       </c>
       <c r="B236" t="n">
@@ -15242,7 +15230,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="2" t="n">
+      <c r="A237" s="1" t="n">
         <v>45505</v>
       </c>
       <c r="B237" t="n">
@@ -15286,7 +15274,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="2" t="n">
+      <c r="A238" s="1" t="n">
         <v>45536</v>
       </c>
       <c r="B238" t="n">
@@ -15330,7 +15318,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="2" t="n">
+      <c r="A239" s="1" t="n">
         <v>45566</v>
       </c>
       <c r="B239" t="n">
@@ -15374,7 +15362,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="2" t="n">
+      <c r="A240" s="1" t="n">
         <v>45597</v>
       </c>
       <c r="B240" t="n">
@@ -15418,7 +15406,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="2" t="n">
+      <c r="A241" s="1" t="n">
         <v>45627</v>
       </c>
       <c r="B241" t="n">
@@ -15462,7 +15450,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="2" t="n">
+      <c r="A242" s="1" t="n">
         <v>45658</v>
       </c>
       <c r="B242" t="n">
@@ -15506,7 +15494,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="2" t="n">
+      <c r="A243" s="1" t="n">
         <v>45689</v>
       </c>
       <c r="B243" t="n">
@@ -15550,7 +15538,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="2" t="n">
+      <c r="A244" s="1" t="n">
         <v>45717</v>
       </c>
       <c r="B244" t="n">
@@ -15594,7 +15582,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="2" t="n">
+      <c r="A245" s="1" t="n">
         <v>45748</v>
       </c>
       <c r="B245" t="n">
@@ -15638,7 +15626,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="2" t="n">
+      <c r="A246" s="1" t="n">
         <v>45778</v>
       </c>
       <c r="B246" t="n">
@@ -15682,7 +15670,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="2" t="n">
+      <c r="A247" s="1" t="n">
         <v>45809</v>
       </c>
       <c r="B247" t="n">
@@ -15726,7 +15714,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="2" t="n">
+      <c r="A248" s="1" t="n">
         <v>45839</v>
       </c>
       <c r="B248" t="n">
@@ -15770,7 +15758,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="2" t="n">
+      <c r="A249" s="1" t="n">
         <v>45870</v>
       </c>
       <c r="B249" t="n">
@@ -15814,7 +15802,7 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="2" t="n">
+      <c r="A250" s="1" t="n">
         <v>45901</v>
       </c>
       <c r="B250" t="n">
@@ -15858,7 +15846,7 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="2" t="n">
+      <c r="A251" s="1" t="n">
         <v>45931</v>
       </c>
       <c r="B251" t="n">
@@ -15902,7 +15890,7 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="2" t="n">
+      <c r="A252" s="1" t="n">
         <v>45962</v>
       </c>
       <c r="B252" t="n">
@@ -15946,7 +15934,7 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="2" t="n">
+      <c r="A253" s="1" t="n">
         <v>45992</v>
       </c>
       <c r="B253" t="n">
@@ -15990,7 +15978,7 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="2" t="n">
+      <c r="A254" s="1" t="n">
         <v>46023</v>
       </c>
       <c r="B254" t="n">
@@ -16034,7 +16022,7 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="2" t="n">
+      <c r="A255" s="1" t="n">
         <v>46054</v>
       </c>
       <c r="B255" t="n">
@@ -16078,7 +16066,7 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="2" t="n">
+      <c r="A256" s="1" t="n">
         <v>46082</v>
       </c>
       <c r="B256" t="n">
@@ -16122,7 +16110,7 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="2" t="n">
+      <c r="A257" s="1" t="n">
         <v>46113</v>
       </c>
       <c r="B257" t="n">
@@ -16166,7 +16154,7 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="2" t="n">
+      <c r="A258" s="1" t="n">
         <v>46143</v>
       </c>
       <c r="B258" t="n">
@@ -16210,7 +16198,7 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="2" t="n">
+      <c r="A259" s="1" t="n">
         <v>46174</v>
       </c>
       <c r="B259" t="n">
@@ -16254,7 +16242,7 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="2" t="n">
+      <c r="A260" s="1" t="n">
         <v>46204</v>
       </c>
       <c r="B260" t="n">
@@ -16312,79 +16300,79 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>tarih</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>01. Gıda Ve Alkolsüz İçecekler</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>02. Alkollü İçecekler, Tütün Ve Tütün Ürünleri</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>03. Giyim Ve Ayakkabı</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>04. Konut, Su, Elektrik, Gaz Ve Diğer Yakıtlar</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>05. Mobilya, Mefruşat Ve Evde Kullanılan Ekipmanlar İle Rutin Ev Bakım Ve Onarımı</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>06. Sağlık</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>07. Ulaştırma</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>08. Bilgi Ve İletişim</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>09. Eğlence, Dinlence, Spor Ve Kültür</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>10. Eğitim Hizmetleri</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>11. Lokantalar Ve Konaklama Hizmetleri</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>12. Sigorta Ve Finansal Hizmetler</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>13. Kişisel Bakım, Sosyal Koruma Ve Çeşitli Mal Ve Hizmetler</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="1" t="n">
         <v>38353</v>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -16402,7 +16390,7 @@
       <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="1" t="n">
         <v>38384</v>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -16420,7 +16408,7 @@
       <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="1" t="n">
         <v>38412</v>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -16438,7 +16426,7 @@
       <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="1" t="n">
         <v>38443</v>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -16456,7 +16444,7 @@
       <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="1" t="n">
         <v>38473</v>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -16474,7 +16462,7 @@
       <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="1" t="n">
         <v>38504</v>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -16492,7 +16480,7 @@
       <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="1" t="n">
         <v>38534</v>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -16510,7 +16498,7 @@
       <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="1" t="n">
         <v>38565</v>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -16528,7 +16516,7 @@
       <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="1" t="n">
         <v>38596</v>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -16546,7 +16534,7 @@
       <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="1" t="n">
         <v>38626</v>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -16564,7 +16552,7 @@
       <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="1" t="n">
         <v>38657</v>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -16582,7 +16570,7 @@
       <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="1" t="n">
         <v>38687</v>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -16600,7 +16588,7 @@
       <c r="N13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="1" t="n">
         <v>38718</v>
       </c>
       <c r="B14" t="n">
@@ -16644,7 +16632,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="1" t="n">
         <v>38749</v>
       </c>
       <c r="B15" t="n">
@@ -16688,7 +16676,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="1" t="n">
         <v>38777</v>
       </c>
       <c r="B16" t="n">
@@ -16732,7 +16720,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="1" t="n">
         <v>38808</v>
       </c>
       <c r="B17" t="n">
@@ -16776,7 +16764,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="1" t="n">
         <v>38838</v>
       </c>
       <c r="B18" t="n">
@@ -16820,7 +16808,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="1" t="n">
         <v>38869</v>
       </c>
       <c r="B19" t="n">
@@ -16864,7 +16852,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="1" t="n">
         <v>38899</v>
       </c>
       <c r="B20" t="n">
@@ -16908,7 +16896,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="1" t="n">
         <v>38930</v>
       </c>
       <c r="B21" t="n">
@@ -16952,7 +16940,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="1" t="n">
         <v>38961</v>
       </c>
       <c r="B22" t="n">
@@ -16996,7 +16984,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="1" t="n">
         <v>38991</v>
       </c>
       <c r="B23" t="n">
@@ -17040,7 +17028,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="1" t="n">
         <v>39022</v>
       </c>
       <c r="B24" t="n">
@@ -17084,7 +17072,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="1" t="n">
         <v>39052</v>
       </c>
       <c r="B25" t="n">
@@ -17128,7 +17116,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="1" t="n">
         <v>39083</v>
       </c>
       <c r="B26" t="n">
@@ -17172,7 +17160,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="1" t="n">
         <v>39114</v>
       </c>
       <c r="B27" t="n">
@@ -17216,7 +17204,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="1" t="n">
         <v>39142</v>
       </c>
       <c r="B28" t="n">
@@ -17260,7 +17248,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="1" t="n">
         <v>39173</v>
       </c>
       <c r="B29" t="n">
@@ -17304,7 +17292,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="1" t="n">
         <v>39203</v>
       </c>
       <c r="B30" t="n">
@@ -17348,7 +17336,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="1" t="n">
         <v>39234</v>
       </c>
       <c r="B31" t="n">
@@ -17392,7 +17380,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="1" t="n">
         <v>39264</v>
       </c>
       <c r="B32" t="n">
@@ -17436,7 +17424,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="1" t="n">
         <v>39295</v>
       </c>
       <c r="B33" t="n">
@@ -17480,7 +17468,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="1" t="n">
         <v>39326</v>
       </c>
       <c r="B34" t="n">
@@ -17524,7 +17512,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="1" t="n">
         <v>39356</v>
       </c>
       <c r="B35" t="n">
@@ -17568,7 +17556,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="1" t="n">
         <v>39387</v>
       </c>
       <c r="B36" t="n">
@@ -17612,7 +17600,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="1" t="n">
         <v>39417</v>
       </c>
       <c r="B37" t="n">
@@ -17656,7 +17644,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="1" t="n">
         <v>39448</v>
       </c>
       <c r="B38" t="n">
@@ -17700,7 +17688,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="1" t="n">
         <v>39479</v>
       </c>
       <c r="B39" t="n">
@@ -17744,7 +17732,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="1" t="n">
         <v>39508</v>
       </c>
       <c r="B40" t="n">
@@ -17788,7 +17776,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" s="1" t="n">
         <v>39539</v>
       </c>
       <c r="B41" t="n">
@@ -17832,7 +17820,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="1" t="n">
         <v>39569</v>
       </c>
       <c r="B42" t="n">
@@ -17876,7 +17864,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" s="1" t="n">
         <v>39600</v>
       </c>
       <c r="B43" t="n">
@@ -17920,7 +17908,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" s="1" t="n">
         <v>39630</v>
       </c>
       <c r="B44" t="n">
@@ -17964,7 +17952,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" s="1" t="n">
         <v>39661</v>
       </c>
       <c r="B45" t="n">
@@ -18008,7 +17996,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="1" t="n">
         <v>39692</v>
       </c>
       <c r="B46" t="n">
@@ -18052,7 +18040,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="A47" s="1" t="n">
         <v>39722</v>
       </c>
       <c r="B47" t="n">
@@ -18096,7 +18084,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="1" t="n">
         <v>39753</v>
       </c>
       <c r="B48" t="n">
@@ -18140,7 +18128,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="A49" s="1" t="n">
         <v>39783</v>
       </c>
       <c r="B49" t="n">
@@ -18184,7 +18172,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="1" t="n">
         <v>39814</v>
       </c>
       <c r="B50" t="n">
@@ -18228,7 +18216,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" s="1" t="n">
         <v>39845</v>
       </c>
       <c r="B51" t="n">
@@ -18272,7 +18260,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="A52" s="1" t="n">
         <v>39873</v>
       </c>
       <c r="B52" t="n">
@@ -18316,7 +18304,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" s="1" t="n">
         <v>39904</v>
       </c>
       <c r="B53" t="n">
@@ -18360,7 +18348,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n">
+      <c r="A54" s="1" t="n">
         <v>39934</v>
       </c>
       <c r="B54" t="n">
@@ -18404,7 +18392,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n">
+      <c r="A55" s="1" t="n">
         <v>39965</v>
       </c>
       <c r="B55" t="n">
@@ -18448,7 +18436,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
+      <c r="A56" s="1" t="n">
         <v>39995</v>
       </c>
       <c r="B56" t="n">
@@ -18492,7 +18480,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="A57" s="1" t="n">
         <v>40026</v>
       </c>
       <c r="B57" t="n">
@@ -18536,7 +18524,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
+      <c r="A58" s="1" t="n">
         <v>40057</v>
       </c>
       <c r="B58" t="n">
@@ -18580,7 +18568,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
+      <c r="A59" s="1" t="n">
         <v>40087</v>
       </c>
       <c r="B59" t="n">
@@ -18624,7 +18612,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
+      <c r="A60" s="1" t="n">
         <v>40118</v>
       </c>
       <c r="B60" t="n">
@@ -18668,7 +18656,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
+      <c r="A61" s="1" t="n">
         <v>40148</v>
       </c>
       <c r="B61" t="n">
@@ -18712,7 +18700,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
+      <c r="A62" s="1" t="n">
         <v>40179</v>
       </c>
       <c r="B62" t="n">
@@ -18756,7 +18744,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n">
+      <c r="A63" s="1" t="n">
         <v>40210</v>
       </c>
       <c r="B63" t="n">
@@ -18800,7 +18788,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n">
+      <c r="A64" s="1" t="n">
         <v>40238</v>
       </c>
       <c r="B64" t="n">
@@ -18844,7 +18832,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n">
+      <c r="A65" s="1" t="n">
         <v>40269</v>
       </c>
       <c r="B65" t="n">
@@ -18888,7 +18876,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n">
+      <c r="A66" s="1" t="n">
         <v>40299</v>
       </c>
       <c r="B66" t="n">
@@ -18932,7 +18920,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n">
+      <c r="A67" s="1" t="n">
         <v>40330</v>
       </c>
       <c r="B67" t="n">
@@ -18976,7 +18964,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n">
+      <c r="A68" s="1" t="n">
         <v>40360</v>
       </c>
       <c r="B68" t="n">
@@ -19020,7 +19008,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n">
+      <c r="A69" s="1" t="n">
         <v>40391</v>
       </c>
       <c r="B69" t="n">
@@ -19064,7 +19052,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="n">
+      <c r="A70" s="1" t="n">
         <v>40422</v>
       </c>
       <c r="B70" t="n">
@@ -19108,7 +19096,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="n">
+      <c r="A71" s="1" t="n">
         <v>40452</v>
       </c>
       <c r="B71" t="n">
@@ -19152,7 +19140,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="n">
+      <c r="A72" s="1" t="n">
         <v>40483</v>
       </c>
       <c r="B72" t="n">
@@ -19196,7 +19184,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="n">
+      <c r="A73" s="1" t="n">
         <v>40513</v>
       </c>
       <c r="B73" t="n">
@@ -19240,7 +19228,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="n">
+      <c r="A74" s="1" t="n">
         <v>40544</v>
       </c>
       <c r="B74" t="n">
@@ -19284,7 +19272,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="n">
+      <c r="A75" s="1" t="n">
         <v>40575</v>
       </c>
       <c r="B75" t="n">
@@ -19328,7 +19316,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="n">
+      <c r="A76" s="1" t="n">
         <v>40603</v>
       </c>
       <c r="B76" t="n">
@@ -19372,7 +19360,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n">
+      <c r="A77" s="1" t="n">
         <v>40634</v>
       </c>
       <c r="B77" t="n">
@@ -19416,7 +19404,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n">
+      <c r="A78" s="1" t="n">
         <v>40664</v>
       </c>
       <c r="B78" t="n">
@@ -19460,7 +19448,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="n">
+      <c r="A79" s="1" t="n">
         <v>40695</v>
       </c>
       <c r="B79" t="n">
@@ -19504,7 +19492,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="n">
+      <c r="A80" s="1" t="n">
         <v>40725</v>
       </c>
       <c r="B80" t="n">
@@ -19548,7 +19536,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="n">
+      <c r="A81" s="1" t="n">
         <v>40756</v>
       </c>
       <c r="B81" t="n">
@@ -19592,7 +19580,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="n">
+      <c r="A82" s="1" t="n">
         <v>40787</v>
       </c>
       <c r="B82" t="n">
@@ -19636,7 +19624,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="n">
+      <c r="A83" s="1" t="n">
         <v>40817</v>
       </c>
       <c r="B83" t="n">
@@ -19680,7 +19668,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="n">
+      <c r="A84" s="1" t="n">
         <v>40848</v>
       </c>
       <c r="B84" t="n">
@@ -19724,7 +19712,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="n">
+      <c r="A85" s="1" t="n">
         <v>40878</v>
       </c>
       <c r="B85" t="n">
@@ -19768,7 +19756,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="n">
+      <c r="A86" s="1" t="n">
         <v>40909</v>
       </c>
       <c r="B86" t="n">
@@ -19812,7 +19800,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="n">
+      <c r="A87" s="1" t="n">
         <v>40940</v>
       </c>
       <c r="B87" t="n">
@@ -19856,7 +19844,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="n">
+      <c r="A88" s="1" t="n">
         <v>40969</v>
       </c>
       <c r="B88" t="n">
@@ -19900,7 +19888,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="n">
+      <c r="A89" s="1" t="n">
         <v>41000</v>
       </c>
       <c r="B89" t="n">
@@ -19944,7 +19932,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="n">
+      <c r="A90" s="1" t="n">
         <v>41030</v>
       </c>
       <c r="B90" t="n">
@@ -19988,7 +19976,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="n">
+      <c r="A91" s="1" t="n">
         <v>41061</v>
       </c>
       <c r="B91" t="n">
@@ -20032,7 +20020,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="n">
+      <c r="A92" s="1" t="n">
         <v>41091</v>
       </c>
       <c r="B92" t="n">
@@ -20076,7 +20064,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="n">
+      <c r="A93" s="1" t="n">
         <v>41122</v>
       </c>
       <c r="B93" t="n">
@@ -20120,7 +20108,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="n">
+      <c r="A94" s="1" t="n">
         <v>41153</v>
       </c>
       <c r="B94" t="n">
@@ -20164,7 +20152,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="n">
+      <c r="A95" s="1" t="n">
         <v>41183</v>
       </c>
       <c r="B95" t="n">
@@ -20208,7 +20196,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="n">
+      <c r="A96" s="1" t="n">
         <v>41214</v>
       </c>
       <c r="B96" t="n">
@@ -20252,7 +20240,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="n">
+      <c r="A97" s="1" t="n">
         <v>41244</v>
       </c>
       <c r="B97" t="n">
@@ -20296,7 +20284,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="n">
+      <c r="A98" s="1" t="n">
         <v>41275</v>
       </c>
       <c r="B98" t="n">
@@ -20340,7 +20328,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="n">
+      <c r="A99" s="1" t="n">
         <v>41306</v>
       </c>
       <c r="B99" t="n">
@@ -20384,7 +20372,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="n">
+      <c r="A100" s="1" t="n">
         <v>41334</v>
       </c>
       <c r="B100" t="n">
@@ -20428,7 +20416,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="n">
+      <c r="A101" s="1" t="n">
         <v>41365</v>
       </c>
       <c r="B101" t="n">
@@ -20472,7 +20460,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="n">
+      <c r="A102" s="1" t="n">
         <v>41395</v>
       </c>
       <c r="B102" t="n">
@@ -20516,7 +20504,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="n">
+      <c r="A103" s="1" t="n">
         <v>41426</v>
       </c>
       <c r="B103" t="n">
@@ -20560,7 +20548,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="2" t="n">
+      <c r="A104" s="1" t="n">
         <v>41456</v>
       </c>
       <c r="B104" t="n">
@@ -20604,7 +20592,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="2" t="n">
+      <c r="A105" s="1" t="n">
         <v>41487</v>
       </c>
       <c r="B105" t="n">
@@ -20648,7 +20636,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="n">
+      <c r="A106" s="1" t="n">
         <v>41518</v>
       </c>
       <c r="B106" t="n">
@@ -20692,7 +20680,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="n">
+      <c r="A107" s="1" t="n">
         <v>41548</v>
       </c>
       <c r="B107" t="n">
@@ -20736,7 +20724,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="n">
+      <c r="A108" s="1" t="n">
         <v>41579</v>
       </c>
       <c r="B108" t="n">
@@ -20780,7 +20768,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="n">
+      <c r="A109" s="1" t="n">
         <v>41609</v>
       </c>
       <c r="B109" t="n">
@@ -20824,7 +20812,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="n">
+      <c r="A110" s="1" t="n">
         <v>41640</v>
       </c>
       <c r="B110" t="n">
@@ -20868,7 +20856,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="n">
+      <c r="A111" s="1" t="n">
         <v>41671</v>
       </c>
       <c r="B111" t="n">
@@ -20912,7 +20900,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="n">
+      <c r="A112" s="1" t="n">
         <v>41699</v>
       </c>
       <c r="B112" t="n">
@@ -20956,7 +20944,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="2" t="n">
+      <c r="A113" s="1" t="n">
         <v>41730</v>
       </c>
       <c r="B113" t="n">
@@ -21000,7 +20988,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="2" t="n">
+      <c r="A114" s="1" t="n">
         <v>41760</v>
       </c>
       <c r="B114" t="n">
@@ -21044,7 +21032,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="n">
+      <c r="A115" s="1" t="n">
         <v>41791</v>
       </c>
       <c r="B115" t="n">
@@ -21088,7 +21076,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="n">
+      <c r="A116" s="1" t="n">
         <v>41821</v>
       </c>
       <c r="B116" t="n">
@@ -21132,7 +21120,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="2" t="n">
+      <c r="A117" s="1" t="n">
         <v>41852</v>
       </c>
       <c r="B117" t="n">
@@ -21176,7 +21164,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="2" t="n">
+      <c r="A118" s="1" t="n">
         <v>41883</v>
       </c>
       <c r="B118" t="n">
@@ -21220,7 +21208,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="n">
+      <c r="A119" s="1" t="n">
         <v>41913</v>
       </c>
       <c r="B119" t="n">
@@ -21264,7 +21252,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="n">
+      <c r="A120" s="1" t="n">
         <v>41944</v>
       </c>
       <c r="B120" t="n">
@@ -21308,7 +21296,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="2" t="n">
+      <c r="A121" s="1" t="n">
         <v>41974</v>
       </c>
       <c r="B121" t="n">
@@ -21352,7 +21340,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="2" t="n">
+      <c r="A122" s="1" t="n">
         <v>42005</v>
       </c>
       <c r="B122" t="n">
@@ -21396,7 +21384,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="2" t="n">
+      <c r="A123" s="1" t="n">
         <v>42036</v>
       </c>
       <c r="B123" t="n">
@@ -21440,7 +21428,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="n">
+      <c r="A124" s="1" t="n">
         <v>42064</v>
       </c>
       <c r="B124" t="n">
@@ -21484,7 +21472,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="2" t="n">
+      <c r="A125" s="1" t="n">
         <v>42095</v>
       </c>
       <c r="B125" t="n">
@@ -21528,7 +21516,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="2" t="n">
+      <c r="A126" s="1" t="n">
         <v>42125</v>
       </c>
       <c r="B126" t="n">
@@ -21572,7 +21560,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="2" t="n">
+      <c r="A127" s="1" t="n">
         <v>42156</v>
       </c>
       <c r="B127" t="n">
@@ -21616,7 +21604,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="2" t="n">
+      <c r="A128" s="1" t="n">
         <v>42186</v>
       </c>
       <c r="B128" t="n">
@@ -21660,7 +21648,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="2" t="n">
+      <c r="A129" s="1" t="n">
         <v>42217</v>
       </c>
       <c r="B129" t="n">
@@ -21704,7 +21692,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="2" t="n">
+      <c r="A130" s="1" t="n">
         <v>42248</v>
       </c>
       <c r="B130" t="n">
@@ -21748,7 +21736,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="2" t="n">
+      <c r="A131" s="1" t="n">
         <v>42278</v>
       </c>
       <c r="B131" t="n">
@@ -21792,7 +21780,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="2" t="n">
+      <c r="A132" s="1" t="n">
         <v>42309</v>
       </c>
       <c r="B132" t="n">
@@ -21836,7 +21824,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="2" t="n">
+      <c r="A133" s="1" t="n">
         <v>42339</v>
       </c>
       <c r="B133" t="n">
@@ -21880,7 +21868,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="2" t="n">
+      <c r="A134" s="1" t="n">
         <v>42370</v>
       </c>
       <c r="B134" t="n">
@@ -21924,7 +21912,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="2" t="n">
+      <c r="A135" s="1" t="n">
         <v>42401</v>
       </c>
       <c r="B135" t="n">
@@ -21968,7 +21956,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="2" t="n">
+      <c r="A136" s="1" t="n">
         <v>42430</v>
       </c>
       <c r="B136" t="n">
@@ -22012,7 +22000,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="2" t="n">
+      <c r="A137" s="1" t="n">
         <v>42461</v>
       </c>
       <c r="B137" t="n">
@@ -22056,7 +22044,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="2" t="n">
+      <c r="A138" s="1" t="n">
         <v>42491</v>
       </c>
       <c r="B138" t="n">
@@ -22100,7 +22088,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="2" t="n">
+      <c r="A139" s="1" t="n">
         <v>42522</v>
       </c>
       <c r="B139" t="n">
@@ -22144,7 +22132,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="2" t="n">
+      <c r="A140" s="1" t="n">
         <v>42552</v>
       </c>
       <c r="B140" t="n">
@@ -22188,7 +22176,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="2" t="n">
+      <c r="A141" s="1" t="n">
         <v>42583</v>
       </c>
       <c r="B141" t="n">
@@ -22232,7 +22220,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="2" t="n">
+      <c r="A142" s="1" t="n">
         <v>42614</v>
       </c>
       <c r="B142" t="n">
@@ -22276,7 +22264,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="2" t="n">
+      <c r="A143" s="1" t="n">
         <v>42644</v>
       </c>
       <c r="B143" t="n">
@@ -22320,7 +22308,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="2" t="n">
+      <c r="A144" s="1" t="n">
         <v>42675</v>
       </c>
       <c r="B144" t="n">
@@ -22364,7 +22352,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="2" t="n">
+      <c r="A145" s="1" t="n">
         <v>42705</v>
       </c>
       <c r="B145" t="n">
@@ -22408,7 +22396,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="2" t="n">
+      <c r="A146" s="1" t="n">
         <v>42736</v>
       </c>
       <c r="B146" t="n">
@@ -22452,7 +22440,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="2" t="n">
+      <c r="A147" s="1" t="n">
         <v>42767</v>
       </c>
       <c r="B147" t="n">
@@ -22496,7 +22484,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="2" t="n">
+      <c r="A148" s="1" t="n">
         <v>42795</v>
       </c>
       <c r="B148" t="n">
@@ -22540,7 +22528,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="2" t="n">
+      <c r="A149" s="1" t="n">
         <v>42826</v>
       </c>
       <c r="B149" t="n">
@@ -22584,7 +22572,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="2" t="n">
+      <c r="A150" s="1" t="n">
         <v>42856</v>
       </c>
       <c r="B150" t="n">
@@ -22628,7 +22616,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="2" t="n">
+      <c r="A151" s="1" t="n">
         <v>42887</v>
       </c>
       <c r="B151" t="n">
@@ -22672,7 +22660,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="2" t="n">
+      <c r="A152" s="1" t="n">
         <v>42917</v>
       </c>
       <c r="B152" t="n">
@@ -22716,7 +22704,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="2" t="n">
+      <c r="A153" s="1" t="n">
         <v>42948</v>
       </c>
       <c r="B153" t="n">
@@ -22760,7 +22748,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="2" t="n">
+      <c r="A154" s="1" t="n">
         <v>42979</v>
       </c>
       <c r="B154" t="n">
@@ -22804,7 +22792,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="2" t="n">
+      <c r="A155" s="1" t="n">
         <v>43009</v>
       </c>
       <c r="B155" t="n">
@@ -22848,7 +22836,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="2" t="n">
+      <c r="A156" s="1" t="n">
         <v>43040</v>
       </c>
       <c r="B156" t="n">
@@ -22892,7 +22880,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="2" t="n">
+      <c r="A157" s="1" t="n">
         <v>43070</v>
       </c>
       <c r="B157" t="n">
@@ -22936,7 +22924,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="2" t="n">
+      <c r="A158" s="1" t="n">
         <v>43101</v>
       </c>
       <c r="B158" t="n">
@@ -22980,7 +22968,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="2" t="n">
+      <c r="A159" s="1" t="n">
         <v>43132</v>
       </c>
       <c r="B159" t="n">
@@ -23024,7 +23012,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="2" t="n">
+      <c r="A160" s="1" t="n">
         <v>43160</v>
       </c>
       <c r="B160" t="n">
@@ -23068,7 +23056,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="2" t="n">
+      <c r="A161" s="1" t="n">
         <v>43191</v>
       </c>
       <c r="B161" t="n">
@@ -23112,7 +23100,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="2" t="n">
+      <c r="A162" s="1" t="n">
         <v>43221</v>
       </c>
       <c r="B162" t="n">
@@ -23156,7 +23144,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="2" t="n">
+      <c r="A163" s="1" t="n">
         <v>43252</v>
       </c>
       <c r="B163" t="n">
@@ -23200,7 +23188,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="2" t="n">
+      <c r="A164" s="1" t="n">
         <v>43282</v>
       </c>
       <c r="B164" t="n">
@@ -23244,7 +23232,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="2" t="n">
+      <c r="A165" s="1" t="n">
         <v>43313</v>
       </c>
       <c r="B165" t="n">
@@ -23288,7 +23276,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="2" t="n">
+      <c r="A166" s="1" t="n">
         <v>43344</v>
       </c>
       <c r="B166" t="n">
@@ -23332,7 +23320,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="2" t="n">
+      <c r="A167" s="1" t="n">
         <v>43374</v>
       </c>
       <c r="B167" t="n">
@@ -23376,7 +23364,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="2" t="n">
+      <c r="A168" s="1" t="n">
         <v>43405</v>
       </c>
       <c r="B168" t="n">
@@ -23420,7 +23408,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="2" t="n">
+      <c r="A169" s="1" t="n">
         <v>43435</v>
       </c>
       <c r="B169" t="n">
@@ -23464,7 +23452,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="2" t="n">
+      <c r="A170" s="1" t="n">
         <v>43466</v>
       </c>
       <c r="B170" t="n">
@@ -23508,7 +23496,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="2" t="n">
+      <c r="A171" s="1" t="n">
         <v>43497</v>
       </c>
       <c r="B171" t="n">
@@ -23552,7 +23540,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="2" t="n">
+      <c r="A172" s="1" t="n">
         <v>43525</v>
       </c>
       <c r="B172" t="n">
@@ -23596,7 +23584,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="2" t="n">
+      <c r="A173" s="1" t="n">
         <v>43556</v>
       </c>
       <c r="B173" t="n">
@@ -23640,7 +23628,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="2" t="n">
+      <c r="A174" s="1" t="n">
         <v>43586</v>
       </c>
       <c r="B174" t="n">
@@ -23684,7 +23672,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="2" t="n">
+      <c r="A175" s="1" t="n">
         <v>43617</v>
       </c>
       <c r="B175" t="n">
@@ -23728,7 +23716,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="2" t="n">
+      <c r="A176" s="1" t="n">
         <v>43647</v>
       </c>
       <c r="B176" t="n">
@@ -23772,7 +23760,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="2" t="n">
+      <c r="A177" s="1" t="n">
         <v>43678</v>
       </c>
       <c r="B177" t="n">
@@ -23816,7 +23804,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="2" t="n">
+      <c r="A178" s="1" t="n">
         <v>43709</v>
       </c>
       <c r="B178" t="n">
@@ -23860,7 +23848,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="2" t="n">
+      <c r="A179" s="1" t="n">
         <v>43739</v>
       </c>
       <c r="B179" t="n">
@@ -23904,7 +23892,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="2" t="n">
+      <c r="A180" s="1" t="n">
         <v>43770</v>
       </c>
       <c r="B180" t="n">
@@ -23948,7 +23936,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="2" t="n">
+      <c r="A181" s="1" t="n">
         <v>43800</v>
       </c>
       <c r="B181" t="n">
@@ -23992,7 +23980,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="2" t="n">
+      <c r="A182" s="1" t="n">
         <v>43831</v>
       </c>
       <c r="B182" t="n">
@@ -24036,7 +24024,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="2" t="n">
+      <c r="A183" s="1" t="n">
         <v>43862</v>
       </c>
       <c r="B183" t="n">
@@ -24080,7 +24068,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="2" t="n">
+      <c r="A184" s="1" t="n">
         <v>43891</v>
       </c>
       <c r="B184" t="n">
@@ -24124,7 +24112,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="2" t="n">
+      <c r="A185" s="1" t="n">
         <v>43922</v>
       </c>
       <c r="B185" t="n">
@@ -24168,7 +24156,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="2" t="n">
+      <c r="A186" s="1" t="n">
         <v>43952</v>
       </c>
       <c r="B186" t="n">
@@ -24212,7 +24200,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="2" t="n">
+      <c r="A187" s="1" t="n">
         <v>43983</v>
       </c>
       <c r="B187" t="n">
@@ -24256,7 +24244,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="2" t="n">
+      <c r="A188" s="1" t="n">
         <v>44013</v>
       </c>
       <c r="B188" t="n">
@@ -24300,7 +24288,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="2" t="n">
+      <c r="A189" s="1" t="n">
         <v>44044</v>
       </c>
       <c r="B189" t="n">
@@ -24344,7 +24332,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="2" t="n">
+      <c r="A190" s="1" t="n">
         <v>44075</v>
       </c>
       <c r="B190" t="n">
@@ -24388,7 +24376,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="2" t="n">
+      <c r="A191" s="1" t="n">
         <v>44105</v>
       </c>
       <c r="B191" t="n">
@@ -24432,7 +24420,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="2" t="n">
+      <c r="A192" s="1" t="n">
         <v>44136</v>
       </c>
       <c r="B192" t="n">
@@ -24476,7 +24464,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="2" t="n">
+      <c r="A193" s="1" t="n">
         <v>44166</v>
       </c>
       <c r="B193" t="n">
@@ -24520,7 +24508,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="2" t="n">
+      <c r="A194" s="1" t="n">
         <v>44197</v>
       </c>
       <c r="B194" t="n">
@@ -24564,7 +24552,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="2" t="n">
+      <c r="A195" s="1" t="n">
         <v>44228</v>
       </c>
       <c r="B195" t="n">
@@ -24608,7 +24596,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="2" t="n">
+      <c r="A196" s="1" t="n">
         <v>44256</v>
       </c>
       <c r="B196" t="n">
@@ -24652,7 +24640,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="2" t="n">
+      <c r="A197" s="1" t="n">
         <v>44287</v>
       </c>
       <c r="B197" t="n">
@@ -24696,7 +24684,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="2" t="n">
+      <c r="A198" s="1" t="n">
         <v>44317</v>
       </c>
       <c r="B198" t="n">
@@ -24740,7 +24728,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="2" t="n">
+      <c r="A199" s="1" t="n">
         <v>44348</v>
       </c>
       <c r="B199" t="n">
@@ -24784,7 +24772,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="2" t="n">
+      <c r="A200" s="1" t="n">
         <v>44378</v>
       </c>
       <c r="B200" t="n">
@@ -24828,7 +24816,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="2" t="n">
+      <c r="A201" s="1" t="n">
         <v>44409</v>
       </c>
       <c r="B201" t="n">
@@ -24872,7 +24860,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="2" t="n">
+      <c r="A202" s="1" t="n">
         <v>44440</v>
       </c>
       <c r="B202" t="n">
@@ -24916,7 +24904,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="2" t="n">
+      <c r="A203" s="1" t="n">
         <v>44470</v>
       </c>
       <c r="B203" t="n">
@@ -24960,7 +24948,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="2" t="n">
+      <c r="A204" s="1" t="n">
         <v>44501</v>
       </c>
       <c r="B204" t="n">
@@ -25004,7 +24992,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="2" t="n">
+      <c r="A205" s="1" t="n">
         <v>44531</v>
       </c>
       <c r="B205" t="n">
@@ -25048,7 +25036,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="2" t="n">
+      <c r="A206" s="1" t="n">
         <v>44562</v>
       </c>
       <c r="B206" t="n">
@@ -25092,7 +25080,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="2" t="n">
+      <c r="A207" s="1" t="n">
         <v>44593</v>
       </c>
       <c r="B207" t="n">
@@ -25136,7 +25124,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="2" t="n">
+      <c r="A208" s="1" t="n">
         <v>44621</v>
       </c>
       <c r="B208" t="n">
@@ -25180,7 +25168,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="2" t="n">
+      <c r="A209" s="1" t="n">
         <v>44652</v>
       </c>
       <c r="B209" t="n">
@@ -25224,7 +25212,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="2" t="n">
+      <c r="A210" s="1" t="n">
         <v>44682</v>
       </c>
       <c r="B210" t="n">
@@ -25268,7 +25256,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="2" t="n">
+      <c r="A211" s="1" t="n">
         <v>44713</v>
       </c>
       <c r="B211" t="n">
@@ -25312,7 +25300,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="2" t="n">
+      <c r="A212" s="1" t="n">
         <v>44743</v>
       </c>
       <c r="B212" t="n">
@@ -25356,7 +25344,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="2" t="n">
+      <c r="A213" s="1" t="n">
         <v>44774</v>
       </c>
       <c r="B213" t="n">
@@ -25400,7 +25388,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="2" t="n">
+      <c r="A214" s="1" t="n">
         <v>44805</v>
       </c>
       <c r="B214" t="n">
@@ -25444,7 +25432,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="2" t="n">
+      <c r="A215" s="1" t="n">
         <v>44835</v>
       </c>
       <c r="B215" t="n">
@@ -25488,7 +25476,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="2" t="n">
+      <c r="A216" s="1" t="n">
         <v>44866</v>
       </c>
       <c r="B216" t="n">
@@ -25532,7 +25520,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="2" t="n">
+      <c r="A217" s="1" t="n">
         <v>44896</v>
       </c>
       <c r="B217" t="n">
@@ -25576,7 +25564,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="2" t="n">
+      <c r="A218" s="1" t="n">
         <v>44927</v>
       </c>
       <c r="B218" t="n">
@@ -25620,7 +25608,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="2" t="n">
+      <c r="A219" s="1" t="n">
         <v>44958</v>
       </c>
       <c r="B219" t="n">
@@ -25664,7 +25652,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="2" t="n">
+      <c r="A220" s="1" t="n">
         <v>44986</v>
       </c>
       <c r="B220" t="n">
@@ -25708,7 +25696,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="2" t="n">
+      <c r="A221" s="1" t="n">
         <v>45017</v>
       </c>
       <c r="B221" t="n">
@@ -25752,7 +25740,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="2" t="n">
+      <c r="A222" s="1" t="n">
         <v>45047</v>
       </c>
       <c r="B222" t="n">
@@ -25796,7 +25784,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="2" t="n">
+      <c r="A223" s="1" t="n">
         <v>45078</v>
       </c>
       <c r="B223" t="n">
@@ -25840,7 +25828,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="2" t="n">
+      <c r="A224" s="1" t="n">
         <v>45108</v>
       </c>
       <c r="B224" t="n">
@@ -25884,7 +25872,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="2" t="n">
+      <c r="A225" s="1" t="n">
         <v>45139</v>
       </c>
       <c r="B225" t="n">
@@ -25928,7 +25916,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="2" t="n">
+      <c r="A226" s="1" t="n">
         <v>45170</v>
       </c>
       <c r="B226" t="n">
@@ -25972,7 +25960,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="2" t="n">
+      <c r="A227" s="1" t="n">
         <v>45200</v>
       </c>
       <c r="B227" t="n">
@@ -26016,7 +26004,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="2" t="n">
+      <c r="A228" s="1" t="n">
         <v>45231</v>
       </c>
       <c r="B228" t="n">
@@ -26060,7 +26048,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="2" t="n">
+      <c r="A229" s="1" t="n">
         <v>45261</v>
       </c>
       <c r="B229" t="n">
@@ -26104,7 +26092,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="2" t="n">
+      <c r="A230" s="1" t="n">
         <v>45292</v>
       </c>
       <c r="B230" t="n">
@@ -26148,7 +26136,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="2" t="n">
+      <c r="A231" s="1" t="n">
         <v>45323</v>
       </c>
       <c r="B231" t="n">
@@ -26192,7 +26180,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="2" t="n">
+      <c r="A232" s="1" t="n">
         <v>45352</v>
       </c>
       <c r="B232" t="n">
@@ -26236,7 +26224,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="2" t="n">
+      <c r="A233" s="1" t="n">
         <v>45383</v>
       </c>
       <c r="B233" t="n">
@@ -26280,7 +26268,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="2" t="n">
+      <c r="A234" s="1" t="n">
         <v>45413</v>
       </c>
       <c r="B234" t="n">
@@ -26324,7 +26312,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="2" t="n">
+      <c r="A235" s="1" t="n">
         <v>45444</v>
       </c>
       <c r="B235" t="n">
@@ -26368,7 +26356,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="2" t="n">
+      <c r="A236" s="1" t="n">
         <v>45474</v>
       </c>
       <c r="B236" t="n">
@@ -26412,7 +26400,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="2" t="n">
+      <c r="A237" s="1" t="n">
         <v>45505</v>
       </c>
       <c r="B237" t="n">
@@ -26456,7 +26444,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="2" t="n">
+      <c r="A238" s="1" t="n">
         <v>45536</v>
       </c>
       <c r="B238" t="n">
@@ -26500,7 +26488,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="2" t="n">
+      <c r="A239" s="1" t="n">
         <v>45566</v>
       </c>
       <c r="B239" t="n">
@@ -26544,7 +26532,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="2" t="n">
+      <c r="A240" s="1" t="n">
         <v>45597</v>
       </c>
       <c r="B240" t="n">
@@ -26588,7 +26576,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="2" t="n">
+      <c r="A241" s="1" t="n">
         <v>45627</v>
       </c>
       <c r="B241" t="n">
@@ -26632,7 +26620,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="2" t="n">
+      <c r="A242" s="1" t="n">
         <v>45658</v>
       </c>
       <c r="B242" t="n">
@@ -26676,7 +26664,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="2" t="n">
+      <c r="A243" s="1" t="n">
         <v>45689</v>
       </c>
       <c r="B243" t="n">
@@ -26720,7 +26708,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="2" t="n">
+      <c r="A244" s="1" t="n">
         <v>45717</v>
       </c>
       <c r="B244" t="n">
@@ -26764,7 +26752,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="2" t="n">
+      <c r="A245" s="1" t="n">
         <v>45748</v>
       </c>
       <c r="B245" t="n">
@@ -26808,7 +26796,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="2" t="n">
+      <c r="A246" s="1" t="n">
         <v>45778</v>
       </c>
       <c r="B246" t="n">
@@ -26852,7 +26840,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="2" t="n">
+      <c r="A247" s="1" t="n">
         <v>45809</v>
       </c>
       <c r="B247" t="n">
@@ -26896,7 +26884,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="2" t="n">
+      <c r="A248" s="1" t="n">
         <v>45839</v>
       </c>
       <c r="B248" t="n">
@@ -26940,7 +26928,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="2" t="n">
+      <c r="A249" s="1" t="n">
         <v>45870</v>
       </c>
       <c r="B249" t="n">
@@ -26984,7 +26972,7 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="2" t="n">
+      <c r="A250" s="1" t="n">
         <v>45901</v>
       </c>
       <c r="B250" t="n">
@@ -27028,7 +27016,7 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="2" t="n">
+      <c r="A251" s="1" t="n">
         <v>45931</v>
       </c>
       <c r="B251" t="n">
@@ -27072,7 +27060,7 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="2" t="n">
+      <c r="A252" s="1" t="n">
         <v>45962</v>
       </c>
       <c r="B252" t="n">
@@ -27116,7 +27104,7 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="2" t="n">
+      <c r="A253" s="1" t="n">
         <v>45992</v>
       </c>
       <c r="B253" t="n">
@@ -27160,7 +27148,7 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="2" t="n">
+      <c r="A254" s="1" t="n">
         <v>46023</v>
       </c>
       <c r="B254" t="n">
@@ -27204,7 +27192,7 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="2" t="n">
+      <c r="A255" s="1" t="n">
         <v>46054</v>
       </c>
       <c r="B255" t="n">
@@ -27248,7 +27236,7 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="2" t="n">
+      <c r="A256" s="1" t="n">
         <v>46082</v>
       </c>
       <c r="B256" t="n">
@@ -27292,7 +27280,7 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="2" t="n">
+      <c r="A257" s="1" t="n">
         <v>46113</v>
       </c>
       <c r="B257" t="n">
@@ -27336,7 +27324,7 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="2" t="n">
+      <c r="A258" s="1" t="n">
         <v>46143</v>
       </c>
       <c r="B258" t="n">
@@ -27380,7 +27368,7 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="2" t="n">
+      <c r="A259" s="1" t="n">
         <v>46174</v>
       </c>
       <c r="B259" t="n">
@@ -27424,7 +27412,7 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="2" t="n">
+      <c r="A260" s="1" t="n">
         <v>46204</v>
       </c>
       <c r="B260" t="n">
@@ -27482,32 +27470,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Kalem</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Endeks</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Aylık %</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Yıllık %</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Yılbaşından %</t>
         </is>

--- a/enflasyon/enflasyon.xlsx
+++ b/enflasyon/enflasyon.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E260"/>
+  <dimension ref="A1:E261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4801,6 +4801,23 @@
       </c>
       <c r="E260" t="n">
         <v>19.86016871927905</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B261" t="n">
+        <v>134.75</v>
+      </c>
+      <c r="C261" t="n">
+        <v>1.844153881036958</v>
+      </c>
+      <c r="D261" t="n">
+        <v>31.50734282091285</v>
+      </c>
+      <c r="E261" t="n">
+        <v>22.07057467253308</v>
       </c>
     </row>
   </sheetData>
@@ -4814,7 +4831,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N260"/>
+  <dimension ref="A1:N261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16283,6 +16300,50 @@
       </c>
       <c r="N260" t="n">
         <v>123.47</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B261" t="n">
+        <v>134.31</v>
+      </c>
+      <c r="C261" t="n">
+        <v>139.12</v>
+      </c>
+      <c r="D261" t="n">
+        <v>107.77</v>
+      </c>
+      <c r="E261" t="n">
+        <v>148.08</v>
+      </c>
+      <c r="F261" t="n">
+        <v>126.49</v>
+      </c>
+      <c r="G261" t="n">
+        <v>146.07</v>
+      </c>
+      <c r="H261" t="n">
+        <v>140.14</v>
+      </c>
+      <c r="I261" t="n">
+        <v>128.48</v>
+      </c>
+      <c r="J261" t="n">
+        <v>128.56</v>
+      </c>
+      <c r="K261" t="n">
+        <v>153.83</v>
+      </c>
+      <c r="L261" t="n">
+        <v>135.7</v>
+      </c>
+      <c r="M261" t="n">
+        <v>130.54</v>
+      </c>
+      <c r="N261" t="n">
+        <v>126.42</v>
       </c>
     </row>
   </sheetData>
@@ -16296,7 +16357,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N260"/>
+  <dimension ref="A1:N261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27453,6 +27514,50 @@
       </c>
       <c r="N260" t="n">
         <v>21.73888482986941</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B261" t="n">
+        <v>33.78988040090669</v>
+      </c>
+      <c r="C261" t="n">
+        <v>30.42224822913602</v>
+      </c>
+      <c r="D261" t="n">
+        <v>13.15707827013983</v>
+      </c>
+      <c r="E261" t="n">
+        <v>39.77455728429897</v>
+      </c>
+      <c r="F261" t="n">
+        <v>23.5763577628787</v>
+      </c>
+      <c r="G261" t="n">
+        <v>43.45661506527607</v>
+      </c>
+      <c r="H261" t="n">
+        <v>35.07642610694981</v>
+      </c>
+      <c r="I261" t="n">
+        <v>25.66465697868268</v>
+      </c>
+      <c r="J261" t="n">
+        <v>23.42910595461436</v>
+      </c>
+      <c r="K261" t="n">
+        <v>53.44298409541148</v>
+      </c>
+      <c r="L261" t="n">
+        <v>31.1578146221104</v>
+      </c>
+      <c r="M261" t="n">
+        <v>25.07890495260689</v>
+      </c>
+      <c r="N261" t="n">
+        <v>23.64687142352469</v>
       </c>
     </row>
   </sheetData>
@@ -27513,16 +27618,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>134.02</v>
+        <v>134.31</v>
       </c>
       <c r="D2" t="n">
-        <v>1.614982182121483</v>
+        <v>0.2163856140874332</v>
       </c>
       <c r="E2" t="n">
-        <v>37.53005127954092</v>
+        <v>33.78988040090669</v>
       </c>
       <c r="F2" t="n">
-        <v>21.82652154856619</v>
+        <v>22.09013661534045</v>
       </c>
     </row>
     <row r="3">
@@ -27537,16 +27642,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>130.15</v>
+        <v>139.12</v>
       </c>
       <c r="D3" t="n">
-        <v>1.934523809523814</v>
+        <v>6.892047637341525</v>
       </c>
       <c r="E3" t="n">
-        <v>29.38189201377268</v>
+        <v>30.42224822913602</v>
       </c>
       <c r="F3" t="n">
-        <v>16.2868521420896</v>
+        <v>24.30139738768733</v>
       </c>
     </row>
     <row r="4">
@@ -27561,16 +27666,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>111.73</v>
+        <v>107.77</v>
       </c>
       <c r="D4" t="n">
-        <v>-3.929492691315561</v>
+        <v>-3.544258480264928</v>
       </c>
       <c r="E4" t="n">
-        <v>16.47854628756089</v>
+        <v>13.15707827013983</v>
       </c>
       <c r="F4" t="n">
-        <v>2.758604569261713</v>
+        <v>-0.8834259873862438</v>
       </c>
     </row>
     <row r="5">
@@ -27585,16 +27690,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>144.81</v>
+        <v>148.08</v>
       </c>
       <c r="D5" t="n">
-        <v>2.252506708092072</v>
+        <v>2.25813134452042</v>
       </c>
       <c r="E5" t="n">
-        <v>40.32266749804405</v>
+        <v>39.77455728429897</v>
       </c>
       <c r="F5" t="n">
-        <v>25.91930196781995</v>
+        <v>28.76272519435659</v>
       </c>
     </row>
     <row r="6">
@@ -27609,16 +27714,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>124.31</v>
+        <v>126.49</v>
       </c>
       <c r="D6" t="n">
-        <v>1.701709891188741</v>
+        <v>1.753680315340667</v>
       </c>
       <c r="E6" t="n">
-        <v>22.40688250729537</v>
+        <v>23.5763577628787</v>
       </c>
       <c r="F6" t="n">
-        <v>14.93137419771335</v>
+        <v>16.94690308316918</v>
       </c>
     </row>
     <row r="7">
@@ -27633,16 +27738,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>145.05</v>
+        <v>146.07</v>
       </c>
       <c r="D7" t="n">
-        <v>10.74209803023365</v>
+        <v>0.7032057911064982</v>
       </c>
       <c r="E7" t="n">
-        <v>43.89126368322292</v>
+        <v>43.45661506527607</v>
       </c>
       <c r="F7" t="n">
-        <v>37.44541483745827</v>
+        <v>38.41193895420565</v>
       </c>
     </row>
     <row r="8">
@@ -27657,16 +27762,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>133.69</v>
+        <v>140.14</v>
       </c>
       <c r="D8" t="n">
-        <v>2.593814749443624</v>
+        <v>4.824594210486932</v>
       </c>
       <c r="E8" t="n">
-        <v>30.83239164895124</v>
+        <v>35.07642610694981</v>
       </c>
       <c r="F8" t="n">
-        <v>23.18060143994056</v>
+        <v>29.12356560545493</v>
       </c>
     </row>
     <row r="9">
@@ -27681,16 +27786,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>125.22</v>
+        <v>128.48</v>
       </c>
       <c r="D9" t="n">
-        <v>2.037157757496733</v>
+        <v>2.603417984347534</v>
       </c>
       <c r="E9" t="n">
-        <v>23.96797719523978</v>
+        <v>25.66465697868268</v>
       </c>
       <c r="F9" t="n">
-        <v>15.66146216337521</v>
+        <v>18.67261347029583</v>
       </c>
     </row>
     <row r="10">
@@ -27705,16 +27810,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>126.2</v>
+        <v>128.56</v>
       </c>
       <c r="D10" t="n">
-        <v>1.243481748896902</v>
+        <v>1.870047543581621</v>
       </c>
       <c r="E10" t="n">
-        <v>23.35550153845947</v>
+        <v>23.42910595461436</v>
       </c>
       <c r="F10" t="n">
-        <v>16.23457161737625</v>
+        <v>18.4082133686996</v>
       </c>
     </row>
     <row r="11">
@@ -27729,16 +27834,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>141.62</v>
+        <v>153.83</v>
       </c>
       <c r="D11" t="n">
-        <v>1.323603062173562</v>
+        <v>8.621663606835206</v>
       </c>
       <c r="E11" t="n">
-        <v>44.18197132280049</v>
+        <v>53.44298409541148</v>
       </c>
       <c r="F11" t="n">
-        <v>19.22085640017788</v>
+        <v>29.49967758818928</v>
       </c>
     </row>
     <row r="12">
@@ -27753,16 +27858,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>133.7</v>
+        <v>135.7</v>
       </c>
       <c r="D12" t="n">
-        <v>2.279681762545893</v>
+        <v>1.495886312640238</v>
       </c>
       <c r="E12" t="n">
-        <v>31.65071076529042</v>
+        <v>31.1578146221104</v>
       </c>
       <c r="F12" t="n">
-        <v>21.26344905273177</v>
+        <v>23.07741238934704</v>
       </c>
     </row>
     <row r="13">
@@ -27777,16 +27882,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>130.47</v>
+        <v>130.54</v>
       </c>
       <c r="D13" t="n">
-        <v>1.006425640628628</v>
+        <v>0.05365218057791221</v>
       </c>
       <c r="E13" t="n">
-        <v>25.64466844969539</v>
+        <v>25.07890495260689</v>
       </c>
       <c r="F13" t="n">
-        <v>27.72877684119763</v>
+        <v>27.79730611519842</v>
       </c>
     </row>
     <row r="14">
@@ -27801,16 +27906,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>123.47</v>
+        <v>126.42</v>
       </c>
       <c r="D14" t="n">
-        <v>1.113749897633287</v>
+        <v>2.389244350854458</v>
       </c>
       <c r="E14" t="n">
-        <v>21.73888482986941</v>
+        <v>23.64687142352469</v>
       </c>
       <c r="F14" t="n">
-        <v>12.78695511386278</v>
+        <v>15.48171106742151</v>
       </c>
     </row>
   </sheetData>
